--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="133">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,165 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Turkish 1 Lig</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Belgian Pro League</t>
+  </si>
+  <si>
+    <t>Swiss Super League</t>
+  </si>
+  <si>
+    <t>Scottish Premiership</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:25:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>15:55:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Barcelona (Ecu)</t>
+  </si>
+  <si>
+    <t>Deportes Limache</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>76 Igdir Belediyespor</t>
+  </si>
+  <si>
+    <t>Al-Feiha</t>
+  </si>
+  <si>
+    <t>NEOM Sports Club</t>
+  </si>
+  <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Bursaspor</t>
+  </si>
+  <si>
+    <t>FC Copenhagen</t>
+  </si>
+  <si>
+    <t>Gent</t>
+  </si>
+  <si>
+    <t>Anderlecht</t>
+  </si>
+  <si>
+    <t>FC Basel</t>
+  </si>
+  <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Ecu)</t>
+  </si>
+  <si>
+    <t>Independiente (Ecu)</t>
+  </si>
+  <si>
+    <t>Nublense</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>Manisa FK</t>
+  </si>
+  <si>
+    <t>Al-Kholood Club</t>
+  </si>
+  <si>
+    <t>Al-Khaleej Saihat</t>
+  </si>
+  <si>
+    <t>Smouha</t>
+  </si>
+  <si>
+    <t>Istanbulspor</t>
+  </si>
+  <si>
+    <t>FC Nordsjaelland</t>
+  </si>
+  <si>
+    <t>Oud-Heverlee Leuven</t>
+  </si>
+  <si>
+    <t>Kortrijk</t>
+  </si>
+  <si>
+    <t>Sion</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Aucas</t>
+  </si>
+  <si>
+    <t>2026-09-01 00:10:39</t>
   </si>
 </sst>
 </file>
@@ -585,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +987,3636 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2">
+        <v>3.3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2.24</v>
+      </c>
+      <c r="I2">
+        <v>2.48</v>
+      </c>
+      <c r="J2">
+        <v>3.25</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>1.35</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>3.05</v>
+      </c>
+      <c r="O2">
+        <v>1.37</v>
+      </c>
+      <c r="P2">
+        <v>1.7</v>
+      </c>
+      <c r="Q2">
+        <v>2.08</v>
+      </c>
+      <c r="R2">
+        <v>1.25</v>
+      </c>
+      <c r="S2">
+        <v>3.6</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.67</v>
+      </c>
+      <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3">
+        <v>2.38</v>
+      </c>
+      <c r="G3">
+        <v>2.6</v>
+      </c>
+      <c r="H3">
+        <v>2.94</v>
+      </c>
+      <c r="I3">
+        <v>3.3</v>
+      </c>
+      <c r="J3">
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <v>4.2</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.06</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3">
+        <v>1.27</v>
+      </c>
+      <c r="P3">
+        <v>2.02</v>
+      </c>
+      <c r="Q3">
+        <v>1.8</v>
+      </c>
+      <c r="R3">
+        <v>1.4</v>
+      </c>
+      <c r="S3">
+        <v>3.05</v>
+      </c>
+      <c r="T3">
+        <v>1.67</v>
+      </c>
+      <c r="U3">
+        <v>2.26</v>
+      </c>
+      <c r="V3">
+        <v>1.47</v>
+      </c>
+      <c r="W3">
+        <v>1.63</v>
+      </c>
+      <c r="X3">
+        <v>21</v>
+      </c>
+      <c r="Y3">
+        <v>14.5</v>
+      </c>
+      <c r="Z3">
+        <v>24</v>
+      </c>
+      <c r="AA3">
+        <v>55</v>
+      </c>
+      <c r="AB3">
+        <v>12.5</v>
+      </c>
+      <c r="AC3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>14.5</v>
+      </c>
+      <c r="AE3">
+        <v>36</v>
+      </c>
+      <c r="AF3">
+        <v>17.5</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>17</v>
+      </c>
+      <c r="AI3">
+        <v>44</v>
+      </c>
+      <c r="AJ3">
+        <v>36</v>
+      </c>
+      <c r="AK3">
+        <v>26</v>
+      </c>
+      <c r="AL3">
+        <v>38</v>
+      </c>
+      <c r="AM3">
+        <v>80</v>
+      </c>
+      <c r="AN3">
+        <v>18.5</v>
+      </c>
+      <c r="AO3">
+        <v>28</v>
+      </c>
+      <c r="AP3">
+        <v>12</v>
+      </c>
+      <c r="AQ3">
+        <v>11.5</v>
+      </c>
+      <c r="AR3">
+        <v>18.5</v>
+      </c>
+      <c r="AS3">
+        <v>1.01</v>
+      </c>
+      <c r="AT3">
+        <v>10</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>11.5</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>1.01</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>21</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>15</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>4.6</v>
+      </c>
+      <c r="BI3">
+        <v>2.9</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4">
+        <v>2.88</v>
+      </c>
+      <c r="G4">
+        <v>3.3</v>
+      </c>
+      <c r="H4">
+        <v>2.56</v>
+      </c>
+      <c r="I4">
+        <v>2.9</v>
+      </c>
+      <c r="J4">
+        <v>3.25</v>
+      </c>
+      <c r="K4">
+        <v>3.85</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>3.05</v>
+      </c>
+      <c r="O4">
+        <v>1.4</v>
+      </c>
+      <c r="P4">
+        <v>1.7</v>
+      </c>
+      <c r="Q4">
+        <v>1.98</v>
+      </c>
+      <c r="R4">
+        <v>1.22</v>
+      </c>
+      <c r="S4">
+        <v>3.4</v>
+      </c>
+      <c r="T4">
+        <v>1.8</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.52</v>
+      </c>
+      <c r="W4">
+        <v>1.43</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>14.5</v>
+      </c>
+      <c r="Z4">
+        <v>25</v>
+      </c>
+      <c r="AA4">
+        <v>65</v>
+      </c>
+      <c r="AB4">
+        <v>15.5</v>
+      </c>
+      <c r="AC4">
+        <v>10.5</v>
+      </c>
+      <c r="AD4">
+        <v>18</v>
+      </c>
+      <c r="AE4">
+        <v>48</v>
+      </c>
+      <c r="AF4">
+        <v>29</v>
+      </c>
+      <c r="AG4">
+        <v>20</v>
+      </c>
+      <c r="AH4">
+        <v>28</v>
+      </c>
+      <c r="AI4">
+        <v>70</v>
+      </c>
+      <c r="AJ4">
+        <v>75</v>
+      </c>
+      <c r="AK4">
+        <v>55</v>
+      </c>
+      <c r="AL4">
+        <v>75</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>55</v>
+      </c>
+      <c r="AO4">
+        <v>48</v>
+      </c>
+      <c r="AP4">
+        <v>2.36</v>
+      </c>
+      <c r="AQ4">
+        <v>2.04</v>
+      </c>
+      <c r="AR4">
+        <v>10.5</v>
+      </c>
+      <c r="AS4">
+        <v>2.28</v>
+      </c>
+      <c r="AT4">
+        <v>2.04</v>
+      </c>
+      <c r="AU4">
+        <v>1.93</v>
+      </c>
+      <c r="AV4">
+        <v>2.08</v>
+      </c>
+      <c r="AW4">
+        <v>2.26</v>
+      </c>
+      <c r="AX4">
+        <v>2.18</v>
+      </c>
+      <c r="AY4">
+        <v>2.12</v>
+      </c>
+      <c r="AZ4">
+        <v>2.18</v>
+      </c>
+      <c r="BA4">
+        <v>2.28</v>
+      </c>
+      <c r="BB4">
+        <v>2.3</v>
+      </c>
+      <c r="BC4">
+        <v>2.26</v>
+      </c>
+      <c r="BD4">
+        <v>2.3</v>
+      </c>
+      <c r="BE4">
+        <v>2.36</v>
+      </c>
+      <c r="BF4">
+        <v>2.26</v>
+      </c>
+      <c r="BG4">
+        <v>19</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>2.02</v>
+      </c>
+      <c r="G5">
+        <v>2.5</v>
+      </c>
+      <c r="H5">
+        <v>3.05</v>
+      </c>
+      <c r="I5">
+        <v>4.4</v>
+      </c>
+      <c r="J5">
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <v>5.7</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.82</v>
+      </c>
+      <c r="Q5">
+        <v>1.71</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6">
+        <v>2.66</v>
+      </c>
+      <c r="G6">
+        <v>3.1</v>
+      </c>
+      <c r="H6">
+        <v>2.7</v>
+      </c>
+      <c r="I6">
+        <v>3.1</v>
+      </c>
+      <c r="J6">
+        <v>3.05</v>
+      </c>
+      <c r="K6">
+        <v>3.9</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.7</v>
+      </c>
+      <c r="Q6">
+        <v>2.12</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7">
+        <v>1.22</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3.35</v>
+      </c>
+      <c r="I7">
+        <v>5.4</v>
+      </c>
+      <c r="J7">
+        <v>3.4</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.86</v>
+      </c>
+      <c r="Q7">
+        <v>1.7</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8">
+        <v>1.42</v>
+      </c>
+      <c r="G8">
+        <v>1.58</v>
+      </c>
+      <c r="H8">
+        <v>3.2</v>
+      </c>
+      <c r="I8">
+        <v>19.5</v>
+      </c>
+      <c r="J8">
+        <v>4.1</v>
+      </c>
+      <c r="K8">
+        <v>5.8</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.79</v>
+      </c>
+      <c r="Q8">
+        <v>2.02</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9">
+        <v>1.32</v>
+      </c>
+      <c r="G9">
+        <v>1.58</v>
+      </c>
+      <c r="H9">
+        <v>6.6</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>4.2</v>
+      </c>
+      <c r="K9">
+        <v>11</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.96</v>
+      </c>
+      <c r="Q9">
+        <v>1.59</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10">
+        <v>2.06</v>
+      </c>
+      <c r="G10">
+        <v>2.24</v>
+      </c>
+      <c r="H10">
+        <v>3.25</v>
+      </c>
+      <c r="I10">
+        <v>3.5</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>4.5</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.74</v>
+      </c>
+      <c r="Q10">
+        <v>1.48</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11">
+        <v>1.63</v>
+      </c>
+      <c r="G11">
+        <v>1.7</v>
+      </c>
+      <c r="H11">
+        <v>5.5</v>
+      </c>
+      <c r="I11">
+        <v>7.2</v>
+      </c>
+      <c r="J11">
+        <v>3.65</v>
+      </c>
+      <c r="K11">
+        <v>4.9</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.25</v>
+      </c>
+      <c r="Q11">
+        <v>1.65</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12">
+        <v>1.55</v>
+      </c>
+      <c r="G12">
+        <v>1.57</v>
+      </c>
+      <c r="H12">
+        <v>5.9</v>
+      </c>
+      <c r="I12">
+        <v>7.6</v>
+      </c>
+      <c r="J12">
+        <v>4.5</v>
+      </c>
+      <c r="K12">
+        <v>5.4</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.38</v>
+      </c>
+      <c r="Q12">
+        <v>1.57</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13">
+        <v>2.46</v>
+      </c>
+      <c r="G13">
+        <v>2.78</v>
+      </c>
+      <c r="H13">
+        <v>2.64</v>
+      </c>
+      <c r="I13">
+        <v>2.88</v>
+      </c>
+      <c r="J13">
+        <v>3.85</v>
+      </c>
+      <c r="K13">
+        <v>4.4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.52</v>
+      </c>
+      <c r="Q13">
+        <v>1.5</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14">
+        <v>2.06</v>
+      </c>
+      <c r="G14">
+        <v>2.22</v>
+      </c>
+      <c r="H14">
+        <v>3.4</v>
+      </c>
+      <c r="I14">
+        <v>3.8</v>
+      </c>
+      <c r="J14">
+        <v>3.75</v>
+      </c>
+      <c r="K14">
+        <v>4.3</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.06</v>
+      </c>
+      <c r="Q14">
+        <v>1.58</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15">
+        <v>2.6</v>
+      </c>
+      <c r="G15">
+        <v>2.78</v>
+      </c>
+      <c r="H15">
+        <v>2.74</v>
+      </c>
+      <c r="I15">
+        <v>2.96</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>3.65</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>3.85</v>
+      </c>
+      <c r="O15">
+        <v>1.29</v>
+      </c>
+      <c r="P15">
+        <v>1.98</v>
+      </c>
+      <c r="Q15">
+        <v>1.86</v>
+      </c>
+      <c r="R15">
+        <v>1.38</v>
+      </c>
+      <c r="S15">
+        <v>3.2</v>
+      </c>
+      <c r="T15">
+        <v>1.69</v>
+      </c>
+      <c r="U15">
+        <v>2.22</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>17.5</v>
+      </c>
+      <c r="Y15">
+        <v>12.5</v>
+      </c>
+      <c r="Z15">
+        <v>22</v>
+      </c>
+      <c r="AA15">
+        <v>48</v>
+      </c>
+      <c r="AB15">
+        <v>12.5</v>
+      </c>
+      <c r="AC15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15">
+        <v>14.5</v>
+      </c>
+      <c r="AE15">
+        <v>34</v>
+      </c>
+      <c r="AF15">
+        <v>20</v>
+      </c>
+      <c r="AG15">
+        <v>13.5</v>
+      </c>
+      <c r="AH15">
+        <v>18.5</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>44</v>
+      </c>
+      <c r="AK15">
+        <v>30</v>
+      </c>
+      <c r="AL15">
+        <v>44</v>
+      </c>
+      <c r="AM15">
+        <v>85</v>
+      </c>
+      <c r="AN15">
+        <v>24</v>
+      </c>
+      <c r="AO15">
+        <v>28</v>
+      </c>
+      <c r="AP15">
+        <v>13.5</v>
+      </c>
+      <c r="AQ15">
+        <v>10.5</v>
+      </c>
+      <c r="AR15">
+        <v>5.8</v>
+      </c>
+      <c r="AS15">
+        <v>36</v>
+      </c>
+      <c r="AT15">
+        <v>10</v>
+      </c>
+      <c r="AU15">
+        <v>7.2</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>6.4</v>
+      </c>
+      <c r="AX15">
+        <v>16</v>
+      </c>
+      <c r="AY15">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
+        <v>6.6</v>
+      </c>
+      <c r="BB15">
+        <v>6.6</v>
+      </c>
+      <c r="BC15">
+        <v>6.4</v>
+      </c>
+      <c r="BD15">
+        <v>32</v>
+      </c>
+      <c r="BE15">
+        <v>7</v>
+      </c>
+      <c r="BF15">
+        <v>17</v>
+      </c>
+      <c r="BG15">
+        <v>21</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16">
+        <v>1.74</v>
+      </c>
+      <c r="G16">
+        <v>2.2</v>
+      </c>
+      <c r="H16">
+        <v>3.7</v>
+      </c>
+      <c r="I16">
+        <v>6.2</v>
+      </c>
+      <c r="J16">
+        <v>3.3</v>
+      </c>
+      <c r="K16">
+        <v>6.6</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.76</v>
+      </c>
+      <c r="Q16">
+        <v>1.77</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -412,7 +412,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 00:10:39</t>
+    <t>2026-09-01 02:23:02</t>
   </si>
 </sst>
 </file>
@@ -1006,22 +1006,22 @@
         <v>117</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J2">
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1036,10 +1036,10 @@
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>1.25</v>
@@ -1054,7 +1054,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W2">
         <v>1.33</v>
@@ -1248,7 +1248,7 @@
         <v>118</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
         <v>2.6</v>
@@ -1260,10 +1260,10 @@
         <v>3.3</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1287,7 +1287,7 @@
         <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T3">
         <v>1.67</v>
@@ -1365,7 +1365,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1407,7 +1407,7 @@
         <v>15</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH3">
         <v>4.6</v>
@@ -1493,7 +1493,7 @@
         <v>2.88</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H4">
         <v>2.56</v>
@@ -1520,10 +1520,10 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
         <v>1.22</v>
@@ -1535,13 +1535,13 @@
         <v>1.8</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V4">
         <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1977,10 +1977,10 @@
         <v>2.66</v>
       </c>
       <c r="G6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I6">
         <v>3.1</v>
@@ -1989,7 +1989,7 @@
         <v>3.05</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>122</v>
       </c>
       <c r="F7">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -2231,7 +2231,7 @@
         <v>3.4</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2700,22 +2700,22 @@
         <v>124</v>
       </c>
       <c r="F9">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="G9">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="H9">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="K9">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q9">
         <v>1.59</v>
@@ -2945,7 +2945,7 @@
         <v>2.06</v>
       </c>
       <c r="G10">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
         <v>3.25</v>
@@ -2975,7 +2975,7 @@
         <v>2.74</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3196,7 +3196,7 @@
         <v>7.2</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K11">
         <v>4.9</v>
@@ -3919,7 +3919,7 @@
         <v>3.4</v>
       </c>
       <c r="I14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J14">
         <v>3.75</v>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q14">
         <v>1.58</v>
@@ -4155,10 +4155,10 @@
         <v>2.6</v>
       </c>
       <c r="G15">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H15">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I15">
         <v>2.96</v>
@@ -4233,7 +4233,7 @@
         <v>20</v>
       </c>
       <c r="AG15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
         <v>18.5</v>
@@ -4242,7 +4242,7 @@
         <v>55</v>
       </c>
       <c r="AJ15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK15">
         <v>30</v>
@@ -4257,7 +4257,7 @@
         <v>24</v>
       </c>
       <c r="AO15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP15">
         <v>13.5</v>
@@ -4266,10 +4266,10 @@
         <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS15">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="AT15">
         <v>10</v>
@@ -4281,7 +4281,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX15">
         <v>16</v>
@@ -4293,25 +4293,25 @@
         <v>14</v>
       </c>
       <c r="BA15">
+        <v>28</v>
+      </c>
+      <c r="BB15">
+        <v>7</v>
+      </c>
+      <c r="BC15">
         <v>6.6</v>
       </c>
-      <c r="BB15">
-        <v>6.6</v>
-      </c>
-      <c r="BC15">
-        <v>6.4</v>
-      </c>
       <c r="BD15">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF15">
         <v>17</v>
       </c>
       <c r="BG15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BH15">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -412,7 +412,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 02:23:02</t>
+    <t>2026-09-01 03:53:20</t>
   </si>
 </sst>
 </file>
@@ -1009,10 +1009,10 @@
         <v>3.35</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I2">
         <v>2.46</v>
@@ -1027,10 +1027,10 @@
         <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.37</v>
@@ -1039,112 +1039,112 @@
         <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
         <v>1.68</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
         <v>1.01</v>
@@ -1165,7 +1165,7 @@
         <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1260,7 +1260,7 @@
         <v>3.3</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
         <v>4.4</v>
@@ -1287,7 +1287,7 @@
         <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T3">
         <v>1.67</v>
@@ -1514,7 +1514,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>1.4</v>
@@ -1535,7 +1535,7 @@
         <v>1.8</v>
       </c>
       <c r="U4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
         <v>1.52</v>
@@ -1547,13 +1547,13 @@
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB4">
         <v>15.5</v>
@@ -1568,7 +1568,7 @@
         <v>48</v>
       </c>
       <c r="AF4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG4">
         <v>20</v>
@@ -1580,7 +1580,7 @@
         <v>70</v>
       </c>
       <c r="AJ4">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK4">
         <v>55</v>
@@ -1592,64 +1592,64 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AQ4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS4">
-        <v>2.28</v>
+        <v>24</v>
       </c>
       <c r="AT4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AU4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AV4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AW4">
         <v>2.26</v>
       </c>
       <c r="AX4">
-        <v>2.18</v>
+        <v>14</v>
       </c>
       <c r="AY4">
         <v>2.12</v>
       </c>
       <c r="AZ4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BA4">
+        <v>2.3</v>
+      </c>
+      <c r="BB4">
+        <v>2.32</v>
+      </c>
+      <c r="BC4">
         <v>2.28</v>
-      </c>
-      <c r="BB4">
-        <v>2.3</v>
-      </c>
-      <c r="BC4">
-        <v>2.26</v>
       </c>
       <c r="BD4">
         <v>2.3</v>
       </c>
       <c r="BE4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BF4">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BG4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1732,22 +1732,22 @@
         <v>120</v>
       </c>
       <c r="F5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="H5">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3.5</v>
       </c>
       <c r="K5">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1762,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q5">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>3.05</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2216,22 +2216,22 @@
         <v>122</v>
       </c>
       <c r="F7">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>330</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2246,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2700,40 +2700,40 @@
         <v>124</v>
       </c>
       <c r="F9">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="G9">
+        <v>1.55</v>
+      </c>
+      <c r="H9">
+        <v>7.2</v>
+      </c>
+      <c r="I9">
+        <v>8.6</v>
+      </c>
+      <c r="J9">
+        <v>4.5</v>
+      </c>
+      <c r="K9">
+        <v>5.2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>2.14</v>
+      </c>
+      <c r="Q9">
         <v>1.72</v>
-      </c>
-      <c r="H9">
-        <v>5.4</v>
-      </c>
-      <c r="I9">
-        <v>1000</v>
-      </c>
-      <c r="J9">
-        <v>2.38</v>
-      </c>
-      <c r="K9">
-        <v>9.6</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1.91</v>
-      </c>
-      <c r="Q9">
-        <v>1.59</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2945,13 +2945,13 @@
         <v>2.06</v>
       </c>
       <c r="G10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H10">
         <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q10">
         <v>1.43</v>
@@ -3193,13 +3193,13 @@
         <v>5.5</v>
       </c>
       <c r="I11">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="J11">
         <v>4.1</v>
       </c>
       <c r="K11">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3214,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3426,22 +3426,22 @@
         <v>127</v>
       </c>
       <c r="F12">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G12">
         <v>1.57</v>
       </c>
       <c r="H12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>4.5</v>
       </c>
       <c r="K12">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3668,7 +3668,7 @@
         <v>128</v>
       </c>
       <c r="F13">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G13">
         <v>2.78</v>
@@ -3698,10 +3698,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q13">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         <v>2.06</v>
       </c>
       <c r="G14">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I14">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J14">
         <v>3.75</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>6</v>
       </c>
       <c r="AS15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT15">
         <v>10</v>
@@ -4281,7 +4281,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX15">
         <v>16</v>
@@ -4302,7 +4302,7 @@
         <v>6.6</v>
       </c>
       <c r="BD15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE15">
         <v>7.6</v>
@@ -4314,55 +4314,55 @@
         <v>19</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
         <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
@@ -4394,22 +4394,22 @@
         <v>131</v>
       </c>
       <c r="F16">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="G16">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="H16">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="I16">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="Q16">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="R16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -412,7 +412,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 03:53:20</t>
+    <t>2026-09-01 06:05:44</t>
   </si>
 </sst>
 </file>
@@ -1009,19 +1009,19 @@
         <v>3.35</v>
       </c>
       <c r="G2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H2">
         <v>2.22</v>
       </c>
       <c r="I2">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J2">
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1030,34 +1030,34 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1257,7 +1257,7 @@
         <v>2.94</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>3.5</v>
@@ -1272,7 +1272,7 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O3">
         <v>1.27</v>
@@ -1281,7 +1281,7 @@
         <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1290,10 +1290,10 @@
         <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
         <v>1.47</v>
@@ -1365,7 +1365,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1398,7 +1398,7 @@
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE3">
         <v>1.01</v>
@@ -1407,7 +1407,7 @@
         <v>15</v>
       </c>
       <c r="BG3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>4.6</v>
@@ -1490,7 +1490,7 @@
         <v>119</v>
       </c>
       <c r="F4">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G4">
         <v>3.25</v>
@@ -1499,19 +1499,19 @@
         <v>2.56</v>
       </c>
       <c r="I4">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J4">
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.1</v>
@@ -1520,136 +1520,136 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
         <v>1.44</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y4">
+        <v>11.5</v>
+      </c>
+      <c r="Z4">
+        <v>21</v>
+      </c>
+      <c r="AA4">
+        <v>50</v>
+      </c>
+      <c r="AB4">
+        <v>13</v>
+      </c>
+      <c r="AC4">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <v>40</v>
+      </c>
+      <c r="AF4">
+        <v>25</v>
+      </c>
+      <c r="AG4">
+        <v>16.5</v>
+      </c>
+      <c r="AH4">
+        <v>23</v>
+      </c>
+      <c r="AI4">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
+        <v>48</v>
+      </c>
+      <c r="AL4">
+        <v>65</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
+        <v>50</v>
+      </c>
+      <c r="AO4">
+        <v>38</v>
+      </c>
+      <c r="AP4">
+        <v>8.4</v>
+      </c>
+      <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>14</v>
+      </c>
+      <c r="AS4">
+        <v>3.95</v>
+      </c>
+      <c r="AT4">
+        <v>8.6</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>3.9</v>
+      </c>
+      <c r="AX4">
+        <v>15</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
         <v>13.5</v>
       </c>
-      <c r="Z4">
-        <v>25</v>
-      </c>
-      <c r="AA4">
-        <v>60</v>
-      </c>
-      <c r="AB4">
-        <v>15.5</v>
-      </c>
-      <c r="AC4">
-        <v>10.5</v>
-      </c>
-      <c r="AD4">
-        <v>18</v>
-      </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
-      <c r="AF4">
-        <v>30</v>
-      </c>
-      <c r="AG4">
-        <v>20</v>
-      </c>
-      <c r="AH4">
-        <v>28</v>
-      </c>
-      <c r="AI4">
-        <v>70</v>
-      </c>
-      <c r="AJ4">
-        <v>85</v>
-      </c>
-      <c r="AK4">
-        <v>55</v>
-      </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>60</v>
-      </c>
-      <c r="AO4">
-        <v>46</v>
-      </c>
-      <c r="AP4">
-        <v>2.38</v>
-      </c>
-      <c r="AQ4">
-        <v>2.02</v>
-      </c>
-      <c r="AR4">
-        <v>11</v>
-      </c>
-      <c r="AS4">
-        <v>24</v>
-      </c>
-      <c r="AT4">
-        <v>2.06</v>
-      </c>
-      <c r="AU4">
-        <v>1.94</v>
-      </c>
-      <c r="AV4">
-        <v>2.1</v>
-      </c>
-      <c r="AW4">
-        <v>2.26</v>
-      </c>
-      <c r="AX4">
-        <v>14</v>
-      </c>
-      <c r="AY4">
-        <v>2.12</v>
-      </c>
-      <c r="AZ4">
-        <v>2.2</v>
-      </c>
       <c r="BA4">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="BB4">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BC4">
-        <v>2.28</v>
+        <v>3.95</v>
       </c>
       <c r="BD4">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="BE4">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="BF4">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="BG4">
-        <v>18.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1741,7 +1741,7 @@
         <v>3.4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1974,7 +1974,7 @@
         <v>121</v>
       </c>
       <c r="F6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G6">
         <v>3.05</v>
@@ -1983,7 +1983,7 @@
         <v>2.74</v>
       </c>
       <c r="I6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J6">
         <v>3.05</v>
@@ -2007,7 +2007,7 @@
         <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>4.1</v>
       </c>
       <c r="I7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
         <v>3.7</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q7">
         <v>1.74</v>
@@ -2461,19 +2461,19 @@
         <v>1.42</v>
       </c>
       <c r="G8">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="H8">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2730,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="Q9">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2942,16 +2942,16 @@
         <v>125</v>
       </c>
       <c r="F10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -2975,7 +2975,7 @@
         <v>2.72</v>
       </c>
       <c r="Q10">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3184,22 +3184,22 @@
         <v>126</v>
       </c>
       <c r="F11">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="G11">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H11">
         <v>5.5</v>
       </c>
       <c r="I11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>4.1</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q11">
         <v>1.68</v>
@@ -3426,22 +3426,22 @@
         <v>127</v>
       </c>
       <c r="F12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G12">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
       <c r="I12">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3456,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>2.48</v>
       </c>
       <c r="G13">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="H13">
         <v>2.64</v>
@@ -3680,10 +3680,10 @@
         <v>2.88</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>2.06</v>
       </c>
       <c r="G14">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H14">
         <v>3.35</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>2.6</v>
       </c>
       <c r="G15">
+        <v>2.76</v>
+      </c>
+      <c r="H15">
         <v>2.74</v>
-      </c>
-      <c r="H15">
-        <v>2.76</v>
       </c>
       <c r="I15">
         <v>2.96</v>
@@ -4185,13 +4185,13 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R15">
         <v>1.38</v>
       </c>
       <c r="S15">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T15">
         <v>1.69</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q16">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -412,7 +412,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 06:05:44</t>
+    <t>2026-09-01 08:18:05</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1009,7 @@
         <v>3.35</v>
       </c>
       <c r="G2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H2">
         <v>2.22</v>
@@ -1021,7 +1021,7 @@
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1030,25 +1030,25 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
         <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
         <v>1.98</v>
@@ -1057,7 +1057,7 @@
         <v>1.66</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1278,10 +1278,10 @@
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1290,10 +1290,10 @@
         <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
         <v>1.47</v>
@@ -1398,7 +1398,7 @@
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
         <v>1.01</v>
@@ -1407,7 +1407,7 @@
         <v>15</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH3">
         <v>4.6</v>
@@ -1523,7 +1523,7 @@
         <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1532,10 +1532,10 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
         <v>1.54</v>
@@ -1604,16 +1604,16 @@
         <v>7</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS4">
         <v>3.95</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AV4">
         <v>9.199999999999999</v>
@@ -1735,7 +1735,7 @@
         <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
         <v>3.4</v>
@@ -2219,10 +2219,10 @@
         <v>1.95</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I7">
         <v>4.8</v>
@@ -2231,7 +2231,7 @@
         <v>3.7</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>1.99</v>
       </c>
       <c r="Q7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2458,22 +2458,22 @@
         <v>123</v>
       </c>
       <c r="F8">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="G8">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="H8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2488,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>124</v>
       </c>
       <c r="F9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G9">
         <v>1.55</v>
@@ -2730,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2942,19 +2942,19 @@
         <v>125</v>
       </c>
       <c r="F10">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G10">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I10">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
         <v>4.5</v>
@@ -3429,7 +3429,7 @@
         <v>1.54</v>
       </c>
       <c r="G12">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q12">
         <v>1.61</v>
@@ -3910,7 +3910,7 @@
         <v>129</v>
       </c>
       <c r="F14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G14">
         <v>2.2</v>
@@ -3922,7 +3922,7 @@
         <v>3.75</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
         <v>4.2</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q14">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>130</v>
       </c>
       <c r="F15">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G15">
         <v>2.76</v>
@@ -4161,7 +4161,7 @@
         <v>2.74</v>
       </c>
       <c r="I15">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y15">
         <v>12.5</v>
@@ -4215,7 +4215,7 @@
         <v>22</v>
       </c>
       <c r="AA15">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB15">
         <v>12.5</v>
@@ -4227,16 +4227,16 @@
         <v>14.5</v>
       </c>
       <c r="AE15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG15">
         <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI15">
         <v>55</v>
@@ -4245,7 +4245,7 @@
         <v>42</v>
       </c>
       <c r="AK15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL15">
         <v>44</v>
@@ -4254,10 +4254,10 @@
         <v>85</v>
       </c>
       <c r="AN15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AP15">
         <v>13.5</v>
@@ -4266,10 +4266,10 @@
         <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AS15">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT15">
         <v>10</v>
@@ -4281,7 +4281,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX15">
         <v>16</v>
@@ -4296,16 +4296,16 @@
         <v>28</v>
       </c>
       <c r="BB15">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BC15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD15">
         <v>32</v>
       </c>
       <c r="BE15">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BF15">
         <v>17</v>
@@ -4394,7 +4394,7 @@
         <v>131</v>
       </c>
       <c r="F16">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G16">
         <v>2.04</v>
@@ -4427,7 +4427,7 @@
         <v>1.91</v>
       </c>
       <c r="Q16">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="R16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -412,7 +412,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 08:18:05</t>
+    <t>2026-09-01 10:30:31</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1021,7 @@
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1030,31 +1030,31 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W2">
         <v>1.35</v>
@@ -1111,7 +1111,7 @@
         <v>60</v>
       </c>
       <c r="AO2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP2">
         <v>9</v>
@@ -1126,7 +1126,7 @@
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU2">
         <v>5.8</v>
@@ -1254,7 +1254,7 @@
         <v>2.6</v>
       </c>
       <c r="H3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I3">
         <v>3.25</v>
@@ -1272,16 +1272,16 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P3">
         <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1332,10 +1332,10 @@
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ3">
         <v>36</v>
@@ -1365,7 +1365,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1398,7 +1398,7 @@
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE3">
         <v>1.01</v>
@@ -1490,7 +1490,7 @@
         <v>119</v>
       </c>
       <c r="F4">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G4">
         <v>3.25</v>
@@ -1505,7 +1505,7 @@
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1520,10 +1520,10 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1532,13 +1532,13 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
         <v>1.44</v>
@@ -1598,7 +1598,7 @@
         <v>38</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>7</v>
@@ -1613,10 +1613,10 @@
         <v>8</v>
       </c>
       <c r="AU4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>3.9</v>
@@ -1735,7 +1735,7 @@
         <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H5">
         <v>3.4</v>
@@ -1977,7 +1977,7 @@
         <v>2.64</v>
       </c>
       <c r="G6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>2.74</v>
@@ -2007,7 +2007,7 @@
         <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>1.95</v>
       </c>
       <c r="G7">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I7">
         <v>4.8</v>
@@ -2231,7 +2231,7 @@
         <v>3.7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>1.99</v>
       </c>
       <c r="Q7">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2458,22 +2458,22 @@
         <v>123</v>
       </c>
       <c r="F8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H8">
         <v>10</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J8">
         <v>4.4</v>
       </c>
       <c r="K8">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2488,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>2.06</v>
       </c>
       <c r="G10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H10">
         <v>3.3</v>
@@ -2954,10 +2954,10 @@
         <v>3.55</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3193,7 +3193,7 @@
         <v>5.5</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
         <v>4.1</v>
@@ -3426,22 +3426,22 @@
         <v>127</v>
       </c>
       <c r="F12">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G12">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I12">
         <v>7.6</v>
       </c>
       <c r="J12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K12">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3456,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         <v>2.64</v>
       </c>
       <c r="I13">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J13">
         <v>3.8</v>
@@ -3913,7 +3913,7 @@
         <v>2.08</v>
       </c>
       <c r="G14">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H14">
         <v>3.35</v>
@@ -3922,7 +3922,7 @@
         <v>3.75</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
         <v>4.2</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q14">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>130</v>
       </c>
       <c r="F15">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="G15">
         <v>2.76</v>
@@ -4161,7 +4161,7 @@
         <v>2.74</v>
       </c>
       <c r="I15">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4230,19 +4230,19 @@
         <v>32</v>
       </c>
       <c r="AF15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG15">
         <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK15">
         <v>29</v>
@@ -4266,10 +4266,10 @@
         <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT15">
         <v>10</v>
@@ -4281,7 +4281,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX15">
         <v>16</v>
@@ -4296,16 +4296,16 @@
         <v>28</v>
       </c>
       <c r="BB15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD15">
         <v>32</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF15">
         <v>17</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q16">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R16">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="141">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
     <t>Turkish 1 Lig</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>15:55:00</t>
   </si>
   <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -331,24 +337,33 @@
     <t>Santa Fe</t>
   </si>
   <si>
+    <t>Al Ahli (QAT)</t>
+  </si>
+  <si>
     <t>76 Igdir Belediyespor</t>
   </si>
   <si>
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>Al Sailiya</t>
+  </si>
+  <si>
     <t>NEOM Sports Club</t>
   </si>
   <si>
+    <t>Bursaspor</t>
+  </si>
+  <si>
     <t>Al Ahly Cairo</t>
   </si>
   <si>
-    <t>Bursaspor</t>
-  </si>
-  <si>
     <t>FC Copenhagen</t>
   </si>
   <si>
+    <t>Al Draih</t>
+  </si>
+  <si>
     <t>Gent</t>
   </si>
   <si>
@@ -376,24 +391,33 @@
     <t>Millonarios</t>
   </si>
   <si>
+    <t>Qatar SC</t>
+  </si>
+  <si>
     <t>Manisa FK</t>
   </si>
   <si>
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>Al Arabi (QAT)</t>
+  </si>
+  <si>
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
+    <t>Istanbulspor</t>
+  </si>
+  <si>
     <t>Smouha</t>
   </si>
   <si>
-    <t>Istanbulspor</t>
-  </si>
-  <si>
     <t>FC Nordsjaelland</t>
   </si>
   <si>
+    <t>Al-Quadisiya (KSA)</t>
+  </si>
+  <si>
     <t>Oud-Heverlee Leuven</t>
   </si>
   <si>
@@ -412,7 +436,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 10:30:31</t>
+    <t>2026-09-01 12:43:06</t>
   </si>
 </sst>
 </file>
@@ -744,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -994,34 +1018,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1030,22 +1054,22 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
         <v>1.82</v>
@@ -1054,10 +1078,10 @@
         <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1066,10 +1090,10 @@
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB2">
         <v>14.5</v>
@@ -1078,10 +1102,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF2">
         <v>30</v>
@@ -1093,7 +1117,7 @@
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
         <v>85</v>
@@ -1111,10 +1135,10 @@
         <v>60</v>
       </c>
       <c r="AO2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2">
         <v>6.8</v>
@@ -1126,10 +1150,10 @@
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV2">
         <v>8.4</v>
@@ -1228,7 +1252,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1236,22 +1260,22 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
         <v>2.92</v>
@@ -1263,7 +1287,7 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1365,7 +1389,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1377,7 +1401,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1398,7 +1422,7 @@
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
         <v>1.01</v>
@@ -1407,7 +1431,7 @@
         <v>15</v>
       </c>
       <c r="BG3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>4.6</v>
@@ -1470,7 +1494,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1478,22 +1502,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F4">
         <v>2.92</v>
       </c>
       <c r="G4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
         <v>2.56</v>
@@ -1505,7 +1529,7 @@
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1520,10 +1544,10 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1532,10 +1556,10 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
         <v>1.55</v>
@@ -1598,10 +1622,10 @@
         <v>38</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4">
         <v>12</v>
@@ -1610,25 +1634,25 @@
         <v>3.95</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU4">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW4">
         <v>3.9</v>
       </c>
       <c r="AX4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
         <v>4</v>
@@ -1712,7 +1736,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1720,241 +1744,241 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1962,276 +1986,276 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
         <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F6">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="H6">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="Q6">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F7">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2246,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2438,42 +2462,42 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
         <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F8">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="G8">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>1.61</v>
       </c>
       <c r="I8">
-        <v>13.5</v>
+        <v>1.72</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2488,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2680,42 +2704,42 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F9">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="G9">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2730,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2922,42 +2946,42 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="I10">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2972,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3164,42 +3188,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F11">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="G11">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="H11">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="J11">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3214,10 +3238,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3406,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3414,34 +3438,34 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F12">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="G12">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="I12">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="J12">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3456,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="Q12">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3648,42 +3672,42 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F13">
-        <v>2.48</v>
+        <v>1.08</v>
       </c>
       <c r="G13">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>2.64</v>
+        <v>1.08</v>
       </c>
       <c r="I13">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="K13">
-        <v>4.6</v>
+        <v>320</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3698,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="Q13">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3890,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3898,34 +3922,34 @@
         <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F14">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="G14">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="I14">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3940,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q14">
         <v>1.69</v>
@@ -4132,72 +4156,72 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F15">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="G15">
-        <v>2.76</v>
+        <v>1.6</v>
       </c>
       <c r="H15">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="I15">
-        <v>2.88</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="Q15">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="R15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4206,166 +4230,166 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BH15">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI15">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL15">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN15">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BO15">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT15">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU15">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX15">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4374,249 +4398,975 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F16">
+        <v>2.48</v>
+      </c>
+      <c r="G16">
+        <v>2.66</v>
+      </c>
+      <c r="H16">
+        <v>2.64</v>
+      </c>
+      <c r="I16">
+        <v>2.84</v>
+      </c>
+      <c r="J16">
+        <v>3.8</v>
+      </c>
+      <c r="K16">
+        <v>4.6</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.56</v>
+      </c>
+      <c r="Q16">
+        <v>1.52</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17">
+        <v>2.08</v>
+      </c>
+      <c r="G17">
+        <v>2.24</v>
+      </c>
+      <c r="H17">
+        <v>3.35</v>
+      </c>
+      <c r="I17">
+        <v>3.75</v>
+      </c>
+      <c r="J17">
+        <v>3.75</v>
+      </c>
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.22</v>
+      </c>
+      <c r="Q17">
+        <v>1.68</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18">
+        <v>2.7</v>
+      </c>
+      <c r="G18">
+        <v>2.78</v>
+      </c>
+      <c r="H18">
+        <v>2.76</v>
+      </c>
+      <c r="I18">
+        <v>2.88</v>
+      </c>
+      <c r="J18">
+        <v>3.55</v>
+      </c>
+      <c r="K18">
+        <v>3.65</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>3.85</v>
+      </c>
+      <c r="O18">
+        <v>1.29</v>
+      </c>
+      <c r="P18">
+        <v>1.98</v>
+      </c>
+      <c r="Q18">
+        <v>1.84</v>
+      </c>
+      <c r="R18">
+        <v>1.38</v>
+      </c>
+      <c r="S18">
+        <v>3.15</v>
+      </c>
+      <c r="T18">
+        <v>1.69</v>
+      </c>
+      <c r="U18">
+        <v>2.22</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>18</v>
+      </c>
+      <c r="Y18">
+        <v>12.5</v>
+      </c>
+      <c r="Z18">
+        <v>22</v>
+      </c>
+      <c r="AA18">
+        <v>44</v>
+      </c>
+      <c r="AB18">
+        <v>12.5</v>
+      </c>
+      <c r="AC18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD18">
+        <v>14.5</v>
+      </c>
+      <c r="AE18">
+        <v>32</v>
+      </c>
+      <c r="AF18">
+        <v>20</v>
+      </c>
+      <c r="AG18">
+        <v>12.5</v>
+      </c>
+      <c r="AH18">
+        <v>18.5</v>
+      </c>
+      <c r="AI18">
+        <v>50</v>
+      </c>
+      <c r="AJ18">
+        <v>40</v>
+      </c>
+      <c r="AK18">
+        <v>29</v>
+      </c>
+      <c r="AL18">
+        <v>44</v>
+      </c>
+      <c r="AM18">
+        <v>85</v>
+      </c>
+      <c r="AN18">
+        <v>25</v>
+      </c>
+      <c r="AO18">
+        <v>30</v>
+      </c>
+      <c r="AP18">
+        <v>13.5</v>
+      </c>
+      <c r="AQ18">
+        <v>10.5</v>
+      </c>
+      <c r="AR18">
+        <v>5.9</v>
+      </c>
+      <c r="AS18">
+        <v>6.8</v>
+      </c>
+      <c r="AT18">
+        <v>10</v>
+      </c>
+      <c r="AU18">
+        <v>7.2</v>
+      </c>
+      <c r="AV18">
+        <v>11</v>
+      </c>
+      <c r="AW18">
+        <v>6.6</v>
+      </c>
+      <c r="AX18">
+        <v>16</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>14</v>
+      </c>
+      <c r="BA18">
+        <v>28</v>
+      </c>
+      <c r="BB18">
+        <v>6.6</v>
+      </c>
+      <c r="BC18">
+        <v>6.4</v>
+      </c>
+      <c r="BD18">
+        <v>32</v>
+      </c>
+      <c r="BE18">
+        <v>7.2</v>
+      </c>
+      <c r="BF18">
+        <v>17.5</v>
+      </c>
+      <c r="BG18">
+        <v>19.5</v>
+      </c>
+      <c r="BH18">
+        <v>3.95</v>
+      </c>
+      <c r="BI18">
+        <v>2.92</v>
+      </c>
+      <c r="BJ18">
+        <v>10.5</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>120</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>6.6</v>
+      </c>
+      <c r="BO18">
+        <v>4.5</v>
+      </c>
+      <c r="BP18">
+        <v>23</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>36</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>6.8</v>
+      </c>
+      <c r="BU18">
+        <v>4.7</v>
+      </c>
+      <c r="BV18">
+        <v>25</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>38</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19">
         <v>1.86</v>
       </c>
-      <c r="G16">
+      <c r="G19">
         <v>2.04</v>
       </c>
-      <c r="H16">
+      <c r="H19">
         <v>4.2</v>
       </c>
-      <c r="I16">
+      <c r="I19">
         <v>5</v>
       </c>
-      <c r="J16">
-        <v>3.55</v>
-      </c>
-      <c r="K16">
+      <c r="J19">
+        <v>3.6</v>
+      </c>
+      <c r="K19">
         <v>4</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>1.93</v>
       </c>
-      <c r="Q16">
+      <c r="Q19">
         <v>1.89</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16">
-        <v>0</v>
-      </c>
-      <c r="BE16">
-        <v>0</v>
-      </c>
-      <c r="BF16">
-        <v>0</v>
-      </c>
-      <c r="BG16">
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
-      </c>
-      <c r="BJ16">
-        <v>0</v>
-      </c>
-      <c r="BK16">
-        <v>0</v>
-      </c>
-      <c r="BL16">
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <v>0</v>
-      </c>
-      <c r="BN16">
-        <v>0</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16">
-        <v>0</v>
-      </c>
-      <c r="BS16">
-        <v>0</v>
-      </c>
-      <c r="BT16">
-        <v>0</v>
-      </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>0</v>
-      </c>
-      <c r="BX16">
-        <v>0</v>
-      </c>
-      <c r="BY16">
-        <v>0</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>132</v>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="163">
   <si>
     <t>League</t>
   </si>
@@ -274,9 +274,27 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
@@ -307,6 +325,9 @@
     <t>15:55:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>16:15:00</t>
   </si>
   <si>
@@ -316,6 +337,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -346,6 +370,15 @@
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>Alashkert</t>
+  </si>
+  <si>
+    <t>FK Banga Gargzdu</t>
+  </si>
+  <si>
+    <t>Rakow Czestochowa</t>
+  </si>
+  <si>
     <t>Al Sailiya</t>
   </si>
   <si>
@@ -355,9 +388,18 @@
     <t>Bursaspor</t>
   </si>
   <si>
+    <t>Mjallby</t>
+  </si>
+  <si>
     <t>Al Ahly Cairo</t>
   </si>
   <si>
+    <t>Gyori</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
     <t>FC Copenhagen</t>
   </si>
   <si>
@@ -370,6 +412,9 @@
     <t>Anderlecht</t>
   </si>
   <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
     <t>FC Basel</t>
   </si>
   <si>
@@ -400,6 +445,15 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>FC Van Yerevan</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>Gornik Zabrze</t>
+  </si>
+  <si>
     <t>Al Arabi (QAT)</t>
   </si>
   <si>
@@ -409,9 +463,18 @@
     <t>Istanbulspor</t>
   </si>
   <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
     <t>Smouha</t>
   </si>
   <si>
+    <t>Ferencvaros</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
     <t>FC Nordsjaelland</t>
   </si>
   <si>
@@ -424,6 +487,9 @@
     <t>Kortrijk</t>
   </si>
   <si>
+    <t>Jagiellonia Bialystock</t>
+  </si>
+  <si>
     <t>Sion</t>
   </si>
   <si>
@@ -436,7 +502,7 @@
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 12:43:06</t>
+    <t>2026-09-01 14:56:32</t>
   </si>
 </sst>
 </file>
@@ -768,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1018,16 +1084,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F2">
         <v>3.5</v>
@@ -1036,16 +1102,16 @@
         <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J2">
         <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1054,13 +1120,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -1078,7 +1144,7 @@
         <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W2">
         <v>1.3</v>
@@ -1252,7 +1318,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1260,19 +1326,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
         <v>2.58</v>
@@ -1287,7 +1353,7 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1305,7 +1371,7 @@
         <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1494,7 +1560,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1502,16 +1568,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F4">
         <v>2.92</v>
@@ -1544,10 +1610,10 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1556,10 +1622,10 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V4">
         <v>1.55</v>
@@ -1622,10 +1688,10 @@
         <v>38</v>
       </c>
       <c r="AP4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AR4">
         <v>12</v>
@@ -1640,7 +1706,7 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>3.9</v>
@@ -1652,7 +1718,7 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
         <v>4</v>
@@ -1736,7 +1802,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1744,16 +1810,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F5">
         <v>2.3</v>
@@ -1978,7 +2044,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1986,16 +2052,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F6">
         <v>2.04</v>
@@ -2007,7 +2073,7 @@
         <v>3.4</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -2019,10 +2085,10 @@
         <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O6">
         <v>1.28</v>
@@ -2034,22 +2100,22 @@
         <v>1.83</v>
       </c>
       <c r="R6">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2220,7 +2286,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2228,19 +2294,19 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F7">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -2258,2696 +2324,2696 @@
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
         <v>1.69</v>
       </c>
       <c r="Q7">
+        <v>2.04</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
+        <v>3.4</v>
+      </c>
+      <c r="T7">
+        <v>1.7</v>
+      </c>
+      <c r="U7">
+        <v>1.8</v>
+      </c>
+      <c r="V7">
+        <v>1.5</v>
+      </c>
+      <c r="W7">
+        <v>1.5</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>14.5</v>
+      </c>
+      <c r="Z7">
+        <v>26</v>
+      </c>
+      <c r="AA7">
+        <v>65</v>
+      </c>
+      <c r="AB7">
+        <v>13.5</v>
+      </c>
+      <c r="AC7">
+        <v>10</v>
+      </c>
+      <c r="AD7">
+        <v>18</v>
+      </c>
+      <c r="AE7">
+        <v>50</v>
+      </c>
+      <c r="AF7">
+        <v>25</v>
+      </c>
+      <c r="AG7">
+        <v>18</v>
+      </c>
+      <c r="AH7">
+        <v>26</v>
+      </c>
+      <c r="AI7">
+        <v>70</v>
+      </c>
+      <c r="AJ7">
+        <v>65</v>
+      </c>
+      <c r="AK7">
+        <v>48</v>
+      </c>
+      <c r="AL7">
+        <v>70</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>48</v>
+      </c>
+      <c r="AO7">
+        <v>50</v>
+      </c>
+      <c r="AP7">
+        <v>2.56</v>
+      </c>
+      <c r="AQ7">
         <v>2.18</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
       <c r="AR7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>4.9</v>
+        <v>1.16</v>
       </c>
       <c r="G8">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="H8">
-        <v>1.61</v>
+        <v>2.88</v>
       </c>
       <c r="I8">
-        <v>1.72</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>220</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="Q8">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F9">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H9">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Q9">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F10">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>3.25</v>
       </c>
       <c r="I10">
-        <v>8.6</v>
+        <v>3.85</v>
       </c>
       <c r="J10">
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <v>4.3</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>3.5</v>
+      </c>
+      <c r="O10">
+        <v>1.26</v>
+      </c>
+      <c r="P10">
+        <v>1.85</v>
+      </c>
+      <c r="Q10">
+        <v>1.52</v>
+      </c>
+      <c r="R10">
+        <v>1.2</v>
+      </c>
+      <c r="S10">
+        <v>2.74</v>
+      </c>
+      <c r="T10">
+        <v>1.56</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.72</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
         <v>4.5</v>
       </c>
-      <c r="K10">
-        <v>5.2</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>2.14</v>
-      </c>
-      <c r="Q10">
-        <v>1.62</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>0</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>0</v>
-      </c>
-      <c r="BC10">
-        <v>0</v>
-      </c>
-      <c r="BD10">
-        <v>0</v>
-      </c>
-      <c r="BE10">
-        <v>0</v>
-      </c>
-      <c r="BF10">
-        <v>0</v>
-      </c>
-      <c r="BG10">
-        <v>0</v>
-      </c>
-      <c r="BH10">
-        <v>0</v>
-      </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F11">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="G11">
-        <v>1.46</v>
+        <v>6.4</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>1.61</v>
       </c>
       <c r="I11">
-        <v>13.5</v>
+        <v>1.72</v>
       </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F12">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="H12">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="I12">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P12">
-        <v>2.72</v>
+        <v>1.88</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13">
+        <v>1.45</v>
+      </c>
+      <c r="G13">
+        <v>1.55</v>
+      </c>
+      <c r="H13">
+        <v>7.2</v>
+      </c>
+      <c r="I13">
+        <v>8.6</v>
+      </c>
+      <c r="J13">
+        <v>4.5</v>
+      </c>
+      <c r="K13">
+        <v>5.2</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.03</v>
+      </c>
+      <c r="N13">
+        <v>2.22</v>
+      </c>
+      <c r="O13">
+        <v>1.22</v>
+      </c>
+      <c r="P13">
+        <v>2.14</v>
+      </c>
+      <c r="Q13">
+        <v>1.73</v>
+      </c>
+      <c r="R13">
+        <v>1.35</v>
+      </c>
+      <c r="S13">
+        <v>2.54</v>
+      </c>
+      <c r="T13">
+        <v>1.73</v>
+      </c>
+      <c r="U13">
+        <v>1.01</v>
+      </c>
+      <c r="V13">
+        <v>1.13</v>
+      </c>
+      <c r="W13">
+        <v>2.8</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>40</v>
+      </c>
+      <c r="Z13">
+        <v>100</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>12.5</v>
+      </c>
+      <c r="AC13">
+        <v>16</v>
+      </c>
+      <c r="AD13">
+        <v>46</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>13</v>
+      </c>
+      <c r="AG13">
+        <v>15</v>
+      </c>
+      <c r="AH13">
+        <v>36</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>19</v>
+      </c>
+      <c r="AK13">
+        <v>23</v>
+      </c>
+      <c r="AL13">
+        <v>50</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>10</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>16</v>
+      </c>
+      <c r="AR13">
+        <v>42</v>
+      </c>
+      <c r="AS13">
         <v>85</v>
       </c>
-      <c r="B13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13">
-        <v>1.08</v>
-      </c>
-      <c r="G13">
-        <v>1000</v>
-      </c>
-      <c r="H13">
-        <v>1.08</v>
-      </c>
-      <c r="I13">
-        <v>1000</v>
-      </c>
-      <c r="J13">
-        <v>1.08</v>
-      </c>
-      <c r="K13">
-        <v>320</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>1.1</v>
-      </c>
-      <c r="Q13">
-        <v>1.01</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
       <c r="AT13">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F14">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="G14">
-        <v>1.75</v>
+        <v>4.4</v>
       </c>
       <c r="H14">
-        <v>5.5</v>
+        <v>1.85</v>
       </c>
       <c r="I14">
-        <v>5.9</v>
+        <v>1.86</v>
       </c>
       <c r="J14">
+        <v>4.2</v>
+      </c>
+      <c r="K14">
+        <v>4.4</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>4.8</v>
+      </c>
+      <c r="O14">
+        <v>1.22</v>
+      </c>
+      <c r="P14">
+        <v>2.38</v>
+      </c>
+      <c r="Q14">
+        <v>1.64</v>
+      </c>
+      <c r="R14">
+        <v>1.54</v>
+      </c>
+      <c r="S14">
+        <v>2.6</v>
+      </c>
+      <c r="T14">
+        <v>1.64</v>
+      </c>
+      <c r="U14">
+        <v>2.36</v>
+      </c>
+      <c r="V14">
+        <v>2.16</v>
+      </c>
+      <c r="W14">
+        <v>1.29</v>
+      </c>
+      <c r="X14">
+        <v>27</v>
+      </c>
+      <c r="Y14">
+        <v>14</v>
+      </c>
+      <c r="Z14">
+        <v>16.5</v>
+      </c>
+      <c r="AA14">
+        <v>27</v>
+      </c>
+      <c r="AB14">
+        <v>24</v>
+      </c>
+      <c r="AC14">
+        <v>10.5</v>
+      </c>
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
+        <v>22</v>
+      </c>
+      <c r="AF14">
+        <v>42</v>
+      </c>
+      <c r="AG14">
+        <v>22</v>
+      </c>
+      <c r="AH14">
+        <v>21</v>
+      </c>
+      <c r="AI14">
+        <v>34</v>
+      </c>
+      <c r="AJ14">
+        <v>100</v>
+      </c>
+      <c r="AK14">
+        <v>55</v>
+      </c>
+      <c r="AL14">
+        <v>60</v>
+      </c>
+      <c r="AM14">
+        <v>85</v>
+      </c>
+      <c r="AN14">
+        <v>44</v>
+      </c>
+      <c r="AO14">
+        <v>9.4</v>
+      </c>
+      <c r="AP14">
+        <v>4.2</v>
+      </c>
+      <c r="AQ14">
+        <v>10</v>
+      </c>
+      <c r="AR14">
+        <v>12</v>
+      </c>
+      <c r="AS14">
+        <v>4.2</v>
+      </c>
+      <c r="AT14">
         <v>4.1</v>
       </c>
-      <c r="K14">
+      <c r="AU14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV14">
+        <v>9.4</v>
+      </c>
+      <c r="AW14">
+        <v>15.5</v>
+      </c>
+      <c r="AX14">
+        <v>4.4</v>
+      </c>
+      <c r="AY14">
+        <v>15</v>
+      </c>
+      <c r="AZ14">
+        <v>14.5</v>
+      </c>
+      <c r="BA14">
         <v>4.3</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>2.16</v>
-      </c>
-      <c r="Q14">
-        <v>1.69</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
       <c r="BB14">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F15">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="G15">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="H15">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="I15">
+        <v>13.5</v>
+      </c>
+      <c r="J15">
+        <v>4.4</v>
+      </c>
+      <c r="K15">
+        <v>5.4</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>3.3</v>
+      </c>
+      <c r="O15">
+        <v>1.34</v>
+      </c>
+      <c r="P15">
+        <v>1.85</v>
+      </c>
+      <c r="Q15">
+        <v>2</v>
+      </c>
+      <c r="R15">
+        <v>1.27</v>
+      </c>
+      <c r="S15">
+        <v>3.35</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.63</v>
+      </c>
+      <c r="V15">
+        <v>1.08</v>
+      </c>
+      <c r="W15">
+        <v>3.15</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>34</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>8</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>9</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>40</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>22</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>19</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>95</v>
+      </c>
+      <c r="AT15">
+        <v>5.1</v>
+      </c>
+      <c r="AU15">
+        <v>8</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>95</v>
+      </c>
+      <c r="AX15">
+        <v>5.6</v>
+      </c>
+      <c r="AY15">
         <v>7.6</v>
       </c>
-      <c r="J15">
-        <v>4.7</v>
-      </c>
-      <c r="K15">
-        <v>5.5</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>2.46</v>
-      </c>
-      <c r="Q15">
-        <v>1.6</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F16">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="G16">
-        <v>2.66</v>
+        <v>5.8</v>
       </c>
       <c r="H16">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="I16">
-        <v>2.84</v>
+        <v>2.12</v>
       </c>
       <c r="J16">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="F17">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="G17">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="H17">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="I17">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P17">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q17">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F18">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G18">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="H18">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="I18">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="Q18">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4956,166 +5022,166 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB18">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BD18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE18">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BF18">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG18">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BH18">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI18">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL18">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN18">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BO18">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP18">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR18">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT18">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU18">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX18">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5124,249 +5190,1943 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19">
+        <v>2.64</v>
+      </c>
+      <c r="G19">
+        <v>1000</v>
+      </c>
+      <c r="H19">
+        <v>1.08</v>
+      </c>
+      <c r="I19">
+        <v>1.63</v>
+      </c>
+      <c r="J19">
+        <v>4.6</v>
+      </c>
+      <c r="K19">
+        <v>1000</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2.46</v>
+      </c>
+      <c r="Q19">
+        <v>1.48</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20">
+        <v>1.72</v>
+      </c>
+      <c r="G20">
+        <v>1.75</v>
+      </c>
+      <c r="H20">
+        <v>5.5</v>
+      </c>
+      <c r="I20">
+        <v>5.9</v>
+      </c>
+      <c r="J20">
+        <v>4.1</v>
+      </c>
+      <c r="K20">
+        <v>4.3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>2.16</v>
+      </c>
+      <c r="Q20">
+        <v>1.69</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>156</v>
+      </c>
+      <c r="F21">
+        <v>1.56</v>
+      </c>
+      <c r="G21">
+        <v>1.6</v>
+      </c>
+      <c r="H21">
+        <v>6.2</v>
+      </c>
+      <c r="I21">
+        <v>7.6</v>
+      </c>
+      <c r="J21">
+        <v>4.7</v>
+      </c>
+      <c r="K21">
+        <v>5.5</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.46</v>
+      </c>
+      <c r="Q21">
+        <v>1.6</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22">
+        <v>1.62</v>
+      </c>
+      <c r="G22">
+        <v>1.75</v>
+      </c>
+      <c r="H22">
+        <v>4.7</v>
+      </c>
+      <c r="I22">
+        <v>6.2</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>5.7</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.8</v>
+      </c>
+      <c r="Q22">
+        <v>1.43</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23">
+        <v>2.48</v>
+      </c>
+      <c r="G23">
+        <v>2.66</v>
+      </c>
+      <c r="H23">
+        <v>2.64</v>
+      </c>
+      <c r="I23">
+        <v>2.84</v>
+      </c>
+      <c r="J23">
+        <v>3.8</v>
+      </c>
+      <c r="K23">
+        <v>4.6</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.56</v>
+      </c>
+      <c r="Q23">
+        <v>1.52</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24">
+        <v>2.08</v>
+      </c>
+      <c r="G24">
+        <v>2.24</v>
+      </c>
+      <c r="H24">
+        <v>3.35</v>
+      </c>
+      <c r="I24">
+        <v>3.75</v>
+      </c>
+      <c r="J24">
+        <v>3.75</v>
+      </c>
+      <c r="K24">
+        <v>4.2</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2.22</v>
+      </c>
+      <c r="Q24">
+        <v>1.66</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25">
+        <v>2.6</v>
+      </c>
+      <c r="G25">
+        <v>2.82</v>
+      </c>
+      <c r="H25">
+        <v>2.76</v>
+      </c>
+      <c r="I25">
+        <v>2.96</v>
+      </c>
+      <c r="J25">
+        <v>3.4</v>
+      </c>
+      <c r="K25">
+        <v>3.65</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1.06</v>
+      </c>
+      <c r="N25">
+        <v>3.85</v>
+      </c>
+      <c r="O25">
+        <v>1.29</v>
+      </c>
+      <c r="P25">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>1.84</v>
+      </c>
+      <c r="R25">
+        <v>1.39</v>
+      </c>
+      <c r="S25">
+        <v>3.15</v>
+      </c>
+      <c r="T25">
+        <v>1.69</v>
+      </c>
+      <c r="U25">
+        <v>2.42</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>18</v>
+      </c>
+      <c r="Y25">
+        <v>12.5</v>
+      </c>
+      <c r="Z25">
+        <v>22</v>
+      </c>
+      <c r="AA25">
+        <v>44</v>
+      </c>
+      <c r="AB25">
+        <v>12.5</v>
+      </c>
+      <c r="AC25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD25">
+        <v>13.5</v>
+      </c>
+      <c r="AE25">
+        <v>32</v>
+      </c>
+      <c r="AF25">
+        <v>20</v>
+      </c>
+      <c r="AG25">
+        <v>12.5</v>
+      </c>
+      <c r="AH25">
+        <v>18.5</v>
+      </c>
+      <c r="AI25">
+        <v>50</v>
+      </c>
+      <c r="AJ25">
+        <v>40</v>
+      </c>
+      <c r="AK25">
+        <v>29</v>
+      </c>
+      <c r="AL25">
+        <v>44</v>
+      </c>
+      <c r="AM25">
+        <v>85</v>
+      </c>
+      <c r="AN25">
+        <v>23</v>
+      </c>
+      <c r="AO25">
+        <v>29</v>
+      </c>
+      <c r="AP25">
+        <v>13.5</v>
+      </c>
+      <c r="AQ25">
+        <v>10.5</v>
+      </c>
+      <c r="AR25">
+        <v>6.2</v>
+      </c>
+      <c r="AS25">
+        <v>7.2</v>
+      </c>
+      <c r="AT25">
+        <v>10</v>
+      </c>
+      <c r="AU25">
+        <v>7.2</v>
+      </c>
+      <c r="AV25">
+        <v>11</v>
+      </c>
+      <c r="AW25">
+        <v>7</v>
+      </c>
+      <c r="AX25">
+        <v>16</v>
+      </c>
+      <c r="AY25">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>28</v>
+      </c>
+      <c r="BB25">
+        <v>7</v>
+      </c>
+      <c r="BC25">
+        <v>6.8</v>
+      </c>
+      <c r="BD25">
+        <v>32</v>
+      </c>
+      <c r="BE25">
+        <v>7.6</v>
+      </c>
+      <c r="BF25">
+        <v>18.5</v>
+      </c>
+      <c r="BG25">
+        <v>6.6</v>
+      </c>
+      <c r="BH25">
+        <v>3.95</v>
+      </c>
+      <c r="BI25">
+        <v>2.92</v>
+      </c>
+      <c r="BJ25">
+        <v>10.5</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>120</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>6.6</v>
+      </c>
+      <c r="BO25">
+        <v>4.5</v>
+      </c>
+      <c r="BP25">
+        <v>23</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>36</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>6.8</v>
+      </c>
+      <c r="BU25">
+        <v>4.7</v>
+      </c>
+      <c r="BV25">
+        <v>25</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>38</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
         <v>80</v>
       </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F19">
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26">
         <v>1.86</v>
       </c>
-      <c r="G19">
+      <c r="G26">
         <v>2.04</v>
       </c>
-      <c r="H19">
+      <c r="H26">
         <v>4.2</v>
       </c>
-      <c r="I19">
+      <c r="I26">
         <v>5</v>
       </c>
-      <c r="J19">
+      <c r="J26">
         <v>3.6</v>
       </c>
-      <c r="K19">
+      <c r="K26">
         <v>4</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
         <v>1.93</v>
       </c>
-      <c r="Q19">
+      <c r="Q26">
         <v>1.89</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>0</v>
-      </c>
-      <c r="BC19">
-        <v>0</v>
-      </c>
-      <c r="BD19">
-        <v>0</v>
-      </c>
-      <c r="BE19">
-        <v>0</v>
-      </c>
-      <c r="BF19">
-        <v>0</v>
-      </c>
-      <c r="BG19">
-        <v>0</v>
-      </c>
-      <c r="BH19">
-        <v>0</v>
-      </c>
-      <c r="BI19">
-        <v>0</v>
-      </c>
-      <c r="BJ19">
-        <v>0</v>
-      </c>
-      <c r="BK19">
-        <v>0</v>
-      </c>
-      <c r="BL19">
-        <v>0</v>
-      </c>
-      <c r="BM19">
-        <v>0</v>
-      </c>
-      <c r="BN19">
-        <v>0</v>
-      </c>
-      <c r="BO19">
-        <v>0</v>
-      </c>
-      <c r="BP19">
-        <v>0</v>
-      </c>
-      <c r="BQ19">
-        <v>0</v>
-      </c>
-      <c r="BR19">
-        <v>0</v>
-      </c>
-      <c r="BS19">
-        <v>0</v>
-      </c>
-      <c r="BT19">
-        <v>0</v>
-      </c>
-      <c r="BU19">
-        <v>0</v>
-      </c>
-      <c r="BV19">
-        <v>0</v>
-      </c>
-      <c r="BW19">
-        <v>0</v>
-      </c>
-      <c r="BX19">
-        <v>0</v>
-      </c>
-      <c r="BY19">
-        <v>0</v>
-      </c>
-      <c r="BZ19">
-        <v>0</v>
-      </c>
-      <c r="CA19">
-        <v>0</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>140</v>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="175">
   <si>
     <t>League</t>
   </si>
@@ -283,16 +283,19 @@
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
     <t>Swedish Allsvenskan</t>
   </si>
   <si>
-    <t>Egyptian Premier</t>
+    <t>Israeli Premier League</t>
   </si>
   <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
-    <t>Israeli Premier League</t>
+    <t>Algerian Ligue 1</t>
   </si>
   <si>
     <t>Danish Superliga</t>
@@ -304,9 +307,15 @@
     <t>Swiss Super League</t>
   </si>
   <si>
+    <t>French Ligue 1</t>
+  </si>
+  <si>
     <t>Scottish Premiership</t>
   </si>
   <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
     <t>2026-09-03</t>
   </si>
   <si>
@@ -352,6 +361,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Barcelona (Ecu)</t>
   </si>
   <si>
@@ -385,19 +397,22 @@
     <t>NEOM Sports Club</t>
   </si>
   <si>
+    <t>Al Ahly Cairo</t>
+  </si>
+  <si>
+    <t>Mjallby</t>
+  </si>
+  <si>
     <t>Bursaspor</t>
   </si>
   <si>
-    <t>Mjallby</t>
-  </si>
-  <si>
-    <t>Al Ahly Cairo</t>
+    <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Gyori</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
+    <t>ES Setif</t>
   </si>
   <si>
     <t>FC Copenhagen</t>
@@ -421,12 +436,21 @@
     <t>Lugano</t>
   </si>
   <si>
+    <t>Toulouse</t>
+  </si>
+  <si>
     <t>Hibernian</t>
   </si>
   <si>
     <t>Univ Catolica (Ecu)</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>JS El Biar</t>
+  </si>
+  <si>
     <t>Independiente (Ecu)</t>
   </si>
   <si>
@@ -460,19 +484,22 @@
     <t>Al-Khaleej Saihat</t>
   </si>
   <si>
+    <t>Smouha</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
     <t>Istanbulspor</t>
   </si>
   <si>
-    <t>Djurgardens</t>
-  </si>
-  <si>
-    <t>Smouha</t>
+    <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>Ferencvaros</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
+    <t>ES Ben Aknoun</t>
   </si>
   <si>
     <t>FC Nordsjaelland</t>
@@ -496,13 +523,22 @@
     <t>Servette</t>
   </si>
   <si>
+    <t>Lille</t>
+  </si>
+  <si>
     <t>Hearts</t>
   </si>
   <si>
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-09-01 14:56:32</t>
+    <t>Celta Vigo</t>
+  </si>
+  <si>
+    <t>Olympique Akbou</t>
+  </si>
+  <si>
+    <t>2026-09-01 17:09:02</t>
   </si>
 </sst>
 </file>
@@ -834,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1084,16 +1120,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F2">
         <v>3.5</v>
@@ -1102,7 +1138,7 @@
         <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
         <v>2.32</v>
@@ -1111,7 +1147,7 @@
         <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1120,13 +1156,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
         <v>2.06</v>
@@ -1144,10 +1180,10 @@
         <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1318,7 +1354,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1326,16 +1362,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>2.34</v>
@@ -1365,7 +1401,7 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P3">
         <v>2.04</v>
@@ -1560,7 +1596,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1568,16 +1604,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F4">
         <v>2.92</v>
@@ -1595,7 +1631,7 @@
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1607,7 +1643,7 @@
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
         <v>1.73</v>
@@ -1628,7 +1664,7 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
         <v>1.44</v>
@@ -1691,7 +1727,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
         <v>12</v>
@@ -1802,7 +1838,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1810,16 +1846,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F5">
         <v>2.3</v>
@@ -2044,7 +2080,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2052,16 +2088,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F6">
         <v>2.04</v>
@@ -2286,7 +2322,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2294,34 +2330,34 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
         <v>2.74</v>
       </c>
       <c r="I7">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J7">
         <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2339,7 +2375,7 @@
         <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
         <v>1.22</v>
@@ -2354,10 +2390,10 @@
         <v>1.8</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2528,7 +2564,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2536,16 +2572,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F8">
         <v>1.16</v>
@@ -2557,7 +2593,7 @@
         <v>2.88</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
         <v>2.88</v>
@@ -2575,7 +2611,7 @@
         <v>2.34</v>
       </c>
       <c r="O8">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
         <v>2.34</v>
@@ -2770,7 +2806,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2778,19 +2814,19 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F9">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G9">
         <v>2.1</v>
@@ -2799,13 +2835,13 @@
         <v>4.5</v>
       </c>
       <c r="I9">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="K9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2814,31 +2850,31 @@
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P9">
+        <v>1.8</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <v>1.31</v>
+      </c>
+      <c r="S9">
+        <v>1.01</v>
+      </c>
+      <c r="T9">
         <v>1.79</v>
       </c>
-      <c r="Q9">
-        <v>2.02</v>
-      </c>
-      <c r="R9">
-        <v>1.3</v>
-      </c>
-      <c r="S9">
-        <v>3.15</v>
-      </c>
-      <c r="T9">
-        <v>1.82</v>
-      </c>
       <c r="U9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V9">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
         <v>1.9</v>
@@ -3012,7 +3048,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3020,16 +3056,16 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>2.2</v>
@@ -3065,19 +3101,19 @@
         <v>1.85</v>
       </c>
       <c r="Q10">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
         <v>2.74</v>
       </c>
       <c r="T10">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V10">
         <v>1.38</v>
@@ -3254,7 +3290,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3262,16 +3298,16 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F11">
         <v>4.9</v>
@@ -3289,7 +3325,7 @@
         <v>4.5</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3496,7 +3532,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3504,19 +3540,19 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F12">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G12">
         <v>1.97</v>
@@ -3525,52 +3561,52 @@
         <v>4.2</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J12">
         <v>3.65</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W12">
         <v>2.02</v>
       </c>
       <c r="X12">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y12">
         <v>23</v>
@@ -3630,52 +3666,52 @@
         <v>10.5</v>
       </c>
       <c r="AR12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AS12">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AT12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU12">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AV12">
         <v>11.5</v>
       </c>
       <c r="AW12">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AX12">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AY12">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AZ12">
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BB12">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BC12">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BD12">
         <v>22</v>
       </c>
       <c r="BE12">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BF12">
         <v>8.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3738,186 +3774,186 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F13">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="G13">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="H13">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="I13">
+        <v>13.5</v>
+      </c>
+      <c r="J13">
+        <v>4.4</v>
+      </c>
+      <c r="K13">
+        <v>5.4</v>
+      </c>
+      <c r="L13">
+        <v>1.33</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>3.3</v>
+      </c>
+      <c r="O13">
+        <v>1.34</v>
+      </c>
+      <c r="P13">
+        <v>1.85</v>
+      </c>
+      <c r="Q13">
+        <v>2</v>
+      </c>
+      <c r="R13">
+        <v>1.27</v>
+      </c>
+      <c r="S13">
+        <v>3.35</v>
+      </c>
+      <c r="T13">
+        <v>1.01</v>
+      </c>
+      <c r="U13">
+        <v>1.64</v>
+      </c>
+      <c r="V13">
+        <v>1.08</v>
+      </c>
+      <c r="W13">
+        <v>3.15</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>34</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>8</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>40</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>22</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>19</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>5.1</v>
+      </c>
+      <c r="AU13">
+        <v>8</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>5.6</v>
+      </c>
+      <c r="AY13">
+        <v>7.6</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
         <v>8.6</v>
       </c>
-      <c r="J13">
-        <v>4.5</v>
-      </c>
-      <c r="K13">
-        <v>5.2</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.03</v>
-      </c>
-      <c r="N13">
-        <v>2.22</v>
-      </c>
-      <c r="O13">
-        <v>1.22</v>
-      </c>
-      <c r="P13">
-        <v>2.14</v>
-      </c>
-      <c r="Q13">
-        <v>1.73</v>
-      </c>
-      <c r="R13">
-        <v>1.35</v>
-      </c>
-      <c r="S13">
-        <v>2.54</v>
-      </c>
-      <c r="T13">
-        <v>1.73</v>
-      </c>
-      <c r="U13">
-        <v>1.01</v>
-      </c>
-      <c r="V13">
-        <v>1.13</v>
-      </c>
-      <c r="W13">
-        <v>2.8</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>40</v>
-      </c>
-      <c r="Z13">
-        <v>100</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>12.5</v>
-      </c>
-      <c r="AC13">
-        <v>16</v>
-      </c>
-      <c r="AD13">
-        <v>46</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>13</v>
-      </c>
-      <c r="AG13">
-        <v>15</v>
-      </c>
-      <c r="AH13">
-        <v>36</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>19</v>
-      </c>
-      <c r="AK13">
-        <v>23</v>
-      </c>
-      <c r="AL13">
-        <v>50</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>10</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13">
-        <v>16</v>
-      </c>
-      <c r="AR13">
-        <v>42</v>
-      </c>
-      <c r="AS13">
-        <v>85</v>
-      </c>
-      <c r="AT13">
-        <v>5.6</v>
-      </c>
-      <c r="AU13">
-        <v>6.8</v>
-      </c>
-      <c r="AV13">
-        <v>17.5</v>
-      </c>
-      <c r="AW13">
-        <v>70</v>
-      </c>
-      <c r="AX13">
-        <v>5.8</v>
-      </c>
-      <c r="AY13">
-        <v>6.2</v>
-      </c>
-      <c r="AZ13">
-        <v>14.5</v>
-      </c>
-      <c r="BA13">
-        <v>60</v>
-      </c>
-      <c r="BB13">
-        <v>8</v>
-      </c>
       <c r="BC13">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3980,27 +4016,27 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G14">
         <v>4.4</v>
@@ -4009,7 +4045,7 @@
         <v>1.85</v>
       </c>
       <c r="I14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="J14">
         <v>4.2</v>
@@ -4030,7 +4066,7 @@
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q14">
         <v>1.64</v>
@@ -4048,7 +4084,7 @@
         <v>2.36</v>
       </c>
       <c r="V14">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="W14">
         <v>1.29</v>
@@ -4057,34 +4093,34 @@
         <v>27</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AB14">
         <v>24</v>
       </c>
       <c r="AC14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>13</v>
       </c>
       <c r="AE14">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AF14">
         <v>42</v>
       </c>
       <c r="AG14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
         <v>34</v>
@@ -4108,55 +4144,55 @@
         <v>9.4</v>
       </c>
       <c r="AP14">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14">
         <v>10</v>
       </c>
       <c r="AR14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS14">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT14">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AU14">
         <v>8.800000000000001</v>
       </c>
       <c r="AV14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AX14">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ14">
         <v>14.5</v>
       </c>
       <c r="BA14">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BB14">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC14">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD14">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE14">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF14">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG14">
         <v>8.199999999999999</v>
@@ -4222,186 +4258,186 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G15">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="H15">
+        <v>7.2</v>
+      </c>
+      <c r="I15">
+        <v>8.6</v>
+      </c>
+      <c r="J15">
+        <v>4.5</v>
+      </c>
+      <c r="K15">
+        <v>5.2</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>2.22</v>
+      </c>
+      <c r="O15">
+        <v>1.22</v>
+      </c>
+      <c r="P15">
+        <v>2.14</v>
+      </c>
+      <c r="Q15">
+        <v>1.73</v>
+      </c>
+      <c r="R15">
+        <v>1.35</v>
+      </c>
+      <c r="S15">
+        <v>2.54</v>
+      </c>
+      <c r="T15">
+        <v>1.78</v>
+      </c>
+      <c r="U15">
+        <v>1.61</v>
+      </c>
+      <c r="V15">
+        <v>1.13</v>
+      </c>
+      <c r="W15">
+        <v>2.8</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>40</v>
+      </c>
+      <c r="Z15">
+        <v>100</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>12.5</v>
+      </c>
+      <c r="AC15">
+        <v>16</v>
+      </c>
+      <c r="AD15">
+        <v>46</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>13</v>
+      </c>
+      <c r="AG15">
+        <v>15</v>
+      </c>
+      <c r="AH15">
+        <v>36</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>19</v>
+      </c>
+      <c r="AK15">
+        <v>23</v>
+      </c>
+      <c r="AL15">
+        <v>50</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
         <v>10</v>
       </c>
-      <c r="I15">
-        <v>13.5</v>
-      </c>
-      <c r="J15">
-        <v>4.4</v>
-      </c>
-      <c r="K15">
-        <v>5.4</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.06</v>
-      </c>
-      <c r="N15">
-        <v>3.3</v>
-      </c>
-      <c r="O15">
-        <v>1.34</v>
-      </c>
-      <c r="P15">
-        <v>1.85</v>
-      </c>
-      <c r="Q15">
-        <v>2</v>
-      </c>
-      <c r="R15">
-        <v>1.27</v>
-      </c>
-      <c r="S15">
-        <v>3.35</v>
-      </c>
-      <c r="T15">
-        <v>1.01</v>
-      </c>
-      <c r="U15">
-        <v>1.63</v>
-      </c>
-      <c r="V15">
-        <v>1.08</v>
-      </c>
-      <c r="W15">
-        <v>3.15</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>34</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>16</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>5.6</v>
+      </c>
+      <c r="AU15">
+        <v>6.8</v>
+      </c>
+      <c r="AV15">
+        <v>17.5</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>5.8</v>
+      </c>
+      <c r="AY15">
+        <v>6.2</v>
+      </c>
+      <c r="AZ15">
+        <v>14.5</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
         <v>8</v>
       </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>9</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>40</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>22</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>19</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>95</v>
-      </c>
-      <c r="AT15">
-        <v>5.1</v>
-      </c>
-      <c r="AU15">
-        <v>8</v>
-      </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>95</v>
-      </c>
-      <c r="AX15">
-        <v>5.6</v>
-      </c>
-      <c r="AY15">
-        <v>7.6</v>
-      </c>
-      <c r="AZ15">
-        <v>1.01</v>
-      </c>
-      <c r="BA15">
-        <v>95</v>
-      </c>
-      <c r="BB15">
-        <v>8.6</v>
-      </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BD15">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG15">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4464,7 +4500,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4472,157 +4508,157 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F16">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="G16">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="H16">
+        <v>2.46</v>
+      </c>
+      <c r="I16">
+        <v>2.84</v>
+      </c>
+      <c r="J16">
+        <v>3.55</v>
+      </c>
+      <c r="K16">
+        <v>4.6</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>4.3</v>
+      </c>
+      <c r="O16">
+        <v>1.25</v>
+      </c>
+      <c r="P16">
+        <v>2.12</v>
+      </c>
+      <c r="Q16">
         <v>1.73</v>
       </c>
-      <c r="I16">
+      <c r="R16">
+        <v>1.44</v>
+      </c>
+      <c r="S16">
+        <v>2.82</v>
+      </c>
+      <c r="T16">
+        <v>1.52</v>
+      </c>
+      <c r="U16">
         <v>2.12</v>
       </c>
-      <c r="J16">
-        <v>3.45</v>
-      </c>
-      <c r="K16">
-        <v>6.2</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>2.24</v>
-      </c>
-      <c r="O16">
-        <v>1.17</v>
-      </c>
-      <c r="P16">
-        <v>2.24</v>
-      </c>
-      <c r="Q16">
-        <v>1.47</v>
-      </c>
-      <c r="R16">
-        <v>1.51</v>
-      </c>
-      <c r="S16">
-        <v>2.1</v>
-      </c>
-      <c r="T16">
-        <v>1.43</v>
-      </c>
-      <c r="U16">
-        <v>1.01</v>
-      </c>
       <c r="V16">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS16">
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA16">
         <v>1.01</v>
@@ -4631,7 +4667,7 @@
         <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD16">
         <v>1.01</v>
@@ -4640,10 +4676,10 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4706,7 +4742,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4714,58 +4750,58 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>2.64</v>
+        <v>3.9</v>
       </c>
       <c r="G17">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="H17">
-        <v>2.44</v>
+        <v>1.73</v>
       </c>
       <c r="I17">
-        <v>2.94</v>
+        <v>2.1</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q17">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="R17">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="S17">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4774,118 +4810,118 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="W17">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="X17">
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
         <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4948,7 +4984,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4956,1693 +4992,1693 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F18">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="G18">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H18">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>1.08</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>320</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P18">
-        <v>2.72</v>
+        <v>1.08</v>
       </c>
       <c r="Q18">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F19">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H19">
-        <v>1.08</v>
+        <v>3.3</v>
       </c>
       <c r="I19">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="J19">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="Q19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F20">
-        <v>1.72</v>
+        <v>5.3</v>
       </c>
       <c r="G20">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H20">
-        <v>5.5</v>
+        <v>1.56</v>
       </c>
       <c r="I20">
-        <v>5.9</v>
+        <v>1.63</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P20">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F21">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G21">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="H21">
+        <v>5.5</v>
+      </c>
+      <c r="I21">
+        <v>5.9</v>
+      </c>
+      <c r="J21">
+        <v>4.1</v>
+      </c>
+      <c r="K21">
+        <v>4.4</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>3.7</v>
+      </c>
+      <c r="O21">
+        <v>1.25</v>
+      </c>
+      <c r="P21">
+        <v>2.1</v>
+      </c>
+      <c r="Q21">
+        <v>1.77</v>
+      </c>
+      <c r="R21">
+        <v>1.39</v>
+      </c>
+      <c r="S21">
+        <v>2.78</v>
+      </c>
+      <c r="T21">
+        <v>1.79</v>
+      </c>
+      <c r="U21">
+        <v>1.94</v>
+      </c>
+      <c r="V21">
+        <v>1.2</v>
+      </c>
+      <c r="W21">
+        <v>2.34</v>
+      </c>
+      <c r="X21">
+        <v>19.5</v>
+      </c>
+      <c r="Y21">
+        <v>22</v>
+      </c>
+      <c r="Z21">
+        <v>55</v>
+      </c>
+      <c r="AA21">
+        <v>170</v>
+      </c>
+      <c r="AB21">
+        <v>10</v>
+      </c>
+      <c r="AC21">
+        <v>9.6</v>
+      </c>
+      <c r="AD21">
+        <v>23</v>
+      </c>
+      <c r="AE21">
+        <v>100</v>
+      </c>
+      <c r="AF21">
+        <v>12.5</v>
+      </c>
+      <c r="AG21">
+        <v>11</v>
+      </c>
+      <c r="AH21">
+        <v>20</v>
+      </c>
+      <c r="AI21">
+        <v>85</v>
+      </c>
+      <c r="AJ21">
+        <v>18</v>
+      </c>
+      <c r="AK21">
+        <v>18.5</v>
+      </c>
+      <c r="AL21">
+        <v>36</v>
+      </c>
+      <c r="AM21">
+        <v>120</v>
+      </c>
+      <c r="AN21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO21">
+        <v>95</v>
+      </c>
+      <c r="AP21">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21">
+        <v>16</v>
+      </c>
+      <c r="AR21">
+        <v>6.6</v>
+      </c>
+      <c r="AS21">
+        <v>7.2</v>
+      </c>
+      <c r="AT21">
+        <v>8</v>
+      </c>
+      <c r="AU21">
+        <v>8</v>
+      </c>
+      <c r="AV21">
+        <v>18.5</v>
+      </c>
+      <c r="AW21">
+        <v>7</v>
+      </c>
+      <c r="AX21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY21">
+        <v>8.6</v>
+      </c>
+      <c r="AZ21">
+        <v>5.5</v>
+      </c>
+      <c r="BA21">
+        <v>7</v>
+      </c>
+      <c r="BB21">
+        <v>13</v>
+      </c>
+      <c r="BC21">
+        <v>14.5</v>
+      </c>
+      <c r="BD21">
         <v>6.2</v>
       </c>
-      <c r="I21">
-        <v>7.6</v>
-      </c>
-      <c r="J21">
-        <v>4.7</v>
-      </c>
-      <c r="K21">
-        <v>5.5</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>2.46</v>
-      </c>
-      <c r="Q21">
-        <v>1.6</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21">
-        <v>0</v>
-      </c>
       <c r="BE21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F22">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="G22">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="H22">
+        <v>6.2</v>
+      </c>
+      <c r="I22">
+        <v>7.6</v>
+      </c>
+      <c r="J22">
         <v>4.7</v>
       </c>
-      <c r="I22">
-        <v>6.2</v>
-      </c>
-      <c r="J22">
-        <v>4</v>
-      </c>
       <c r="K22">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q22">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F23">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="G23">
-        <v>2.66</v>
+        <v>1.75</v>
       </c>
       <c r="H23">
-        <v>2.64</v>
+        <v>4.7</v>
       </c>
       <c r="I23">
-        <v>2.84</v>
+        <v>6.2</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K23">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P23">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F24">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="G24">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="H24">
-        <v>3.35</v>
+        <v>2.64</v>
       </c>
       <c r="I24">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="J24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K24">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P24">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6650,474 +6686,474 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F25">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="G25">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="H25">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="I25">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="J25">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
         <v>3.85</v>
       </c>
       <c r="O25">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q25">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S25">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="T25">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X25">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
         <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
         <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F26">
-        <v>1.86</v>
+        <v>3.6</v>
       </c>
       <c r="G26">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="H26">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="J26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q26">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7126,7 +7162,975 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>162</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27">
+        <v>2.58</v>
+      </c>
+      <c r="G27">
+        <v>2.82</v>
+      </c>
+      <c r="H27">
+        <v>2.76</v>
+      </c>
+      <c r="I27">
+        <v>2.98</v>
+      </c>
+      <c r="J27">
+        <v>3.4</v>
+      </c>
+      <c r="K27">
+        <v>3.65</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.06</v>
+      </c>
+      <c r="N27">
+        <v>3.85</v>
+      </c>
+      <c r="O27">
+        <v>1.29</v>
+      </c>
+      <c r="P27">
+        <v>1.99</v>
+      </c>
+      <c r="Q27">
+        <v>1.84</v>
+      </c>
+      <c r="R27">
+        <v>1.39</v>
+      </c>
+      <c r="S27">
+        <v>3.15</v>
+      </c>
+      <c r="T27">
+        <v>1.69</v>
+      </c>
+      <c r="U27">
+        <v>2.22</v>
+      </c>
+      <c r="V27">
+        <v>1.51</v>
+      </c>
+      <c r="W27">
+        <v>1.55</v>
+      </c>
+      <c r="X27">
+        <v>18</v>
+      </c>
+      <c r="Y27">
+        <v>12.5</v>
+      </c>
+      <c r="Z27">
+        <v>22</v>
+      </c>
+      <c r="AA27">
+        <v>44</v>
+      </c>
+      <c r="AB27">
+        <v>12.5</v>
+      </c>
+      <c r="AC27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>13.5</v>
+      </c>
+      <c r="AE27">
+        <v>32</v>
+      </c>
+      <c r="AF27">
+        <v>20</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>19</v>
+      </c>
+      <c r="AI27">
+        <v>50</v>
+      </c>
+      <c r="AJ27">
+        <v>40</v>
+      </c>
+      <c r="AK27">
+        <v>29</v>
+      </c>
+      <c r="AL27">
+        <v>44</v>
+      </c>
+      <c r="AM27">
+        <v>85</v>
+      </c>
+      <c r="AN27">
+        <v>23</v>
+      </c>
+      <c r="AO27">
+        <v>29</v>
+      </c>
+      <c r="AP27">
+        <v>13.5</v>
+      </c>
+      <c r="AQ27">
+        <v>10.5</v>
+      </c>
+      <c r="AR27">
+        <v>6.2</v>
+      </c>
+      <c r="AS27">
+        <v>7.2</v>
+      </c>
+      <c r="AT27">
+        <v>10</v>
+      </c>
+      <c r="AU27">
+        <v>7.2</v>
+      </c>
+      <c r="AV27">
+        <v>11</v>
+      </c>
+      <c r="AW27">
+        <v>7</v>
+      </c>
+      <c r="AX27">
+        <v>16</v>
+      </c>
+      <c r="AY27">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27">
+        <v>14</v>
+      </c>
+      <c r="BA27">
+        <v>28</v>
+      </c>
+      <c r="BB27">
+        <v>7</v>
+      </c>
+      <c r="BC27">
+        <v>6.8</v>
+      </c>
+      <c r="BD27">
+        <v>32</v>
+      </c>
+      <c r="BE27">
+        <v>7.8</v>
+      </c>
+      <c r="BF27">
+        <v>18.5</v>
+      </c>
+      <c r="BG27">
+        <v>6.6</v>
+      </c>
+      <c r="BH27">
+        <v>3.95</v>
+      </c>
+      <c r="BI27">
+        <v>3.15</v>
+      </c>
+      <c r="BJ27">
+        <v>10.5</v>
+      </c>
+      <c r="BK27">
+        <v>3.7</v>
+      </c>
+      <c r="BL27">
+        <v>120</v>
+      </c>
+      <c r="BM27">
+        <v>5.5</v>
+      </c>
+      <c r="BN27">
+        <v>6.6</v>
+      </c>
+      <c r="BO27">
+        <v>4.5</v>
+      </c>
+      <c r="BP27">
+        <v>23</v>
+      </c>
+      <c r="BQ27">
+        <v>4.6</v>
+      </c>
+      <c r="BR27">
+        <v>36</v>
+      </c>
+      <c r="BS27">
+        <v>4.9</v>
+      </c>
+      <c r="BT27">
+        <v>6.8</v>
+      </c>
+      <c r="BU27">
+        <v>4.7</v>
+      </c>
+      <c r="BV27">
+        <v>25</v>
+      </c>
+      <c r="BW27">
+        <v>4.7</v>
+      </c>
+      <c r="BX27">
+        <v>38</v>
+      </c>
+      <c r="BY27">
+        <v>5</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28">
+        <v>1.86</v>
+      </c>
+      <c r="G28">
+        <v>2.04</v>
+      </c>
+      <c r="H28">
+        <v>4.2</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>3.6</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28">
+        <v>1.31</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>3.2</v>
+      </c>
+      <c r="O28">
+        <v>1.3</v>
+      </c>
+      <c r="P28">
+        <v>1.93</v>
+      </c>
+      <c r="Q28">
+        <v>1.9</v>
+      </c>
+      <c r="R28">
+        <v>1.28</v>
+      </c>
+      <c r="S28">
+        <v>2.88</v>
+      </c>
+      <c r="T28">
+        <v>1.01</v>
+      </c>
+      <c r="U28">
+        <v>1.01</v>
+      </c>
+      <c r="V28">
+        <v>1.25</v>
+      </c>
+      <c r="W28">
+        <v>1.96</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>1000</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>1000</v>
+      </c>
+      <c r="AC28">
+        <v>1000</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>1000</v>
+      </c>
+      <c r="AG28">
+        <v>1000</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28">
+        <v>1.01</v>
+      </c>
+      <c r="AR28">
+        <v>1.01</v>
+      </c>
+      <c r="AS28">
+        <v>1.01</v>
+      </c>
+      <c r="AT28">
+        <v>1.01</v>
+      </c>
+      <c r="AU28">
+        <v>1.01</v>
+      </c>
+      <c r="AV28">
+        <v>1.01</v>
+      </c>
+      <c r="AW28">
+        <v>1.01</v>
+      </c>
+      <c r="AX28">
+        <v>1.01</v>
+      </c>
+      <c r="AY28">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28">
+        <v>1.01</v>
+      </c>
+      <c r="BA28">
+        <v>1.01</v>
+      </c>
+      <c r="BB28">
+        <v>1.01</v>
+      </c>
+      <c r="BC28">
+        <v>1.01</v>
+      </c>
+      <c r="BD28">
+        <v>1.01</v>
+      </c>
+      <c r="BE28">
+        <v>1.01</v>
+      </c>
+      <c r="BF28">
+        <v>1.01</v>
+      </c>
+      <c r="BG28">
+        <v>1.01</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.01</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.01</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.01</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.01</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.01</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.01</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29">
+        <v>1.99</v>
+      </c>
+      <c r="G29">
+        <v>2.02</v>
+      </c>
+      <c r="H29">
+        <v>4.2</v>
+      </c>
+      <c r="I29">
+        <v>4.3</v>
+      </c>
+      <c r="J29">
+        <v>3.75</v>
+      </c>
+      <c r="K29">
+        <v>3.8</v>
+      </c>
+      <c r="L29">
+        <v>1.4</v>
+      </c>
+      <c r="M29">
+        <v>1.07</v>
+      </c>
+      <c r="N29">
+        <v>3.85</v>
+      </c>
+      <c r="O29">
+        <v>1.32</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>1.98</v>
+      </c>
+      <c r="R29">
+        <v>1.37</v>
+      </c>
+      <c r="S29">
+        <v>3.5</v>
+      </c>
+      <c r="T29">
+        <v>1.82</v>
+      </c>
+      <c r="U29">
+        <v>2.14</v>
+      </c>
+      <c r="V29">
+        <v>1.3</v>
+      </c>
+      <c r="W29">
+        <v>1.98</v>
+      </c>
+      <c r="X29">
+        <v>14.5</v>
+      </c>
+      <c r="Y29">
+        <v>15.5</v>
+      </c>
+      <c r="Z29">
+        <v>32</v>
+      </c>
+      <c r="AA29">
+        <v>90</v>
+      </c>
+      <c r="AB29">
+        <v>9.6</v>
+      </c>
+      <c r="AC29">
+        <v>8.4</v>
+      </c>
+      <c r="AD29">
+        <v>17</v>
+      </c>
+      <c r="AE29">
+        <v>55</v>
+      </c>
+      <c r="AF29">
+        <v>12.5</v>
+      </c>
+      <c r="AG29">
+        <v>10.5</v>
+      </c>
+      <c r="AH29">
+        <v>18.5</v>
+      </c>
+      <c r="AI29">
+        <v>65</v>
+      </c>
+      <c r="AJ29">
+        <v>24</v>
+      </c>
+      <c r="AK29">
+        <v>21</v>
+      </c>
+      <c r="AL29">
+        <v>38</v>
+      </c>
+      <c r="AM29">
+        <v>110</v>
+      </c>
+      <c r="AN29">
+        <v>14.5</v>
+      </c>
+      <c r="AO29">
+        <v>55</v>
+      </c>
+      <c r="AP29">
+        <v>13</v>
+      </c>
+      <c r="AQ29">
+        <v>14</v>
+      </c>
+      <c r="AR29">
+        <v>26</v>
+      </c>
+      <c r="AS29">
+        <v>34</v>
+      </c>
+      <c r="AT29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>15.5</v>
+      </c>
+      <c r="AW29">
+        <v>44</v>
+      </c>
+      <c r="AX29">
+        <v>11</v>
+      </c>
+      <c r="AY29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29">
+        <v>16.5</v>
+      </c>
+      <c r="BA29">
+        <v>30</v>
+      </c>
+      <c r="BB29">
+        <v>21</v>
+      </c>
+      <c r="BC29">
+        <v>19</v>
+      </c>
+      <c r="BD29">
+        <v>32</v>
+      </c>
+      <c r="BE29">
+        <v>38</v>
+      </c>
+      <c r="BF29">
+        <v>12.5</v>
+      </c>
+      <c r="BG29">
+        <v>46</v>
+      </c>
+      <c r="BH29">
+        <v>3.6</v>
+      </c>
+      <c r="BI29">
+        <v>3.1</v>
+      </c>
+      <c r="BJ29">
+        <v>11.5</v>
+      </c>
+      <c r="BK29">
+        <v>3.9</v>
+      </c>
+      <c r="BL29">
+        <v>150</v>
+      </c>
+      <c r="BM29">
+        <v>5.5</v>
+      </c>
+      <c r="BN29">
+        <v>5.6</v>
+      </c>
+      <c r="BO29">
+        <v>3.65</v>
+      </c>
+      <c r="BP29">
+        <v>17</v>
+      </c>
+      <c r="BQ29">
+        <v>4.2</v>
+      </c>
+      <c r="BR29">
+        <v>34</v>
+      </c>
+      <c r="BS29">
+        <v>4.9</v>
+      </c>
+      <c r="BT29">
+        <v>9</v>
+      </c>
+      <c r="BU29">
+        <v>5.7</v>
+      </c>
+      <c r="BV29">
+        <v>42</v>
+      </c>
+      <c r="BW29">
+        <v>5</v>
+      </c>
+      <c r="BX29">
+        <v>55</v>
+      </c>
+      <c r="BY29">
+        <v>5.1</v>
+      </c>
+      <c r="BZ29">
+        <v>29</v>
+      </c>
+      <c r="CA29">
+        <v>4.7</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30">
+        <v>1.08</v>
+      </c>
+      <c r="G30">
+        <v>1000</v>
+      </c>
+      <c r="H30">
+        <v>1.08</v>
+      </c>
+      <c r="I30">
+        <v>1000</v>
+      </c>
+      <c r="J30">
+        <v>1.08</v>
+      </c>
+      <c r="K30">
+        <v>280</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>1.09</v>
+      </c>
+      <c r="O30">
+        <v>1.02</v>
+      </c>
+      <c r="P30">
+        <v>1.09</v>
+      </c>
+      <c r="Q30">
+        <v>1.47</v>
+      </c>
+      <c r="R30">
+        <v>1.08</v>
+      </c>
+      <c r="S30">
+        <v>1.48</v>
+      </c>
+      <c r="T30">
+        <v>1.01</v>
+      </c>
+      <c r="U30">
+        <v>1.01</v>
+      </c>
+      <c r="V30">
+        <v>1.02</v>
+      </c>
+      <c r="W30">
+        <v>1.02</v>
+      </c>
+      <c r="X30">
+        <v>1000</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>1000</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>1000</v>
+      </c>
+      <c r="AC30">
+        <v>1000</v>
+      </c>
+      <c r="AD30">
+        <v>1000</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
+        <v>1000</v>
+      </c>
+      <c r="AG30">
+        <v>1000</v>
+      </c>
+      <c r="AH30">
+        <v>1000</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>1000</v>
+      </c>
+      <c r="AK30">
+        <v>1000</v>
+      </c>
+      <c r="AL30">
+        <v>1000</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>1000</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30">
+        <v>1.01</v>
+      </c>
+      <c r="AR30">
+        <v>1.01</v>
+      </c>
+      <c r="AS30">
+        <v>1.01</v>
+      </c>
+      <c r="AT30">
+        <v>1.01</v>
+      </c>
+      <c r="AU30">
+        <v>1.01</v>
+      </c>
+      <c r="AV30">
+        <v>1.01</v>
+      </c>
+      <c r="AW30">
+        <v>1.01</v>
+      </c>
+      <c r="AX30">
+        <v>1.01</v>
+      </c>
+      <c r="AY30">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30">
+        <v>1.01</v>
+      </c>
+      <c r="BA30">
+        <v>1.01</v>
+      </c>
+      <c r="BB30">
+        <v>1.01</v>
+      </c>
+      <c r="BC30">
+        <v>1.01</v>
+      </c>
+      <c r="BD30">
+        <v>1.01</v>
+      </c>
+      <c r="BE30">
+        <v>1.01</v>
+      </c>
+      <c r="BF30">
+        <v>1.01</v>
+      </c>
+      <c r="BG30">
+        <v>1.01</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.01</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.01</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.01</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.01</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.01</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.01</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -538,7 +538,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-09-01 17:09:02</t>
+    <t>2026-09-01 19:21:03</t>
   </si>
 </sst>
 </file>
@@ -1132,79 +1132,79 @@
         <v>145</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
         <v>2.1</v>
       </c>
       <c r="I2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J2">
         <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
+        <v>1.83</v>
+      </c>
+      <c r="Q2">
+        <v>2.02</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>2.36</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
         <v>1.76</v>
       </c>
-      <c r="Q2">
-        <v>2.06</v>
-      </c>
-      <c r="R2">
-        <v>1.25</v>
-      </c>
-      <c r="S2">
-        <v>3.7</v>
-      </c>
-      <c r="T2">
-        <v>1.82</v>
-      </c>
-      <c r="U2">
-        <v>1.99</v>
-      </c>
-      <c r="V2">
-        <v>1.75</v>
-      </c>
       <c r="W2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AA2">
         <v>36</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE2">
         <v>32</v>
@@ -1213,7 +1213,7 @@
         <v>30</v>
       </c>
       <c r="AG2">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH2">
         <v>23</v>
@@ -1231,7 +1231,7 @@
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2">
         <v>60</v>
@@ -1240,58 +1240,58 @@
         <v>25</v>
       </c>
       <c r="AP2">
-        <v>9.6</v>
+        <v>1.37</v>
       </c>
       <c r="AQ2">
-        <v>6.8</v>
+        <v>1.37</v>
       </c>
       <c r="AR2">
-        <v>10.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT2">
-        <v>9.6</v>
+        <v>1.37</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>1.37</v>
       </c>
       <c r="AV2">
-        <v>8.4</v>
+        <v>1.37</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>1.31</v>
       </c>
       <c r="AX2">
-        <v>17.5</v>
+        <v>1.31</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>1.37</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>1.29</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>1.3</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1374,145 +1374,145 @@
         <v>146</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="T3">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
         <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
         <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
         <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
@@ -1521,7 +1521,7 @@
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -1530,7 +1530,7 @@
         <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
         <v>1.01</v>
@@ -1625,7 +1625,7 @@
         <v>2.56</v>
       </c>
       <c r="I4">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J4">
         <v>3.25</v>
@@ -1643,7 +1643,7 @@
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
         <v>1.73</v>
@@ -1664,7 +1664,7 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
         <v>1.44</v>
@@ -1727,7 +1727,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4">
         <v>12</v>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
         <v>4</v>
@@ -2342,13 +2342,13 @@
         <v>150</v>
       </c>
       <c r="F7">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G7">
         <v>3.1</v>
       </c>
       <c r="H7">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
         <v>3.05</v>
@@ -2357,7 +2357,7 @@
         <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2375,13 +2375,13 @@
         <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
         <v>1.22</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
         <v>1.7</v>
@@ -2390,7 +2390,7 @@
         <v>1.8</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
         <v>1.47</v>
@@ -2632,7 +2632,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8">
         <v>2.8</v>
@@ -2862,16 +2862,16 @@
         <v>2</v>
       </c>
       <c r="R9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
         <v>1.01</v>
       </c>
       <c r="T9">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -3077,7 +3077,7 @@
         <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J10">
         <v>3.5</v>
@@ -3089,145 +3089,145 @@
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O10">
         <v>1.26</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q10">
+        <v>1.84</v>
+      </c>
+      <c r="R10">
+        <v>1.39</v>
+      </c>
+      <c r="S10">
+        <v>3.15</v>
+      </c>
+      <c r="T10">
         <v>1.71</v>
       </c>
-      <c r="R10">
-        <v>1.24</v>
-      </c>
-      <c r="S10">
-        <v>2.74</v>
-      </c>
-      <c r="T10">
-        <v>1.01</v>
-      </c>
       <c r="U10">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH10">
         <v>4.5</v>
@@ -3552,166 +3552,166 @@
         <v>155</v>
       </c>
       <c r="F12">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="G12">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H12">
+        <v>4.4</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
         <v>4.2</v>
       </c>
-      <c r="I12">
-        <v>5.1</v>
-      </c>
-      <c r="J12">
-        <v>3.65</v>
-      </c>
-      <c r="K12">
-        <v>4.4</v>
-      </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
         <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="R12">
+        <v>1.39</v>
+      </c>
+      <c r="S12">
+        <v>3.15</v>
+      </c>
+      <c r="T12">
+        <v>1.67</v>
+      </c>
+      <c r="U12">
+        <v>1.96</v>
+      </c>
+      <c r="V12">
         <v>1.27</v>
       </c>
-      <c r="S12">
-        <v>2.92</v>
-      </c>
-      <c r="T12">
-        <v>1.61</v>
-      </c>
-      <c r="U12">
-        <v>1.92</v>
-      </c>
-      <c r="V12">
-        <v>1.24</v>
-      </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y12">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Z12">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB12">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AC12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE12">
         <v>75</v>
       </c>
       <c r="AF12">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AI12">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AK12">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AL12">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN12">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AO12">
         <v>75</v>
       </c>
       <c r="AP12">
-        <v>2.62</v>
+        <v>14</v>
       </c>
       <c r="AQ12">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AR12">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="AS12">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12">
-        <v>2.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AW12">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="AX12">
-        <v>2.56</v>
+        <v>10</v>
       </c>
       <c r="AY12">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA12">
-        <v>2.92</v>
+        <v>8.6</v>
       </c>
       <c r="BB12">
-        <v>2.74</v>
+        <v>6.6</v>
       </c>
       <c r="BC12">
-        <v>2.72</v>
+        <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BE12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BF12">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG12">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3797,7 +3797,7 @@
         <v>1.4</v>
       </c>
       <c r="G13">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H13">
         <v>10</v>
@@ -3815,31 +3815,31 @@
         <v>1.33</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O13">
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S13">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V13">
         <v>1.08</v>
@@ -3848,61 +3848,61 @@
         <v>3.15</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y13">
         <v>34</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK13">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13">
         <v>19</v>
@@ -3914,43 +3914,43 @@
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>10</v>
+      </c>
+      <c r="BC13">
+        <v>13.5</v>
+      </c>
+      <c r="BD13">
+        <v>36</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
         <v>7.6</v>
-      </c>
-      <c r="AZ13">
-        <v>1.01</v>
-      </c>
-      <c r="BA13">
-        <v>1.01</v>
-      </c>
-      <c r="BB13">
-        <v>8.6</v>
-      </c>
-      <c r="BC13">
-        <v>1.01</v>
-      </c>
-      <c r="BD13">
-        <v>1.01</v>
-      </c>
-      <c r="BE13">
-        <v>1.01</v>
-      </c>
-      <c r="BF13">
-        <v>1.01</v>
       </c>
       <c r="BG13">
         <v>1.01</v>
@@ -4057,7 +4057,7 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
         <v>4.8</v>
@@ -4090,7 +4090,7 @@
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y14">
         <v>12.5</v>
@@ -4180,13 +4180,13 @@
         <v>20</v>
       </c>
       <c r="BB14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE14">
         <v>6.6</v>
@@ -4281,10 +4281,10 @@
         <v>1.45</v>
       </c>
       <c r="G15">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H15">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I15">
         <v>8.6</v>
@@ -4329,13 +4329,13 @@
         <v>1.13</v>
       </c>
       <c r="W15">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X15">
         <v>1000</v>
       </c>
       <c r="Y15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z15">
         <v>100</v>
@@ -4350,7 +4350,7 @@
         <v>16</v>
       </c>
       <c r="AD15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE15">
         <v>1000</v>
@@ -4362,7 +4362,7 @@
         <v>15</v>
       </c>
       <c r="AH15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI15">
         <v>1000</v>
@@ -4398,7 +4398,7 @@
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU15">
         <v>6.8</v>
@@ -4434,7 +4434,7 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
@@ -4520,7 +4520,7 @@
         <v>159</v>
       </c>
       <c r="F16">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G16">
         <v>3.2</v>
@@ -4535,13 +4535,13 @@
         <v>3.55</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
         <v>4.3</v>
@@ -4553,7 +4553,7 @@
         <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="R16">
         <v>1.44</v>
@@ -4562,7 +4562,7 @@
         <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="U16">
         <v>2.12</v>
@@ -4765,7 +4765,7 @@
         <v>3.9</v>
       </c>
       <c r="G17">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="H17">
         <v>1.73</v>
@@ -4786,22 +4786,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="O17">
         <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="R17">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S17">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4813,7 +4813,7 @@
         <v>1.9</v>
       </c>
       <c r="W17">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5004,19 +5004,19 @@
         <v>161</v>
       </c>
       <c r="F18">
+        <v>1.41</v>
+      </c>
+      <c r="G18">
+        <v>110</v>
+      </c>
+      <c r="H18">
+        <v>1.41</v>
+      </c>
+      <c r="I18">
+        <v>110</v>
+      </c>
+      <c r="J18">
         <v>1.1</v>
-      </c>
-      <c r="G18">
-        <v>1000</v>
-      </c>
-      <c r="H18">
-        <v>1.1</v>
-      </c>
-      <c r="I18">
-        <v>1000</v>
-      </c>
-      <c r="J18">
-        <v>1.08</v>
       </c>
       <c r="K18">
         <v>320</v>
@@ -5028,7 +5028,7 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O18">
         <v>1.02</v>
@@ -5052,10 +5052,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5246,7 +5246,7 @@
         <v>162</v>
       </c>
       <c r="F19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G19">
         <v>2.2</v>
@@ -5261,13 +5261,13 @@
         <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -5294,7 +5294,7 @@
         <v>2.48</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
         <v>1.83</v>
@@ -5348,22 +5348,22 @@
         <v>60</v>
       </c>
       <c r="AN19">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO19">
         <v>970</v>
       </c>
       <c r="AP19">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR19">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT19">
         <v>14</v>
@@ -5375,7 +5375,7 @@
         <v>13</v>
       </c>
       <c r="AW19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX19">
         <v>15.5</v>
@@ -5387,22 +5387,22 @@
         <v>13</v>
       </c>
       <c r="BA19">
+        <v>5.9</v>
+      </c>
+      <c r="BB19">
         <v>5.8</v>
-      </c>
-      <c r="BB19">
-        <v>5.7</v>
       </c>
       <c r="BC19">
         <v>5.4</v>
       </c>
       <c r="BD19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF19">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BG19">
         <v>16.5</v>
@@ -5751,28 +5751,28 @@
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O21">
         <v>1.25</v>
       </c>
       <c r="P21">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="R21">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T21">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U21">
         <v>1.94</v>
@@ -5808,7 +5808,7 @@
         <v>100</v>
       </c>
       <c r="AF21">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -5829,7 +5829,7 @@
         <v>36</v>
       </c>
       <c r="AM21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN21">
         <v>9.800000000000001</v>
@@ -5841,13 +5841,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ21">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR21">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS21">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT21">
         <v>8</v>
@@ -5859,7 +5859,7 @@
         <v>18.5</v>
       </c>
       <c r="AW21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX21">
         <v>9.199999999999999</v>
@@ -5868,28 +5868,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ21">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA21">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB21">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC21">
         <v>14.5</v>
       </c>
       <c r="BD21">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE21">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF21">
         <v>8</v>
       </c>
       <c r="BG21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5972,22 +5972,22 @@
         <v>165</v>
       </c>
       <c r="F22">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G22">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I22">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>4.7</v>
       </c>
       <c r="K22">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6008,10 +6008,10 @@
         <v>1.6</v>
       </c>
       <c r="R22">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S22">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T22">
         <v>1.7</v>
@@ -6020,7 +6020,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W22">
         <v>2.78</v>
@@ -6214,7 +6214,7 @@
         <v>166</v>
       </c>
       <c r="F23">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G23">
         <v>1.75</v>
@@ -6223,13 +6223,13 @@
         <v>4.7</v>
       </c>
       <c r="I23">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J23">
         <v>4.3</v>
       </c>
       <c r="K23">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6238,10 +6238,10 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P23">
         <v>2.8</v>
@@ -6253,127 +6253,127 @@
         <v>1.74</v>
       </c>
       <c r="S23">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
         <v>2.32</v>
       </c>
       <c r="X23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB23">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH23">
+        <v>20</v>
+      </c>
+      <c r="AI23">
+        <v>55</v>
+      </c>
+      <c r="AJ23">
         <v>21</v>
       </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>22</v>
-      </c>
       <c r="AK23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN23">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP23">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23">
+        <v>1.01</v>
+      </c>
+      <c r="AR23">
+        <v>32</v>
+      </c>
+      <c r="AS23">
+        <v>75</v>
+      </c>
+      <c r="AT23">
+        <v>11.5</v>
+      </c>
+      <c r="AU23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV23">
+        <v>15.5</v>
+      </c>
+      <c r="AW23">
+        <v>1.01</v>
+      </c>
+      <c r="AX23">
+        <v>11.5</v>
+      </c>
+      <c r="AY23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ23">
+        <v>13</v>
+      </c>
+      <c r="BA23">
+        <v>1.01</v>
+      </c>
+      <c r="BB23">
+        <v>13.5</v>
+      </c>
+      <c r="BC23">
+        <v>12</v>
+      </c>
+      <c r="BD23">
         <v>21</v>
       </c>
-      <c r="AQ23">
-        <v>19</v>
-      </c>
-      <c r="AR23">
-        <v>1.01</v>
-      </c>
-      <c r="AS23">
-        <v>1.01</v>
-      </c>
-      <c r="AT23">
-        <v>10</v>
-      </c>
-      <c r="AU23">
-        <v>8.6</v>
-      </c>
-      <c r="AV23">
-        <v>1.01</v>
-      </c>
-      <c r="AW23">
-        <v>1.01</v>
-      </c>
-      <c r="AX23">
-        <v>10</v>
-      </c>
-      <c r="AY23">
-        <v>7.8</v>
-      </c>
-      <c r="AZ23">
-        <v>1.01</v>
-      </c>
-      <c r="BA23">
-        <v>1.01</v>
-      </c>
-      <c r="BB23">
-        <v>1.01</v>
-      </c>
-      <c r="BC23">
-        <v>1.01</v>
-      </c>
-      <c r="BD23">
-        <v>18</v>
-      </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF23">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6459,7 +6459,7 @@
         <v>2.48</v>
       </c>
       <c r="G24">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H24">
         <v>2.64</v>
@@ -6468,7 +6468,7 @@
         <v>2.84</v>
       </c>
       <c r="J24">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K24">
         <v>4.6</v>
@@ -6480,13 +6480,13 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.56</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q24">
         <v>1.52</v>
@@ -6495,7 +6495,7 @@
         <v>1.65</v>
       </c>
       <c r="S24">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6507,7 +6507,7 @@
         <v>1.54</v>
       </c>
       <c r="W24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6540,25 +6540,25 @@
         <v>1000</v>
       </c>
       <c r="AH24">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
         <v>38</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK24">
         <v>1000</v>
       </c>
       <c r="AL24">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
         <v>18.5</v>
@@ -6698,7 +6698,7 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G25">
         <v>2.3</v>
@@ -6707,7 +6707,7 @@
         <v>3.35</v>
       </c>
       <c r="I25">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J25">
         <v>3.75</v>
@@ -6731,7 +6731,7 @@
         <v>2.22</v>
       </c>
       <c r="Q25">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R25">
         <v>1.4</v>
@@ -6740,13 +6740,13 @@
         <v>2.44</v>
       </c>
       <c r="T25">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="U25">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
         <v>1.76</v>
@@ -6946,7 +6946,7 @@
         <v>3.7</v>
       </c>
       <c r="H26">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I26">
         <v>2.28</v>
@@ -6970,10 +6970,10 @@
         <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R26">
         <v>1.32</v>
@@ -6982,10 +6982,10 @@
         <v>3.85</v>
       </c>
       <c r="T26">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U26">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26">
         <v>1.78</v>
@@ -7000,7 +7000,7 @@
         <v>9.4</v>
       </c>
       <c r="Z26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA26">
         <v>32</v>
@@ -7027,13 +7027,13 @@
         <v>18.5</v>
       </c>
       <c r="AI26">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ26">
         <v>75</v>
       </c>
       <c r="AK26">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL26">
         <v>65</v>
@@ -7093,10 +7093,10 @@
         <v>50</v>
       </c>
       <c r="BE26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG26">
         <v>17.5</v>
@@ -7185,7 +7185,7 @@
         <v>2.58</v>
       </c>
       <c r="G27">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H27">
         <v>2.76</v>
@@ -7194,10 +7194,10 @@
         <v>2.98</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7212,10 +7212,10 @@
         <v>1.29</v>
       </c>
       <c r="P27">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q27">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R27">
         <v>1.39</v>
@@ -7230,7 +7230,7 @@
         <v>2.22</v>
       </c>
       <c r="V27">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
         <v>1.55</v>
@@ -7260,7 +7260,7 @@
         <v>32</v>
       </c>
       <c r="AF27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27">
         <v>12.5</v>
@@ -7275,7 +7275,7 @@
         <v>40</v>
       </c>
       <c r="AK27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL27">
         <v>44</v>
@@ -7296,10 +7296,10 @@
         <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT27">
         <v>10</v>
@@ -7311,7 +7311,7 @@
         <v>11</v>
       </c>
       <c r="AW27">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AX27">
         <v>16</v>
@@ -7326,7 +7326,7 @@
         <v>28</v>
       </c>
       <c r="BB27">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC27">
         <v>6.8</v>
@@ -7335,13 +7335,13 @@
         <v>32</v>
       </c>
       <c r="BE27">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF27">
         <v>18.5</v>
       </c>
       <c r="BG27">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH27">
         <v>3.95</v>
@@ -7454,7 +7454,7 @@
         <v>1.3</v>
       </c>
       <c r="P28">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q28">
         <v>1.9</v>
@@ -7666,7 +7666,7 @@
         <v>172</v>
       </c>
       <c r="F29">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G29">
         <v>2.02</v>
@@ -7684,13 +7684,13 @@
         <v>3.8</v>
       </c>
       <c r="L29">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M29">
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>1.32</v>
@@ -7699,16 +7699,16 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R29">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S29">
         <v>3.5</v>
       </c>
       <c r="T29">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U29">
         <v>2.14</v>
@@ -7726,7 +7726,7 @@
         <v>15.5</v>
       </c>
       <c r="Z29">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA29">
         <v>90</v>
@@ -7753,7 +7753,7 @@
         <v>18.5</v>
       </c>
       <c r="AI29">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ29">
         <v>24</v>
@@ -7762,13 +7762,13 @@
         <v>21</v>
       </c>
       <c r="AL29">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN29">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO29">
         <v>55</v>
@@ -7795,7 +7795,7 @@
         <v>15.5</v>
       </c>
       <c r="AW29">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX29">
         <v>11</v>
@@ -7807,7 +7807,7 @@
         <v>16.5</v>
       </c>
       <c r="BA29">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB29">
         <v>21</v>
@@ -7828,64 +7828,64 @@
         <v>46</v>
       </c>
       <c r="BH29">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BI29">
         <v>3.1</v>
       </c>
       <c r="BJ29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK29">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="BL29">
         <v>150</v>
       </c>
       <c r="BM29">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BN29">
         <v>5.6</v>
       </c>
       <c r="BO29">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BP29">
         <v>17</v>
       </c>
       <c r="BQ29">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BR29">
         <v>34</v>
       </c>
       <c r="BS29">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BT29">
         <v>9</v>
       </c>
       <c r="BU29">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BV29">
         <v>42</v>
       </c>
       <c r="BW29">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BX29">
         <v>55</v>
       </c>
       <c r="BY29">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BZ29">
         <v>29</v>
       </c>
       <c r="CA29">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="CB29" t="s">
         <v>174</v>
@@ -7911,13 +7911,13 @@
         <v>1.08</v>
       </c>
       <c r="G30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H30">
         <v>1.08</v>
       </c>
       <c r="I30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J30">
         <v>1.08</v>
@@ -7956,10 +7956,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -538,7 +538,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-09-01 19:21:03</t>
+    <t>2026-09-01 21:35:40</t>
   </si>
 </sst>
 </file>
@@ -1132,88 +1132,88 @@
         <v>145</v>
       </c>
       <c r="F2">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H2">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="I2">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="J2">
         <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
         <v>1.83</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>2.36</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
         <v>36</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE2">
         <v>32</v>
       </c>
       <c r="AF2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH2">
         <v>23</v>
@@ -1225,73 +1225,73 @@
         <v>85</v>
       </c>
       <c r="AK2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL2">
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO2">
         <v>25</v>
       </c>
       <c r="AP2">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>1.37</v>
+        <v>7.6</v>
       </c>
       <c r="AR2">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>1.32</v>
+        <v>21</v>
       </c>
       <c r="AT2">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>1.37</v>
+        <v>6</v>
       </c>
       <c r="AV2">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>1.31</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>1.31</v>
+        <v>18</v>
       </c>
       <c r="AY2">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>1.29</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>1.33</v>
+        <v>4.3</v>
       </c>
       <c r="BB2">
-        <v>1.35</v>
+        <v>4.4</v>
       </c>
       <c r="BC2">
-        <v>1.34</v>
+        <v>4.3</v>
       </c>
       <c r="BD2">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="BE2">
-        <v>1.36</v>
+        <v>4.5</v>
       </c>
       <c r="BF2">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="BG2">
-        <v>1.3</v>
+        <v>14.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1622,10 +1622,10 @@
         <v>3.3</v>
       </c>
       <c r="H4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J4">
         <v>3.25</v>
@@ -1640,34 +1640,34 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1676,10 +1676,10 @@
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB4">
         <v>13</v>
@@ -1691,7 +1691,7 @@
         <v>15</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF4">
         <v>25</v>
@@ -1706,7 +1706,7 @@
         <v>60</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK4">
         <v>48</v>
@@ -1715,13 +1715,13 @@
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN4">
         <v>50</v>
       </c>
       <c r="AO4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP4">
         <v>9.800000000000001</v>
@@ -1733,7 +1733,7 @@
         <v>12</v>
       </c>
       <c r="AS4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1745,7 +1745,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX4">
         <v>14.5</v>
@@ -1757,25 +1757,25 @@
         <v>16</v>
       </c>
       <c r="BA4">
+        <v>4.2</v>
+      </c>
+      <c r="BB4">
+        <v>4.2</v>
+      </c>
+      <c r="BC4">
+        <v>4.1</v>
+      </c>
+      <c r="BD4">
+        <v>4.2</v>
+      </c>
+      <c r="BE4">
+        <v>4.3</v>
+      </c>
+      <c r="BF4">
+        <v>4.1</v>
+      </c>
+      <c r="BG4">
         <v>4</v>
-      </c>
-      <c r="BB4">
-        <v>4</v>
-      </c>
-      <c r="BC4">
-        <v>3.95</v>
-      </c>
-      <c r="BD4">
-        <v>4</v>
-      </c>
-      <c r="BE4">
-        <v>4.2</v>
-      </c>
-      <c r="BF4">
-        <v>3.95</v>
-      </c>
-      <c r="BG4">
-        <v>3.9</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2366,7 +2366,7 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O7">
         <v>1.38</v>
@@ -2375,7 +2375,7 @@
         <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
         <v>1.22</v>
@@ -2596,7 +2596,7 @@
         <v>110</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
         <v>220</v>
@@ -2632,7 +2632,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
         <v>2.8</v>
@@ -2868,7 +2868,7 @@
         <v>1.01</v>
       </c>
       <c r="T9">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="U9">
         <v>2.04</v>
@@ -3092,10 +3092,10 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O10">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P10">
         <v>2</v>
@@ -3152,7 +3152,7 @@
         <v>11.5</v>
       </c>
       <c r="AH10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>60</v>
@@ -3170,7 +3170,7 @@
         <v>100</v>
       </c>
       <c r="AN10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO10">
         <v>36</v>
@@ -3185,7 +3185,7 @@
         <v>21</v>
       </c>
       <c r="AS10">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
         <v>8</v>
@@ -3197,7 +3197,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
         <v>11</v>
@@ -3218,16 +3218,16 @@
         <v>20</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>4.5</v>
@@ -3352,10 +3352,10 @@
         <v>2.04</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V11">
         <v>2.38</v>
@@ -3573,31 +3573,31 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
         <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R12">
         <v>1.39</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
         <v>1.67</v>
       </c>
       <c r="U12">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
         <v>1.27</v>
@@ -3609,7 +3609,7 @@
         <v>19</v>
       </c>
       <c r="Y12">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z12">
         <v>38</v>
@@ -3681,7 +3681,7 @@
         <v>16</v>
       </c>
       <c r="AW12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3693,10 +3693,10 @@
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
@@ -3705,7 +3705,7 @@
         <v>7.8</v>
       </c>
       <c r="BE12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12">
         <v>10</v>
@@ -3830,16 +3830,16 @@
         <v>2.02</v>
       </c>
       <c r="R13">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13">
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V13">
         <v>1.08</v>
@@ -3926,7 +3926,7 @@
         <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY13">
         <v>9.199999999999999</v>
@@ -3950,7 +3950,7 @@
         <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG13">
         <v>1.01</v>
@@ -4036,16 +4036,16 @@
         <v>157</v>
       </c>
       <c r="F14">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G14">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H14">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="I14">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="J14">
         <v>4.2</v>
@@ -4075,49 +4075,49 @@
         <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T14">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="W14">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X14">
+        <v>27</v>
+      </c>
+      <c r="Y14">
+        <v>12</v>
+      </c>
+      <c r="Z14">
+        <v>13.5</v>
+      </c>
+      <c r="AA14">
+        <v>25</v>
+      </c>
+      <c r="AB14">
         <v>26</v>
       </c>
-      <c r="Y14">
+      <c r="AC14">
+        <v>10.5</v>
+      </c>
+      <c r="AD14">
         <v>12.5</v>
       </c>
-      <c r="Z14">
-        <v>14.5</v>
-      </c>
-      <c r="AA14">
+      <c r="AE14">
+        <v>18</v>
+      </c>
+      <c r="AF14">
+        <v>48</v>
+      </c>
+      <c r="AG14">
         <v>23</v>
-      </c>
-      <c r="AB14">
-        <v>24</v>
-      </c>
-      <c r="AC14">
-        <v>10</v>
-      </c>
-      <c r="AD14">
-        <v>13</v>
-      </c>
-      <c r="AE14">
-        <v>18.5</v>
-      </c>
-      <c r="AF14">
-        <v>42</v>
-      </c>
-      <c r="AG14">
-        <v>19</v>
       </c>
       <c r="AH14">
         <v>17.5</v>
@@ -4126,37 +4126,37 @@
         <v>34</v>
       </c>
       <c r="AJ14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AK14">
+        <v>65</v>
+      </c>
+      <c r="AL14">
+        <v>65</v>
+      </c>
+      <c r="AM14">
+        <v>90</v>
+      </c>
+      <c r="AN14">
         <v>55</v>
       </c>
-      <c r="AL14">
-        <v>60</v>
-      </c>
-      <c r="AM14">
-        <v>85</v>
-      </c>
-      <c r="AN14">
-        <v>44</v>
-      </c>
       <c r="AO14">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP14">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AQ14">
         <v>10</v>
       </c>
       <c r="AR14">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS14">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT14">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="AU14">
         <v>8.800000000000001</v>
@@ -4165,37 +4165,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX14">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY14">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AZ14">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA14">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BB14">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BC14">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BD14">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BE14">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BF14">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG14">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4523,7 +4523,7 @@
         <v>2.64</v>
       </c>
       <c r="G16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H16">
         <v>2.46</v>
@@ -4550,10 +4550,10 @@
         <v>1.25</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q16">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="R16">
         <v>1.44</v>
@@ -4562,10 +4562,10 @@
         <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
         <v>1.54</v>
@@ -4801,7 +4801,7 @@
         <v>1.45</v>
       </c>
       <c r="S17">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -5004,13 +5004,13 @@
         <v>161</v>
       </c>
       <c r="F18">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="G18">
         <v>110</v>
       </c>
       <c r="H18">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="I18">
         <v>110</v>
@@ -5034,7 +5034,7 @@
         <v>1.02</v>
       </c>
       <c r="P18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q18">
         <v>1.43</v>
@@ -5052,10 +5052,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5255,7 +5255,7 @@
         <v>3.3</v>
       </c>
       <c r="I19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J19">
         <v>4.1</v>
@@ -5348,22 +5348,22 @@
         <v>60</v>
       </c>
       <c r="AN19">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AO19">
         <v>970</v>
       </c>
       <c r="AP19">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AQ19">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR19">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS19">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT19">
         <v>14</v>
@@ -5375,7 +5375,7 @@
         <v>13</v>
       </c>
       <c r="AW19">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX19">
         <v>15.5</v>
@@ -5387,22 +5387,22 @@
         <v>13</v>
       </c>
       <c r="BA19">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB19">
+        <v>5.4</v>
+      </c>
+      <c r="BC19">
+        <v>5</v>
+      </c>
+      <c r="BD19">
+        <v>5.3</v>
+      </c>
+      <c r="BE19">
         <v>5.8</v>
       </c>
-      <c r="BC19">
-        <v>5.4</v>
-      </c>
-      <c r="BD19">
-        <v>5.8</v>
-      </c>
-      <c r="BE19">
-        <v>6.4</v>
-      </c>
       <c r="BF19">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19">
         <v>16.5</v>
@@ -5497,7 +5497,7 @@
         <v>1.56</v>
       </c>
       <c r="I20">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J20">
         <v>4.6</v>
@@ -5730,7 +5730,7 @@
         <v>164</v>
       </c>
       <c r="F21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="G21">
         <v>1.72</v>
@@ -5763,19 +5763,19 @@
         <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R21">
         <v>1.46</v>
       </c>
       <c r="S21">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T21">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U21">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V21">
         <v>1.2</v>
@@ -5832,10 +5832,10 @@
         <v>110</v>
       </c>
       <c r="AN21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO21">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP21">
         <v>14.5</v>
@@ -5844,10 +5844,10 @@
         <v>17.5</v>
       </c>
       <c r="AR21">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="AS21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT21">
         <v>8</v>
@@ -5868,10 +5868,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB21">
         <v>14.5</v>
@@ -5880,10 +5880,10 @@
         <v>14.5</v>
       </c>
       <c r="BD21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF21">
         <v>8</v>
@@ -6214,7 +6214,7 @@
         <v>166</v>
       </c>
       <c r="F23">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G23">
         <v>1.75</v>
@@ -6223,10 +6223,10 @@
         <v>4.7</v>
       </c>
       <c r="I23">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
         <v>5.2</v>
@@ -6256,7 +6256,7 @@
         <v>2.18</v>
       </c>
       <c r="T23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U23">
         <v>2.28</v>
@@ -6298,16 +6298,16 @@
         <v>12.5</v>
       </c>
       <c r="AH23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI23">
         <v>55</v>
       </c>
       <c r="AJ23">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK23">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL23">
         <v>29</v>
@@ -6328,10 +6328,10 @@
         <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
         <v>11.5</v>
@@ -6340,7 +6340,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV23">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW23">
         <v>1.01</v>
@@ -6367,13 +6367,13 @@
         <v>21</v>
       </c>
       <c r="BE23">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
         <v>5.4</v>
       </c>
       <c r="BG23">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6698,7 +6698,7 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G25">
         <v>2.3</v>
@@ -6731,7 +6731,7 @@
         <v>2.22</v>
       </c>
       <c r="Q25">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R25">
         <v>1.4</v>
@@ -6979,7 +6979,7 @@
         <v>1.32</v>
       </c>
       <c r="S26">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T26">
         <v>1.88</v>
@@ -7188,7 +7188,7 @@
         <v>2.8</v>
       </c>
       <c r="H27">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I27">
         <v>2.98</v>
@@ -7239,10 +7239,10 @@
         <v>18</v>
       </c>
       <c r="Y27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA27">
         <v>44</v>
@@ -7281,7 +7281,7 @@
         <v>44</v>
       </c>
       <c r="AM27">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN27">
         <v>23</v>
@@ -7296,10 +7296,10 @@
         <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AS27">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT27">
         <v>10</v>
@@ -7326,10 +7326,10 @@
         <v>28</v>
       </c>
       <c r="BB27">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC27">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD27">
         <v>32</v>
@@ -7338,10 +7338,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF27">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG27">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BH27">
         <v>3.95</v>
@@ -7783,7 +7783,7 @@
         <v>26</v>
       </c>
       <c r="AS29">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AT29">
         <v>8.800000000000001</v>
@@ -7819,7 +7819,7 @@
         <v>32</v>
       </c>
       <c r="BE29">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF29">
         <v>12.5</v>
@@ -7920,7 +7920,7 @@
         <v>110</v>
       </c>
       <c r="J30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K30">
         <v>280</v>
@@ -7956,10 +7956,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -538,7 +538,7 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-09-01 21:35:40</t>
+    <t>2026-09-01 23:47:07</t>
   </si>
 </sst>
 </file>
@@ -1138,10 +1138,10 @@
         <v>3.9</v>
       </c>
       <c r="H2">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="I2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J2">
         <v>3.3</v>
@@ -1150,13 +1150,13 @@
         <v>3.75</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.37</v>
@@ -1168,10 +1168,10 @@
         <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
         <v>1.83</v>
@@ -1180,7 +1180,7 @@
         <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
         <v>1.34</v>
@@ -1192,10 +1192,10 @@
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB2">
         <v>15</v>
@@ -1204,7 +1204,7 @@
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
         <v>32</v>
@@ -1216,10 +1216,10 @@
         <v>18.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>85</v>
@@ -1228,7 +1228,7 @@
         <v>60</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>140</v>
@@ -1237,61 +1237,61 @@
         <v>65</v>
       </c>
       <c r="AO2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP2">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX2">
         <v>18</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2">
         <v>4.3</v>
       </c>
       <c r="BB2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC2">
         <v>4.3</v>
       </c>
       <c r="BD2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1374,154 +1374,154 @@
         <v>146</v>
       </c>
       <c r="F3">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
+        <v>1.8</v>
+      </c>
+      <c r="R3">
+        <v>1.41</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3">
         <v>1.67</v>
       </c>
-      <c r="R3">
-        <v>1.31</v>
-      </c>
-      <c r="S3">
-        <v>2.42</v>
-      </c>
-      <c r="T3">
-        <v>1.54</v>
-      </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V3">
         <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
         <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
         <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -1530,13 +1530,13 @@
         <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI3">
         <v>2.9</v>
@@ -1619,19 +1619,19 @@
         <v>2.92</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I4">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="J4">
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1643,13 +1643,13 @@
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>1.27</v>
@@ -1658,52 +1658,52 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
         <v>14</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>20</v>
       </c>
       <c r="AA4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB4">
+        <v>11.5</v>
+      </c>
+      <c r="AC4">
+        <v>8</v>
+      </c>
+      <c r="AD4">
         <v>13</v>
       </c>
-      <c r="AC4">
-        <v>9</v>
-      </c>
-      <c r="AD4">
-        <v>15</v>
-      </c>
       <c r="AE4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG4">
         <v>16.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
         <v>60</v>
@@ -1712,70 +1712,70 @@
         <v>48</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4">
         <v>140</v>
       </c>
       <c r="AN4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>8.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS4">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="AT4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AX4">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BD4">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>4.1</v>
+        <v>29</v>
       </c>
       <c r="BG4">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1858,7 +1858,7 @@
         <v>148</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
         <v>2.54</v>
@@ -1870,10 +1870,10 @@
         <v>3.1</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1882,7 +1882,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
         <v>1.17</v>
@@ -1897,7 +1897,7 @@
         <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2100,13 +2100,13 @@
         <v>149</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -2115,7 +2115,7 @@
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -2130,19 +2130,19 @@
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q6">
         <v>1.83</v>
       </c>
       <c r="R6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
         <v>2.14</v>
@@ -2342,169 +2342,169 @@
         <v>150</v>
       </c>
       <c r="F7">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G7">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>2.68</v>
+        <v>1.52</v>
       </c>
       <c r="I7">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J7">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>410</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="Q7">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="R7">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
         <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.47</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
         <v>1.01</v>
@@ -2584,7 +2584,7 @@
         <v>151</v>
       </c>
       <c r="F8">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="G8">
         <v>1.55</v>
@@ -2868,7 +2868,7 @@
         <v>1.01</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="U9">
         <v>2.04</v>
@@ -3068,22 +3068,22 @@
         <v>153</v>
       </c>
       <c r="F10">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="I10">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3092,16 +3092,16 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O10">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P10">
         <v>2</v>
       </c>
       <c r="Q10">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="R10">
         <v>1.39</v>
@@ -3110,46 +3110,46 @@
         <v>3.15</v>
       </c>
       <c r="T10">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="X10">
         <v>19.5</v>
       </c>
       <c r="Y10">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA10">
         <v>75</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
         <v>48</v>
       </c>
       <c r="AF10">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG10">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH10">
         <v>21</v>
@@ -3158,13 +3158,13 @@
         <v>60</v>
       </c>
       <c r="AJ10">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL10">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM10">
         <v>100</v>
@@ -3173,16 +3173,16 @@
         <v>21</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP10">
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
@@ -3209,13 +3209,13 @@
         <v>12</v>
       </c>
       <c r="BA10">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD10">
         <v>1.01</v>
@@ -3230,10 +3230,10 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
@@ -3313,19 +3313,19 @@
         <v>4.9</v>
       </c>
       <c r="G11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H11">
         <v>1.61</v>
       </c>
       <c r="I11">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="J11">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3334,7 +3334,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.7</v>
+        <v>2.68</v>
       </c>
       <c r="O11">
         <v>1.15</v>
@@ -3346,19 +3346,19 @@
         <v>1.5</v>
       </c>
       <c r="R11">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="T11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="W11">
         <v>1.19</v>
@@ -3567,7 +3567,7 @@
         <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3582,22 +3582,22 @@
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q12">
         <v>1.74</v>
       </c>
       <c r="R12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
         <v>1.67</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
         <v>1.27</v>
@@ -3627,7 +3627,7 @@
         <v>19</v>
       </c>
       <c r="AE12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF12">
         <v>12.5</v>
@@ -3666,10 +3666,10 @@
         <v>15</v>
       </c>
       <c r="AR12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT12">
         <v>8.199999999999999</v>
@@ -3794,7 +3794,7 @@
         <v>156</v>
       </c>
       <c r="F13">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="G13">
         <v>1.45</v>
@@ -3806,13 +3806,13 @@
         <v>13.5</v>
       </c>
       <c r="J13">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L13">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.07</v>
@@ -3836,10 +3836,10 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="V13">
         <v>1.08</v>
@@ -3851,7 +3851,7 @@
         <v>16.5</v>
       </c>
       <c r="Y13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z13">
         <v>120</v>
@@ -3860,7 +3860,7 @@
         <v>570</v>
       </c>
       <c r="AB13">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC13">
         <v>12.5</v>
@@ -3872,13 +3872,13 @@
         <v>270</v>
       </c>
       <c r="AF13">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI13">
         <v>220</v>
@@ -3887,7 +3887,7 @@
         <v>13.5</v>
       </c>
       <c r="AK13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL13">
         <v>60</v>
@@ -3905,7 +3905,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR13">
         <v>1.01</v>
@@ -3914,13 +3914,13 @@
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AU13">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV13">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -3929,7 +3929,7 @@
         <v>5.8</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
         <v>1.01</v>
@@ -3938,13 +3938,13 @@
         <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC13">
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
         <v>1.01</v>
@@ -4099,7 +4099,7 @@
         <v>13.5</v>
       </c>
       <c r="AA14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB14">
         <v>26</v>
@@ -4114,13 +4114,13 @@
         <v>18</v>
       </c>
       <c r="AF14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG14">
         <v>23</v>
       </c>
       <c r="AH14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI14">
         <v>34</v>
@@ -4135,7 +4135,7 @@
         <v>65</v>
       </c>
       <c r="AM14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN14">
         <v>55</v>
@@ -4156,7 +4156,7 @@
         <v>5.1</v>
       </c>
       <c r="AT14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU14">
         <v>8.800000000000001</v>
@@ -4168,7 +4168,7 @@
         <v>15</v>
       </c>
       <c r="AX14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY14">
         <v>16.5</v>
@@ -4177,7 +4177,7 @@
         <v>4.7</v>
       </c>
       <c r="BA14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB14">
         <v>6</v>
@@ -4192,7 +4192,7 @@
         <v>6</v>
       </c>
       <c r="BF14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG14">
         <v>7.6</v>
@@ -4299,13 +4299,13 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
         <v>2.14</v>
@@ -4314,16 +4314,16 @@
         <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="T15">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="U15">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="V15">
         <v>1.13</v>
@@ -4332,64 +4332,64 @@
         <v>2.88</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y15">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB15">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AC15">
+        <v>11.5</v>
+      </c>
+      <c r="AD15">
+        <v>30</v>
+      </c>
+      <c r="AE15">
+        <v>150</v>
+      </c>
+      <c r="AF15">
+        <v>9.4</v>
+      </c>
+      <c r="AG15">
+        <v>10.5</v>
+      </c>
+      <c r="AH15">
+        <v>25</v>
+      </c>
+      <c r="AI15">
+        <v>130</v>
+      </c>
+      <c r="AJ15">
+        <v>13.5</v>
+      </c>
+      <c r="AK15">
         <v>16</v>
       </c>
-      <c r="AD15">
-        <v>44</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>13</v>
-      </c>
-      <c r="AG15">
-        <v>15</v>
-      </c>
-      <c r="AH15">
-        <v>34</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>19</v>
-      </c>
-      <c r="AK15">
-        <v>23</v>
-      </c>
       <c r="AL15">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN15">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ15">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
         <v>1.01</v>
@@ -4398,43 +4398,43 @@
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV15">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
         <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AY15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15">
+        <v>21</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>11</v>
+      </c>
+      <c r="BC15">
+        <v>13.5</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
         <v>6.2</v>
-      </c>
-      <c r="AZ15">
-        <v>14.5</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>8</v>
-      </c>
-      <c r="BC15">
-        <v>9.6</v>
-      </c>
-      <c r="BD15">
-        <v>1.01</v>
-      </c>
-      <c r="BE15">
-        <v>1.01</v>
-      </c>
-      <c r="BF15">
-        <v>4.6</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
@@ -4520,10 +4520,10 @@
         <v>159</v>
       </c>
       <c r="F16">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H16">
         <v>2.46</v>
@@ -4535,7 +4535,7 @@
         <v>3.55</v>
       </c>
       <c r="K16">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4553,7 +4553,7 @@
         <v>2.14</v>
       </c>
       <c r="Q16">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
         <v>1.44</v>
@@ -4562,10 +4562,10 @@
         <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
         <v>1.54</v>
@@ -4762,22 +4762,22 @@
         <v>160</v>
       </c>
       <c r="F17">
-        <v>3.9</v>
+        <v>1.08</v>
       </c>
       <c r="G17">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="H17">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="I17">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="J17">
-        <v>3.45</v>
+        <v>1.08</v>
       </c>
       <c r="K17">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4786,22 +4786,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="O17">
         <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q17">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R17">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S17">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4810,10 +4810,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5255,7 +5255,7 @@
         <v>3.3</v>
       </c>
       <c r="I19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J19">
         <v>4.1</v>
@@ -5309,7 +5309,7 @@
         <v>34</v>
       </c>
       <c r="AA19">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB19">
         <v>16.5</v>
@@ -5318,13 +5318,13 @@
         <v>11</v>
       </c>
       <c r="AD19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE19">
         <v>32</v>
       </c>
       <c r="AF19">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG19">
         <v>13.5</v>
@@ -5354,16 +5354,16 @@
         <v>970</v>
       </c>
       <c r="AP19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ19">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS19">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT19">
         <v>14</v>
@@ -5375,7 +5375,7 @@
         <v>13</v>
       </c>
       <c r="AW19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX19">
         <v>15.5</v>
@@ -5387,25 +5387,25 @@
         <v>13</v>
       </c>
       <c r="BA19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BC19">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD19">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE19">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF19">
         <v>8.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5488,22 +5488,22 @@
         <v>163</v>
       </c>
       <c r="F20">
-        <v>5.3</v>
+        <v>1.08</v>
       </c>
       <c r="G20">
         <v>1000</v>
       </c>
       <c r="H20">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="I20">
-        <v>1.62</v>
+        <v>1000</v>
       </c>
       <c r="J20">
-        <v>4.6</v>
+        <v>1.23</v>
       </c>
       <c r="K20">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5512,22 +5512,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.46</v>
+        <v>1.27</v>
       </c>
       <c r="O20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P20">
-        <v>2.46</v>
+        <v>1.27</v>
       </c>
       <c r="Q20">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="R20">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="S20">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5536,7 +5536,7 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="W20">
         <v>1.2</v>
@@ -5763,7 +5763,7 @@
         <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R21">
         <v>1.46</v>
@@ -5772,10 +5772,10 @@
         <v>2.92</v>
       </c>
       <c r="T21">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="U21">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V21">
         <v>1.2</v>
@@ -6005,13 +6005,13 @@
         <v>2.56</v>
       </c>
       <c r="Q22">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R22">
         <v>1.6</v>
       </c>
       <c r="S22">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
         <v>1.7</v>
@@ -6223,7 +6223,7 @@
         <v>4.7</v>
       </c>
       <c r="I23">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J23">
         <v>4.4</v>
@@ -6259,10 +6259,10 @@
         <v>1.57</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W23">
         <v>2.32</v>
@@ -6319,7 +6319,7 @@
         <v>6.6</v>
       </c>
       <c r="AO23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP23">
         <v>1.01</v>
@@ -6698,7 +6698,7 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G25">
         <v>2.3</v>
@@ -6731,7 +6731,7 @@
         <v>2.22</v>
       </c>
       <c r="Q25">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R25">
         <v>1.4</v>
@@ -6964,7 +6964,7 @@
         <v>1.08</v>
       </c>
       <c r="N26">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
         <v>1.37</v>
@@ -6994,7 +6994,7 @@
         <v>1.37</v>
       </c>
       <c r="X26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y26">
         <v>9.4</v>
@@ -7093,10 +7093,10 @@
         <v>50</v>
       </c>
       <c r="BE26">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG26">
         <v>17.5</v>
@@ -7714,7 +7714,7 @@
         <v>2.14</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W29">
         <v>1.98</v>
@@ -7768,13 +7768,13 @@
         <v>100</v>
       </c>
       <c r="AN29">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AO29">
         <v>55</v>
       </c>
       <c r="AP29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29">
         <v>14</v>
@@ -7792,10 +7792,10 @@
         <v>7.6</v>
       </c>
       <c r="AV29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW29">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AX29">
         <v>11</v>
@@ -7804,7 +7804,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA29">
         <v>50</v>
@@ -7822,10 +7822,10 @@
         <v>75</v>
       </c>
       <c r="BF29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG29">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH29">
         <v>3.45</v>
@@ -7834,7 +7834,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ29">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK29">
         <v>8.6</v>
@@ -7843,7 +7843,7 @@
         <v>150</v>
       </c>
       <c r="BM29">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BN29">
         <v>5.6</v>
@@ -7855,13 +7855,13 @@
         <v>17</v>
       </c>
       <c r="BQ29">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR29">
         <v>34</v>
       </c>
       <c r="BS29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT29">
         <v>9</v>
@@ -7873,19 +7873,19 @@
         <v>42</v>
       </c>
       <c r="BW29">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX29">
         <v>55</v>
       </c>
       <c r="BY29">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ29">
         <v>29</v>
       </c>
       <c r="CA29">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB29" t="s">
         <v>174</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="188">
   <si>
     <t>League</t>
   </si>
@@ -274,15 +274,15 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
     <t>Armenian Premier League</t>
   </si>
   <si>
-    <t>Lithuanian A Lyga</t>
-  </si>
-  <si>
-    <t>Polish Ekstraklasa</t>
-  </si>
-  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
@@ -316,6 +316,12 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-09-03</t>
   </si>
   <si>
@@ -364,6 +370,15 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Barcelona (Ecu)</t>
   </si>
   <si>
@@ -382,15 +397,15 @@
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>FK Banga Gargzdu</t>
+  </si>
+  <si>
+    <t>Rakow Czestochowa</t>
+  </si>
+  <si>
     <t>Alashkert</t>
   </si>
   <si>
-    <t>FK Banga Gargzdu</t>
-  </si>
-  <si>
-    <t>Rakow Czestochowa</t>
-  </si>
-  <si>
     <t>Al Sailiya</t>
   </si>
   <si>
@@ -412,15 +427,15 @@
     <t>Gyori</t>
   </si>
   <si>
+    <t>Al Draih</t>
+  </si>
+  <si>
     <t>ES Setif</t>
   </si>
   <si>
     <t>FC Copenhagen</t>
   </si>
   <si>
-    <t>Al Draih</t>
-  </si>
-  <si>
     <t>Gent</t>
   </si>
   <si>
@@ -451,6 +466,18 @@
     <t>JS El Biar</t>
   </si>
   <si>
+    <t>America de Cali S.A</t>
+  </si>
+  <si>
+    <t>Deportivo Recoleta</t>
+  </si>
+  <si>
+    <t>CD Leones del Norte</t>
+  </si>
+  <si>
+    <t>Nautico PE</t>
+  </si>
+  <si>
     <t>Independiente (Ecu)</t>
   </si>
   <si>
@@ -469,15 +496,15 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>Gornik Zabrze</t>
+  </si>
+  <si>
     <t>FC Van Yerevan</t>
   </si>
   <si>
-    <t>Panevezys</t>
-  </si>
-  <si>
-    <t>Gornik Zabrze</t>
-  </si>
-  <si>
     <t>Al Arabi (QAT)</t>
   </si>
   <si>
@@ -499,15 +526,15 @@
     <t>Ferencvaros</t>
   </si>
   <si>
+    <t>Al-Quadisiya (KSA)</t>
+  </si>
+  <si>
     <t>ES Ben Aknoun</t>
   </si>
   <si>
     <t>FC Nordsjaelland</t>
   </si>
   <si>
-    <t>Al-Quadisiya (KSA)</t>
-  </si>
-  <si>
     <t>Oud-Heverlee Leuven</t>
   </si>
   <si>
@@ -538,7 +565,19 @@
     <t>Olympique Akbou</t>
   </si>
   <si>
-    <t>2026-09-01 23:47:07</t>
+    <t>Alianza FC Valledupar</t>
+  </si>
+  <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
+    <t>Orense Sporting Club</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>2026-09-02 01:59:28</t>
   </si>
 </sst>
 </file>
@@ -870,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1120,43 +1159,43 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F2">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G2">
         <v>3.9</v>
       </c>
       <c r="H2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
         <v>1.37</v>
@@ -1165,61 +1204,61 @@
         <v>1.83</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="T2">
         <v>1.83</v>
       </c>
       <c r="U2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
         <v>15</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
         <v>32</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
         <v>85</v>
@@ -1228,7 +1267,7 @@
         <v>60</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>140</v>
@@ -1237,31 +1276,31 @@
         <v>65</v>
       </c>
       <c r="AO2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV2">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="AX2">
         <v>18</v>
@@ -1273,22 +1312,22 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB2">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC2">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD2">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE2">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG2">
         <v>16</v>
@@ -1354,7 +1393,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1362,70 +1401,70 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F3">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
         <v>1.67</v>
       </c>
       <c r="U3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V3">
         <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X3">
         <v>21</v>
@@ -1434,7 +1473,7 @@
         <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA3">
         <v>55</v>
@@ -1446,10 +1485,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF3">
         <v>18</v>
@@ -1473,13 +1512,13 @@
         <v>38</v>
       </c>
       <c r="AM3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN3">
         <v>19</v>
       </c>
       <c r="AO3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP3">
         <v>12</v>
@@ -1596,7 +1635,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1604,58 +1643,58 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F4">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="I4">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
         <v>1.84</v>
@@ -1664,10 +1703,10 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1682,7 +1721,7 @@
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -1697,7 +1736,7 @@
         <v>22</v>
       </c>
       <c r="AG4">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AH4">
         <v>20</v>
@@ -1706,10 +1745,10 @@
         <v>50</v>
       </c>
       <c r="AJ4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL4">
         <v>55</v>
@@ -1718,7 +1757,7 @@
         <v>140</v>
       </c>
       <c r="AN4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO4">
         <v>32</v>
@@ -1733,7 +1772,7 @@
         <v>14</v>
       </c>
       <c r="AS4">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
         <v>9.199999999999999</v>
@@ -1745,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>17</v>
@@ -1757,88 +1796,88 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="BB4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
         <v>21</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1846,157 +1885,157 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H5">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I5">
         <v>3.1</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
         <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS5">
         <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
@@ -2005,19 +2044,19 @@
         <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2080,7 +2119,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2088,19 +2127,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F6">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G6">
         <v>2.3</v>
@@ -2118,13 +2157,13 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
         <v>1.28</v>
@@ -2133,7 +2172,7 @@
         <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
         <v>1.38</v>
@@ -2142,7 +2181,7 @@
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U6">
         <v>2.14</v>
@@ -2154,100 +2193,100 @@
         <v>1.76</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
         <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA6">
         <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD6">
         <v>1.01</v>
@@ -2256,73 +2295,73 @@
         <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2330,178 +2369,178 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F7">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H7">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="I7">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
-        <v>410</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="Q7">
-        <v>1.37</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2564,7 +2603,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2572,70 +2611,70 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F8">
-        <v>1.09</v>
+        <v>1.79</v>
       </c>
       <c r="G8">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="H8">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>5.7</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>220</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="P8">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="Q8">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="R8">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2806,7 +2845,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2814,184 +2853,184 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9">
+        <v>2.2</v>
+      </c>
+      <c r="G9">
+        <v>2.38</v>
+      </c>
+      <c r="H9">
+        <v>3.25</v>
+      </c>
+      <c r="I9">
+        <v>3.7</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>4.3</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.06</v>
+      </c>
+      <c r="N9">
+        <v>3.95</v>
+      </c>
+      <c r="O9">
+        <v>1.29</v>
+      </c>
+      <c r="P9">
+        <v>2.02</v>
+      </c>
+      <c r="Q9">
+        <v>1.86</v>
+      </c>
+      <c r="R9">
+        <v>1.4</v>
+      </c>
+      <c r="S9">
+        <v>3.2</v>
+      </c>
+      <c r="T9">
+        <v>1.58</v>
+      </c>
+      <c r="U9">
+        <v>2.22</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.73</v>
+      </c>
+      <c r="X9">
+        <v>19.5</v>
+      </c>
+      <c r="Y9">
+        <v>14.5</v>
+      </c>
+      <c r="Z9">
+        <v>25</v>
+      </c>
+      <c r="AA9">
+        <v>75</v>
+      </c>
+      <c r="AB9">
+        <v>11</v>
+      </c>
+      <c r="AC9">
+        <v>8.4</v>
+      </c>
+      <c r="AD9">
+        <v>15</v>
+      </c>
+      <c r="AE9">
+        <v>48</v>
+      </c>
+      <c r="AF9">
+        <v>15.5</v>
+      </c>
+      <c r="AG9">
+        <v>11.5</v>
+      </c>
+      <c r="AH9">
+        <v>17</v>
+      </c>
+      <c r="AI9">
+        <v>60</v>
+      </c>
+      <c r="AJ9">
+        <v>30</v>
+      </c>
+      <c r="AK9">
+        <v>24</v>
+      </c>
+      <c r="AL9">
+        <v>36</v>
+      </c>
+      <c r="AM9">
         <v>100</v>
       </c>
-      <c r="C9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9">
-        <v>1.95</v>
-      </c>
-      <c r="G9">
-        <v>2.1</v>
-      </c>
-      <c r="H9">
+      <c r="AN9">
+        <v>17</v>
+      </c>
+      <c r="AO9">
+        <v>36</v>
+      </c>
+      <c r="AP9">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9">
+        <v>10</v>
+      </c>
+      <c r="AR9">
+        <v>18</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>8</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>10.5</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>13.5</v>
+      </c>
+      <c r="AY9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>12</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>18</v>
+      </c>
+      <c r="BC9">
+        <v>17</v>
+      </c>
+      <c r="BD9">
+        <v>25</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>12</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
         <v>4.5</v>
       </c>
-      <c r="I9">
-        <v>5.5</v>
-      </c>
-      <c r="J9">
-        <v>2.92</v>
-      </c>
-      <c r="K9">
-        <v>3.8</v>
-      </c>
-      <c r="L9">
-        <v>1.31</v>
-      </c>
-      <c r="M9">
-        <v>1.08</v>
-      </c>
-      <c r="N9">
-        <v>3.2</v>
-      </c>
-      <c r="O9">
-        <v>1.33</v>
-      </c>
-      <c r="P9">
-        <v>1.8</v>
-      </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
-        <v>1.32</v>
-      </c>
-      <c r="S9">
-        <v>1.01</v>
-      </c>
-      <c r="T9">
-        <v>1.79</v>
-      </c>
-      <c r="U9">
-        <v>2.04</v>
-      </c>
-      <c r="V9">
-        <v>1.22</v>
-      </c>
-      <c r="W9">
-        <v>1.9</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>1000</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>1000</v>
-      </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9">
-        <v>1.01</v>
-      </c>
-      <c r="AR9">
-        <v>1.01</v>
-      </c>
-      <c r="AS9">
-        <v>1.01</v>
-      </c>
-      <c r="AT9">
-        <v>1.01</v>
-      </c>
-      <c r="AU9">
-        <v>1.01</v>
-      </c>
-      <c r="AV9">
-        <v>1.01</v>
-      </c>
-      <c r="AW9">
-        <v>1.01</v>
-      </c>
-      <c r="AX9">
-        <v>1.01</v>
-      </c>
-      <c r="AY9">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9">
-        <v>1.01</v>
-      </c>
-      <c r="BA9">
-        <v>1.01</v>
-      </c>
-      <c r="BB9">
-        <v>1.01</v>
-      </c>
-      <c r="BC9">
-        <v>1.01</v>
-      </c>
-      <c r="BD9">
-        <v>1.01</v>
-      </c>
-      <c r="BE9">
-        <v>1.01</v>
-      </c>
-      <c r="BF9">
-        <v>1.01</v>
-      </c>
-      <c r="BG9">
-        <v>1.01</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3048,7 +3087,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3056,58 +3095,58 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F10">
-        <v>1.98</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>220</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="O10">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="Q10">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="S10">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3116,106 +3155,106 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="X10">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
         <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
         <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
         <v>1.01</v>
@@ -3224,7 +3263,7 @@
         <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
         <v>1.01</v>
@@ -3290,7 +3329,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3298,160 +3337,160 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F11">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H11">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="I11">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P11">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q11">
         <v>1.5</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="S11">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="W11">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT11">
         <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX11">
         <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB11">
         <v>1.01</v>
@@ -3466,73 +3505,73 @@
         <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
         <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO11">
         <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ11">
         <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS11">
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3540,19 +3579,19 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G12">
         <v>1.95</v>
@@ -3561,7 +3600,7 @@
         <v>4.4</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
         <v>3.7</v>
@@ -3573,19 +3612,19 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
         <v>2.02</v>
       </c>
       <c r="Q12">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
         <v>1.4</v>
@@ -3594,19 +3633,19 @@
         <v>3.15</v>
       </c>
       <c r="T12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U12">
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
         <v>2.04</v>
       </c>
       <c r="X12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y12">
         <v>970</v>
@@ -3657,7 +3696,7 @@
         <v>12</v>
       </c>
       <c r="AO12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP12">
         <v>14</v>
@@ -3666,10 +3705,10 @@
         <v>15</v>
       </c>
       <c r="AR12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT12">
         <v>8.199999999999999</v>
@@ -3681,7 +3720,7 @@
         <v>16</v>
       </c>
       <c r="AW12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3693,7 +3732,7 @@
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB12">
         <v>6.8</v>
@@ -3702,16 +3741,16 @@
         <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF12">
         <v>10</v>
       </c>
       <c r="BG12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3774,7 +3813,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3782,19 +3821,19 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F13">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="G13">
         <v>1.45</v>
@@ -3806,28 +3845,28 @@
         <v>13.5</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q13">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R13">
         <v>1.31</v>
@@ -3836,16 +3875,16 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="V13">
         <v>1.08</v>
       </c>
       <c r="W13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X13">
         <v>16.5</v>
@@ -3863,7 +3902,7 @@
         <v>7.6</v>
       </c>
       <c r="AC13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
         <v>48</v>
@@ -3872,13 +3911,13 @@
         <v>270</v>
       </c>
       <c r="AF13">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH13">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI13">
         <v>220</v>
@@ -3914,13 +3953,13 @@
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AU13">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -3929,7 +3968,7 @@
         <v>5.8</v>
       </c>
       <c r="AY13">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
         <v>1.01</v>
@@ -3956,67 +3995,67 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK13">
         <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS13">
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU13">
         <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW13">
         <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY13">
         <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA13">
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4024,16 +4063,16 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F14">
         <v>4.6</v>
@@ -4048,40 +4087,40 @@
         <v>1.8</v>
       </c>
       <c r="J14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
         <v>4.4</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O14">
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R14">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
         <v>1.66</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
         <v>2.24</v>
@@ -4102,19 +4141,19 @@
         <v>24</v>
       </c>
       <c r="AB14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE14">
         <v>18</v>
       </c>
       <c r="AF14">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AG14">
         <v>23</v>
@@ -4123,10 +4162,10 @@
         <v>18</v>
       </c>
       <c r="AI14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
         <v>65</v>
@@ -4135,7 +4174,7 @@
         <v>65</v>
       </c>
       <c r="AM14">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
         <v>55</v>
@@ -4144,43 +4183,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP14">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS14">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AT14">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW14">
         <v>15</v>
       </c>
       <c r="AX14">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="AY14">
         <v>16.5</v>
       </c>
       <c r="AZ14">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="BB14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC14">
         <v>34</v>
@@ -4189,76 +4228,76 @@
         <v>34</v>
       </c>
       <c r="BE14">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF14">
-        <v>5.7</v>
+        <v>25</v>
       </c>
       <c r="BG14">
         <v>7.6</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM14">
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO14">
         <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA14">
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4266,16 +4305,16 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F15">
         <v>1.45</v>
@@ -4287,7 +4326,7 @@
         <v>7.6</v>
       </c>
       <c r="I15">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="J15">
         <v>4.5</v>
@@ -4296,13 +4335,13 @@
         <v>5.2</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
         <v>1.25</v>
@@ -4314,19 +4353,19 @@
         <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="T15">
         <v>1.92</v>
       </c>
       <c r="U15">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="V15">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W15">
         <v>2.88</v>
@@ -4335,7 +4374,7 @@
         <v>23</v>
       </c>
       <c r="Y15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z15">
         <v>85</v>
@@ -4344,52 +4383,52 @@
         <v>310</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AE15">
         <v>150</v>
       </c>
       <c r="AF15">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AG15">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI15">
         <v>130</v>
       </c>
       <c r="AJ15">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AK15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM15">
         <v>160</v>
       </c>
       <c r="AN15">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AO15">
         <v>190</v>
       </c>
       <c r="AP15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AR15">
         <v>1.01</v>
@@ -4398,34 +4437,34 @@
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU15">
+        <v>8</v>
+      </c>
+      <c r="AV15">
+        <v>21</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>6.8</v>
+      </c>
+      <c r="AY15">
+        <v>7.4</v>
+      </c>
+      <c r="AZ15">
+        <v>17.5</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
         <v>9.6</v>
       </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>1.01</v>
-      </c>
-      <c r="AX15">
-        <v>8</v>
-      </c>
-      <c r="AY15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15">
-        <v>21</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>11</v>
-      </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD15">
         <v>1.01</v>
@@ -4434,7 +4473,7 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
@@ -4500,7 +4539,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4508,28 +4547,28 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F16">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G16">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H16">
         <v>2.46</v>
       </c>
       <c r="I16">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J16">
         <v>3.55</v>
@@ -4538,7 +4577,7 @@
         <v>4.6</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M16">
         <v>1.05</v>
@@ -4550,10 +4589,10 @@
         <v>1.25</v>
       </c>
       <c r="P16">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R16">
         <v>1.44</v>
@@ -4562,16 +4601,16 @@
         <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
         <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="X16">
         <v>23</v>
@@ -4661,7 +4700,7 @@
         <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BB16">
         <v>1.01</v>
@@ -4676,73 +4715,73 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4750,34 +4789,34 @@
         <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F17">
-        <v>1.08</v>
+        <v>3.8</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>5.1</v>
       </c>
       <c r="H17">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>1.08</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4792,28 +4831,28 @@
         <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q17">
         <v>1.53</v>
       </c>
       <c r="R17">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S17">
         <v>2.32</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4984,42 +5023,42 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F18">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>110</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H18">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="I18">
-        <v>110</v>
+        <v>1.59</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="K18">
-        <v>320</v>
+        <v>5.4</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5028,22 +5067,22 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="P18">
-        <v>1.09</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="R18">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>2.24</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5052,10 +5091,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5226,186 +5265,186 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F19">
-        <v>2.12</v>
+        <v>1.1</v>
       </c>
       <c r="G19">
-        <v>2.2</v>
+        <v>110</v>
       </c>
       <c r="H19">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="I19">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>1.15</v>
       </c>
       <c r="K19">
-        <v>4.3</v>
+        <v>320</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>1.09</v>
       </c>
       <c r="O19">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="P19">
-        <v>2.72</v>
+        <v>1.09</v>
       </c>
       <c r="Q19">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R19">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
       <c r="S19">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="W19">
-        <v>1.83</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5468,186 +5507,186 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F20">
-        <v>1.08</v>
+        <v>2.12</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H20">
-        <v>1.22</v>
+        <v>3.3</v>
       </c>
       <c r="I20">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J20">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N20">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P20">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="Q20">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="R20">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="S20">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5656,61 +5695,61 @@
         <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK20">
         <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM20">
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY20">
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5718,19 +5757,19 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F21">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G21">
         <v>1.72</v>
@@ -5748,7 +5787,7 @@
         <v>4.4</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M21">
         <v>1.06</v>
@@ -5775,7 +5814,7 @@
         <v>1.69</v>
       </c>
       <c r="U21">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V21">
         <v>1.2</v>
@@ -5835,7 +5874,7 @@
         <v>9.6</v>
       </c>
       <c r="AO21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP21">
         <v>14.5</v>
@@ -5844,7 +5883,7 @@
         <v>17.5</v>
       </c>
       <c r="AR21">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="AS21">
         <v>8</v>
@@ -5892,67 +5931,67 @@
         <v>7.6</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM21">
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB21" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5960,46 +5999,46 @@
         <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F22">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G22">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I22">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
         <v>4.7</v>
       </c>
       <c r="K22">
+        <v>5.7</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
         <v>5.4</v>
       </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>2.56</v>
-      </c>
       <c r="O22">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.56</v>
@@ -6011,127 +6050,127 @@
         <v>1.6</v>
       </c>
       <c r="S22">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T22">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W22">
         <v>2.78</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP22">
-        <v>18.5</v>
+        <v>3.9</v>
       </c>
       <c r="AQ22">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR22">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="AS22">
-        <v>46</v>
+        <v>4.3</v>
       </c>
       <c r="AT22">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU22">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV22">
-        <v>18</v>
+        <v>3.9</v>
       </c>
       <c r="AW22">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="AX22">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY22">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ22">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BA22">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BB22">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC22">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD22">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE22">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6194,27 +6233,27 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E23" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F23">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G23">
         <v>1.75</v>
@@ -6223,7 +6262,7 @@
         <v>4.7</v>
       </c>
       <c r="I23">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J23">
         <v>4.4</v>
@@ -6232,7 +6271,7 @@
         <v>5.2</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6259,10 +6298,10 @@
         <v>1.57</v>
       </c>
       <c r="U23">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
         <v>2.32</v>
@@ -6376,67 +6415,67 @@
         <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU23">
         <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6444,19 +6483,19 @@
         <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E24" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F24">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G24">
         <v>2.6</v>
@@ -6471,13 +6510,13 @@
         <v>3.9</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
         <v>5.8</v>
@@ -6492,16 +6531,16 @@
         <v>1.52</v>
       </c>
       <c r="R24">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S24">
         <v>2.28</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="V24">
         <v>1.54</v>
@@ -6510,112 +6549,112 @@
         <v>1.62</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y24">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB24">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD24">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE24">
+        <v>27</v>
+      </c>
+      <c r="AF24">
+        <v>26</v>
+      </c>
+      <c r="AG24">
+        <v>15.5</v>
+      </c>
+      <c r="AH24">
+        <v>17.5</v>
+      </c>
+      <c r="AI24">
+        <v>32</v>
+      </c>
+      <c r="AJ24">
+        <v>36</v>
+      </c>
+      <c r="AK24">
+        <v>28</v>
+      </c>
+      <c r="AL24">
         <v>34</v>
       </c>
-      <c r="AF24">
-        <v>1000</v>
-      </c>
-      <c r="AG24">
-        <v>1000</v>
-      </c>
-      <c r="AH24">
-        <v>1000</v>
-      </c>
-      <c r="AI24">
-        <v>38</v>
-      </c>
-      <c r="AJ24">
-        <v>40</v>
-      </c>
-      <c r="AK24">
-        <v>1000</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO24">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS24">
         <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU24">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AV24">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW24">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY24">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB24">
         <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BD24">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
         <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6678,7 +6717,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6686,34 +6725,34 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E25" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F25">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="G25">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H25">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I25">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J25">
         <v>3.75</v>
       </c>
       <c r="K25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6722,16 +6761,16 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
         <v>1.22</v>
       </c>
       <c r="P25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R25">
         <v>1.4</v>
@@ -6740,16 +6779,16 @@
         <v>2.44</v>
       </c>
       <c r="T25">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
         <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6920,7 +6959,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6928,16 +6967,16 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="F26">
         <v>3.6</v>
@@ -6958,7 +6997,7 @@
         <v>3.55</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M26">
         <v>1.08</v>
@@ -6994,7 +7033,7 @@
         <v>1.37</v>
       </c>
       <c r="X26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y26">
         <v>9.4</v>
@@ -7093,10 +7132,10 @@
         <v>50</v>
       </c>
       <c r="BE26">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BF26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG26">
         <v>17.5</v>
@@ -7120,7 +7159,7 @@
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO26">
         <v>5.1</v>
@@ -7141,7 +7180,7 @@
         <v>5.9</v>
       </c>
       <c r="BU26">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV26">
         <v>21</v>
@@ -7162,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7170,19 +7209,19 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F27">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G27">
         <v>2.8</v>
@@ -7212,7 +7251,7 @@
         <v>1.29</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q27">
         <v>1.86</v>
@@ -7245,13 +7284,13 @@
         <v>21</v>
       </c>
       <c r="AA27">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB27">
         <v>12.5</v>
       </c>
       <c r="AC27">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD27">
         <v>13.5</v>
@@ -7299,7 +7338,7 @@
         <v>17</v>
       </c>
       <c r="AS27">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT27">
         <v>10</v>
@@ -7326,16 +7365,16 @@
         <v>28</v>
       </c>
       <c r="BB27">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC27">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD27">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BE27">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF27">
         <v>17</v>
@@ -7350,52 +7389,52 @@
         <v>3.15</v>
       </c>
       <c r="BJ27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK27">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="BL27">
         <v>120</v>
       </c>
       <c r="BM27">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BN27">
         <v>6.6</v>
       </c>
       <c r="BO27">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP27">
         <v>23</v>
       </c>
       <c r="BQ27">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BR27">
         <v>36</v>
       </c>
       <c r="BS27">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BT27">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU27">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV27">
         <v>25</v>
       </c>
       <c r="BW27">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BX27">
         <v>38</v>
       </c>
       <c r="BY27">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7404,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7412,16 +7451,16 @@
         <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F28">
         <v>1.86</v>
@@ -7445,31 +7484,31 @@
         <v>1.31</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="O28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R28">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S28">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V28">
         <v>1.25</v>
@@ -7478,64 +7517,64 @@
         <v>1.96</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR28">
         <v>1.01</v>
@@ -7544,34 +7583,34 @@
         <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW28">
         <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA28">
         <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD28">
         <v>1.01</v>
@@ -7580,7 +7619,7 @@
         <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG28">
         <v>1.01</v>
@@ -7646,7 +7685,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7654,16 +7693,16 @@
         <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -7672,10 +7711,10 @@
         <v>2.02</v>
       </c>
       <c r="H29">
+        <v>4.1</v>
+      </c>
+      <c r="I29">
         <v>4.2</v>
-      </c>
-      <c r="I29">
-        <v>4.3</v>
       </c>
       <c r="J29">
         <v>3.75</v>
@@ -7768,7 +7807,7 @@
         <v>100</v>
       </c>
       <c r="AN29">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AO29">
         <v>55</v>
@@ -7795,7 +7834,7 @@
         <v>15</v>
       </c>
       <c r="AW29">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX29">
         <v>11</v>
@@ -7828,7 +7867,7 @@
         <v>44</v>
       </c>
       <c r="BH29">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI29">
         <v>3.1</v>
@@ -7840,10 +7879,10 @@
         <v>8.6</v>
       </c>
       <c r="BL29">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BM29">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BN29">
         <v>5.6</v>
@@ -7861,7 +7900,7 @@
         <v>34</v>
       </c>
       <c r="BS29">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT29">
         <v>9</v>
@@ -7873,22 +7912,22 @@
         <v>42</v>
       </c>
       <c r="BW29">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX29">
         <v>55</v>
       </c>
       <c r="BY29">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ29">
         <v>29</v>
       </c>
       <c r="CA29">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB29" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7896,25 +7935,25 @@
         <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G30">
         <v>110</v>
       </c>
       <c r="H30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I30">
         <v>110</v>
@@ -7956,10 +7995,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8130,7 +8169,975 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>174</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31">
+        <v>1.39</v>
+      </c>
+      <c r="G31">
+        <v>1.49</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>14.5</v>
+      </c>
+      <c r="J31">
+        <v>4.3</v>
+      </c>
+      <c r="K31">
+        <v>5.6</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.07</v>
+      </c>
+      <c r="N31">
+        <v>3.25</v>
+      </c>
+      <c r="O31">
+        <v>1.36</v>
+      </c>
+      <c r="P31">
+        <v>1.76</v>
+      </c>
+      <c r="Q31">
+        <v>2.04</v>
+      </c>
+      <c r="R31">
+        <v>1.28</v>
+      </c>
+      <c r="S31">
+        <v>3.8</v>
+      </c>
+      <c r="T31">
+        <v>2.32</v>
+      </c>
+      <c r="U31">
+        <v>1.61</v>
+      </c>
+      <c r="V31">
+        <v>1.07</v>
+      </c>
+      <c r="W31">
+        <v>3.05</v>
+      </c>
+      <c r="X31">
+        <v>16</v>
+      </c>
+      <c r="Y31">
+        <v>32</v>
+      </c>
+      <c r="Z31">
+        <v>130</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>7.6</v>
+      </c>
+      <c r="AC31">
+        <v>13</v>
+      </c>
+      <c r="AD31">
+        <v>55</v>
+      </c>
+      <c r="AE31">
+        <v>300</v>
+      </c>
+      <c r="AF31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG31">
+        <v>13</v>
+      </c>
+      <c r="AH31">
+        <v>42</v>
+      </c>
+      <c r="AI31">
+        <v>260</v>
+      </c>
+      <c r="AJ31">
+        <v>14.5</v>
+      </c>
+      <c r="AK31">
+        <v>22</v>
+      </c>
+      <c r="AL31">
+        <v>70</v>
+      </c>
+      <c r="AM31">
+        <v>330</v>
+      </c>
+      <c r="AN31">
+        <v>11</v>
+      </c>
+      <c r="AO31">
+        <v>580</v>
+      </c>
+      <c r="AP31">
+        <v>11</v>
+      </c>
+      <c r="AQ31">
+        <v>19</v>
+      </c>
+      <c r="AR31">
+        <v>4.2</v>
+      </c>
+      <c r="AS31">
+        <v>4.4</v>
+      </c>
+      <c r="AT31">
+        <v>5.5</v>
+      </c>
+      <c r="AU31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV31">
+        <v>4</v>
+      </c>
+      <c r="AW31">
+        <v>4.3</v>
+      </c>
+      <c r="AX31">
+        <v>6.2</v>
+      </c>
+      <c r="AY31">
+        <v>9</v>
+      </c>
+      <c r="AZ31">
+        <v>4</v>
+      </c>
+      <c r="BA31">
+        <v>4.3</v>
+      </c>
+      <c r="BB31">
+        <v>10</v>
+      </c>
+      <c r="BC31">
+        <v>15.5</v>
+      </c>
+      <c r="BD31">
+        <v>4.1</v>
+      </c>
+      <c r="BE31">
+        <v>4.3</v>
+      </c>
+      <c r="BF31">
+        <v>7.8</v>
+      </c>
+      <c r="BG31">
+        <v>4.3</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.01</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.01</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.01</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.01</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.01</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.01</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.01</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.01</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.01</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>1.26</v>
+      </c>
+      <c r="O32">
+        <v>1.33</v>
+      </c>
+      <c r="P32">
+        <v>1.25</v>
+      </c>
+      <c r="Q32">
+        <v>1.33</v>
+      </c>
+      <c r="R32">
+        <v>1.18</v>
+      </c>
+      <c r="S32">
+        <v>1.34</v>
+      </c>
+      <c r="T32">
+        <v>1.01</v>
+      </c>
+      <c r="U32">
+        <v>1.01</v>
+      </c>
+      <c r="V32">
+        <v>1.01</v>
+      </c>
+      <c r="W32">
+        <v>1.01</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32">
+        <v>1.01</v>
+      </c>
+      <c r="AR32">
+        <v>1.01</v>
+      </c>
+      <c r="AS32">
+        <v>1.01</v>
+      </c>
+      <c r="AT32">
+        <v>1.01</v>
+      </c>
+      <c r="AU32">
+        <v>1.01</v>
+      </c>
+      <c r="AV32">
+        <v>1.01</v>
+      </c>
+      <c r="AW32">
+        <v>1.01</v>
+      </c>
+      <c r="AX32">
+        <v>1.01</v>
+      </c>
+      <c r="AY32">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32">
+        <v>1.01</v>
+      </c>
+      <c r="BA32">
+        <v>1.01</v>
+      </c>
+      <c r="BB32">
+        <v>1.01</v>
+      </c>
+      <c r="BC32">
+        <v>1.01</v>
+      </c>
+      <c r="BD32">
+        <v>1.01</v>
+      </c>
+      <c r="BE32">
+        <v>1.01</v>
+      </c>
+      <c r="BF32">
+        <v>1.01</v>
+      </c>
+      <c r="BG32">
+        <v>1.01</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.01</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.01</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.01</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.01</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.01</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.01</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33">
+        <v>2.14</v>
+      </c>
+      <c r="G33">
+        <v>2.36</v>
+      </c>
+      <c r="H33">
+        <v>3.8</v>
+      </c>
+      <c r="I33">
+        <v>4.3</v>
+      </c>
+      <c r="J33">
+        <v>3.1</v>
+      </c>
+      <c r="K33">
+        <v>3.4</v>
+      </c>
+      <c r="L33">
+        <v>1.43</v>
+      </c>
+      <c r="M33">
+        <v>1.09</v>
+      </c>
+      <c r="N33">
+        <v>2.72</v>
+      </c>
+      <c r="O33">
+        <v>1.48</v>
+      </c>
+      <c r="P33">
+        <v>1.57</v>
+      </c>
+      <c r="Q33">
+        <v>2.44</v>
+      </c>
+      <c r="R33">
+        <v>1.2</v>
+      </c>
+      <c r="S33">
+        <v>4.8</v>
+      </c>
+      <c r="T33">
+        <v>2.02</v>
+      </c>
+      <c r="U33">
+        <v>1.8</v>
+      </c>
+      <c r="V33">
+        <v>1.3</v>
+      </c>
+      <c r="W33">
+        <v>1.73</v>
+      </c>
+      <c r="X33">
+        <v>11.5</v>
+      </c>
+      <c r="Y33">
+        <v>14</v>
+      </c>
+      <c r="Z33">
+        <v>36</v>
+      </c>
+      <c r="AA33">
+        <v>120</v>
+      </c>
+      <c r="AB33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC33">
+        <v>9</v>
+      </c>
+      <c r="AD33">
+        <v>22</v>
+      </c>
+      <c r="AE33">
+        <v>80</v>
+      </c>
+      <c r="AF33">
+        <v>15.5</v>
+      </c>
+      <c r="AG33">
+        <v>14</v>
+      </c>
+      <c r="AH33">
+        <v>28</v>
+      </c>
+      <c r="AI33">
+        <v>110</v>
+      </c>
+      <c r="AJ33">
+        <v>38</v>
+      </c>
+      <c r="AK33">
+        <v>36</v>
+      </c>
+      <c r="AL33">
+        <v>70</v>
+      </c>
+      <c r="AM33">
+        <v>210</v>
+      </c>
+      <c r="AN33">
+        <v>34</v>
+      </c>
+      <c r="AO33">
+        <v>120</v>
+      </c>
+      <c r="AP33">
+        <v>7</v>
+      </c>
+      <c r="AQ33">
+        <v>8.4</v>
+      </c>
+      <c r="AR33">
+        <v>20</v>
+      </c>
+      <c r="AS33">
+        <v>1.01</v>
+      </c>
+      <c r="AT33">
+        <v>5.5</v>
+      </c>
+      <c r="AU33">
+        <v>5.6</v>
+      </c>
+      <c r="AV33">
+        <v>12.5</v>
+      </c>
+      <c r="AW33">
+        <v>1.01</v>
+      </c>
+      <c r="AX33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY33">
+        <v>8.4</v>
+      </c>
+      <c r="AZ33">
+        <v>16.5</v>
+      </c>
+      <c r="BA33">
+        <v>1.01</v>
+      </c>
+      <c r="BB33">
+        <v>1.01</v>
+      </c>
+      <c r="BC33">
+        <v>21</v>
+      </c>
+      <c r="BD33">
+        <v>1.01</v>
+      </c>
+      <c r="BE33">
+        <v>1.01</v>
+      </c>
+      <c r="BF33">
+        <v>20</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>2.28</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>2.22</v>
+      </c>
+      <c r="H34">
+        <v>3.85</v>
+      </c>
+      <c r="I34">
+        <v>5.7</v>
+      </c>
+      <c r="J34">
+        <v>2.68</v>
+      </c>
+      <c r="K34">
+        <v>3.7</v>
+      </c>
+      <c r="L34">
+        <v>1.41</v>
+      </c>
+      <c r="M34">
+        <v>1.07</v>
+      </c>
+      <c r="N34">
+        <v>2.68</v>
+      </c>
+      <c r="O34">
+        <v>1.39</v>
+      </c>
+      <c r="P34">
+        <v>1.57</v>
+      </c>
+      <c r="Q34">
+        <v>2.14</v>
+      </c>
+      <c r="R34">
+        <v>1.24</v>
+      </c>
+      <c r="S34">
+        <v>3.55</v>
+      </c>
+      <c r="T34">
+        <v>1.01</v>
+      </c>
+      <c r="U34">
+        <v>1.01</v>
+      </c>
+      <c r="V34">
+        <v>1.21</v>
+      </c>
+      <c r="W34">
+        <v>1.81</v>
+      </c>
+      <c r="X34">
+        <v>1000</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>1000</v>
+      </c>
+      <c r="AC34">
+        <v>1000</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>1000</v>
+      </c>
+      <c r="AG34">
+        <v>1000</v>
+      </c>
+      <c r="AH34">
+        <v>1000</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>1000</v>
+      </c>
+      <c r="AK34">
+        <v>1000</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34">
+        <v>1.01</v>
+      </c>
+      <c r="AR34">
+        <v>1.01</v>
+      </c>
+      <c r="AS34">
+        <v>1.01</v>
+      </c>
+      <c r="AT34">
+        <v>1.01</v>
+      </c>
+      <c r="AU34">
+        <v>1.01</v>
+      </c>
+      <c r="AV34">
+        <v>1.01</v>
+      </c>
+      <c r="AW34">
+        <v>1.01</v>
+      </c>
+      <c r="AX34">
+        <v>1.01</v>
+      </c>
+      <c r="AY34">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34">
+        <v>1.01</v>
+      </c>
+      <c r="BA34">
+        <v>1.01</v>
+      </c>
+      <c r="BB34">
+        <v>1.01</v>
+      </c>
+      <c r="BC34">
+        <v>1.01</v>
+      </c>
+      <c r="BD34">
+        <v>1.01</v>
+      </c>
+      <c r="BE34">
+        <v>1.01</v>
+      </c>
+      <c r="BF34">
+        <v>1.01</v>
+      </c>
+      <c r="BG34">
+        <v>1.01</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.01</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.01</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.01</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -577,7 +577,7 @@
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>2026-09-02 01:59:28</t>
+    <t>2026-09-02 03:17:29</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1171,7 @@
         <v>154</v>
       </c>
       <c r="F2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
         <v>3.9</v>
@@ -1180,10 +1180,10 @@
         <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.7</v>
@@ -1213,7 +1213,7 @@
         <v>3.95</v>
       </c>
       <c r="T2">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1228,7 +1228,7 @@
         <v>15</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
         <v>16.5</v>
@@ -1237,13 +1237,13 @@
         <v>36</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
         <v>32</v>
@@ -1252,7 +1252,7 @@
         <v>30</v>
       </c>
       <c r="AG2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH2">
         <v>23</v>
@@ -1270,7 +1270,7 @@
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2">
         <v>65</v>
@@ -1288,7 +1288,7 @@
         <v>12</v>
       </c>
       <c r="AS2">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1300,94 +1300,94 @@
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB2">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC2">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD2">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE2">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF2">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG2">
         <v>16</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1455,7 +1455,7 @@
         <v>3.1</v>
       </c>
       <c r="T3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
         <v>2.24</v>
@@ -1542,7 +1542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1554,7 +1554,7 @@
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB3">
         <v>21</v>
@@ -1563,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE3">
         <v>1.01</v>
@@ -1575,61 +1575,61 @@
         <v>19.5</v>
       </c>
       <c r="BH3">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BI3">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1655,19 +1655,19 @@
         <v>156</v>
       </c>
       <c r="F4">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1679,64 +1679,64 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U4">
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AA4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
         <v>20</v>
@@ -1745,37 +1745,37 @@
         <v>50</v>
       </c>
       <c r="AJ4">
+        <v>65</v>
+      </c>
+      <c r="AK4">
+        <v>44</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
         <v>55</v>
       </c>
-      <c r="AK4">
-        <v>40</v>
-      </c>
-      <c r="AL4">
-        <v>55</v>
-      </c>
-      <c r="AM4">
-        <v>140</v>
-      </c>
-      <c r="AN4">
-        <v>40</v>
-      </c>
       <c r="AO4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP4">
         <v>10</v>
       </c>
       <c r="AQ4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS4">
         <v>6.8</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU4">
         <v>6.6</v>
@@ -1787,40 +1787,40 @@
         <v>6.6</v>
       </c>
       <c r="AX4">
+        <v>18.5</v>
+      </c>
+      <c r="AY4">
+        <v>12</v>
+      </c>
+      <c r="AZ4">
         <v>17</v>
-      </c>
-      <c r="AY4">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4">
-        <v>16.5</v>
       </c>
       <c r="BA4">
         <v>7</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC4">
         <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
         <v>7.8</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4">
         <v>12</v>
@@ -1829,43 +1829,43 @@
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
@@ -2059,64 +2059,64 @@
         <v>12.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
         <v>187</v>
@@ -2139,7 +2139,7 @@
         <v>158</v>
       </c>
       <c r="F6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
         <v>2.3</v>
@@ -2148,22 +2148,22 @@
         <v>3.45</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O6">
         <v>1.28</v>
@@ -2172,7 +2172,7 @@
         <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
         <v>1.38</v>
@@ -2181,22 +2181,22 @@
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V6">
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z6">
         <v>32</v>
@@ -2211,7 +2211,7 @@
         <v>9.6</v>
       </c>
       <c r="AD6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE6">
         <v>50</v>
@@ -2235,7 +2235,7 @@
         <v>26</v>
       </c>
       <c r="AL6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM6">
         <v>100</v>
@@ -2301,10 +2301,10 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6">
         <v>11</v>
@@ -2325,7 +2325,7 @@
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="BU6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
         <v>34</v>
@@ -2355,7 +2355,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2381,13 +2381,13 @@
         <v>159</v>
       </c>
       <c r="F7">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
         <v>3.05</v>
@@ -2426,13 +2426,13 @@
         <v>1.74</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X7">
         <v>12</v>
@@ -2444,7 +2444,7 @@
         <v>19</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2471,7 +2471,7 @@
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK7">
         <v>38</v>
@@ -2483,7 +2483,7 @@
         <v>140</v>
       </c>
       <c r="AN7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO7">
         <v>36</v>
@@ -2498,7 +2498,7 @@
         <v>15.5</v>
       </c>
       <c r="AS7">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
         <v>8.800000000000001</v>
@@ -2510,7 +2510,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
         <v>15.5</v>
@@ -2522,25 +2522,25 @@
         <v>16</v>
       </c>
       <c r="BA7">
+        <v>8.4</v>
+      </c>
+      <c r="BB7">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB7">
-        <v>8</v>
-      </c>
       <c r="BC7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2626,55 +2626,55 @@
         <v>1.79</v>
       </c>
       <c r="G8">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H8">
         <v>4.8</v>
       </c>
       <c r="I8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S8">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T8">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W8">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2785,64 +2785,64 @@
         <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB8" t="s">
         <v>187</v>
@@ -2874,16 +2874,16 @@
         <v>3.25</v>
       </c>
       <c r="I9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J9">
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -2895,7 +2895,7 @@
         <v>1.29</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
         <v>1.86</v>
@@ -2910,7 +2910,7 @@
         <v>1.58</v>
       </c>
       <c r="U9">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
         <v>1.38</v>
@@ -2937,10 +2937,10 @@
         <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>15.5</v>
@@ -2952,7 +2952,7 @@
         <v>17</v>
       </c>
       <c r="AI9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
         <v>30</v>
@@ -2967,10 +2967,10 @@
         <v>100</v>
       </c>
       <c r="AN9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP9">
         <v>11.5</v>
@@ -3009,13 +3009,13 @@
         <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
         <v>17</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
         <v>1.01</v>
@@ -3027,64 +3027,64 @@
         <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI9">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="CB9" t="s">
         <v>187</v>
@@ -3107,226 +3107,226 @@
         <v>162</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="H10">
-        <v>2.88</v>
+        <v>16</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="K10">
+        <v>9.6</v>
+      </c>
+      <c r="L10">
+        <v>1.23</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>5.8</v>
+      </c>
+      <c r="O10">
+        <v>1.17</v>
+      </c>
+      <c r="P10">
+        <v>2.64</v>
+      </c>
+      <c r="Q10">
+        <v>1.51</v>
+      </c>
+      <c r="R10">
+        <v>1.66</v>
+      </c>
+      <c r="S10">
+        <v>2.24</v>
+      </c>
+      <c r="T10">
+        <v>2.28</v>
+      </c>
+      <c r="U10">
+        <v>1.64</v>
+      </c>
+      <c r="V10">
+        <v>1.04</v>
+      </c>
+      <c r="W10">
+        <v>5.3</v>
+      </c>
+      <c r="X10">
+        <v>36</v>
+      </c>
+      <c r="Y10">
+        <v>70</v>
+      </c>
+      <c r="Z10">
+        <v>240</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>12</v>
+      </c>
+      <c r="AC10">
+        <v>21</v>
+      </c>
+      <c r="AD10">
+        <v>85</v>
+      </c>
+      <c r="AE10">
+        <v>440</v>
+      </c>
+      <c r="AF10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG10">
+        <v>14.5</v>
+      </c>
+      <c r="AH10">
+        <v>50</v>
+      </c>
+      <c r="AI10">
+        <v>300</v>
+      </c>
+      <c r="AJ10">
+        <v>10</v>
+      </c>
+      <c r="AK10">
+        <v>17</v>
+      </c>
+      <c r="AL10">
+        <v>55</v>
+      </c>
+      <c r="AM10">
+        <v>290</v>
+      </c>
+      <c r="AN10">
+        <v>4.1</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>22</v>
+      </c>
+      <c r="AQ10">
+        <v>44</v>
+      </c>
+      <c r="AR10">
+        <v>150</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>7.8</v>
+      </c>
+      <c r="AU10">
+        <v>14</v>
+      </c>
+      <c r="AV10">
+        <v>50</v>
+      </c>
+      <c r="AW10">
+        <v>280</v>
+      </c>
+      <c r="AX10">
+        <v>6.2</v>
+      </c>
+      <c r="AY10">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10">
+        <v>32</v>
+      </c>
+      <c r="BA10">
+        <v>190</v>
+      </c>
+      <c r="BB10">
+        <v>6.6</v>
+      </c>
+      <c r="BC10">
+        <v>11</v>
+      </c>
+      <c r="BD10">
+        <v>34</v>
+      </c>
+      <c r="BE10">
+        <v>180</v>
+      </c>
+      <c r="BF10">
+        <v>3</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>5.4</v>
+      </c>
+      <c r="BI10">
+        <v>3.8</v>
+      </c>
+      <c r="BJ10">
+        <v>16.5</v>
+      </c>
+      <c r="BK10">
+        <v>11</v>
+      </c>
+      <c r="BL10">
         <v>220</v>
       </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>2.34</v>
-      </c>
-      <c r="O10">
-        <v>1.16</v>
-      </c>
-      <c r="P10">
-        <v>2.34</v>
-      </c>
-      <c r="Q10">
-        <v>1.43</v>
-      </c>
-      <c r="R10">
-        <v>1.59</v>
-      </c>
-      <c r="S10">
-        <v>2.02</v>
-      </c>
-      <c r="T10">
-        <v>1.01</v>
-      </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>1.07</v>
-      </c>
-      <c r="W10">
-        <v>2.8</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>1000</v>
-      </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10">
-        <v>1.01</v>
-      </c>
-      <c r="AR10">
-        <v>1.01</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>1.01</v>
-      </c>
-      <c r="AU10">
-        <v>1.01</v>
-      </c>
-      <c r="AV10">
-        <v>1.01</v>
-      </c>
-      <c r="AW10">
-        <v>1.01</v>
-      </c>
-      <c r="AX10">
-        <v>1.01</v>
-      </c>
-      <c r="AY10">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10">
-        <v>1.01</v>
-      </c>
-      <c r="BA10">
-        <v>1.01</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
-        <v>1.01</v>
-      </c>
-      <c r="BD10">
-        <v>1.01</v>
-      </c>
-      <c r="BE10">
-        <v>1.01</v>
-      </c>
-      <c r="BF10">
-        <v>1.01</v>
-      </c>
-      <c r="BG10">
-        <v>1.01</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.01</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
         <v>187</v>
@@ -3349,22 +3349,22 @@
         <v>163</v>
       </c>
       <c r="F11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="G11">
         <v>7</v>
       </c>
       <c r="H11">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="I11">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>1.21</v>
@@ -3376,46 +3376,46 @@
         <v>6</v>
       </c>
       <c r="O11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="Q11">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R11">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V11">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="W11">
         <v>1.17</v>
       </c>
       <c r="X11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AB11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC11">
         <v>14.5</v>
@@ -3433,28 +3433,28 @@
         <v>28</v>
       </c>
       <c r="AH11">
+        <v>970</v>
+      </c>
+      <c r="AI11">
         <v>26</v>
       </c>
-      <c r="AI11">
-        <v>38</v>
-      </c>
       <c r="AJ11">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AK11">
         <v>75</v>
       </c>
       <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
         <v>75</v>
-      </c>
-      <c r="AM11">
-        <v>100</v>
       </c>
       <c r="AN11">
         <v>60</v>
       </c>
       <c r="AO11">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AP11">
         <v>21</v>
@@ -3463,19 +3463,19 @@
         <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AU11">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW11">
         <v>11</v>
@@ -3484,7 +3484,7 @@
         <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ11">
         <v>13</v>
@@ -3505,16 +3505,16 @@
         <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
         <v>4.4</v>
       </c>
       <c r="BH11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3523,37 +3523,37 @@
         <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BO11">
         <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BQ11">
         <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS11">
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
@@ -3565,7 +3565,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
@@ -3591,7 +3591,7 @@
         <v>164</v>
       </c>
       <c r="F12">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G12">
         <v>1.95</v>
@@ -3606,7 +3606,7 @@
         <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3639,7 +3639,7 @@
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W12">
         <v>2.04</v>
@@ -3833,7 +3833,7 @@
         <v>165</v>
       </c>
       <c r="F13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G13">
         <v>1.45</v>
@@ -3848,25 +3848,25 @@
         <v>4.5</v>
       </c>
       <c r="K13">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O13">
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
         <v>1.31</v>
@@ -3878,13 +3878,13 @@
         <v>2.14</v>
       </c>
       <c r="U13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V13">
         <v>1.08</v>
       </c>
       <c r="W13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X13">
         <v>16.5</v>
@@ -3896,13 +3896,13 @@
         <v>120</v>
       </c>
       <c r="AA13">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="AB13">
         <v>7.6</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD13">
         <v>48</v>
@@ -3911,13 +3911,13 @@
         <v>270</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI13">
         <v>220</v>
@@ -3953,13 +3953,13 @@
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AU13">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV13">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -3968,7 +3968,7 @@
         <v>5.8</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
         <v>1.01</v>
@@ -4001,13 +4001,13 @@
         <v>2.8</v>
       </c>
       <c r="BJ13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK13">
         <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
@@ -4016,10 +4016,10 @@
         <v>4.1</v>
       </c>
       <c r="BO13">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BP13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ13">
         <v>1.01</v>
@@ -4031,7 +4031,7 @@
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU13">
         <v>1.01</v>
@@ -4087,25 +4087,25 @@
         <v>1.8</v>
       </c>
       <c r="J14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K14">
         <v>4.4</v>
       </c>
       <c r="L14">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q14">
         <v>1.65</v>
@@ -4114,13 +4114,13 @@
         <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U14">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
         <v>2.24</v>
@@ -4141,13 +4141,13 @@
         <v>24</v>
       </c>
       <c r="AB14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE14">
         <v>18</v>
@@ -4162,16 +4162,16 @@
         <v>18</v>
       </c>
       <c r="AI14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ14">
         <v>1000</v>
       </c>
       <c r="AK14">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AL14">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AM14">
         <v>1000</v>
@@ -4180,10 +4180,10 @@
         <v>55</v>
       </c>
       <c r="AO14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14">
         <v>10.5</v>
@@ -4192,10 +4192,10 @@
         <v>11</v>
       </c>
       <c r="AS14">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AT14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU14">
         <v>9</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="BB14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14">
         <v>34</v>
@@ -4237,10 +4237,10 @@
         <v>7.6</v>
       </c>
       <c r="BH14">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI14">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14">
         <v>11</v>
@@ -4255,10 +4255,10 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP14">
         <v>40</v>
@@ -4273,25 +4273,25 @@
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU14">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW14">
         <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA14">
         <v>1.01</v>
@@ -4317,7 +4317,7 @@
         <v>167</v>
       </c>
       <c r="F15">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G15">
         <v>1.53</v>
@@ -4332,7 +4332,7 @@
         <v>4.5</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L15">
         <v>1.28</v>
@@ -4341,10 +4341,10 @@
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
         <v>2.14</v>
@@ -4353,16 +4353,16 @@
         <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T15">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V15">
         <v>1.11</v>
@@ -4419,7 +4419,7 @@
         <v>160</v>
       </c>
       <c r="AN15">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO15">
         <v>190</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU15">
         <v>8</v>
@@ -4473,67 +4473,67 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK15">
         <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM15">
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ15">
         <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS15">
         <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU15">
         <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY15">
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4559,16 +4559,16 @@
         <v>168</v>
       </c>
       <c r="F16">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G16">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H16">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I16">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J16">
         <v>3.55</v>
@@ -4577,13 +4577,13 @@
         <v>4.6</v>
       </c>
       <c r="L16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
         <v>1.25</v>
@@ -4592,34 +4592,34 @@
         <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S16">
         <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
         <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X16">
         <v>23</v>
       </c>
       <c r="Y16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA16">
         <v>46</v>
@@ -4634,7 +4634,7 @@
         <v>15</v>
       </c>
       <c r="AE16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF16">
         <v>25</v>
@@ -4649,10 +4649,10 @@
         <v>44</v>
       </c>
       <c r="AJ16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL16">
         <v>44</v>
@@ -4661,7 +4661,7 @@
         <v>85</v>
       </c>
       <c r="AN16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO16">
         <v>23</v>
@@ -4670,10 +4670,10 @@
         <v>13.5</v>
       </c>
       <c r="AQ16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS16">
         <v>1.01</v>
@@ -4685,22 +4685,22 @@
         <v>6.4</v>
       </c>
       <c r="AV16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
         <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
         <v>1.01</v>
@@ -4715,7 +4715,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG16">
         <v>13.5</v>
@@ -4724,7 +4724,7 @@
         <v>4.5</v>
       </c>
       <c r="BI16">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ16">
         <v>11</v>
@@ -4739,13 +4739,13 @@
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO16">
         <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
@@ -4757,13 +4757,13 @@
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU16">
         <v>4.4</v>
       </c>
       <c r="BV16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
@@ -4810,7 +4810,7 @@
         <v>1.81</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J17">
         <v>3.55</v>
@@ -4819,28 +4819,28 @@
         <v>4.6</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M17">
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
         <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
         <v>1.53</v>
       </c>
       <c r="R17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S17">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T17">
         <v>1.47</v>
@@ -4849,7 +4849,7 @@
         <v>2.44</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W17">
         <v>1.24</v>
@@ -4963,64 +4963,64 @@
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="s">
         <v>187</v>
@@ -5046,10 +5046,10 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H18">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I18">
         <v>1.59</v>
@@ -5058,31 +5058,31 @@
         <v>4.7</v>
       </c>
       <c r="K18">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="O18">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="P18">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q18">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R18">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S18">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5097,172 +5097,172 @@
         <v>1.14</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB18" t="s">
         <v>187</v>
@@ -5545,7 +5545,7 @@
         <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M20">
         <v>1.03</v>
@@ -5557,13 +5557,13 @@
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q20">
         <v>1.5</v>
       </c>
       <c r="R20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S20">
         <v>2.22</v>
@@ -5578,7 +5578,7 @@
         <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X20">
         <v>34</v>
@@ -5590,7 +5590,7 @@
         <v>34</v>
       </c>
       <c r="AA20">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AB20">
         <v>16.5</v>
@@ -5602,10 +5602,10 @@
         <v>17</v>
       </c>
       <c r="AE20">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AF20">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG20">
         <v>13.5</v>
@@ -5614,13 +5614,13 @@
         <v>17</v>
       </c>
       <c r="AI20">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AJ20">
         <v>32</v>
       </c>
       <c r="AK20">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AL20">
         <v>30</v>
@@ -5635,16 +5635,16 @@
         <v>970</v>
       </c>
       <c r="AP20">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AQ20">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT20">
         <v>14</v>
@@ -5656,7 +5656,7 @@
         <v>13</v>
       </c>
       <c r="AW20">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX20">
         <v>15.5</v>
@@ -5668,19 +5668,19 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB20">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC20">
         <v>5</v>
       </c>
       <c r="BD20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF20">
         <v>8.199999999999999</v>
@@ -5689,61 +5689,61 @@
         <v>14</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ20">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK20">
         <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BM20">
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO20">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV20">
+        <v>25</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
         <v>30</v>
       </c>
-      <c r="BW20">
-        <v>1.01</v>
-      </c>
-      <c r="BX20">
-        <v>36</v>
-      </c>
       <c r="BY20">
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5802,7 +5802,7 @@
         <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R21">
         <v>1.46</v>
@@ -5811,13 +5811,13 @@
         <v>2.92</v>
       </c>
       <c r="T21">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U21">
         <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W21">
         <v>2.34</v>
@@ -5931,16 +5931,16 @@
         <v>7.6</v>
       </c>
       <c r="BH21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI21">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL21">
         <v>140</v>
@@ -5964,7 +5964,7 @@
         <v>28</v>
       </c>
       <c r="BS21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BT21">
         <v>10.5</v>
@@ -5988,7 +5988,7 @@
         <v>21</v>
       </c>
       <c r="CA21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB21" t="s">
         <v>187</v>
@@ -6011,10 +6011,10 @@
         <v>174</v>
       </c>
       <c r="F22">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G22">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H22">
         <v>6.6</v>
@@ -6026,10 +6026,10 @@
         <v>4.7</v>
       </c>
       <c r="K22">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M22">
         <v>1.01</v>
@@ -6059,10 +6059,10 @@
         <v>1.95</v>
       </c>
       <c r="V22">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W22">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X22">
         <v>30</v>
@@ -6173,64 +6173,64 @@
         <v>4.2</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB22" t="s">
         <v>187</v>
@@ -6253,13 +6253,13 @@
         <v>175</v>
       </c>
       <c r="F23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G23">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="H23">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I23">
         <v>5.6</v>
@@ -6268,10 +6268,10 @@
         <v>4.4</v>
       </c>
       <c r="K23">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6295,25 +6295,25 @@
         <v>2.18</v>
       </c>
       <c r="T23">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V23">
         <v>1.22</v>
       </c>
       <c r="W23">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X23">
         <v>34</v>
       </c>
       <c r="Y23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA23">
         <v>120</v>
@@ -6325,7 +6325,7 @@
         <v>13.5</v>
       </c>
       <c r="AD23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE23">
         <v>55</v>
@@ -6352,13 +6352,13 @@
         <v>29</v>
       </c>
       <c r="AM23">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN23">
         <v>6.6</v>
       </c>
       <c r="AO23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP23">
         <v>1.01</v>
@@ -6418,7 +6418,7 @@
         <v>5.4</v>
       </c>
       <c r="BI23">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ23">
         <v>10.5</v>
@@ -6427,7 +6427,7 @@
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
@@ -6436,7 +6436,7 @@
         <v>5.5</v>
       </c>
       <c r="BO23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP23">
         <v>12</v>
@@ -6451,13 +6451,13 @@
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU23">
         <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
@@ -6495,7 +6495,7 @@
         <v>176</v>
       </c>
       <c r="F24">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G24">
         <v>2.6</v>
@@ -6510,10 +6510,10 @@
         <v>3.9</v>
       </c>
       <c r="K24">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M24">
         <v>1.03</v>
@@ -6636,7 +6636,7 @@
         <v>12</v>
       </c>
       <c r="BA24">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
         <v>1.01</v>
@@ -6657,61 +6657,61 @@
         <v>12</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK24">
         <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM24">
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ24">
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS24">
         <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY24">
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA24">
         <v>1.01</v>
@@ -6737,166 +6737,166 @@
         <v>177</v>
       </c>
       <c r="F25">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G25">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H25">
         <v>3.6</v>
       </c>
       <c r="I25">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J25">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K25">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q25">
         <v>1.69</v>
       </c>
       <c r="R25">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S25">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7003,7 +7003,7 @@
         <v>1.08</v>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
         <v>1.37</v>
@@ -7021,7 +7021,7 @@
         <v>3.9</v>
       </c>
       <c r="T26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U26">
         <v>2.06</v>
@@ -7039,7 +7039,7 @@
         <v>9.4</v>
       </c>
       <c r="Z26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA26">
         <v>32</v>
@@ -7075,13 +7075,13 @@
         <v>46</v>
       </c>
       <c r="AL26">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM26">
         <v>110</v>
       </c>
       <c r="AN26">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO26">
         <v>20</v>
@@ -7120,7 +7120,7 @@
         <v>17</v>
       </c>
       <c r="BA26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB26">
         <v>60</v>
@@ -7135,7 +7135,7 @@
         <v>15</v>
       </c>
       <c r="BF26">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="BG26">
         <v>17.5</v>
@@ -7159,7 +7159,7 @@
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO26">
         <v>5.1</v>
@@ -7180,7 +7180,7 @@
         <v>5.9</v>
       </c>
       <c r="BU26">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV26">
         <v>21</v>
@@ -7224,10 +7224,10 @@
         <v>2.6</v>
       </c>
       <c r="G27">
+        <v>2.76</v>
+      </c>
+      <c r="H27">
         <v>2.8</v>
-      </c>
-      <c r="H27">
-        <v>2.74</v>
       </c>
       <c r="I27">
         <v>2.98</v>
@@ -7236,43 +7236,43 @@
         <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M27">
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O27">
         <v>1.29</v>
       </c>
       <c r="P27">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q27">
         <v>1.86</v>
       </c>
       <c r="R27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S27">
         <v>3.15</v>
       </c>
       <c r="T27">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U27">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V27">
         <v>1.5</v>
       </c>
       <c r="W27">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X27">
         <v>18</v>
@@ -7287,7 +7287,7 @@
         <v>55</v>
       </c>
       <c r="AB27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC27">
         <v>9.4</v>
@@ -7299,7 +7299,7 @@
         <v>32</v>
       </c>
       <c r="AF27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG27">
         <v>12.5</v>
@@ -7314,7 +7314,7 @@
         <v>40</v>
       </c>
       <c r="AK27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL27">
         <v>44</v>
@@ -7338,7 +7338,7 @@
         <v>17</v>
       </c>
       <c r="AS27">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT27">
         <v>10</v>
@@ -7350,7 +7350,7 @@
         <v>11</v>
       </c>
       <c r="AW27">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AX27">
         <v>16</v>
@@ -7362,79 +7362,79 @@
         <v>14</v>
       </c>
       <c r="BA27">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BB27">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC27">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD27">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE27">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF27">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="BG27">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BH27">
         <v>3.95</v>
       </c>
       <c r="BI27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="BL27">
         <v>120</v>
       </c>
       <c r="BM27">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BN27">
         <v>6.6</v>
       </c>
       <c r="BO27">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BP27">
         <v>23</v>
       </c>
       <c r="BQ27">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BR27">
         <v>36</v>
       </c>
       <c r="BS27">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BT27">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU27">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV27">
         <v>25</v>
       </c>
       <c r="BW27">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BX27">
         <v>38</v>
       </c>
       <c r="BY27">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7499,10 +7499,10 @@
         <v>1.89</v>
       </c>
       <c r="R28">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S28">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T28">
         <v>1.8</v>
@@ -7550,7 +7550,7 @@
         <v>19.5</v>
       </c>
       <c r="AI28">
-        <v>970</v>
+        <v>920</v>
       </c>
       <c r="AJ28">
         <v>23</v>
@@ -7568,7 +7568,7 @@
         <v>14</v>
       </c>
       <c r="AO28">
-        <v>970</v>
+        <v>920</v>
       </c>
       <c r="AP28">
         <v>11</v>
@@ -7747,10 +7747,10 @@
         <v>3.5</v>
       </c>
       <c r="T29">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U29">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V29">
         <v>1.31</v>
@@ -7813,7 +7813,7 @@
         <v>55</v>
       </c>
       <c r="AP29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ29">
         <v>14</v>
@@ -7822,7 +7822,7 @@
         <v>26</v>
       </c>
       <c r="AS29">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT29">
         <v>8.800000000000001</v>
@@ -7867,7 +7867,7 @@
         <v>44</v>
       </c>
       <c r="BH29">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI29">
         <v>3.1</v>
@@ -7882,7 +7882,7 @@
         <v>140</v>
       </c>
       <c r="BM29">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BN29">
         <v>5.6</v>
@@ -7894,13 +7894,13 @@
         <v>17</v>
       </c>
       <c r="BQ29">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BR29">
         <v>34</v>
       </c>
       <c r="BS29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT29">
         <v>9</v>
@@ -7912,19 +7912,19 @@
         <v>42</v>
       </c>
       <c r="BW29">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX29">
         <v>55</v>
       </c>
       <c r="BY29">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ29">
         <v>29</v>
       </c>
       <c r="CA29">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB29" t="s">
         <v>187</v>
@@ -8189,85 +8189,85 @@
         <v>183</v>
       </c>
       <c r="F31">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G31">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H31">
         <v>10</v>
       </c>
       <c r="I31">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K31">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
         <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O31">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P31">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q31">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S31">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T31">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U31">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V31">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W31">
         <v>3.05</v>
       </c>
       <c r="X31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y31">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z31">
         <v>130</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AB31">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE31">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AF31">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG31">
         <v>13</v>
@@ -8276,7 +8276,7 @@
         <v>42</v>
       </c>
       <c r="AI31">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AJ31">
         <v>14.5</v>
@@ -8285,127 +8285,127 @@
         <v>22</v>
       </c>
       <c r="AL31">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM31">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO31">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="AP31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ31">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR31">
+        <v>4.1</v>
+      </c>
+      <c r="AS31">
         <v>4.2</v>
       </c>
-      <c r="AS31">
-        <v>4.4</v>
-      </c>
       <c r="AT31">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AU31">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AW31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX31">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY31">
         <v>9</v>
       </c>
       <c r="AZ31">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BA31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB31">
         <v>10</v>
       </c>
       <c r="BC31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF31">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK31">
         <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM31">
         <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ31">
         <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS31">
         <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU31">
         <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BW31">
         <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY31">
         <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA31">
         <v>1.01</v>
@@ -8673,10 +8673,10 @@
         <v>185</v>
       </c>
       <c r="F33">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G33">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H33">
         <v>3.8</v>
@@ -8685,28 +8685,28 @@
         <v>4.3</v>
       </c>
       <c r="J33">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K33">
         <v>3.4</v>
       </c>
       <c r="L33">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M33">
         <v>1.09</v>
       </c>
       <c r="N33">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
         <v>1.48</v>
       </c>
       <c r="P33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q33">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R33">
         <v>1.2</v>
@@ -8724,19 +8724,19 @@
         <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X33">
         <v>11.5</v>
       </c>
       <c r="Y33">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA33">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB33">
         <v>8.800000000000001</v>
@@ -8745,13 +8745,13 @@
         <v>9</v>
       </c>
       <c r="AD33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE33">
         <v>80</v>
       </c>
       <c r="AF33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG33">
         <v>14</v>
@@ -8760,13 +8760,13 @@
         <v>28</v>
       </c>
       <c r="AI33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ33">
+        <v>40</v>
+      </c>
+      <c r="AK33">
         <v>38</v>
-      </c>
-      <c r="AK33">
-        <v>36</v>
       </c>
       <c r="AL33">
         <v>70</v>
@@ -8775,19 +8775,19 @@
         <v>210</v>
       </c>
       <c r="AN33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO33">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP33">
         <v>7</v>
       </c>
       <c r="AQ33">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR33">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS33">
         <v>1.01</v>
@@ -8805,7 +8805,7 @@
         <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY33">
         <v>8.4</v>
@@ -8820,76 +8820,76 @@
         <v>1.01</v>
       </c>
       <c r="BC33">
+        <v>1.01</v>
+      </c>
+      <c r="BD33">
+        <v>1.01</v>
+      </c>
+      <c r="BE33">
+        <v>1.01</v>
+      </c>
+      <c r="BF33">
         <v>21</v>
       </c>
-      <c r="BD33">
-        <v>1.01</v>
-      </c>
-      <c r="BE33">
-        <v>1.01</v>
-      </c>
-      <c r="BF33">
-        <v>20</v>
-      </c>
       <c r="BG33">
         <v>1.01</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI33">
         <v>2.28</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK33">
         <v>1.01</v>
       </c>
       <c r="BL33">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM33">
         <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ33">
         <v>1.01</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS33">
         <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW33">
         <v>1.01</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY33">
         <v>1.01</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA33">
         <v>1.01</v>
@@ -8915,166 +8915,166 @@
         <v>186</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G34">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H34">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I34">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J34">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="K34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L34">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="O34">
         <v>1.39</v>
       </c>
       <c r="P34">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q34">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S34">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V34">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W34">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV34">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW34">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY34">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA34">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH34">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="190">
   <si>
     <t>League</t>
   </si>
@@ -274,15 +274,15 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
     <t>Lithuanian A Lyga</t>
   </si>
   <si>
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
-    <t>Armenian Premier League</t>
-  </si>
-  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
@@ -301,12 +301,12 @@
     <t>Danish Superliga</t>
   </si>
   <si>
+    <t>Swiss Super League</t>
+  </si>
+  <si>
     <t>Belgian Pro League</t>
   </si>
   <si>
-    <t>Swiss Super League</t>
-  </si>
-  <si>
     <t>French Ligue 1</t>
   </si>
   <si>
@@ -397,15 +397,15 @@
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>Alashkert</t>
+  </si>
+  <si>
     <t>FK Banga Gargzdu</t>
   </si>
   <si>
     <t>Rakow Czestochowa</t>
   </si>
   <si>
-    <t>Alashkert</t>
-  </si>
-  <si>
     <t>Al Sailiya</t>
   </si>
   <si>
@@ -421,19 +421,25 @@
     <t>Bursaspor</t>
   </si>
   <si>
+    <t>Bodrum Belediyesi Bodrumspor</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Gyori</t>
   </si>
   <si>
+    <t>ES Setif</t>
+  </si>
+  <si>
+    <t>FC Copenhagen</t>
+  </si>
+  <si>
     <t>Al Draih</t>
   </si>
   <si>
-    <t>ES Setif</t>
-  </si>
-  <si>
-    <t>FC Copenhagen</t>
+    <t>Lugano</t>
   </si>
   <si>
     <t>Gent</t>
@@ -448,9 +454,6 @@
     <t>FC Basel</t>
   </si>
   <si>
-    <t>Lugano</t>
-  </si>
-  <si>
     <t>Toulouse</t>
   </si>
   <si>
@@ -496,15 +499,15 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>FC Van Yerevan</t>
+  </si>
+  <si>
     <t>Panevezys</t>
   </si>
   <si>
     <t>Gornik Zabrze</t>
   </si>
   <si>
-    <t>FC Van Yerevan</t>
-  </si>
-  <si>
     <t>Al Arabi (QAT)</t>
   </si>
   <si>
@@ -520,19 +523,25 @@
     <t>Istanbulspor</t>
   </si>
   <si>
+    <t>Erokspor A.S</t>
+  </si>
+  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>Ferencvaros</t>
   </si>
   <si>
+    <t>ES Ben Aknoun</t>
+  </si>
+  <si>
+    <t>FC Nordsjaelland</t>
+  </si>
+  <si>
     <t>Al-Quadisiya (KSA)</t>
   </si>
   <si>
-    <t>ES Ben Aknoun</t>
-  </si>
-  <si>
-    <t>FC Nordsjaelland</t>
+    <t>Servette</t>
   </si>
   <si>
     <t>Oud-Heverlee Leuven</t>
@@ -547,9 +556,6 @@
     <t>Sion</t>
   </si>
   <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Lille</t>
   </si>
   <si>
@@ -577,7 +583,7 @@
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>2026-09-02 03:17:29</t>
+    <t>2026-09-02 05:30:21</t>
   </si>
 </sst>
 </file>
@@ -909,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB34"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1168,22 +1174,22 @@
         <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I2">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
         <v>3.7</v>
@@ -1207,7 +1213,7 @@
         <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
         <v>3.95</v>
@@ -1219,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="V2">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1231,19 +1237,19 @@
         <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA2">
         <v>36</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC2">
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
         <v>32</v>
@@ -1252,19 +1258,19 @@
         <v>30</v>
       </c>
       <c r="AG2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>50</v>
       </c>
       <c r="AJ2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AK2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL2">
         <v>70</v>
@@ -1273,7 +1279,7 @@
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO2">
         <v>25</v>
@@ -1285,10 +1291,10 @@
         <v>7.6</v>
       </c>
       <c r="AR2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1300,10 +1306,10 @@
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY2">
         <v>13.5</v>
@@ -1312,25 +1318,25 @@
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BD2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE2">
+        <v>5.8</v>
+      </c>
+      <c r="BF2">
         <v>5.6</v>
       </c>
-      <c r="BF2">
-        <v>5.4</v>
-      </c>
       <c r="BG2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH2">
         <v>3.65</v>
@@ -1342,58 +1348,58 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BL2">
-        <v>990</v>
+        <v>900</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BU2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1410,10 +1416,10 @@
         <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
         <v>2.52</v>
@@ -1422,10 +1428,10 @@
         <v>2.96</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
         <v>3.9</v>
@@ -1455,13 +1461,13 @@
         <v>3.1</v>
       </c>
       <c r="T3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U3">
         <v>2.24</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>1.65</v>
@@ -1476,7 +1482,7 @@
         <v>23</v>
       </c>
       <c r="AA3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB3">
         <v>12.5</v>
@@ -1512,7 +1518,7 @@
         <v>38</v>
       </c>
       <c r="AM3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN3">
         <v>19</v>
@@ -1599,13 +1605,13 @@
         <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
@@ -1635,7 +1641,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1652,25 +1658,25 @@
         <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G4">
         <v>3.35</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J4">
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -1679,22 +1685,22 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
         <v>1.86</v>
@@ -1703,19 +1709,19 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W4">
         <v>1.43</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA4">
         <v>38</v>
@@ -1772,7 +1778,7 @@
         <v>13</v>
       </c>
       <c r="AS4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT4">
         <v>9.4</v>
@@ -1784,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
         <v>18.5</v>
@@ -1796,34 +1802,34 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC4">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BG4">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH4">
         <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
@@ -1835,49 +1841,49 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1894,7 +1900,7 @@
         <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F5">
         <v>2.3</v>
@@ -1939,7 +1945,7 @@
         <v>2.36</v>
       </c>
       <c r="T5">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="U5">
         <v>2.62</v>
@@ -2068,13 +2074,13 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>85</v>
       </c>
       <c r="BM5">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
         <v>7</v>
@@ -2086,13 +2092,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ5">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>28</v>
       </c>
       <c r="BS5">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
         <v>7.8</v>
@@ -2104,22 +2110,22 @@
         <v>24</v>
       </c>
       <c r="BW5">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>32</v>
       </c>
       <c r="BY5">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
         <v>19</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2136,10 +2142,10 @@
         <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G6">
         <v>2.3</v>
@@ -2148,16 +2154,16 @@
         <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2181,16 +2187,16 @@
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X6">
         <v>18.5</v>
@@ -2274,7 +2280,7 @@
         <v>11</v>
       </c>
       <c r="AY6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
         <v>13</v>
@@ -2361,7 +2367,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2378,25 +2384,25 @@
         <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F7">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
         <v>3.05</v>
       </c>
       <c r="H7">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J7">
         <v>3.1</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2405,13 +2411,13 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q7">
         <v>2.14</v>
@@ -2423,16 +2429,16 @@
         <v>4</v>
       </c>
       <c r="T7">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
         <v>12</v>
@@ -2480,7 +2486,7 @@
         <v>55</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7">
         <v>36</v>
@@ -2603,7 +2609,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2620,232 +2626,232 @@
         <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F8">
-        <v>1.79</v>
+        <v>1.17</v>
       </c>
       <c r="G8">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="H8">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>7.4</v>
+      </c>
+      <c r="K8">
+        <v>10.5</v>
+      </c>
+      <c r="L8">
+        <v>1.23</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>5.8</v>
+      </c>
+      <c r="O8">
+        <v>1.17</v>
+      </c>
+      <c r="P8">
+        <v>2.64</v>
+      </c>
+      <c r="Q8">
+        <v>1.51</v>
+      </c>
+      <c r="R8">
+        <v>1.66</v>
+      </c>
+      <c r="S8">
+        <v>2.24</v>
+      </c>
+      <c r="T8">
+        <v>2.34</v>
+      </c>
+      <c r="U8">
+        <v>1.54</v>
+      </c>
+      <c r="V8">
+        <v>1.04</v>
+      </c>
+      <c r="W8">
+        <v>5.3</v>
+      </c>
+      <c r="X8">
+        <v>36</v>
+      </c>
+      <c r="Y8">
+        <v>70</v>
+      </c>
+      <c r="Z8">
+        <v>240</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>11.5</v>
+      </c>
+      <c r="AC8">
+        <v>21</v>
+      </c>
+      <c r="AD8">
+        <v>85</v>
+      </c>
+      <c r="AE8">
+        <v>440</v>
+      </c>
+      <c r="AF8">
+        <v>9</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>50</v>
+      </c>
+      <c r="AI8">
+        <v>300</v>
+      </c>
+      <c r="AJ8">
+        <v>9.6</v>
+      </c>
+      <c r="AK8">
+        <v>17</v>
+      </c>
+      <c r="AL8">
+        <v>55</v>
+      </c>
+      <c r="AM8">
+        <v>290</v>
+      </c>
+      <c r="AN8">
+        <v>4</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>22</v>
+      </c>
+      <c r="AQ8">
+        <v>44</v>
+      </c>
+      <c r="AR8">
+        <v>150</v>
+      </c>
+      <c r="AS8">
+        <v>1.01</v>
+      </c>
+      <c r="AT8">
+        <v>7.8</v>
+      </c>
+      <c r="AU8">
+        <v>14</v>
+      </c>
+      <c r="AV8">
+        <v>50</v>
+      </c>
+      <c r="AW8">
+        <v>280</v>
+      </c>
+      <c r="AX8">
+        <v>6.2</v>
+      </c>
+      <c r="AY8">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8">
+        <v>32</v>
+      </c>
+      <c r="BA8">
+        <v>190</v>
+      </c>
+      <c r="BB8">
+        <v>6.6</v>
+      </c>
+      <c r="BC8">
+        <v>11</v>
+      </c>
+      <c r="BD8">
+        <v>34</v>
+      </c>
+      <c r="BE8">
+        <v>180</v>
+      </c>
+      <c r="BF8">
+        <v>3</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>5.4</v>
+      </c>
+      <c r="BI8">
+        <v>3.85</v>
+      </c>
+      <c r="BJ8">
+        <v>17</v>
+      </c>
+      <c r="BK8">
+        <v>11</v>
+      </c>
+      <c r="BL8">
+        <v>240</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>4.1</v>
+      </c>
+      <c r="BO8">
+        <v>2.98</v>
+      </c>
+      <c r="BP8">
+        <v>7</v>
+      </c>
+      <c r="BQ8">
         <v>4.8</v>
       </c>
-      <c r="I8">
-        <v>5.6</v>
-      </c>
-      <c r="J8">
-        <v>3.75</v>
-      </c>
-      <c r="K8">
-        <v>4.1</v>
-      </c>
-      <c r="L8">
-        <v>1.29</v>
-      </c>
-      <c r="M8">
-        <v>1.05</v>
-      </c>
-      <c r="N8">
-        <v>1.01</v>
-      </c>
-      <c r="O8">
-        <v>1.26</v>
-      </c>
-      <c r="P8">
-        <v>2.1</v>
-      </c>
-      <c r="Q8">
-        <v>1.73</v>
-      </c>
-      <c r="R8">
-        <v>1.46</v>
-      </c>
-      <c r="S8">
-        <v>2.8</v>
-      </c>
-      <c r="T8">
-        <v>1.65</v>
-      </c>
-      <c r="U8">
-        <v>2.28</v>
-      </c>
-      <c r="V8">
-        <v>1.23</v>
-      </c>
-      <c r="W8">
-        <v>2.1</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8">
-        <v>1.01</v>
-      </c>
-      <c r="AR8">
-        <v>1.01</v>
-      </c>
-      <c r="AS8">
-        <v>1.01</v>
-      </c>
-      <c r="AT8">
-        <v>1.01</v>
-      </c>
-      <c r="AU8">
-        <v>1.01</v>
-      </c>
-      <c r="AV8">
-        <v>1.01</v>
-      </c>
-      <c r="AW8">
-        <v>1.01</v>
-      </c>
-      <c r="AX8">
-        <v>1.01</v>
-      </c>
-      <c r="AY8">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8">
-        <v>1.01</v>
-      </c>
-      <c r="BA8">
-        <v>1.01</v>
-      </c>
-      <c r="BB8">
-        <v>1.01</v>
-      </c>
-      <c r="BC8">
-        <v>1.01</v>
-      </c>
-      <c r="BD8">
-        <v>1.01</v>
-      </c>
-      <c r="BE8">
-        <v>1.01</v>
-      </c>
-      <c r="BF8">
-        <v>1.01</v>
-      </c>
-      <c r="BG8">
-        <v>1.01</v>
-      </c>
-      <c r="BH8">
-        <v>4.5</v>
-      </c>
-      <c r="BI8">
-        <v>3</v>
-      </c>
-      <c r="BJ8">
-        <v>11.5</v>
-      </c>
-      <c r="BK8">
-        <v>6.8</v>
-      </c>
-      <c r="BL8">
-        <v>130</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>5.6</v>
-      </c>
-      <c r="BO8">
-        <v>3.65</v>
-      </c>
-      <c r="BP8">
+      <c r="BR8">
+        <v>28</v>
+      </c>
+      <c r="BS8">
+        <v>18</v>
+      </c>
+      <c r="BT8">
+        <v>23</v>
+      </c>
+      <c r="BU8">
         <v>15</v>
       </c>
-      <c r="BQ8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR8">
-        <v>30</v>
-      </c>
-      <c r="BS8">
-        <v>17.5</v>
-      </c>
-      <c r="BT8">
-        <v>9.4</v>
-      </c>
-      <c r="BU8">
-        <v>5.9</v>
-      </c>
       <c r="BV8">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="BW8">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="BY8">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="CA8">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2862,181 +2868,181 @@
         <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="G9">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="H9">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S9">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>4.5</v>
+      </c>
+      <c r="BI9">
+        <v>3</v>
+      </c>
+      <c r="BJ9">
         <v>11.5</v>
       </c>
-      <c r="AH9">
-        <v>17</v>
-      </c>
-      <c r="AI9">
-        <v>55</v>
-      </c>
-      <c r="AJ9">
-        <v>30</v>
-      </c>
-      <c r="AK9">
-        <v>24</v>
-      </c>
-      <c r="AL9">
-        <v>36</v>
-      </c>
-      <c r="AM9">
-        <v>100</v>
-      </c>
-      <c r="AN9">
-        <v>16.5</v>
-      </c>
-      <c r="AO9">
-        <v>34</v>
-      </c>
-      <c r="AP9">
-        <v>11.5</v>
-      </c>
-      <c r="AQ9">
-        <v>10</v>
-      </c>
-      <c r="AR9">
-        <v>18</v>
-      </c>
-      <c r="AS9">
-        <v>1.01</v>
-      </c>
-      <c r="AT9">
-        <v>8</v>
-      </c>
-      <c r="AU9">
-        <v>6.2</v>
-      </c>
-      <c r="AV9">
-        <v>10.5</v>
-      </c>
-      <c r="AW9">
-        <v>1.01</v>
-      </c>
-      <c r="AX9">
-        <v>13.5</v>
-      </c>
-      <c r="AY9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ9">
-        <v>12</v>
-      </c>
-      <c r="BA9">
-        <v>1.01</v>
-      </c>
-      <c r="BB9">
-        <v>1.01</v>
-      </c>
-      <c r="BC9">
-        <v>17</v>
-      </c>
-      <c r="BD9">
-        <v>1.01</v>
-      </c>
-      <c r="BE9">
-        <v>1.01</v>
-      </c>
-      <c r="BF9">
-        <v>12</v>
-      </c>
-      <c r="BG9">
-        <v>1.01</v>
-      </c>
-      <c r="BH9">
-        <v>3.6</v>
-      </c>
-      <c r="BI9">
-        <v>3.25</v>
-      </c>
-      <c r="BJ9">
-        <v>11</v>
-      </c>
       <c r="BK9">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>130</v>
@@ -3045,49 +3051,49 @@
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="BQ9">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BW9">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY9">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="CA9">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3104,232 +3110,232 @@
         <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F10">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="G10">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="H10">
-        <v>16</v>
+        <v>3.25</v>
       </c>
       <c r="I10">
+        <v>3.6</v>
+      </c>
+      <c r="J10">
+        <v>3.55</v>
+      </c>
+      <c r="K10">
+        <v>4.2</v>
+      </c>
+      <c r="L10">
+        <v>1.31</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>3.95</v>
+      </c>
+      <c r="O10">
+        <v>1.29</v>
+      </c>
+      <c r="P10">
+        <v>2.04</v>
+      </c>
+      <c r="Q10">
+        <v>1.86</v>
+      </c>
+      <c r="R10">
+        <v>1.41</v>
+      </c>
+      <c r="S10">
+        <v>3.15</v>
+      </c>
+      <c r="T10">
+        <v>1.58</v>
+      </c>
+      <c r="U10">
+        <v>2.24</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.73</v>
+      </c>
+      <c r="X10">
+        <v>19.5</v>
+      </c>
+      <c r="Y10">
+        <v>14.5</v>
+      </c>
+      <c r="Z10">
+        <v>25</v>
+      </c>
+      <c r="AA10">
+        <v>75</v>
+      </c>
+      <c r="AB10">
+        <v>11</v>
+      </c>
+      <c r="AC10">
+        <v>8.4</v>
+      </c>
+      <c r="AD10">
+        <v>14.5</v>
+      </c>
+      <c r="AE10">
+        <v>46</v>
+      </c>
+      <c r="AF10">
+        <v>15.5</v>
+      </c>
+      <c r="AG10">
+        <v>11.5</v>
+      </c>
+      <c r="AH10">
+        <v>17</v>
+      </c>
+      <c r="AI10">
+        <v>55</v>
+      </c>
+      <c r="AJ10">
+        <v>30</v>
+      </c>
+      <c r="AK10">
         <v>24</v>
       </c>
-      <c r="J10">
-        <v>7.4</v>
-      </c>
-      <c r="K10">
-        <v>9.6</v>
-      </c>
-      <c r="L10">
-        <v>1.23</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>5.8</v>
-      </c>
-      <c r="O10">
-        <v>1.17</v>
-      </c>
-      <c r="P10">
-        <v>2.64</v>
-      </c>
-      <c r="Q10">
-        <v>1.51</v>
-      </c>
-      <c r="R10">
-        <v>1.66</v>
-      </c>
-      <c r="S10">
-        <v>2.24</v>
-      </c>
-      <c r="T10">
-        <v>2.28</v>
-      </c>
-      <c r="U10">
-        <v>1.64</v>
-      </c>
-      <c r="V10">
-        <v>1.04</v>
-      </c>
-      <c r="W10">
-        <v>5.3</v>
-      </c>
-      <c r="X10">
+      <c r="AL10">
         <v>36</v>
       </c>
-      <c r="Y10">
-        <v>70</v>
-      </c>
-      <c r="Z10">
-        <v>240</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
+      <c r="AM10">
+        <v>100</v>
+      </c>
+      <c r="AN10">
+        <v>16.5</v>
+      </c>
+      <c r="AO10">
+        <v>34</v>
+      </c>
+      <c r="AP10">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10">
+        <v>12.5</v>
+      </c>
+      <c r="AR10">
+        <v>21</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>8</v>
+      </c>
+      <c r="AU10">
+        <v>6.2</v>
+      </c>
+      <c r="AV10">
+        <v>10.5</v>
+      </c>
+      <c r="AW10">
+        <v>27</v>
+      </c>
+      <c r="AX10">
+        <v>13.5</v>
+      </c>
+      <c r="AY10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ10">
         <v>12</v>
       </c>
-      <c r="AC10">
-        <v>21</v>
-      </c>
-      <c r="AD10">
-        <v>85</v>
-      </c>
-      <c r="AE10">
-        <v>440</v>
-      </c>
-      <c r="AF10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG10">
-        <v>14.5</v>
-      </c>
-      <c r="AH10">
-        <v>50</v>
-      </c>
-      <c r="AI10">
-        <v>300</v>
-      </c>
-      <c r="AJ10">
-        <v>10</v>
-      </c>
-      <c r="AK10">
-        <v>17</v>
-      </c>
-      <c r="AL10">
-        <v>55</v>
-      </c>
-      <c r="AM10">
-        <v>290</v>
-      </c>
-      <c r="AN10">
-        <v>4.1</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>22</v>
-      </c>
-      <c r="AQ10">
+      <c r="BA10">
+        <v>34</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>20</v>
+      </c>
+      <c r="BD10">
+        <v>25</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>12</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>3.6</v>
+      </c>
+      <c r="BI10">
+        <v>3.25</v>
+      </c>
+      <c r="BJ10">
+        <v>11</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>130</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>6.2</v>
+      </c>
+      <c r="BO10">
+        <v>4</v>
+      </c>
+      <c r="BP10">
+        <v>19.5</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>34</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>8</v>
+      </c>
+      <c r="BU10">
+        <v>5</v>
+      </c>
+      <c r="BV10">
+        <v>32</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
         <v>44</v>
       </c>
-      <c r="AR10">
-        <v>150</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>7.8</v>
-      </c>
-      <c r="AU10">
-        <v>14</v>
-      </c>
-      <c r="AV10">
-        <v>50</v>
-      </c>
-      <c r="AW10">
-        <v>280</v>
-      </c>
-      <c r="AX10">
-        <v>6.2</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>32</v>
-      </c>
-      <c r="BA10">
-        <v>190</v>
-      </c>
-      <c r="BB10">
-        <v>6.6</v>
-      </c>
-      <c r="BC10">
-        <v>11</v>
-      </c>
-      <c r="BD10">
-        <v>34</v>
-      </c>
-      <c r="BE10">
-        <v>180</v>
-      </c>
-      <c r="BF10">
-        <v>3</v>
-      </c>
-      <c r="BG10">
-        <v>1.01</v>
-      </c>
-      <c r="BH10">
-        <v>5.4</v>
-      </c>
-      <c r="BI10">
-        <v>3.8</v>
-      </c>
-      <c r="BJ10">
-        <v>16.5</v>
-      </c>
-      <c r="BK10">
-        <v>11</v>
-      </c>
-      <c r="BL10">
-        <v>220</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>4.1</v>
-      </c>
-      <c r="BO10">
-        <v>3</v>
-      </c>
-      <c r="BP10">
-        <v>7.2</v>
-      </c>
-      <c r="BQ10">
-        <v>4.9</v>
-      </c>
-      <c r="BR10">
-        <v>27</v>
-      </c>
-      <c r="BS10">
-        <v>17.5</v>
-      </c>
-      <c r="BT10">
-        <v>22</v>
-      </c>
-      <c r="BU10">
-        <v>14.5</v>
-      </c>
-      <c r="BV10">
-        <v>190</v>
-      </c>
-      <c r="BW10">
-        <v>1.01</v>
-      </c>
-      <c r="BX10">
-        <v>140</v>
-      </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="CA10">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3346,31 +3352,31 @@
         <v>130</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F11">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="G11">
         <v>7</v>
       </c>
       <c r="H11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J11">
         <v>4.9</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.21</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -3379,7 +3385,7 @@
         <v>1.16</v>
       </c>
       <c r="P11">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q11">
         <v>1.46</v>
@@ -3397,7 +3403,7 @@
         <v>2.32</v>
       </c>
       <c r="V11">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W11">
         <v>1.17</v>
@@ -3418,7 +3424,7 @@
         <v>38</v>
       </c>
       <c r="AC11">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD11">
         <v>13</v>
@@ -3469,7 +3475,7 @@
         <v>12</v>
       </c>
       <c r="AT11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU11">
         <v>9.4</v>
@@ -3481,10 +3487,10 @@
         <v>11</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AY11">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AZ11">
         <v>13</v>
@@ -3499,7 +3505,7 @@
         <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE11">
         <v>1.01</v>
@@ -3508,7 +3514,7 @@
         <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH11">
         <v>5.7</v>
@@ -3571,7 +3577,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3588,7 +3594,7 @@
         <v>131</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F12">
         <v>1.85</v>
@@ -3606,7 +3612,7 @@
         <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3813,7 +3819,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3830,7 +3836,7 @@
         <v>132</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F13">
         <v>1.4</v>
@@ -3848,7 +3854,7 @@
         <v>4.5</v>
       </c>
       <c r="K13">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L13">
         <v>1.41</v>
@@ -3875,10 +3881,10 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="V13">
         <v>1.08</v>
@@ -3896,7 +3902,7 @@
         <v>120</v>
       </c>
       <c r="AA13">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AB13">
         <v>7.6</v>
@@ -3956,7 +3962,7 @@
         <v>5.3</v>
       </c>
       <c r="AU13">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV13">
         <v>1.01</v>
@@ -3989,7 +3995,7 @@
         <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG13">
         <v>1.01</v>
@@ -4055,7 +4061,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4072,7 +4078,7 @@
         <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F14">
         <v>4.6</v>
@@ -4087,13 +4093,13 @@
         <v>1.8</v>
       </c>
       <c r="J14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
         <v>4.4</v>
       </c>
       <c r="L14">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -4114,64 +4120,64 @@
         <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T14">
         <v>1.67</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
         <v>2.24</v>
       </c>
       <c r="W14">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y14">
         <v>12</v>
       </c>
       <c r="Z14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AC14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF14">
         <v>80</v>
       </c>
       <c r="AG14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AH14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
         <v>30</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK14">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AL14">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AM14">
         <v>1000</v>
@@ -4192,10 +4198,10 @@
         <v>11</v>
       </c>
       <c r="AS14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU14">
         <v>9</v>
@@ -4207,7 +4213,7 @@
         <v>15</v>
       </c>
       <c r="AX14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AY14">
         <v>16.5</v>
@@ -4216,22 +4222,22 @@
         <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BB14">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BC14">
+        <v>44</v>
+      </c>
+      <c r="BD14">
+        <v>44</v>
+      </c>
+      <c r="BE14">
         <v>34</v>
       </c>
-      <c r="BD14">
+      <c r="BF14">
         <v>34</v>
-      </c>
-      <c r="BE14">
-        <v>7.8</v>
-      </c>
-      <c r="BF14">
-        <v>25</v>
       </c>
       <c r="BG14">
         <v>7.6</v>
@@ -4243,10 +4249,10 @@
         <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL14">
         <v>110</v>
@@ -4276,7 +4282,7 @@
         <v>5.7</v>
       </c>
       <c r="BU14">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BV14">
         <v>14.5</v>
@@ -4297,7 +4303,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4314,13 +4320,13 @@
         <v>134</v>
       </c>
       <c r="E15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F15">
         <v>1.46</v>
       </c>
       <c r="G15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H15">
         <v>7.6</v>
@@ -4344,7 +4350,7 @@
         <v>4.3</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
         <v>2.14</v>
@@ -4356,7 +4362,7 @@
         <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T15">
         <v>1.94</v>
@@ -4368,7 +4374,7 @@
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -4539,254 +4545,254 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
         <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
         <v>135</v>
       </c>
       <c r="E16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F16">
+        <v>2.76</v>
+      </c>
+      <c r="G16">
+        <v>3.1</v>
+      </c>
+      <c r="H16">
         <v>2.64</v>
       </c>
-      <c r="G16">
-        <v>2.98</v>
-      </c>
-      <c r="H16">
-        <v>2.5</v>
-      </c>
       <c r="I16">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="M16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N16">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="O16">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="Q16">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S16">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="T16">
+        <v>1.8</v>
+      </c>
+      <c r="U16">
+        <v>2.06</v>
+      </c>
+      <c r="V16">
         <v>1.52</v>
       </c>
-      <c r="U16">
-        <v>2.12</v>
-      </c>
-      <c r="V16">
-        <v>1.54</v>
-      </c>
       <c r="W16">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X16">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Y16">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AA16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB16">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE16">
         <v>34</v>
       </c>
       <c r="AF16">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AG16">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK16">
+        <v>36</v>
+      </c>
+      <c r="AL16">
+        <v>48</v>
+      </c>
+      <c r="AM16">
+        <v>120</v>
+      </c>
+      <c r="AN16">
         <v>34</v>
       </c>
-      <c r="AL16">
-        <v>44</v>
-      </c>
-      <c r="AM16">
-        <v>85</v>
-      </c>
-      <c r="AN16">
-        <v>25</v>
-      </c>
       <c r="AO16">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AP16">
+        <v>9.6</v>
+      </c>
+      <c r="AQ16">
+        <v>8</v>
+      </c>
+      <c r="AR16">
         <v>13.5</v>
       </c>
-      <c r="AQ16">
-        <v>10</v>
-      </c>
-      <c r="AR16">
-        <v>14</v>
-      </c>
       <c r="AS16">
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
         <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
+        <v>13.5</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.01</v>
+      </c>
+      <c r="BC16">
+        <v>1.01</v>
+      </c>
+      <c r="BD16">
+        <v>1.01</v>
+      </c>
+      <c r="BE16">
+        <v>1.01</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>3.55</v>
+      </c>
+      <c r="BI16">
+        <v>2.66</v>
+      </c>
+      <c r="BJ16">
         <v>11.5</v>
       </c>
-      <c r="BA16">
-        <v>1.01</v>
-      </c>
-      <c r="BB16">
-        <v>1.01</v>
-      </c>
-      <c r="BC16">
-        <v>20</v>
-      </c>
-      <c r="BD16">
-        <v>1.01</v>
-      </c>
-      <c r="BE16">
-        <v>1.01</v>
-      </c>
-      <c r="BF16">
-        <v>14.5</v>
-      </c>
-      <c r="BG16">
-        <v>13.5</v>
-      </c>
-      <c r="BH16">
-        <v>4.5</v>
-      </c>
-      <c r="BI16">
-        <v>3.05</v>
-      </c>
-      <c r="BJ16">
-        <v>11</v>
-      </c>
       <c r="BK16">
         <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO16">
         <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
       </c>
       <c r="BR16">
+        <v>44</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>6.4</v>
+      </c>
+      <c r="BU16">
+        <v>4.5</v>
+      </c>
+      <c r="BV16">
+        <v>25</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>42</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
         <v>36</v>
       </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>7</v>
-      </c>
-      <c r="BU16">
-        <v>4.4</v>
-      </c>
-      <c r="BV16">
-        <v>23</v>
-      </c>
-      <c r="BW16">
-        <v>1.01</v>
-      </c>
-      <c r="BX16">
-        <v>34</v>
-      </c>
-      <c r="BY16">
-        <v>1.01</v>
-      </c>
-      <c r="BZ16">
-        <v>25</v>
-      </c>
       <c r="CA16">
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
         <v>102</v>
@@ -4798,267 +4804,267 @@
         <v>136</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F17">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="G17">
-        <v>5.1</v>
+        <v>2.96</v>
       </c>
       <c r="H17">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="I17">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
+        <v>4.7</v>
+      </c>
+      <c r="L17">
+        <v>1.28</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>4.4</v>
+      </c>
+      <c r="O17">
+        <v>1.25</v>
+      </c>
+      <c r="P17">
+        <v>2.14</v>
+      </c>
+      <c r="Q17">
+        <v>1.74</v>
+      </c>
+      <c r="R17">
+        <v>1.44</v>
+      </c>
+      <c r="S17">
+        <v>2.82</v>
+      </c>
+      <c r="T17">
+        <v>1.52</v>
+      </c>
+      <c r="U17">
+        <v>2.12</v>
+      </c>
+      <c r="V17">
+        <v>1.53</v>
+      </c>
+      <c r="W17">
+        <v>1.51</v>
+      </c>
+      <c r="X17">
+        <v>23</v>
+      </c>
+      <c r="Y17">
+        <v>16.5</v>
+      </c>
+      <c r="Z17">
+        <v>24</v>
+      </c>
+      <c r="AA17">
+        <v>48</v>
+      </c>
+      <c r="AB17">
+        <v>16.5</v>
+      </c>
+      <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>15.5</v>
+      </c>
+      <c r="AE17">
+        <v>34</v>
+      </c>
+      <c r="AF17">
+        <v>24</v>
+      </c>
+      <c r="AG17">
+        <v>15</v>
+      </c>
+      <c r="AH17">
+        <v>19</v>
+      </c>
+      <c r="AI17">
+        <v>44</v>
+      </c>
+      <c r="AJ17">
+        <v>50</v>
+      </c>
+      <c r="AK17">
+        <v>34</v>
+      </c>
+      <c r="AL17">
+        <v>44</v>
+      </c>
+      <c r="AM17">
+        <v>85</v>
+      </c>
+      <c r="AN17">
+        <v>25</v>
+      </c>
+      <c r="AO17">
+        <v>24</v>
+      </c>
+      <c r="AP17">
+        <v>13.5</v>
+      </c>
+      <c r="AQ17">
+        <v>10</v>
+      </c>
+      <c r="AR17">
+        <v>14</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>10</v>
+      </c>
+      <c r="AU17">
+        <v>6.4</v>
+      </c>
+      <c r="AV17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW17">
+        <v>19.5</v>
+      </c>
+      <c r="AX17">
+        <v>14.5</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>11.5</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>20</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>14.5</v>
+      </c>
+      <c r="BG17">
+        <v>14</v>
+      </c>
+      <c r="BH17">
+        <v>4.5</v>
+      </c>
+      <c r="BI17">
+        <v>3</v>
+      </c>
+      <c r="BJ17">
+        <v>11</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>110</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>7.2</v>
+      </c>
+      <c r="BO17">
         <v>4.6</v>
       </c>
-      <c r="L17">
-        <v>1.23</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>5.4</v>
-      </c>
-      <c r="O17">
-        <v>1.17</v>
-      </c>
-      <c r="P17">
-        <v>2.5</v>
-      </c>
-      <c r="Q17">
-        <v>1.53</v>
-      </c>
-      <c r="R17">
-        <v>1.6</v>
-      </c>
-      <c r="S17">
-        <v>2.34</v>
-      </c>
-      <c r="T17">
-        <v>1.47</v>
-      </c>
-      <c r="U17">
-        <v>2.44</v>
-      </c>
-      <c r="V17">
-        <v>1.98</v>
-      </c>
-      <c r="W17">
-        <v>1.24</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17">
-        <v>1.01</v>
-      </c>
-      <c r="AR17">
-        <v>1.01</v>
-      </c>
-      <c r="AS17">
-        <v>1.01</v>
-      </c>
-      <c r="AT17">
-        <v>1.01</v>
-      </c>
-      <c r="AU17">
-        <v>1.01</v>
-      </c>
-      <c r="AV17">
-        <v>1.01</v>
-      </c>
-      <c r="AW17">
-        <v>1.01</v>
-      </c>
-      <c r="AX17">
-        <v>1.01</v>
-      </c>
-      <c r="AY17">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17">
-        <v>1.01</v>
-      </c>
-      <c r="BA17">
-        <v>1.01</v>
-      </c>
-      <c r="BB17">
-        <v>1.01</v>
-      </c>
-      <c r="BC17">
-        <v>1.01</v>
-      </c>
-      <c r="BD17">
-        <v>1.01</v>
-      </c>
-      <c r="BE17">
-        <v>1.01</v>
-      </c>
-      <c r="BF17">
-        <v>1.01</v>
-      </c>
-      <c r="BG17">
-        <v>1.01</v>
-      </c>
-      <c r="BH17">
-        <v>5.2</v>
-      </c>
-      <c r="BI17">
-        <v>3.45</v>
-      </c>
-      <c r="BJ17">
-        <v>10.5</v>
-      </c>
-      <c r="BK17">
-        <v>6.4</v>
-      </c>
-      <c r="BL17">
-        <v>95</v>
-      </c>
-      <c r="BM17">
-        <v>50</v>
-      </c>
-      <c r="BN17">
-        <v>9.4</v>
-      </c>
-      <c r="BO17">
-        <v>5.9</v>
-      </c>
       <c r="BP17">
+        <v>24</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
         <v>36</v>
       </c>
-      <c r="BQ17">
-        <v>20</v>
-      </c>
-      <c r="BR17">
-        <v>40</v>
-      </c>
       <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>7</v>
+      </c>
+      <c r="BU17">
+        <v>4.4</v>
+      </c>
+      <c r="BV17">
         <v>23</v>
       </c>
-      <c r="BT17">
-        <v>6</v>
-      </c>
-      <c r="BU17">
-        <v>3.9</v>
-      </c>
-      <c r="BV17">
-        <v>14.5</v>
-      </c>
       <c r="BW17">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BY17">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="CA17">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
         <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
         <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="H18">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="I18">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="J18">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L18">
         <v>1.23</v>
@@ -5067,205 +5073,205 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O18">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S18">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>1.01</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>1.01</v>
+      </c>
+      <c r="AU18">
+        <v>1.01</v>
+      </c>
+      <c r="AV18">
+        <v>1.01</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>1.01</v>
+      </c>
+      <c r="AY18">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18">
+        <v>1.01</v>
+      </c>
+      <c r="BA18">
+        <v>1.01</v>
+      </c>
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
+        <v>1.01</v>
+      </c>
+      <c r="BD18">
+        <v>1.01</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>5.3</v>
+      </c>
+      <c r="BI18">
+        <v>3.5</v>
+      </c>
+      <c r="BJ18">
+        <v>10.5</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>90</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>9.4</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
         <v>34</v>
       </c>
-      <c r="Y18">
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>40</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>6</v>
+      </c>
+      <c r="BU18">
+        <v>3.9</v>
+      </c>
+      <c r="BV18">
         <v>14.5</v>
       </c>
-      <c r="Z18">
-        <v>14</v>
-      </c>
-      <c r="AA18">
-        <v>18</v>
-      </c>
-      <c r="AB18">
-        <v>36</v>
-      </c>
-      <c r="AC18">
-        <v>14.5</v>
-      </c>
-      <c r="AD18">
-        <v>13</v>
-      </c>
-      <c r="AE18">
-        <v>18</v>
-      </c>
-      <c r="AF18">
-        <v>70</v>
-      </c>
-      <c r="AG18">
-        <v>30</v>
-      </c>
-      <c r="AH18">
-        <v>24</v>
-      </c>
-      <c r="AI18">
-        <v>34</v>
-      </c>
-      <c r="AJ18">
-        <v>170</v>
-      </c>
-      <c r="AK18">
-        <v>80</v>
-      </c>
-      <c r="AL18">
-        <v>70</v>
-      </c>
-      <c r="AM18">
-        <v>85</v>
-      </c>
-      <c r="AN18">
-        <v>70</v>
-      </c>
-      <c r="AO18">
-        <v>6.8</v>
-      </c>
-      <c r="AP18">
-        <v>3.95</v>
-      </c>
-      <c r="AQ18">
-        <v>10.5</v>
-      </c>
-      <c r="AR18">
-        <v>10</v>
-      </c>
-      <c r="AS18">
-        <v>12.5</v>
-      </c>
-      <c r="AT18">
-        <v>4</v>
-      </c>
-      <c r="AU18">
-        <v>10</v>
-      </c>
-      <c r="AV18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW18">
-        <v>12.5</v>
-      </c>
-      <c r="AX18">
-        <v>4.2</v>
-      </c>
-      <c r="AY18">
-        <v>21</v>
-      </c>
-      <c r="AZ18">
-        <v>17</v>
-      </c>
-      <c r="BA18">
-        <v>3.95</v>
-      </c>
-      <c r="BB18">
-        <v>4.4</v>
-      </c>
-      <c r="BC18">
-        <v>4.2</v>
-      </c>
-      <c r="BD18">
-        <v>4.2</v>
-      </c>
-      <c r="BE18">
-        <v>4.2</v>
-      </c>
-      <c r="BF18">
-        <v>4.2</v>
-      </c>
-      <c r="BG18">
-        <v>4.4</v>
-      </c>
-      <c r="BH18">
-        <v>5.4</v>
-      </c>
-      <c r="BI18">
-        <v>3.55</v>
-      </c>
-      <c r="BJ18">
-        <v>12</v>
-      </c>
-      <c r="BK18">
-        <v>7.2</v>
-      </c>
-      <c r="BL18">
-        <v>110</v>
-      </c>
-      <c r="BM18">
-        <v>60</v>
-      </c>
-      <c r="BN18">
-        <v>12.5</v>
-      </c>
-      <c r="BO18">
-        <v>7.4</v>
-      </c>
-      <c r="BP18">
-        <v>60</v>
-      </c>
-      <c r="BQ18">
-        <v>32</v>
-      </c>
-      <c r="BR18">
-        <v>55</v>
-      </c>
-      <c r="BS18">
-        <v>32</v>
-      </c>
-      <c r="BT18">
-        <v>5.2</v>
-      </c>
-      <c r="BU18">
-        <v>3.45</v>
-      </c>
-      <c r="BV18">
-        <v>11</v>
-      </c>
       <c r="BW18">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY18">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5282,7 +5288,7 @@
         <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F19">
         <v>1.1</v>
@@ -5297,7 +5303,7 @@
         <v>110</v>
       </c>
       <c r="J19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K19">
         <v>320</v>
@@ -5333,10 +5339,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5507,7 +5513,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5524,13 +5530,13 @@
         <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F20">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H20">
         <v>3.3</v>
@@ -5557,19 +5563,19 @@
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R20">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S20">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T20">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U20">
         <v>2.72</v>
@@ -5578,19 +5584,19 @@
         <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X20">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="Y20">
         <v>24</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA20">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AB20">
         <v>16.5</v>
@@ -5614,7 +5620,7 @@
         <v>17</v>
       </c>
       <c r="AI20">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ20">
         <v>32</v>
@@ -5635,16 +5641,16 @@
         <v>970</v>
       </c>
       <c r="AP20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR20">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS20">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT20">
         <v>14</v>
@@ -5656,7 +5662,7 @@
         <v>13</v>
       </c>
       <c r="AW20">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX20">
         <v>15.5</v>
@@ -5668,19 +5674,19 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB20">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC20">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD20">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE20">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF20">
         <v>8.199999999999999</v>
@@ -5689,7 +5695,7 @@
         <v>14</v>
       </c>
       <c r="BH20">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI20">
         <v>3.8</v>
@@ -5749,249 +5755,249 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F21">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="G21">
-        <v>1.72</v>
+        <v>7.8</v>
       </c>
       <c r="H21">
-        <v>5.5</v>
+        <v>1.52</v>
       </c>
       <c r="I21">
-        <v>5.9</v>
+        <v>1.61</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="K21">
+        <v>5.3</v>
+      </c>
+      <c r="L21">
+        <v>1.23</v>
+      </c>
+      <c r="M21">
+        <v>1.02</v>
+      </c>
+      <c r="N21">
+        <v>5.7</v>
+      </c>
+      <c r="O21">
+        <v>1.18</v>
+      </c>
+      <c r="P21">
+        <v>2.58</v>
+      </c>
+      <c r="Q21">
+        <v>1.52</v>
+      </c>
+      <c r="R21">
+        <v>1.64</v>
+      </c>
+      <c r="S21">
+        <v>2.28</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.01</v>
+      </c>
+      <c r="V21">
+        <v>2.64</v>
+      </c>
+      <c r="W21">
+        <v>1.15</v>
+      </c>
+      <c r="X21">
+        <v>34</v>
+      </c>
+      <c r="Y21">
+        <v>14.5</v>
+      </c>
+      <c r="Z21">
+        <v>14</v>
+      </c>
+      <c r="AA21">
+        <v>18</v>
+      </c>
+      <c r="AB21">
+        <v>36</v>
+      </c>
+      <c r="AC21">
+        <v>14.5</v>
+      </c>
+      <c r="AD21">
+        <v>13</v>
+      </c>
+      <c r="AE21">
+        <v>18</v>
+      </c>
+      <c r="AF21">
+        <v>70</v>
+      </c>
+      <c r="AG21">
+        <v>30</v>
+      </c>
+      <c r="AH21">
+        <v>24</v>
+      </c>
+      <c r="AI21">
+        <v>34</v>
+      </c>
+      <c r="AJ21">
+        <v>160</v>
+      </c>
+      <c r="AK21">
+        <v>80</v>
+      </c>
+      <c r="AL21">
+        <v>65</v>
+      </c>
+      <c r="AM21">
+        <v>85</v>
+      </c>
+      <c r="AN21">
+        <v>70</v>
+      </c>
+      <c r="AO21">
+        <v>6.8</v>
+      </c>
+      <c r="AP21">
+        <v>4</v>
+      </c>
+      <c r="AQ21">
+        <v>10.5</v>
+      </c>
+      <c r="AR21">
+        <v>10</v>
+      </c>
+      <c r="AS21">
+        <v>12.5</v>
+      </c>
+      <c r="AT21">
+        <v>4</v>
+      </c>
+      <c r="AU21">
+        <v>10</v>
+      </c>
+      <c r="AV21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW21">
+        <v>12.5</v>
+      </c>
+      <c r="AX21">
+        <v>4.2</v>
+      </c>
+      <c r="AY21">
+        <v>21</v>
+      </c>
+      <c r="AZ21">
+        <v>17</v>
+      </c>
+      <c r="BA21">
+        <v>4</v>
+      </c>
+      <c r="BB21">
         <v>4.4</v>
       </c>
-      <c r="L21">
-        <v>1.31</v>
-      </c>
-      <c r="M21">
-        <v>1.06</v>
-      </c>
-      <c r="N21">
+      <c r="BC21">
+        <v>4.3</v>
+      </c>
+      <c r="BD21">
         <v>4.2</v>
       </c>
-      <c r="O21">
-        <v>1.25</v>
-      </c>
-      <c r="P21">
-        <v>2.18</v>
-      </c>
-      <c r="Q21">
-        <v>1.76</v>
-      </c>
-      <c r="R21">
-        <v>1.46</v>
-      </c>
-      <c r="S21">
-        <v>2.92</v>
-      </c>
-      <c r="T21">
-        <v>1.7</v>
-      </c>
-      <c r="U21">
-        <v>2.1</v>
-      </c>
-      <c r="V21">
-        <v>1.19</v>
-      </c>
-      <c r="W21">
-        <v>2.34</v>
-      </c>
-      <c r="X21">
-        <v>19.5</v>
-      </c>
-      <c r="Y21">
-        <v>22</v>
-      </c>
-      <c r="Z21">
+      <c r="BE21">
+        <v>4.3</v>
+      </c>
+      <c r="BF21">
+        <v>4.2</v>
+      </c>
+      <c r="BG21">
+        <v>4.4</v>
+      </c>
+      <c r="BH21">
+        <v>5.4</v>
+      </c>
+      <c r="BI21">
+        <v>3.55</v>
+      </c>
+      <c r="BJ21">
+        <v>12</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>110</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>12.5</v>
+      </c>
+      <c r="BO21">
+        <v>1.01</v>
+      </c>
+      <c r="BP21">
+        <v>60</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
         <v>55</v>
       </c>
-      <c r="AA21">
-        <v>170</v>
-      </c>
-      <c r="AB21">
-        <v>10</v>
-      </c>
-      <c r="AC21">
-        <v>9.6</v>
-      </c>
-      <c r="AD21">
-        <v>23</v>
-      </c>
-      <c r="AE21">
-        <v>100</v>
-      </c>
-      <c r="AF21">
-        <v>11.5</v>
-      </c>
-      <c r="AG21">
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>5.2</v>
+      </c>
+      <c r="BU21">
+        <v>3.45</v>
+      </c>
+      <c r="BV21">
         <v>11</v>
       </c>
-      <c r="AH21">
-        <v>20</v>
-      </c>
-      <c r="AI21">
-        <v>85</v>
-      </c>
-      <c r="AJ21">
-        <v>18</v>
-      </c>
-      <c r="AK21">
-        <v>18.5</v>
-      </c>
-      <c r="AL21">
-        <v>36</v>
-      </c>
-      <c r="AM21">
-        <v>110</v>
-      </c>
-      <c r="AN21">
-        <v>9.6</v>
-      </c>
-      <c r="AO21">
-        <v>95</v>
-      </c>
-      <c r="AP21">
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>24</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
         <v>14.5</v>
       </c>
-      <c r="AQ21">
-        <v>17.5</v>
-      </c>
-      <c r="AR21">
-        <v>7.2</v>
-      </c>
-      <c r="AS21">
-        <v>8</v>
-      </c>
-      <c r="AT21">
-        <v>8</v>
-      </c>
-      <c r="AU21">
-        <v>8</v>
-      </c>
-      <c r="AV21">
-        <v>18.5</v>
-      </c>
-      <c r="AW21">
-        <v>7.6</v>
-      </c>
-      <c r="AX21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY21">
-        <v>8.6</v>
-      </c>
-      <c r="AZ21">
-        <v>5.9</v>
-      </c>
-      <c r="BA21">
-        <v>7.6</v>
-      </c>
-      <c r="BB21">
-        <v>14.5</v>
-      </c>
-      <c r="BC21">
-        <v>14.5</v>
-      </c>
-      <c r="BD21">
-        <v>6.8</v>
-      </c>
-      <c r="BE21">
-        <v>7.8</v>
-      </c>
-      <c r="BF21">
-        <v>8</v>
-      </c>
-      <c r="BG21">
-        <v>7.6</v>
-      </c>
-      <c r="BH21">
-        <v>4.2</v>
-      </c>
-      <c r="BI21">
-        <v>3.05</v>
-      </c>
-      <c r="BJ21">
-        <v>11.5</v>
-      </c>
-      <c r="BK21">
-        <v>7.8</v>
-      </c>
-      <c r="BL21">
-        <v>140</v>
-      </c>
-      <c r="BM21">
-        <v>1.01</v>
-      </c>
-      <c r="BN21">
-        <v>4.9</v>
-      </c>
-      <c r="BO21">
-        <v>3.5</v>
-      </c>
-      <c r="BP21">
-        <v>12.5</v>
-      </c>
-      <c r="BQ21">
-        <v>8.4</v>
-      </c>
-      <c r="BR21">
-        <v>28</v>
-      </c>
-      <c r="BS21">
-        <v>18.5</v>
-      </c>
-      <c r="BT21">
-        <v>10.5</v>
-      </c>
-      <c r="BU21">
-        <v>7</v>
-      </c>
-      <c r="BV21">
-        <v>55</v>
-      </c>
-      <c r="BW21">
-        <v>34</v>
-      </c>
-      <c r="BX21">
-        <v>60</v>
-      </c>
-      <c r="BY21">
-        <v>36</v>
-      </c>
-      <c r="BZ21">
-        <v>21</v>
-      </c>
       <c r="CA21">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6008,237 +6014,237 @@
         <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F22">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="I22">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="J22">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="K22">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P22">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="Q22">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="T22">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="U22">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
-        <v>2.8</v>
+        <v>1.89</v>
       </c>
       <c r="X22">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Y22">
+        <v>20</v>
+      </c>
+      <c r="Z22">
         <v>34</v>
       </c>
-      <c r="Z22">
-        <v>75</v>
-      </c>
       <c r="AA22">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AB22">
         <v>13.5</v>
       </c>
       <c r="AC22">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD22">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AE22">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AF22">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AI22">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AJ22">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AK22">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AL22">
         <v>36</v>
       </c>
       <c r="AM22">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN22">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AO22">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AP22">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="AQ22">
-        <v>3.95</v>
+        <v>13.5</v>
       </c>
       <c r="AR22">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="AW22">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AY22">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA22">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD22">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
         <v>102</v>
@@ -6250,232 +6256,232 @@
         <v>142</v>
       </c>
       <c r="E23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F23">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G23">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="H23">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I23">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J23">
+        <v>4.1</v>
+      </c>
+      <c r="K23">
         <v>4.4</v>
       </c>
-      <c r="K23">
-        <v>5.1</v>
-      </c>
       <c r="L23">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="Q23">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="R23">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="S23">
-        <v>2.18</v>
+        <v>2.92</v>
       </c>
       <c r="T23">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="U23">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W23">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X23">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="Y23">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Z23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA23">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AB23">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD23">
         <v>23</v>
       </c>
       <c r="AE23">
+        <v>100</v>
+      </c>
+      <c r="AF23">
+        <v>11.5</v>
+      </c>
+      <c r="AG23">
+        <v>11</v>
+      </c>
+      <c r="AH23">
+        <v>20</v>
+      </c>
+      <c r="AI23">
+        <v>85</v>
+      </c>
+      <c r="AJ23">
+        <v>18</v>
+      </c>
+      <c r="AK23">
+        <v>18</v>
+      </c>
+      <c r="AL23">
+        <v>36</v>
+      </c>
+      <c r="AM23">
+        <v>110</v>
+      </c>
+      <c r="AN23">
+        <v>9.6</v>
+      </c>
+      <c r="AO23">
+        <v>100</v>
+      </c>
+      <c r="AP23">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23">
+        <v>17.5</v>
+      </c>
+      <c r="AR23">
+        <v>7.2</v>
+      </c>
+      <c r="AS23">
+        <v>8</v>
+      </c>
+      <c r="AT23">
+        <v>8</v>
+      </c>
+      <c r="AU23">
+        <v>8</v>
+      </c>
+      <c r="AV23">
+        <v>18.5</v>
+      </c>
+      <c r="AW23">
+        <v>7.6</v>
+      </c>
+      <c r="AX23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY23">
+        <v>8.6</v>
+      </c>
+      <c r="AZ23">
+        <v>5.9</v>
+      </c>
+      <c r="BA23">
+        <v>7.6</v>
+      </c>
+      <c r="BB23">
+        <v>14.5</v>
+      </c>
+      <c r="BC23">
+        <v>14.5</v>
+      </c>
+      <c r="BD23">
+        <v>6.8</v>
+      </c>
+      <c r="BE23">
+        <v>7.8</v>
+      </c>
+      <c r="BF23">
+        <v>8</v>
+      </c>
+      <c r="BG23">
+        <v>7.8</v>
+      </c>
+      <c r="BH23">
+        <v>4.2</v>
+      </c>
+      <c r="BI23">
+        <v>3.05</v>
+      </c>
+      <c r="BJ23">
+        <v>11.5</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>140</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>4.9</v>
+      </c>
+      <c r="BO23">
+        <v>3.5</v>
+      </c>
+      <c r="BP23">
+        <v>12.5</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>28</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>10.5</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
         <v>55</v>
       </c>
-      <c r="AF23">
-        <v>15.5</v>
-      </c>
-      <c r="AG23">
-        <v>12.5</v>
-      </c>
-      <c r="AH23">
-        <v>18</v>
-      </c>
-      <c r="AI23">
-        <v>55</v>
-      </c>
-      <c r="AJ23">
-        <v>19</v>
-      </c>
-      <c r="AK23">
-        <v>16.5</v>
-      </c>
-      <c r="AL23">
-        <v>29</v>
-      </c>
-      <c r="AM23">
-        <v>70</v>
-      </c>
-      <c r="AN23">
-        <v>6.6</v>
-      </c>
-      <c r="AO23">
-        <v>42</v>
-      </c>
-      <c r="AP23">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23">
-        <v>1.01</v>
-      </c>
-      <c r="AR23">
-        <v>1.01</v>
-      </c>
-      <c r="AS23">
-        <v>1.01</v>
-      </c>
-      <c r="AT23">
-        <v>11.5</v>
-      </c>
-      <c r="AU23">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV23">
-        <v>17</v>
-      </c>
-      <c r="AW23">
-        <v>1.01</v>
-      </c>
-      <c r="AX23">
-        <v>11.5</v>
-      </c>
-      <c r="AY23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23">
-        <v>13</v>
-      </c>
-      <c r="BA23">
-        <v>1.01</v>
-      </c>
-      <c r="BB23">
-        <v>13.5</v>
-      </c>
-      <c r="BC23">
-        <v>12</v>
-      </c>
-      <c r="BD23">
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>60</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
         <v>21</v>
       </c>
-      <c r="BE23">
-        <v>1.01</v>
-      </c>
-      <c r="BF23">
-        <v>5.4</v>
-      </c>
-      <c r="BG23">
-        <v>1.01</v>
-      </c>
-      <c r="BH23">
-        <v>5.4</v>
-      </c>
-      <c r="BI23">
-        <v>3.85</v>
-      </c>
-      <c r="BJ23">
-        <v>10.5</v>
-      </c>
-      <c r="BK23">
-        <v>1.01</v>
-      </c>
-      <c r="BL23">
-        <v>85</v>
-      </c>
-      <c r="BM23">
-        <v>1.01</v>
-      </c>
-      <c r="BN23">
-        <v>5.5</v>
-      </c>
-      <c r="BO23">
-        <v>3.9</v>
-      </c>
-      <c r="BP23">
-        <v>12</v>
-      </c>
-      <c r="BQ23">
-        <v>1.01</v>
-      </c>
-      <c r="BR23">
-        <v>22</v>
-      </c>
-      <c r="BS23">
-        <v>1.01</v>
-      </c>
-      <c r="BT23">
-        <v>10</v>
-      </c>
-      <c r="BU23">
-        <v>1.01</v>
-      </c>
-      <c r="BV23">
-        <v>38</v>
-      </c>
-      <c r="BW23">
-        <v>1.01</v>
-      </c>
-      <c r="BX23">
-        <v>40</v>
-      </c>
-      <c r="BY23">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23">
-        <v>14</v>
-      </c>
       <c r="CA23">
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6492,237 +6498,237 @@
         <v>143</v>
       </c>
       <c r="E24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F24">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="G24">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="H24">
-        <v>2.64</v>
+        <v>6.6</v>
       </c>
       <c r="I24">
-        <v>2.84</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L24">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="R24">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="S24">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="T24">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="U24">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="W24">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="X24">
+        <v>30</v>
+      </c>
+      <c r="Y24">
+        <v>34</v>
+      </c>
+      <c r="Z24">
+        <v>75</v>
+      </c>
+      <c r="AA24">
+        <v>220</v>
+      </c>
+      <c r="AB24">
+        <v>13.5</v>
+      </c>
+      <c r="AC24">
+        <v>14</v>
+      </c>
+      <c r="AD24">
         <v>32</v>
       </c>
-      <c r="Y24">
-        <v>18.5</v>
-      </c>
-      <c r="Z24">
-        <v>28</v>
-      </c>
-      <c r="AA24">
-        <v>48</v>
-      </c>
-      <c r="AB24">
+      <c r="AE24">
+        <v>110</v>
+      </c>
+      <c r="AF24">
+        <v>13</v>
+      </c>
+      <c r="AG24">
+        <v>12.5</v>
+      </c>
+      <c r="AH24">
+        <v>25</v>
+      </c>
+      <c r="AI24">
+        <v>90</v>
+      </c>
+      <c r="AJ24">
         <v>17.5</v>
       </c>
-      <c r="AC24">
+      <c r="AK24">
+        <v>18</v>
+      </c>
+      <c r="AL24">
+        <v>36</v>
+      </c>
+      <c r="AM24">
+        <v>110</v>
+      </c>
+      <c r="AN24">
+        <v>7</v>
+      </c>
+      <c r="AO24">
+        <v>100</v>
+      </c>
+      <c r="AP24">
+        <v>3.9</v>
+      </c>
+      <c r="AQ24">
+        <v>3.95</v>
+      </c>
+      <c r="AR24">
+        <v>4.2</v>
+      </c>
+      <c r="AS24">
+        <v>4.3</v>
+      </c>
+      <c r="AT24">
+        <v>9.6</v>
+      </c>
+      <c r="AU24">
+        <v>10</v>
+      </c>
+      <c r="AV24">
+        <v>3.9</v>
+      </c>
+      <c r="AW24">
+        <v>4.3</v>
+      </c>
+      <c r="AX24">
+        <v>9.4</v>
+      </c>
+      <c r="AY24">
+        <v>9</v>
+      </c>
+      <c r="AZ24">
+        <v>3.8</v>
+      </c>
+      <c r="BA24">
+        <v>4.2</v>
+      </c>
+      <c r="BB24">
         <v>12.5</v>
       </c>
-      <c r="AD24">
-        <v>14</v>
-      </c>
-      <c r="AE24">
-        <v>27</v>
-      </c>
-      <c r="AF24">
+      <c r="BC24">
+        <v>13</v>
+      </c>
+      <c r="BD24">
+        <v>3.95</v>
+      </c>
+      <c r="BE24">
+        <v>4.3</v>
+      </c>
+      <c r="BF24">
+        <v>4.7</v>
+      </c>
+      <c r="BG24">
+        <v>4.2</v>
+      </c>
+      <c r="BH24">
+        <v>5.1</v>
+      </c>
+      <c r="BI24">
+        <v>3.35</v>
+      </c>
+      <c r="BJ24">
+        <v>12</v>
+      </c>
+      <c r="BK24">
+        <v>7.4</v>
+      </c>
+      <c r="BL24">
+        <v>130</v>
+      </c>
+      <c r="BM24">
+        <v>70</v>
+      </c>
+      <c r="BN24">
+        <v>5.1</v>
+      </c>
+      <c r="BO24">
+        <v>3.35</v>
+      </c>
+      <c r="BP24">
+        <v>11</v>
+      </c>
+      <c r="BQ24">
+        <v>6.8</v>
+      </c>
+      <c r="BR24">
         <v>26</v>
       </c>
-      <c r="AG24">
-        <v>15.5</v>
-      </c>
-      <c r="AH24">
-        <v>17.5</v>
-      </c>
-      <c r="AI24">
-        <v>32</v>
-      </c>
-      <c r="AJ24">
+      <c r="BS24">
+        <v>15</v>
+      </c>
+      <c r="BT24">
+        <v>12.5</v>
+      </c>
+      <c r="BU24">
+        <v>7.6</v>
+      </c>
+      <c r="BV24">
+        <v>65</v>
+      </c>
+      <c r="BW24">
         <v>36</v>
       </c>
-      <c r="AK24">
-        <v>28</v>
-      </c>
-      <c r="AL24">
+      <c r="BX24">
+        <v>60</v>
+      </c>
+      <c r="BY24">
         <v>34</v>
       </c>
-      <c r="AM24">
-        <v>60</v>
-      </c>
-      <c r="AN24">
-        <v>15</v>
-      </c>
-      <c r="AO24">
-        <v>15</v>
-      </c>
-      <c r="AP24">
-        <v>19</v>
-      </c>
-      <c r="AQ24">
-        <v>12.5</v>
-      </c>
-      <c r="AR24">
+      <c r="BZ24">
         <v>16</v>
       </c>
-      <c r="AS24">
-        <v>1.01</v>
-      </c>
-      <c r="AT24">
-        <v>12</v>
-      </c>
-      <c r="AU24">
-        <v>8.6</v>
-      </c>
-      <c r="AV24">
-        <v>11</v>
-      </c>
-      <c r="AW24">
-        <v>21</v>
-      </c>
-      <c r="AX24">
-        <v>15</v>
-      </c>
-      <c r="AY24">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24">
-        <v>12</v>
-      </c>
-      <c r="BA24">
-        <v>1.01</v>
-      </c>
-      <c r="BB24">
-        <v>1.01</v>
-      </c>
-      <c r="BC24">
-        <v>20</v>
-      </c>
-      <c r="BD24">
-        <v>1.01</v>
-      </c>
-      <c r="BE24">
-        <v>1.01</v>
-      </c>
-      <c r="BF24">
+      <c r="CA24">
         <v>9.6</v>
       </c>
-      <c r="BG24">
-        <v>12</v>
-      </c>
-      <c r="BH24">
-        <v>5.4</v>
-      </c>
-      <c r="BI24">
-        <v>3.55</v>
-      </c>
-      <c r="BJ24">
-        <v>10</v>
-      </c>
-      <c r="BK24">
-        <v>1.01</v>
-      </c>
-      <c r="BL24">
-        <v>85</v>
-      </c>
-      <c r="BM24">
-        <v>1.01</v>
-      </c>
-      <c r="BN24">
-        <v>7.2</v>
-      </c>
-      <c r="BO24">
-        <v>4.6</v>
-      </c>
-      <c r="BP24">
-        <v>21</v>
-      </c>
-      <c r="BQ24">
-        <v>1.01</v>
-      </c>
-      <c r="BR24">
-        <v>29</v>
-      </c>
-      <c r="BS24">
-        <v>1.01</v>
-      </c>
-      <c r="BT24">
-        <v>7.6</v>
-      </c>
-      <c r="BU24">
-        <v>4.8</v>
-      </c>
-      <c r="BV24">
-        <v>22</v>
-      </c>
-      <c r="BW24">
-        <v>1.01</v>
-      </c>
-      <c r="BX24">
-        <v>29</v>
-      </c>
-      <c r="BY24">
-        <v>1.01</v>
-      </c>
-      <c r="BZ24">
-        <v>18</v>
-      </c>
-      <c r="CA24">
-        <v>1.01</v>
-      </c>
       <c r="CB24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>102</v>
@@ -6734,479 +6740,479 @@
         <v>144</v>
       </c>
       <c r="E25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F25">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="G25">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="H25">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I25">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="J25">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="K25">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M25">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="P25">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="S25">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="T25">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V25">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="X25">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Y25">
+        <v>30</v>
+      </c>
+      <c r="Z25">
+        <v>50</v>
+      </c>
+      <c r="AA25">
+        <v>120</v>
+      </c>
+      <c r="AB25">
+        <v>16</v>
+      </c>
+      <c r="AC25">
+        <v>13.5</v>
+      </c>
+      <c r="AD25">
         <v>21</v>
       </c>
-      <c r="Z25">
-        <v>34</v>
-      </c>
-      <c r="AA25">
-        <v>80</v>
-      </c>
-      <c r="AB25">
-        <v>14</v>
-      </c>
-      <c r="AC25">
-        <v>11</v>
-      </c>
-      <c r="AD25">
-        <v>18.5</v>
-      </c>
       <c r="AE25">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF25">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG25">
         <v>12.5</v>
       </c>
       <c r="AH25">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI25">
         <v>55</v>
       </c>
       <c r="AJ25">
+        <v>19</v>
+      </c>
+      <c r="AK25">
+        <v>16.5</v>
+      </c>
+      <c r="AL25">
         <v>28</v>
       </c>
-      <c r="AK25">
-        <v>23</v>
-      </c>
-      <c r="AL25">
-        <v>36</v>
-      </c>
       <c r="AM25">
+        <v>70</v>
+      </c>
+      <c r="AN25">
+        <v>6.6</v>
+      </c>
+      <c r="AO25">
+        <v>38</v>
+      </c>
+      <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>11.5</v>
+      </c>
+      <c r="AU25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV25">
+        <v>17</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>11.5</v>
+      </c>
+      <c r="AY25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25">
+        <v>13</v>
+      </c>
+      <c r="BA25">
+        <v>1.01</v>
+      </c>
+      <c r="BB25">
+        <v>13.5</v>
+      </c>
+      <c r="BC25">
+        <v>12</v>
+      </c>
+      <c r="BD25">
+        <v>21</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>5.4</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>5.5</v>
+      </c>
+      <c r="BI25">
+        <v>3.9</v>
+      </c>
+      <c r="BJ25">
+        <v>10.5</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
         <v>85</v>
       </c>
-      <c r="AN25">
-        <v>13.5</v>
-      </c>
-      <c r="AO25">
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>5.5</v>
+      </c>
+      <c r="BO25">
+        <v>3.9</v>
+      </c>
+      <c r="BP25">
+        <v>12</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>22</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>10.5</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>38</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
         <v>40</v>
       </c>
-      <c r="AP25">
-        <v>15</v>
-      </c>
-      <c r="AQ25">
-        <v>13.5</v>
-      </c>
-      <c r="AR25">
-        <v>22</v>
-      </c>
-      <c r="AS25">
-        <v>50</v>
-      </c>
-      <c r="AT25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU25">
-        <v>7.2</v>
-      </c>
-      <c r="AV25">
-        <v>12</v>
-      </c>
-      <c r="AW25">
-        <v>30</v>
-      </c>
-      <c r="AX25">
-        <v>11</v>
-      </c>
-      <c r="AY25">
-        <v>8.4</v>
-      </c>
-      <c r="AZ25">
-        <v>12.5</v>
-      </c>
-      <c r="BA25">
-        <v>32</v>
-      </c>
-      <c r="BB25">
-        <v>18.5</v>
-      </c>
-      <c r="BC25">
-        <v>15</v>
-      </c>
-      <c r="BD25">
-        <v>22</v>
-      </c>
-      <c r="BE25">
-        <v>50</v>
-      </c>
-      <c r="BF25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG25">
-        <v>25</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.01</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.01</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.01</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>1.01</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.01</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>1.01</v>
-      </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
-        <v>1.01</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>1.01</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
         <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
         <v>145</v>
       </c>
       <c r="E26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F26">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="G26">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="H26">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="I26">
+        <v>2.84</v>
+      </c>
+      <c r="J26">
+        <v>3.9</v>
+      </c>
+      <c r="K26">
+        <v>4.6</v>
+      </c>
+      <c r="L26">
+        <v>1.23</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="N26">
+        <v>5.8</v>
+      </c>
+      <c r="O26">
+        <v>1.17</v>
+      </c>
+      <c r="P26">
+        <v>2.62</v>
+      </c>
+      <c r="Q26">
+        <v>1.52</v>
+      </c>
+      <c r="R26">
+        <v>1.65</v>
+      </c>
+      <c r="S26">
         <v>2.28</v>
       </c>
-      <c r="J26">
-        <v>3.5</v>
-      </c>
-      <c r="K26">
-        <v>3.55</v>
-      </c>
-      <c r="L26">
-        <v>1.36</v>
-      </c>
-      <c r="M26">
-        <v>1.08</v>
-      </c>
-      <c r="N26">
-        <v>3.45</v>
-      </c>
-      <c r="O26">
-        <v>1.37</v>
-      </c>
-      <c r="P26">
-        <v>1.83</v>
-      </c>
-      <c r="Q26">
-        <v>2.12</v>
-      </c>
-      <c r="R26">
-        <v>1.32</v>
-      </c>
-      <c r="S26">
-        <v>3.9</v>
-      </c>
       <c r="T26">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="U26">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="V26">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="W26">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="X26">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="Y26">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="Z26">
+        <v>28</v>
+      </c>
+      <c r="AA26">
+        <v>42</v>
+      </c>
+      <c r="AB26">
+        <v>17.5</v>
+      </c>
+      <c r="AC26">
+        <v>12.5</v>
+      </c>
+      <c r="AD26">
         <v>14</v>
-      </c>
-      <c r="AA26">
-        <v>32</v>
-      </c>
-      <c r="AB26">
-        <v>12.5</v>
-      </c>
-      <c r="AC26">
-        <v>7.8</v>
-      </c>
-      <c r="AD26">
-        <v>11.5</v>
       </c>
       <c r="AE26">
         <v>27</v>
       </c>
       <c r="AF26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG26">
+        <v>15.5</v>
+      </c>
+      <c r="AH26">
+        <v>17.5</v>
+      </c>
+      <c r="AI26">
+        <v>32</v>
+      </c>
+      <c r="AJ26">
+        <v>36</v>
+      </c>
+      <c r="AK26">
+        <v>28</v>
+      </c>
+      <c r="AL26">
+        <v>34</v>
+      </c>
+      <c r="AM26">
+        <v>60</v>
+      </c>
+      <c r="AN26">
         <v>15</v>
       </c>
-      <c r="AH26">
-        <v>18.5</v>
-      </c>
-      <c r="AI26">
-        <v>50</v>
-      </c>
-      <c r="AJ26">
-        <v>75</v>
-      </c>
-      <c r="AK26">
-        <v>46</v>
-      </c>
-      <c r="AL26">
-        <v>60</v>
-      </c>
-      <c r="AM26">
-        <v>110</v>
-      </c>
-      <c r="AN26">
-        <v>50</v>
-      </c>
       <c r="AO26">
+        <v>15</v>
+      </c>
+      <c r="AP26">
+        <v>19</v>
+      </c>
+      <c r="AQ26">
+        <v>12.5</v>
+      </c>
+      <c r="AR26">
+        <v>16</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>12</v>
+      </c>
+      <c r="AU26">
+        <v>8.6</v>
+      </c>
+      <c r="AV26">
+        <v>11</v>
+      </c>
+      <c r="AW26">
+        <v>21</v>
+      </c>
+      <c r="AX26">
+        <v>17.5</v>
+      </c>
+      <c r="AY26">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26">
+        <v>12</v>
+      </c>
+      <c r="BA26">
+        <v>1.01</v>
+      </c>
+      <c r="BB26">
+        <v>1.01</v>
+      </c>
+      <c r="BC26">
         <v>20</v>
       </c>
-      <c r="AP26">
-        <v>11.5</v>
-      </c>
-      <c r="AQ26">
-        <v>8.6</v>
-      </c>
-      <c r="AR26">
-        <v>12.5</v>
-      </c>
-      <c r="AS26">
-        <v>26</v>
-      </c>
-      <c r="AT26">
-        <v>11.5</v>
-      </c>
-      <c r="AU26">
+      <c r="BD26">
+        <v>1.01</v>
+      </c>
+      <c r="BE26">
+        <v>1.01</v>
+      </c>
+      <c r="BF26">
+        <v>9.6</v>
+      </c>
+      <c r="BG26">
+        <v>12</v>
+      </c>
+      <c r="BH26">
+        <v>5.4</v>
+      </c>
+      <c r="BI26">
+        <v>3.55</v>
+      </c>
+      <c r="BJ26">
+        <v>10</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>85</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
         <v>7.2</v>
       </c>
-      <c r="AV26">
-        <v>10</v>
-      </c>
-      <c r="AW26">
-        <v>23</v>
-      </c>
-      <c r="AX26">
+      <c r="BO26">
+        <v>4.6</v>
+      </c>
+      <c r="BP26">
+        <v>21</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>28</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>7.6</v>
+      </c>
+      <c r="BU26">
+        <v>4.8</v>
+      </c>
+      <c r="BV26">
         <v>22</v>
       </c>
-      <c r="AY26">
-        <v>13.5</v>
-      </c>
-      <c r="AZ26">
-        <v>17</v>
-      </c>
-      <c r="BA26">
-        <v>14</v>
-      </c>
-      <c r="BB26">
-        <v>60</v>
-      </c>
-      <c r="BC26">
-        <v>40</v>
-      </c>
-      <c r="BD26">
-        <v>50</v>
-      </c>
-      <c r="BE26">
-        <v>15</v>
-      </c>
-      <c r="BF26">
-        <v>40</v>
-      </c>
-      <c r="BG26">
-        <v>17.5</v>
-      </c>
-      <c r="BH26">
-        <v>3.75</v>
-      </c>
-      <c r="BI26">
-        <v>2.6</v>
-      </c>
-      <c r="BJ26">
-        <v>12</v>
-      </c>
-      <c r="BK26">
-        <v>1.01</v>
-      </c>
-      <c r="BL26">
-        <v>160</v>
-      </c>
-      <c r="BM26">
-        <v>1.01</v>
-      </c>
-      <c r="BN26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO26">
-        <v>5.1</v>
-      </c>
-      <c r="BP26">
-        <v>38</v>
-      </c>
-      <c r="BQ26">
-        <v>1.01</v>
-      </c>
-      <c r="BR26">
-        <v>55</v>
-      </c>
-      <c r="BS26">
-        <v>1.01</v>
-      </c>
-      <c r="BT26">
-        <v>5.9</v>
-      </c>
-      <c r="BU26">
-        <v>3.85</v>
-      </c>
-      <c r="BV26">
-        <v>21</v>
-      </c>
       <c r="BW26">
         <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
         <v>102</v>
@@ -7218,223 +7224,223 @@
         <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F27">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G27">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="H27">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="I27">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="J27">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K27">
         <v>3.55</v>
       </c>
       <c r="L27">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
+        <v>3.5</v>
+      </c>
+      <c r="O27">
+        <v>1.37</v>
+      </c>
+      <c r="P27">
+        <v>1.85</v>
+      </c>
+      <c r="Q27">
+        <v>2.12</v>
+      </c>
+      <c r="R27">
+        <v>1.32</v>
+      </c>
+      <c r="S27">
         <v>3.9</v>
       </c>
-      <c r="O27">
-        <v>1.29</v>
-      </c>
-      <c r="P27">
-        <v>2</v>
-      </c>
-      <c r="Q27">
-        <v>1.86</v>
-      </c>
-      <c r="R27">
-        <v>1.4</v>
-      </c>
-      <c r="S27">
-        <v>3.15</v>
-      </c>
       <c r="T27">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="U27">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="W27">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="X27">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y27">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="Z27">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AA27">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AB27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC27">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE27">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AF27">
+        <v>25</v>
+      </c>
+      <c r="AG27">
+        <v>15</v>
+      </c>
+      <c r="AH27">
+        <v>18.5</v>
+      </c>
+      <c r="AI27">
+        <v>42</v>
+      </c>
+      <c r="AJ27">
+        <v>70</v>
+      </c>
+      <c r="AK27">
+        <v>46</v>
+      </c>
+      <c r="AL27">
+        <v>60</v>
+      </c>
+      <c r="AM27">
+        <v>110</v>
+      </c>
+      <c r="AN27">
+        <v>50</v>
+      </c>
+      <c r="AO27">
         <v>20</v>
       </c>
-      <c r="AG27">
+      <c r="AP27">
+        <v>11.5</v>
+      </c>
+      <c r="AQ27">
+        <v>8.6</v>
+      </c>
+      <c r="AR27">
         <v>12.5</v>
       </c>
-      <c r="AH27">
-        <v>19</v>
-      </c>
-      <c r="AI27">
-        <v>50</v>
-      </c>
-      <c r="AJ27">
-        <v>40</v>
-      </c>
-      <c r="AK27">
-        <v>27</v>
-      </c>
-      <c r="AL27">
-        <v>44</v>
-      </c>
-      <c r="AM27">
-        <v>80</v>
-      </c>
-      <c r="AN27">
-        <v>23</v>
-      </c>
-      <c r="AO27">
-        <v>29</v>
-      </c>
-      <c r="AP27">
-        <v>13.5</v>
-      </c>
-      <c r="AQ27">
-        <v>10.5</v>
-      </c>
-      <c r="AR27">
-        <v>17</v>
-      </c>
       <c r="AS27">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="AT27">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU27">
         <v>7.2</v>
       </c>
       <c r="AV27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW27">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AX27">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AY27">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ27">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA27">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BB27">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="BC27">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BD27">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="BE27">
-        <v>7.8</v>
+        <v>95</v>
       </c>
       <c r="BF27">
-        <v>6.4</v>
+        <v>42</v>
       </c>
       <c r="BG27">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH27">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BI27">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="BJ27">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK27">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="BM27">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BN27">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO27">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP27">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BQ27">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BS27">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU27">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV27">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BW27">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY27">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7443,254 +7449,254 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>147</v>
       </c>
       <c r="E28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F28">
+        <v>2.62</v>
+      </c>
+      <c r="G28">
+        <v>2.74</v>
+      </c>
+      <c r="H28">
+        <v>2.82</v>
+      </c>
+      <c r="I28">
+        <v>2.96</v>
+      </c>
+      <c r="J28">
+        <v>3.5</v>
+      </c>
+      <c r="K28">
+        <v>3.55</v>
+      </c>
+      <c r="L28">
+        <v>1.35</v>
+      </c>
+      <c r="M28">
+        <v>1.06</v>
+      </c>
+      <c r="N28">
+        <v>3.9</v>
+      </c>
+      <c r="O28">
+        <v>1.29</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="Q28">
         <v>1.86</v>
       </c>
-      <c r="G28">
-        <v>2.04</v>
-      </c>
-      <c r="H28">
-        <v>4.2</v>
-      </c>
-      <c r="I28">
-        <v>5</v>
-      </c>
-      <c r="J28">
-        <v>3.6</v>
-      </c>
-      <c r="K28">
-        <v>4</v>
-      </c>
-      <c r="L28">
-        <v>1.31</v>
-      </c>
-      <c r="M28">
-        <v>1.07</v>
-      </c>
-      <c r="N28">
-        <v>3.65</v>
-      </c>
-      <c r="O28">
-        <v>1.31</v>
-      </c>
-      <c r="P28">
-        <v>1.9</v>
-      </c>
-      <c r="Q28">
-        <v>1.89</v>
-      </c>
       <c r="R28">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S28">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T28">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="U28">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="W28">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="X28">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Y28">
+        <v>13</v>
+      </c>
+      <c r="Z28">
+        <v>21</v>
+      </c>
+      <c r="AA28">
+        <v>55</v>
+      </c>
+      <c r="AB28">
+        <v>12</v>
+      </c>
+      <c r="AC28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD28">
+        <v>13</v>
+      </c>
+      <c r="AE28">
+        <v>32</v>
+      </c>
+      <c r="AF28">
+        <v>20</v>
+      </c>
+      <c r="AG28">
+        <v>12.5</v>
+      </c>
+      <c r="AH28">
+        <v>19</v>
+      </c>
+      <c r="AI28">
+        <v>50</v>
+      </c>
+      <c r="AJ28">
+        <v>40</v>
+      </c>
+      <c r="AK28">
+        <v>27</v>
+      </c>
+      <c r="AL28">
+        <v>44</v>
+      </c>
+      <c r="AM28">
+        <v>80</v>
+      </c>
+      <c r="AN28">
+        <v>23</v>
+      </c>
+      <c r="AO28">
+        <v>29</v>
+      </c>
+      <c r="AP28">
+        <v>13.5</v>
+      </c>
+      <c r="AQ28">
+        <v>10.5</v>
+      </c>
+      <c r="AR28">
         <v>17</v>
       </c>
-      <c r="Z28">
+      <c r="AS28">
+        <v>7.8</v>
+      </c>
+      <c r="AT28">
+        <v>10</v>
+      </c>
+      <c r="AU28">
+        <v>7.2</v>
+      </c>
+      <c r="AV28">
+        <v>11</v>
+      </c>
+      <c r="AW28">
+        <v>25</v>
+      </c>
+      <c r="AX28">
+        <v>16</v>
+      </c>
+      <c r="AY28">
+        <v>10.5</v>
+      </c>
+      <c r="AZ28">
+        <v>14</v>
+      </c>
+      <c r="BA28">
+        <v>34</v>
+      </c>
+      <c r="BB28">
+        <v>7.6</v>
+      </c>
+      <c r="BC28">
+        <v>7</v>
+      </c>
+      <c r="BD28">
+        <v>32</v>
+      </c>
+      <c r="BE28">
+        <v>8.4</v>
+      </c>
+      <c r="BF28">
+        <v>6.8</v>
+      </c>
+      <c r="BG28">
+        <v>7</v>
+      </c>
+      <c r="BH28">
+        <v>3.55</v>
+      </c>
+      <c r="BI28">
+        <v>3.2</v>
+      </c>
+      <c r="BJ28">
+        <v>10.5</v>
+      </c>
+      <c r="BK28">
+        <v>4.1</v>
+      </c>
+      <c r="BL28">
+        <v>120</v>
+      </c>
+      <c r="BM28">
+        <v>6.4</v>
+      </c>
+      <c r="BN28">
+        <v>6.6</v>
+      </c>
+      <c r="BO28">
+        <v>4.5</v>
+      </c>
+      <c r="BP28">
+        <v>23</v>
+      </c>
+      <c r="BQ28">
+        <v>5.3</v>
+      </c>
+      <c r="BR28">
         <v>36</v>
       </c>
-      <c r="AA28">
-        <v>130</v>
-      </c>
-      <c r="AB28">
-        <v>9.4</v>
-      </c>
-      <c r="AC28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD28">
-        <v>19</v>
-      </c>
-      <c r="AE28">
-        <v>65</v>
-      </c>
-      <c r="AF28">
-        <v>12.5</v>
-      </c>
-      <c r="AG28">
-        <v>11</v>
-      </c>
-      <c r="AH28">
-        <v>19.5</v>
-      </c>
-      <c r="AI28">
-        <v>920</v>
-      </c>
-      <c r="AJ28">
-        <v>23</v>
-      </c>
-      <c r="AK28">
-        <v>22</v>
-      </c>
-      <c r="AL28">
+      <c r="BS28">
+        <v>5.8</v>
+      </c>
+      <c r="BT28">
+        <v>6.8</v>
+      </c>
+      <c r="BU28">
+        <v>4.7</v>
+      </c>
+      <c r="BV28">
+        <v>25</v>
+      </c>
+      <c r="BW28">
+        <v>5.4</v>
+      </c>
+      <c r="BX28">
         <v>38</v>
       </c>
-      <c r="AM28">
-        <v>130</v>
-      </c>
-      <c r="AN28">
-        <v>14</v>
-      </c>
-      <c r="AO28">
-        <v>920</v>
-      </c>
-      <c r="AP28">
-        <v>11</v>
-      </c>
-      <c r="AQ28">
-        <v>11.5</v>
-      </c>
-      <c r="AR28">
-        <v>1.01</v>
-      </c>
-      <c r="AS28">
-        <v>1.01</v>
-      </c>
-      <c r="AT28">
-        <v>6.8</v>
-      </c>
-      <c r="AU28">
-        <v>6.4</v>
-      </c>
-      <c r="AV28">
-        <v>13</v>
-      </c>
-      <c r="AW28">
-        <v>1.01</v>
-      </c>
-      <c r="AX28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY28">
-        <v>7.6</v>
-      </c>
-      <c r="AZ28">
-        <v>13.5</v>
-      </c>
-      <c r="BA28">
-        <v>1.01</v>
-      </c>
-      <c r="BB28">
-        <v>15.5</v>
-      </c>
-      <c r="BC28">
-        <v>14.5</v>
-      </c>
-      <c r="BD28">
-        <v>1.01</v>
-      </c>
-      <c r="BE28">
-        <v>1.01</v>
-      </c>
-      <c r="BF28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG28">
-        <v>1.01</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>1.01</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>1.01</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>1.01</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>1.01</v>
-      </c>
-      <c r="BP28">
-        <v>1000</v>
-      </c>
-      <c r="BQ28">
-        <v>1.01</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
-      <c r="BS28">
-        <v>1.01</v>
-      </c>
-      <c r="BT28">
-        <v>1000</v>
-      </c>
-      <c r="BU28">
-        <v>1.01</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>1.01</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
         <v>102</v>
@@ -7702,963 +7708,963 @@
         <v>148</v>
       </c>
       <c r="E29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="G29">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H29">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I29">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J29">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="M29">
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="O29">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q29">
+        <v>1.91</v>
+      </c>
+      <c r="R29">
+        <v>1.34</v>
+      </c>
+      <c r="S29">
+        <v>3.35</v>
+      </c>
+      <c r="T29">
+        <v>1.8</v>
+      </c>
+      <c r="U29">
+        <v>2.06</v>
+      </c>
+      <c r="V29">
+        <v>1.27</v>
+      </c>
+      <c r="W29">
         <v>1.97</v>
       </c>
-      <c r="R29">
-        <v>1.38</v>
-      </c>
-      <c r="S29">
-        <v>3.5</v>
-      </c>
-      <c r="T29">
-        <v>1.82</v>
-      </c>
-      <c r="U29">
-        <v>2.12</v>
-      </c>
-      <c r="V29">
-        <v>1.31</v>
-      </c>
-      <c r="W29">
-        <v>1.98</v>
-      </c>
       <c r="X29">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y29">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z29">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA29">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AB29">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC29">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE29">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF29">
         <v>12.5</v>
       </c>
       <c r="AG29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH29">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI29">
-        <v>60</v>
+        <v>830</v>
       </c>
       <c r="AJ29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM29">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AN29">
+        <v>14</v>
+      </c>
+      <c r="AO29">
+        <v>830</v>
+      </c>
+      <c r="AP29">
+        <v>11</v>
+      </c>
+      <c r="AQ29">
+        <v>11.5</v>
+      </c>
+      <c r="AR29">
+        <v>1.01</v>
+      </c>
+      <c r="AS29">
+        <v>1.01</v>
+      </c>
+      <c r="AT29">
+        <v>6.8</v>
+      </c>
+      <c r="AU29">
+        <v>6.4</v>
+      </c>
+      <c r="AV29">
+        <v>13</v>
+      </c>
+      <c r="AW29">
+        <v>1.01</v>
+      </c>
+      <c r="AX29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY29">
+        <v>7.6</v>
+      </c>
+      <c r="AZ29">
+        <v>13.5</v>
+      </c>
+      <c r="BA29">
+        <v>1.01</v>
+      </c>
+      <c r="BB29">
+        <v>15.5</v>
+      </c>
+      <c r="BC29">
         <v>14.5</v>
       </c>
-      <c r="AO29">
-        <v>55</v>
-      </c>
-      <c r="AP29">
-        <v>13</v>
-      </c>
-      <c r="AQ29">
-        <v>14</v>
-      </c>
-      <c r="AR29">
-        <v>26</v>
-      </c>
-      <c r="AS29">
-        <v>75</v>
-      </c>
-      <c r="AT29">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU29">
-        <v>7.6</v>
-      </c>
-      <c r="AV29">
-        <v>15</v>
-      </c>
-      <c r="AW29">
-        <v>44</v>
-      </c>
-      <c r="AX29">
-        <v>11</v>
-      </c>
-      <c r="AY29">
+      <c r="BD29">
+        <v>1.01</v>
+      </c>
+      <c r="BE29">
+        <v>1.01</v>
+      </c>
+      <c r="BF29">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ29">
-        <v>17</v>
-      </c>
-      <c r="BA29">
-        <v>50</v>
-      </c>
-      <c r="BB29">
-        <v>21</v>
-      </c>
-      <c r="BC29">
-        <v>19</v>
-      </c>
-      <c r="BD29">
-        <v>32</v>
-      </c>
-      <c r="BE29">
-        <v>75</v>
-      </c>
-      <c r="BF29">
-        <v>13</v>
-      </c>
       <c r="BG29">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
         <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>149</v>
       </c>
       <c r="E30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F30">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>110</v>
+        <v>2.02</v>
       </c>
       <c r="H30">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="I30">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="J30">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K30">
-        <v>280</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="O30">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P30">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="Q30">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="R30">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="S30">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V30">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
         <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>150</v>
       </c>
       <c r="E31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F31">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="G31">
+        <v>110</v>
+      </c>
+      <c r="H31">
+        <v>1.1</v>
+      </c>
+      <c r="I31">
+        <v>110</v>
+      </c>
+      <c r="J31">
+        <v>1.1</v>
+      </c>
+      <c r="K31">
+        <v>280</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.01</v>
+      </c>
+      <c r="N31">
+        <v>1.09</v>
+      </c>
+      <c r="O31">
+        <v>1.02</v>
+      </c>
+      <c r="P31">
+        <v>1.09</v>
+      </c>
+      <c r="Q31">
+        <v>1.47</v>
+      </c>
+      <c r="R31">
+        <v>1.08</v>
+      </c>
+      <c r="S31">
         <v>1.48</v>
       </c>
-      <c r="H31">
-        <v>10</v>
-      </c>
-      <c r="I31">
-        <v>12.5</v>
-      </c>
-      <c r="J31">
-        <v>4.2</v>
-      </c>
-      <c r="K31">
-        <v>5.2</v>
-      </c>
-      <c r="L31">
-        <v>1.34</v>
-      </c>
-      <c r="M31">
-        <v>1.07</v>
-      </c>
-      <c r="N31">
-        <v>3.35</v>
-      </c>
-      <c r="O31">
-        <v>1.34</v>
-      </c>
-      <c r="P31">
-        <v>1.8</v>
-      </c>
-      <c r="Q31">
-        <v>2</v>
-      </c>
-      <c r="R31">
-        <v>1.3</v>
-      </c>
-      <c r="S31">
-        <v>3.6</v>
-      </c>
       <c r="T31">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U31">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V31">
         <v>1.09</v>
       </c>
       <c r="W31">
-        <v>3.05</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
         <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
         <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
         <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
         <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
         <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
         <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
         <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
         <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>151</v>
       </c>
       <c r="E32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
-        <v>1.26</v>
+        <v>3.35</v>
       </c>
       <c r="O32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P32">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q32">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="T32">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U32">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK32">
         <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM32">
         <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ32">
         <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BW32">
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA32">
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
         <v>102</v>
@@ -8670,148 +8676,148 @@
         <v>152</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F33">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>1.26</v>
       </c>
       <c r="O33">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="P33">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q33">
-        <v>2.46</v>
+        <v>1.33</v>
       </c>
       <c r="R33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S33">
-        <v>4.8</v>
+        <v>1.34</v>
       </c>
       <c r="T33">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W33">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG33">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN33">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
         <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
         <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
         <v>1.01</v>
@@ -8829,159 +8835,159 @@
         <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
         <v>1.01</v>
       </c>
       <c r="BH33">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
         <v>1.01</v>
       </c>
       <c r="BL33">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
         <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP33">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
         <v>1.01</v>
       </c>
       <c r="BR33">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
         <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV33">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
         <v>1.01</v>
       </c>
       <c r="BX33">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
         <v>1.01</v>
       </c>
       <c r="BZ33">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
         <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
       </c>
       <c r="E34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F34">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="G34">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="H34">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I34">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J34">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L34">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="M34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N34">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="P34">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="R34">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S34">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="T34">
         <v>1.87</v>
       </c>
       <c r="U34">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="V34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="X34">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y34">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA34">
         <v>110</v>
       </c>
       <c r="AB34">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC34">
         <v>9</v>
@@ -8993,151 +8999,393 @@
         <v>70</v>
       </c>
       <c r="AF34">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG34">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH34">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI34">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ34">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK34">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AL34">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM34">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AN34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AO34">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ34">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR34">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="AS34">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AU34">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV34">
         <v>14.5</v>
       </c>
       <c r="AW34">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX34">
+        <v>9.6</v>
+      </c>
+      <c r="AY34">
+        <v>9.6</v>
+      </c>
+      <c r="AZ34">
+        <v>19</v>
+      </c>
+      <c r="BA34">
+        <v>1.01</v>
+      </c>
+      <c r="BB34">
+        <v>23</v>
+      </c>
+      <c r="BC34">
+        <v>1.01</v>
+      </c>
+      <c r="BD34">
+        <v>38</v>
+      </c>
+      <c r="BE34">
+        <v>1.01</v>
+      </c>
+      <c r="BF34">
+        <v>21</v>
+      </c>
+      <c r="BG34">
+        <v>1.01</v>
+      </c>
+      <c r="BH34">
+        <v>3.2</v>
+      </c>
+      <c r="BI34">
+        <v>2.28</v>
+      </c>
+      <c r="BJ34">
+        <v>13.5</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>230</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>5.8</v>
+      </c>
+      <c r="BO34">
+        <v>3.75</v>
+      </c>
+      <c r="BP34">
+        <v>23</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>50</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU34">
+        <v>5.2</v>
+      </c>
+      <c r="BV34">
+        <v>46</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>70</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>55</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35">
+        <v>2.04</v>
+      </c>
+      <c r="G35">
+        <v>2.18</v>
+      </c>
+      <c r="H35">
+        <v>3.95</v>
+      </c>
+      <c r="I35">
+        <v>4.6</v>
+      </c>
+      <c r="J35">
+        <v>3.3</v>
+      </c>
+      <c r="K35">
+        <v>3.65</v>
+      </c>
+      <c r="L35">
+        <v>1.4</v>
+      </c>
+      <c r="M35">
+        <v>1.08</v>
+      </c>
+      <c r="N35">
+        <v>3.2</v>
+      </c>
+      <c r="O35">
+        <v>1.39</v>
+      </c>
+      <c r="P35">
+        <v>1.75</v>
+      </c>
+      <c r="Q35">
+        <v>2.1</v>
+      </c>
+      <c r="R35">
+        <v>1.27</v>
+      </c>
+      <c r="S35">
+        <v>3.9</v>
+      </c>
+      <c r="T35">
+        <v>1.87</v>
+      </c>
+      <c r="U35">
+        <v>1.96</v>
+      </c>
+      <c r="V35">
+        <v>1.28</v>
+      </c>
+      <c r="W35">
+        <v>1.84</v>
+      </c>
+      <c r="X35">
+        <v>14</v>
+      </c>
+      <c r="Y35">
+        <v>14</v>
+      </c>
+      <c r="Z35">
+        <v>32</v>
+      </c>
+      <c r="AA35">
+        <v>110</v>
+      </c>
+      <c r="AB35">
+        <v>9.6</v>
+      </c>
+      <c r="AC35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD35">
+        <v>18</v>
+      </c>
+      <c r="AE35">
+        <v>70</v>
+      </c>
+      <c r="AF35">
+        <v>13.5</v>
+      </c>
+      <c r="AG35">
+        <v>11.5</v>
+      </c>
+      <c r="AH35">
+        <v>21</v>
+      </c>
+      <c r="AI35">
+        <v>75</v>
+      </c>
+      <c r="AJ35">
+        <v>28</v>
+      </c>
+      <c r="AK35">
+        <v>26</v>
+      </c>
+      <c r="AL35">
+        <v>46</v>
+      </c>
+      <c r="AM35">
+        <v>150</v>
+      </c>
+      <c r="AN35">
+        <v>21</v>
+      </c>
+      <c r="AO35">
+        <v>75</v>
+      </c>
+      <c r="AP35">
+        <v>10</v>
+      </c>
+      <c r="AQ35">
+        <v>11</v>
+      </c>
+      <c r="AR35">
+        <v>6.4</v>
+      </c>
+      <c r="AS35">
+        <v>6.8</v>
+      </c>
+      <c r="AT35">
+        <v>7</v>
+      </c>
+      <c r="AU35">
+        <v>6.6</v>
+      </c>
+      <c r="AV35">
+        <v>14.5</v>
+      </c>
+      <c r="AW35">
+        <v>6.6</v>
+      </c>
+      <c r="AX35">
         <v>10.5</v>
       </c>
-      <c r="AY34">
+      <c r="AY35">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ34">
+      <c r="AZ35">
         <v>17</v>
       </c>
-      <c r="BA34">
-        <v>4.8</v>
-      </c>
-      <c r="BB34">
-        <v>4.8</v>
-      </c>
-      <c r="BC34">
+      <c r="BA35">
+        <v>6.6</v>
+      </c>
+      <c r="BB35">
+        <v>6.6</v>
+      </c>
+      <c r="BC35">
         <v>20</v>
       </c>
-      <c r="BD34">
-        <v>4.6</v>
-      </c>
-      <c r="BE34">
-        <v>4.9</v>
-      </c>
-      <c r="BF34">
-        <v>15</v>
-      </c>
-      <c r="BG34">
-        <v>4.8</v>
-      </c>
-      <c r="BH34">
-        <v>1000</v>
-      </c>
-      <c r="BI34">
-        <v>1.01</v>
-      </c>
-      <c r="BJ34">
-        <v>1000</v>
-      </c>
-      <c r="BK34">
-        <v>1.01</v>
-      </c>
-      <c r="BL34">
-        <v>1000</v>
-      </c>
-      <c r="BM34">
-        <v>1.01</v>
-      </c>
-      <c r="BN34">
-        <v>1000</v>
-      </c>
-      <c r="BO34">
-        <v>1.01</v>
-      </c>
-      <c r="BP34">
-        <v>1000</v>
-      </c>
-      <c r="BQ34">
-        <v>1.01</v>
-      </c>
-      <c r="BR34">
-        <v>1000</v>
-      </c>
-      <c r="BS34">
-        <v>1.01</v>
-      </c>
-      <c r="BT34">
-        <v>1000</v>
-      </c>
-      <c r="BU34">
-        <v>1.01</v>
-      </c>
-      <c r="BV34">
-        <v>1000</v>
-      </c>
-      <c r="BW34">
-        <v>1.01</v>
-      </c>
-      <c r="BX34">
-        <v>1000</v>
-      </c>
-      <c r="BY34">
-        <v>1.01</v>
-      </c>
-      <c r="BZ34">
-        <v>1000</v>
-      </c>
-      <c r="CA34">
-        <v>1.01</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>187</v>
+      <c r="BD35">
+        <v>6.4</v>
+      </c>
+      <c r="BE35">
+        <v>7</v>
+      </c>
+      <c r="BF35">
+        <v>16.5</v>
+      </c>
+      <c r="BG35">
+        <v>6.6</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -583,7 +583,7 @@
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>2026-09-02 05:30:21</t>
+    <t>2026-09-02 07:42:26</t>
   </si>
 </sst>
 </file>
@@ -1180,19 +1180,19 @@
         <v>3.65</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.46</v>
@@ -1213,19 +1213,19 @@
         <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
         <v>3.95</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W2">
         <v>1.34</v>
@@ -1294,13 +1294,13 @@
         <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>24</v>
+        <v>5.6</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>9.4</v>
@@ -1309,7 +1309,7 @@
         <v>5.6</v>
       </c>
       <c r="AX2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY2">
         <v>13.5</v>
@@ -1318,19 +1318,19 @@
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="BB2">
+        <v>5.8</v>
+      </c>
+      <c r="BC2">
+        <v>5.5</v>
+      </c>
+      <c r="BD2">
         <v>5.7</v>
       </c>
-      <c r="BC2">
-        <v>6</v>
-      </c>
-      <c r="BD2">
-        <v>5.6</v>
-      </c>
       <c r="BE2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF2">
         <v>5.6</v>
@@ -1351,7 +1351,7 @@
         <v>3.5</v>
       </c>
       <c r="BL2">
-        <v>900</v>
+        <v>810</v>
       </c>
       <c r="BM2">
         <v>4.8</v>
@@ -1419,16 +1419,16 @@
         <v>156</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="G3">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="I3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1437,7 +1437,7 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1452,31 +1452,31 @@
         <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T3">
         <v>1.67</v>
       </c>
       <c r="U3">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
         <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X3">
         <v>21</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1503,7 +1503,7 @@
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
         <v>42</v>
@@ -1524,7 +1524,7 @@
         <v>19</v>
       </c>
       <c r="AO3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP3">
         <v>12</v>
@@ -1560,7 +1560,7 @@
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
         <v>21</v>
@@ -1575,10 +1575,10 @@
         <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH3">
         <v>3.8</v>
@@ -1602,7 +1602,7 @@
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
         <v>22</v>
@@ -1617,25 +1617,25 @@
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1664,16 +1664,16 @@
         <v>3.15</v>
       </c>
       <c r="G4">
+        <v>3.25</v>
+      </c>
+      <c r="H4">
+        <v>2.54</v>
+      </c>
+      <c r="I4">
+        <v>2.58</v>
+      </c>
+      <c r="J4">
         <v>3.35</v>
-      </c>
-      <c r="H4">
-        <v>2.42</v>
-      </c>
-      <c r="I4">
-        <v>2.56</v>
-      </c>
-      <c r="J4">
-        <v>3.4</v>
       </c>
       <c r="K4">
         <v>3.5</v>
@@ -1685,19 +1685,19 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>4.2</v>
@@ -1712,7 +1712,7 @@
         <v>1.64</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1760,7 +1760,7 @@
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN4">
         <v>55</v>
@@ -1802,7 +1802,7 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BB4">
         <v>7.6</v>
@@ -1820,22 +1820,22 @@
         <v>32</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BH4">
         <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -1847,7 +1847,7 @@
         <v>5.4</v>
       </c>
       <c r="BP4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
@@ -1877,7 +1877,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1921,28 +1921,28 @@
         <v>4.8</v>
       </c>
       <c r="L5">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P5">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="T5">
         <v>1.43</v>
@@ -2154,16 +2154,16 @@
         <v>3.45</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2187,16 +2187,16 @@
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V6">
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X6">
         <v>18.5</v>
@@ -2280,7 +2280,7 @@
         <v>11</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6">
         <v>13</v>
@@ -2310,19 +2310,19 @@
         <v>4</v>
       </c>
       <c r="BI6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6">
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL6">
         <v>130</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BN6">
         <v>5.7</v>
@@ -2334,13 +2334,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
         <v>32</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT6">
         <v>8</v>
@@ -2352,19 +2352,19 @@
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
         <v>44</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BZ6">
         <v>27</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB6" t="s">
         <v>189</v>
@@ -2390,7 +2390,7 @@
         <v>2.68</v>
       </c>
       <c r="G7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>2.72</v>
@@ -2402,34 +2402,34 @@
         <v>3.1</v>
       </c>
       <c r="K7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
         <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="U7">
         <v>1.99</v>
@@ -2632,55 +2632,55 @@
         <v>1.17</v>
       </c>
       <c r="G8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I8">
         <v>25</v>
       </c>
       <c r="J8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K8">
         <v>10.5</v>
       </c>
       <c r="L8">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>2.54</v>
       </c>
       <c r="O8">
         <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U8">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="V8">
         <v>1.04</v>
       </c>
       <c r="W8">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="X8">
         <v>36</v>
@@ -2737,13 +2737,13 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR8">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AS8">
         <v>1.01</v>
@@ -2752,40 +2752,40 @@
         <v>7.8</v>
       </c>
       <c r="AU8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AW8">
-        <v>280</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BA8">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="BB8">
         <v>6.6</v>
       </c>
       <c r="BC8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE8">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="BF8">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
@@ -2794,7 +2794,7 @@
         <v>5.4</v>
       </c>
       <c r="BI8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8">
         <v>17</v>
@@ -2871,58 +2871,58 @@
         <v>162</v>
       </c>
       <c r="F9">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G9">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H9">
         <v>4.8</v>
       </c>
       <c r="I9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
         <v>1.25</v>
       </c>
       <c r="P9">
+        <v>1.99</v>
+      </c>
+      <c r="Q9">
+        <v>1.72</v>
+      </c>
+      <c r="R9">
+        <v>1.37</v>
+      </c>
+      <c r="S9">
+        <v>2.78</v>
+      </c>
+      <c r="T9">
+        <v>1.73</v>
+      </c>
+      <c r="U9">
         <v>2.1</v>
       </c>
-      <c r="Q9">
-        <v>1.7</v>
-      </c>
-      <c r="R9">
-        <v>1.46</v>
-      </c>
-      <c r="S9">
-        <v>2.7</v>
-      </c>
-      <c r="T9">
-        <v>1.55</v>
-      </c>
-      <c r="U9">
-        <v>2.28</v>
-      </c>
       <c r="V9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3033,37 +3033,37 @@
         <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BI9">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
         <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
         <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
@@ -3075,19 +3075,19 @@
         <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BW9">
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
@@ -3122,7 +3122,7 @@
         <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J10">
         <v>3.55</v>
@@ -3236,7 +3236,7 @@
         <v>8</v>
       </c>
       <c r="AU10">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
@@ -3248,10 +3248,10 @@
         <v>13.5</v>
       </c>
       <c r="AY10">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
         <v>34</v>
@@ -3272,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH10">
         <v>3.6</v>
@@ -3358,7 +3358,7 @@
         <v>5.7</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H11">
         <v>1.51</v>
@@ -3370,16 +3370,16 @@
         <v>4.9</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L11">
         <v>1.21</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O11">
         <v>1.16</v>
@@ -3388,7 +3388,7 @@
         <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R11">
         <v>1.74</v>
@@ -3412,13 +3412,13 @@
         <v>38</v>
       </c>
       <c r="Y11">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z11">
         <v>14.5</v>
       </c>
       <c r="AA11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB11">
         <v>38</v>
@@ -3427,10 +3427,10 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF11">
         <v>65</v>
@@ -3460,7 +3460,7 @@
         <v>60</v>
       </c>
       <c r="AO11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP11">
         <v>21</v>
@@ -3469,19 +3469,19 @@
         <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT11">
         <v>21</v>
       </c>
       <c r="AU11">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AW11">
         <v>11</v>
@@ -3496,7 +3496,7 @@
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
         <v>1.01</v>
@@ -3597,46 +3597,46 @@
         <v>165</v>
       </c>
       <c r="F12">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H12">
         <v>4.4</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J12">
         <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R12">
         <v>1.4</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="T12">
         <v>1.66</v>
@@ -3645,7 +3645,7 @@
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
         <v>2.04</v>
@@ -3881,10 +3881,10 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V13">
         <v>1.08</v>
@@ -4120,7 +4120,7 @@
         <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T14">
         <v>1.67</v>
@@ -4138,7 +4138,7 @@
         <v>24</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z14">
         <v>13</v>
@@ -4147,7 +4147,7 @@
         <v>21</v>
       </c>
       <c r="AB14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -4186,7 +4186,7 @@
         <v>55</v>
       </c>
       <c r="AO14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP14">
         <v>19.5</v>
@@ -4249,7 +4249,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK14">
         <v>6.8</v>
@@ -4341,34 +4341,34 @@
         <v>5.5</v>
       </c>
       <c r="L15">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>4.3</v>
+        <v>2.22</v>
       </c>
       <c r="O15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S15">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="T15">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U15">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="V15">
         <v>1.11</v>
@@ -4565,7 +4565,7 @@
         <v>169</v>
       </c>
       <c r="F16">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G16">
         <v>3.1</v>
@@ -4583,7 +4583,7 @@
         <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M16">
         <v>1.08</v>
@@ -4607,7 +4607,7 @@
         <v>3.8</v>
       </c>
       <c r="T16">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U16">
         <v>2.06</v>
@@ -4682,25 +4682,25 @@
         <v>13.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT16">
         <v>8.4</v>
       </c>
       <c r="AU16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV16">
         <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX16">
         <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
         <v>13.5</v>
@@ -4712,10 +4712,10 @@
         <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE16">
         <v>1.01</v>
@@ -4807,25 +4807,25 @@
         <v>170</v>
       </c>
       <c r="F17">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
+        <v>2.74</v>
+      </c>
+      <c r="H17">
+        <v>2.66</v>
+      </c>
+      <c r="I17">
         <v>2.96</v>
-      </c>
-      <c r="H17">
-        <v>2.52</v>
-      </c>
-      <c r="I17">
-        <v>2.88</v>
       </c>
       <c r="J17">
         <v>3.6</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4846,106 +4846,106 @@
         <v>1.44</v>
       </c>
       <c r="S17">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T17">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="U17">
         <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="X17">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y17">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA17">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB17">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AC17">
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE17">
         <v>34</v>
       </c>
       <c r="AF17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG17">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI17">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ17">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK17">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL17">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN17">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP17">
         <v>13.5</v>
       </c>
       <c r="AQ17">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR17">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AT17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU17">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV17">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX17">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY17">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
@@ -4957,13 +4957,13 @@
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG17">
         <v>14</v>
@@ -4987,13 +4987,13 @@
         <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
@@ -5005,19 +5005,19 @@
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW17">
         <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY17">
         <v>1.01</v>
@@ -5067,34 +5067,34 @@
         <v>5.4</v>
       </c>
       <c r="L18">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O18">
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="R18">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="S18">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="T18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U18">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
         <v>2</v>
@@ -5223,7 +5223,7 @@
         <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM18">
         <v>1.01</v>
@@ -5235,7 +5235,7 @@
         <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
@@ -5303,7 +5303,7 @@
         <v>110</v>
       </c>
       <c r="J19">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="K19">
         <v>320</v>
@@ -5533,7 +5533,7 @@
         <v>173</v>
       </c>
       <c r="F20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G20">
         <v>2.2</v>
@@ -5563,25 +5563,25 @@
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q20">
         <v>1.51</v>
       </c>
       <c r="R20">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S20">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T20">
         <v>1.51</v>
       </c>
       <c r="U20">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
         <v>1.83</v>
@@ -5590,7 +5590,7 @@
         <v>65</v>
       </c>
       <c r="Y20">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Z20">
         <v>32</v>
@@ -5620,7 +5620,7 @@
         <v>17</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ20">
         <v>32</v>
@@ -5641,16 +5641,16 @@
         <v>970</v>
       </c>
       <c r="AP20">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20">
         <v>5.5</v>
       </c>
       <c r="AR20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT20">
         <v>14</v>
@@ -5662,7 +5662,7 @@
         <v>13</v>
       </c>
       <c r="AW20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX20">
         <v>15.5</v>
@@ -5674,19 +5674,19 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC20">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD20">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF20">
         <v>8.199999999999999</v>
@@ -5695,7 +5695,7 @@
         <v>14</v>
       </c>
       <c r="BH20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI20">
         <v>3.8</v>
@@ -5790,10 +5790,10 @@
         <v>4.7</v>
       </c>
       <c r="K21">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="L21">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.02</v>
@@ -5802,19 +5802,19 @@
         <v>5.7</v>
       </c>
       <c r="O21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q21">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="S21">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5823,7 +5823,7 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -6023,49 +6023,49 @@
         <v>2.12</v>
       </c>
       <c r="H22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J22">
         <v>3.8</v>
       </c>
       <c r="K22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="O22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P22">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S22">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="T22">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U22">
         <v>2.3</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
         <v>1.89</v>
@@ -6089,7 +6089,7 @@
         <v>11</v>
       </c>
       <c r="AD22">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE22">
         <v>46</v>
@@ -6265,7 +6265,7 @@
         <v>1.72</v>
       </c>
       <c r="H23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I23">
         <v>6.2</v>
@@ -6277,7 +6277,7 @@
         <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
         <v>1.06</v>
@@ -6289,13 +6289,13 @@
         <v>1.25</v>
       </c>
       <c r="P23">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
         <v>1.76</v>
       </c>
       <c r="R23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S23">
         <v>2.92</v>
@@ -6310,7 +6310,7 @@
         <v>1.19</v>
       </c>
       <c r="W23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X23">
         <v>19.5</v>
@@ -6421,61 +6421,61 @@
         <v>7.8</v>
       </c>
       <c r="BH23">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
         <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
@@ -6504,7 +6504,7 @@
         <v>1.5</v>
       </c>
       <c r="G24">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H24">
         <v>6.6</v>
@@ -6519,34 +6519,34 @@
         <v>5.5</v>
       </c>
       <c r="L24">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P24">
         <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S24">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T24">
         <v>1.76</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V24">
         <v>1.15</v>
@@ -6564,7 +6564,7 @@
         <v>75</v>
       </c>
       <c r="AA24">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB24">
         <v>13.5</v>
@@ -6579,19 +6579,19 @@
         <v>110</v>
       </c>
       <c r="AF24">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG24">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH24">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI24">
         <v>90</v>
       </c>
       <c r="AJ24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK24">
         <v>18</v>
@@ -6609,16 +6609,16 @@
         <v>100</v>
       </c>
       <c r="AP24">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AR24">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS24">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT24">
         <v>9.6</v>
@@ -6627,10 +6627,10 @@
         <v>10</v>
       </c>
       <c r="AV24">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AW24">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX24">
         <v>9.4</v>
@@ -6639,10 +6639,10 @@
         <v>9</v>
       </c>
       <c r="AZ24">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BA24">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB24">
         <v>12.5</v>
@@ -6651,16 +6651,16 @@
         <v>13</v>
       </c>
       <c r="BD24">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE24">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF24">
         <v>4.7</v>
       </c>
       <c r="BG24">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH24">
         <v>5.1</v>
@@ -6672,13 +6672,13 @@
         <v>12</v>
       </c>
       <c r="BK24">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
         <v>130</v>
       </c>
       <c r="BM24">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
         <v>5.1</v>
@@ -6690,37 +6690,37 @@
         <v>11</v>
       </c>
       <c r="BQ24">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
         <v>26</v>
       </c>
       <c r="BS24">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
         <v>12.5</v>
       </c>
       <c r="BU24">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
         <v>65</v>
       </c>
       <c r="BW24">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
         <v>60</v>
       </c>
       <c r="BY24">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
         <v>16</v>
       </c>
       <c r="CA24">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
         <v>189</v>
@@ -6752,7 +6752,7 @@
         <v>4.5</v>
       </c>
       <c r="I25">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J25">
         <v>4.4</v>
@@ -6782,7 +6782,7 @@
         <v>1.74</v>
       </c>
       <c r="S25">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T25">
         <v>1.56</v>
@@ -6791,7 +6791,7 @@
         <v>2.32</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W25">
         <v>2.28</v>
@@ -6991,40 +6991,40 @@
         <v>2.6</v>
       </c>
       <c r="H26">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I26">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J26">
         <v>3.9</v>
       </c>
       <c r="K26">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R26">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S26">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T26">
         <v>1.5</v>
@@ -7251,28 +7251,28 @@
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O27">
         <v>1.37</v>
       </c>
       <c r="P27">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q27">
         <v>2.12</v>
       </c>
       <c r="R27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
         <v>3.9</v>
       </c>
       <c r="T27">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U27">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V27">
         <v>1.77</v>
@@ -7296,13 +7296,13 @@
         <v>12.5</v>
       </c>
       <c r="AC27">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27">
         <v>11.5</v>
       </c>
       <c r="AE27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF27">
         <v>25</v>
@@ -7314,7 +7314,7 @@
         <v>18.5</v>
       </c>
       <c r="AI27">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ27">
         <v>70</v>
@@ -7329,7 +7329,7 @@
         <v>110</v>
       </c>
       <c r="AN27">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO27">
         <v>20</v>
@@ -7353,7 +7353,7 @@
         <v>7.2</v>
       </c>
       <c r="AV27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW27">
         <v>23</v>
@@ -7368,7 +7368,7 @@
         <v>17</v>
       </c>
       <c r="BA27">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BB27">
         <v>60</v>
@@ -7380,7 +7380,7 @@
         <v>50</v>
       </c>
       <c r="BE27">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="BF27">
         <v>42</v>
@@ -7484,10 +7484,10 @@
         <v>3.5</v>
       </c>
       <c r="K28">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L28">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M28">
         <v>1.06</v>
@@ -7496,7 +7496,7 @@
         <v>3.9</v>
       </c>
       <c r="O28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P28">
         <v>2</v>
@@ -7532,7 +7532,7 @@
         <v>21</v>
       </c>
       <c r="AA28">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB28">
         <v>12</v>
@@ -7547,7 +7547,7 @@
         <v>32</v>
       </c>
       <c r="AF28">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG28">
         <v>12.5</v>
@@ -7571,7 +7571,7 @@
         <v>80</v>
       </c>
       <c r="AN28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO28">
         <v>29</v>
@@ -7598,7 +7598,7 @@
         <v>11</v>
       </c>
       <c r="AW28">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="AX28">
         <v>16</v>
@@ -7610,7 +7610,7 @@
         <v>14</v>
       </c>
       <c r="BA28">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BB28">
         <v>7.6</v>
@@ -7714,13 +7714,13 @@
         <v>1.87</v>
       </c>
       <c r="G29">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H29">
         <v>4.2</v>
       </c>
       <c r="I29">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J29">
         <v>3.55</v>
@@ -7732,25 +7732,25 @@
         <v>1.31</v>
       </c>
       <c r="M29">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="O29">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P29">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q29">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R29">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S29">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="T29">
         <v>1.8</v>
@@ -7759,10 +7759,10 @@
         <v>2.06</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W29">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X29">
         <v>15.5</v>
@@ -7774,7 +7774,7 @@
         <v>36</v>
       </c>
       <c r="AA29">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB29">
         <v>9.4</v>
@@ -7798,7 +7798,7 @@
         <v>19.5</v>
       </c>
       <c r="AI29">
-        <v>830</v>
+        <v>740</v>
       </c>
       <c r="AJ29">
         <v>23</v>
@@ -7816,7 +7816,7 @@
         <v>14</v>
       </c>
       <c r="AO29">
-        <v>830</v>
+        <v>740</v>
       </c>
       <c r="AP29">
         <v>11</v>
@@ -7825,10 +7825,10 @@
         <v>11.5</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29">
         <v>6.8</v>
@@ -7840,10 +7840,10 @@
         <v>13</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY29">
         <v>7.6</v>
@@ -7852,7 +7852,7 @@
         <v>13.5</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB29">
         <v>15.5</v>
@@ -7861,16 +7861,16 @@
         <v>14.5</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7968,10 +7968,10 @@
         <v>3.75</v>
       </c>
       <c r="K30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L30">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M30">
         <v>1.07</v>
@@ -7995,13 +7995,13 @@
         <v>3.5</v>
       </c>
       <c r="T30">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U30">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
         <v>1.98</v>
@@ -8019,7 +8019,7 @@
         <v>90</v>
       </c>
       <c r="AB30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC30">
         <v>8.4</v>
@@ -8031,7 +8031,7 @@
         <v>55</v>
       </c>
       <c r="AF30">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG30">
         <v>10.5</v>
@@ -8121,7 +8121,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK30">
         <v>8.6</v>
@@ -8130,25 +8130,25 @@
         <v>140</v>
       </c>
       <c r="BM30">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN30">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO30">
         <v>4.3</v>
       </c>
       <c r="BP30">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BQ30">
         <v>12.5</v>
       </c>
       <c r="BR30">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BS30">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT30">
         <v>9</v>
@@ -8157,22 +8157,22 @@
         <v>6.6</v>
       </c>
       <c r="BV30">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BW30">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BX30">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY30">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BZ30">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA30">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="CB30" t="s">
         <v>189</v>
@@ -8437,10 +8437,10 @@
         <v>185</v>
       </c>
       <c r="F32">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="G32">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H32">
         <v>10</v>
@@ -8449,37 +8449,37 @@
         <v>14.5</v>
       </c>
       <c r="J32">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K32">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L32">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M32">
         <v>1.07</v>
       </c>
       <c r="N32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O32">
         <v>1.34</v>
       </c>
       <c r="P32">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q32">
         <v>2</v>
       </c>
       <c r="R32">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T32">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U32">
         <v>1.63</v>
@@ -8488,7 +8488,7 @@
         <v>1.07</v>
       </c>
       <c r="W32">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="X32">
         <v>17</v>
@@ -8500,25 +8500,25 @@
         <v>130</v>
       </c>
       <c r="AA32">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC32">
         <v>13.5</v>
       </c>
       <c r="AD32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE32">
         <v>290</v>
       </c>
       <c r="AF32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH32">
         <v>38</v>
@@ -8527,10 +8527,10 @@
         <v>240</v>
       </c>
       <c r="AJ32">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK32">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL32">
         <v>65</v>
@@ -8539,22 +8539,22 @@
         <v>310</v>
       </c>
       <c r="AN32">
+        <v>8.6</v>
+      </c>
+      <c r="AO32">
+        <v>540</v>
+      </c>
+      <c r="AP32">
         <v>10.5</v>
-      </c>
-      <c r="AO32">
-        <v>530</v>
-      </c>
-      <c r="AP32">
-        <v>10</v>
       </c>
       <c r="AQ32">
         <v>19.5</v>
       </c>
       <c r="AR32">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS32">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT32">
         <v>5.7</v>
@@ -8566,7 +8566,7 @@
         <v>32</v>
       </c>
       <c r="AW32">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AX32">
         <v>6.4</v>
@@ -8575,10 +8575,10 @@
         <v>9</v>
       </c>
       <c r="AZ32">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BA32">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BB32">
         <v>10</v>
@@ -8587,22 +8587,22 @@
         <v>15</v>
       </c>
       <c r="BD32">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BE32">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BF32">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG32">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BH32">
         <v>3.9</v>
       </c>
       <c r="BI32">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="BJ32">
         <v>16</v>
@@ -8647,7 +8647,7 @@
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
@@ -8924,7 +8924,7 @@
         <v>2.16</v>
       </c>
       <c r="G34">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H34">
         <v>3.8</v>
@@ -8933,46 +8933,46 @@
         <v>4.3</v>
       </c>
       <c r="J34">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K34">
         <v>3.4</v>
       </c>
       <c r="L34">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M34">
         <v>1.09</v>
       </c>
       <c r="N34">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O34">
         <v>1.48</v>
       </c>
       <c r="P34">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q34">
         <v>2.42</v>
       </c>
       <c r="R34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S34">
         <v>4.8</v>
       </c>
       <c r="T34">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="U34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V34">
         <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X34">
         <v>11.5</v>
@@ -9005,7 +9005,7 @@
         <v>13.5</v>
       </c>
       <c r="AH34">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI34">
         <v>100</v>
@@ -9014,7 +9014,7 @@
         <v>40</v>
       </c>
       <c r="AK34">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL34">
         <v>60</v>
@@ -9029,10 +9029,10 @@
         <v>110</v>
       </c>
       <c r="AP34">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ34">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR34">
         <v>19.5</v>
@@ -9083,13 +9083,13 @@
         <v>1.01</v>
       </c>
       <c r="BH34">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BI34">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="BJ34">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK34">
         <v>1.01</v>
@@ -9101,7 +9101,7 @@
         <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO34">
         <v>3.75</v>
@@ -9113,7 +9113,7 @@
         <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS34">
         <v>1.01</v>
@@ -9166,7 +9166,7 @@
         <v>2.04</v>
       </c>
       <c r="G35">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H35">
         <v>3.95</v>
@@ -9196,7 +9196,7 @@
         <v>1.75</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R35">
         <v>1.27</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -583,7 +583,7 @@
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>2026-09-02 07:42:26</t>
+    <t>2026-09-02 09:54:29</t>
   </si>
 </sst>
 </file>
@@ -1177,22 +1177,22 @@
         <v>155</v>
       </c>
       <c r="F2">
+        <v>3.75</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2.14</v>
+      </c>
+      <c r="I2">
+        <v>2.24</v>
+      </c>
+      <c r="J2">
+        <v>3.35</v>
+      </c>
+      <c r="K2">
         <v>3.65</v>
-      </c>
-      <c r="G2">
-        <v>3.95</v>
-      </c>
-      <c r="H2">
-        <v>2.18</v>
-      </c>
-      <c r="I2">
-        <v>2.28</v>
-      </c>
-      <c r="J2">
-        <v>3.3</v>
-      </c>
-      <c r="K2">
-        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.46</v>
@@ -1204,7 +1204,7 @@
         <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
         <v>1.83</v>
@@ -1216,31 +1216,31 @@
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
         <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X2">
         <v>15</v>
       </c>
       <c r="Y2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2">
         <v>16</v>
       </c>
       <c r="AA2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB2">
         <v>16</v>
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="AE2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF2">
         <v>30</v>
@@ -1261,7 +1261,7 @@
         <v>20</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>50</v>
@@ -1270,31 +1270,31 @@
         <v>100</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1306,10 +1306,10 @@
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AY2">
         <v>13.5</v>
@@ -1318,58 +1318,58 @@
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="BC2">
-        <v>5.5</v>
+        <v>34</v>
       </c>
       <c r="BD2">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="BE2">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BG2">
         <v>15</v>
       </c>
       <c r="BH2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL2">
-        <v>810</v>
+        <v>720</v>
       </c>
       <c r="BM2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO2">
         <v>5.2</v>
       </c>
       <c r="BP2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS2">
         <v>4.5</v>
@@ -1378,7 +1378,7 @@
         <v>5.8</v>
       </c>
       <c r="BU2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV2">
         <v>21</v>
@@ -1387,16 +1387,16 @@
         <v>4</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY2">
         <v>4.4</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB2" t="s">
         <v>189</v>
@@ -1419,16 +1419,16 @@
         <v>156</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>3.65</v>
@@ -1449,28 +1449,28 @@
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U3">
         <v>2.28</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
         <v>21</v>
@@ -1479,22 +1479,22 @@
         <v>14</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB3">
         <v>12.5</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF3">
         <v>18</v>
@@ -1506,7 +1506,7 @@
         <v>19.5</v>
       </c>
       <c r="AI3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ3">
         <v>36</v>
@@ -1521,22 +1521,22 @@
         <v>80</v>
       </c>
       <c r="AN3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
         <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1545,40 +1545,40 @@
         <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3">
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC3">
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH3">
         <v>3.8</v>
@@ -1599,13 +1599,13 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO3">
         <v>4.3</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
@@ -1620,10 +1620,10 @@
         <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
@@ -1635,7 +1635,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1661,25 +1661,25 @@
         <v>157</v>
       </c>
       <c r="F4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1688,28 +1688,28 @@
         <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W4">
         <v>1.45</v>
@@ -1730,7 +1730,7 @@
         <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
         <v>12.5</v>
@@ -1763,7 +1763,7 @@
         <v>140</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO4">
         <v>29</v>
@@ -1778,7 +1778,7 @@
         <v>13</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AT4">
         <v>9.4</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AX4">
         <v>18.5</v>
@@ -1799,43 +1799,43 @@
         <v>12</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
         <v>38</v>
       </c>
       <c r="BB4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4">
         <v>34</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
         <v>32</v>
       </c>
       <c r="BG4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BH4">
         <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -1847,13 +1847,13 @@
         <v>5.4</v>
       </c>
       <c r="BP4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
@@ -1862,7 +1862,7 @@
         <v>5.5</v>
       </c>
       <c r="BU4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV4">
         <v>21</v>
@@ -1939,7 +1939,7 @@
         <v>1.53</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
         <v>2.28</v>
@@ -2154,22 +2154,22 @@
         <v>3.45</v>
       </c>
       <c r="I6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
         <v>1.28</v>
@@ -2187,7 +2187,7 @@
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U6">
         <v>2.16</v>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="BI6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6">
         <v>11</v>
@@ -2387,70 +2387,70 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
         <v>2.72</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="J7">
         <v>3.1</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="T7">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
         <v>1.99</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X7">
         <v>12</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2462,10 +2462,10 @@
         <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG7">
         <v>13.5</v>
@@ -2480,7 +2480,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2492,7 +2492,7 @@
         <v>36</v>
       </c>
       <c r="AO7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP7">
         <v>10</v>
@@ -2501,13 +2501,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
         <v>6.4</v>
@@ -2516,7 +2516,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AX7">
         <v>15.5</v>
@@ -2525,28 +2525,28 @@
         <v>11</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BB7">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BC7">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BD7">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BE7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BG7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2638,7 +2638,7 @@
         <v>18</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J8">
         <v>7.6</v>
@@ -2653,25 +2653,25 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.54</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
         <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q8">
         <v>1.44</v>
       </c>
       <c r="R8">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="S8">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="T8">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
         <v>1.61</v>
@@ -2689,7 +2689,7 @@
         <v>70</v>
       </c>
       <c r="Z8">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2698,46 +2698,46 @@
         <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD8">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE8">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI8">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AJ8">
         <v>9.6</v>
       </c>
       <c r="AK8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AN8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ8">
         <v>46</v>
@@ -2749,7 +2749,7 @@
         <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU8">
         <v>14.5</v>
@@ -2874,7 +2874,7 @@
         <v>1.82</v>
       </c>
       <c r="G9">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H9">
         <v>4.8</v>
@@ -2883,37 +2883,37 @@
         <v>5.1</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
         <v>1.99</v>
       </c>
       <c r="Q9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
         <v>2.1</v>
@@ -2922,7 +2922,7 @@
         <v>1.24</v>
       </c>
       <c r="W9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3128,7 +3128,7 @@
         <v>3.55</v>
       </c>
       <c r="K10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -3149,76 +3149,76 @@
         <v>1.86</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S10">
         <v>3.15</v>
       </c>
       <c r="T10">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
         <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
         <v>19.5</v>
       </c>
       <c r="Y10">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA10">
         <v>75</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF10">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG10">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL10">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM10">
         <v>100</v>
       </c>
       <c r="AN10">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AO10">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AP10">
         <v>11.5</v>
@@ -3236,34 +3236,34 @@
         <v>8</v>
       </c>
       <c r="AU10">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA10">
         <v>34</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
         <v>1.01</v>
@@ -3272,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>3.6</v>
@@ -3358,10 +3358,10 @@
         <v>5.7</v>
       </c>
       <c r="G11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I11">
         <v>1.59</v>
@@ -3376,7 +3376,7 @@
         <v>1.21</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
         <v>6.2</v>
@@ -3388,7 +3388,7 @@
         <v>2.8</v>
       </c>
       <c r="Q11">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R11">
         <v>1.74</v>
@@ -3397,10 +3397,10 @@
         <v>2.16</v>
       </c>
       <c r="T11">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
         <v>2.68</v>
@@ -3460,7 +3460,7 @@
         <v>60</v>
       </c>
       <c r="AO11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AP11">
         <v>21</v>
@@ -3487,13 +3487,13 @@
         <v>11</v>
       </c>
       <c r="AX11">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
         <v>21</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA11">
         <v>1.01</v>
@@ -3597,28 +3597,28 @@
         <v>165</v>
       </c>
       <c r="F12">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G12">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H12">
         <v>4.4</v>
       </c>
       <c r="I12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
         <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -3627,16 +3627,16 @@
         <v>1.28</v>
       </c>
       <c r="P12">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q12">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S12">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
         <v>1.66</v>
@@ -3645,7 +3645,7 @@
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W12">
         <v>2.04</v>
@@ -3657,7 +3657,7 @@
         <v>970</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA12">
         <v>120</v>
@@ -3669,7 +3669,7 @@
         <v>9</v>
       </c>
       <c r="AD12">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE12">
         <v>65</v>
@@ -3681,7 +3681,7 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI12">
         <v>70</v>
@@ -3690,7 +3690,7 @@
         <v>21</v>
       </c>
       <c r="AK12">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL12">
         <v>36</v>
@@ -3711,10 +3711,10 @@
         <v>15</v>
       </c>
       <c r="AR12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT12">
         <v>8.199999999999999</v>
@@ -3726,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="AW12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3738,25 +3738,25 @@
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE12">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF12">
         <v>10</v>
       </c>
       <c r="BG12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3848,7 +3848,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J13">
         <v>4.5</v>
@@ -3881,13 +3881,13 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="U13">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="V13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W13">
         <v>3.15</v>
@@ -3905,7 +3905,7 @@
         <v>570</v>
       </c>
       <c r="AB13">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC13">
         <v>12.5</v>
@@ -3917,7 +3917,7 @@
         <v>270</v>
       </c>
       <c r="AF13">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -4111,7 +4111,7 @@
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
         <v>1.65</v>
@@ -4120,7 +4120,7 @@
         <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T14">
         <v>1.67</v>
@@ -4132,7 +4132,7 @@
         <v>2.24</v>
       </c>
       <c r="W14">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X14">
         <v>24</v>
@@ -4141,7 +4141,7 @@
         <v>13.5</v>
       </c>
       <c r="Z14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA14">
         <v>21</v>
@@ -4159,7 +4159,7 @@
         <v>17</v>
       </c>
       <c r="AF14">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AG14">
         <v>19</v>
@@ -4207,7 +4207,7 @@
         <v>9</v>
       </c>
       <c r="AV14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14">
         <v>15</v>
@@ -4216,7 +4216,7 @@
         <v>34</v>
       </c>
       <c r="AY14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ14">
         <v>15.5</v>
@@ -4249,7 +4249,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK14">
         <v>6.8</v>
@@ -4261,43 +4261,43 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BO14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BP14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ14">
         <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS14">
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU14">
         <v>4.3</v>
       </c>
       <c r="BV14">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA14">
         <v>1.01</v>
@@ -4338,37 +4338,37 @@
         <v>4.5</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>2.22</v>
+        <v>4.3</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q15">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T15">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="U15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V15">
         <v>1.11</v>
@@ -4583,7 +4583,7 @@
         <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M16">
         <v>1.08</v>
@@ -4607,7 +4607,7 @@
         <v>3.8</v>
       </c>
       <c r="T16">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U16">
         <v>2.06</v>
@@ -4619,55 +4619,55 @@
         <v>1.48</v>
       </c>
       <c r="X16">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
         <v>11</v>
       </c>
       <c r="Z16">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AA16">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB16">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC16">
         <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF16">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AG16">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI16">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ16">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM16">
         <v>120</v>
       </c>
       <c r="AN16">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO16">
         <v>32</v>
@@ -4676,31 +4676,31 @@
         <v>9.6</v>
       </c>
       <c r="AQ16">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16">
         <v>13.5</v>
       </c>
       <c r="AS16">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
         <v>8.4</v>
       </c>
       <c r="AU16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV16">
         <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
         <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
         <v>13.5</v>
@@ -4730,19 +4730,19 @@
         <v>3.55</v>
       </c>
       <c r="BI16">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ16">
         <v>11.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL16">
         <v>150</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN16">
         <v>6.8</v>
@@ -4754,13 +4754,13 @@
         <v>27</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR16">
         <v>44</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT16">
         <v>6.4</v>
@@ -4772,19 +4772,19 @@
         <v>25</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX16">
         <v>42</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BZ16">
         <v>36</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB16" t="s">
         <v>189</v>
@@ -4807,25 +4807,25 @@
         <v>170</v>
       </c>
       <c r="F17">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="G17">
+        <v>2.64</v>
+      </c>
+      <c r="H17">
         <v>2.74</v>
       </c>
-      <c r="H17">
-        <v>2.66</v>
-      </c>
       <c r="I17">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4837,10 +4837,10 @@
         <v>1.25</v>
       </c>
       <c r="P17">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q17">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R17">
         <v>1.44</v>
@@ -4852,13 +4852,13 @@
         <v>1.63</v>
       </c>
       <c r="U17">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X17">
         <v>19.5</v>
@@ -4867,16 +4867,16 @@
         <v>14.5</v>
       </c>
       <c r="Z17">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA17">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AB17">
         <v>14</v>
       </c>
       <c r="AC17">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17">
         <v>13.5</v>
@@ -4891,7 +4891,7 @@
         <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
         <v>38</v>
@@ -4906,13 +4906,13 @@
         <v>36</v>
       </c>
       <c r="AM17">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN17">
         <v>21</v>
       </c>
       <c r="AO17">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP17">
         <v>13.5</v>
@@ -4924,7 +4924,7 @@
         <v>16.5</v>
       </c>
       <c r="AS17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT17">
         <v>11</v>
@@ -4936,10 +4936,10 @@
         <v>10.5</v>
       </c>
       <c r="AW17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY17">
         <v>9.199999999999999</v>
@@ -4972,7 +4972,7 @@
         <v>4.5</v>
       </c>
       <c r="BI17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17">
         <v>11</v>
@@ -4987,31 +4987,31 @@
         <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW17">
         <v>1.01</v>
@@ -5049,58 +5049,58 @@
         <v>171</v>
       </c>
       <c r="F18">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="G18">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H18">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="I18">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18">
+        <v>5.5</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
         <v>5.4</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>5.1</v>
       </c>
       <c r="O18">
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q18">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S18">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T18">
         <v>1.48</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W18">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5214,10 +5214,10 @@
         <v>5.3</v>
       </c>
       <c r="BI18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5229,10 +5229,10 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP18">
         <v>36</v>
@@ -5247,13 +5247,13 @@
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
@@ -5303,7 +5303,7 @@
         <v>110</v>
       </c>
       <c r="J19">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K19">
         <v>320</v>
@@ -5339,10 +5339,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5533,16 +5533,16 @@
         <v>173</v>
       </c>
       <c r="F20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G20">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H20">
+        <v>3.15</v>
+      </c>
+      <c r="I20">
         <v>3.3</v>
-      </c>
-      <c r="I20">
-        <v>3.4</v>
       </c>
       <c r="J20">
         <v>4.1</v>
@@ -5566,94 +5566,94 @@
         <v>2.72</v>
       </c>
       <c r="Q20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S20">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U20">
         <v>2.74</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W20">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X20">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="Y20">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Z20">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB20">
         <v>16.5</v>
       </c>
       <c r="AC20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD20">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE20">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AF20">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI20">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ20">
         <v>32</v>
       </c>
       <c r="AK20">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AL20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN20">
         <v>11</v>
       </c>
       <c r="AO20">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AP20">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AQ20">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR20">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AS20">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="AT20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU20">
         <v>9.199999999999999</v>
@@ -5662,37 +5662,37 @@
         <v>13</v>
       </c>
       <c r="AW20">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AX20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20">
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BB20">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BC20">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BE20">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BF20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG20">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH20">
         <v>5.4</v>
@@ -5737,7 +5737,7 @@
         <v>5.6</v>
       </c>
       <c r="BV20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
@@ -5778,7 +5778,7 @@
         <v>5.8</v>
       </c>
       <c r="G21">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="H21">
         <v>1.52</v>
@@ -5805,16 +5805,16 @@
         <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q21">
         <v>1.51</v>
       </c>
       <c r="R21">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S21">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5823,22 +5823,22 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>34</v>
       </c>
       <c r="Y21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z21">
         <v>14</v>
       </c>
       <c r="AA21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB21">
         <v>36</v>
@@ -5850,13 +5850,13 @@
         <v>13</v>
       </c>
       <c r="AE21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF21">
         <v>70</v>
       </c>
       <c r="AG21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH21">
         <v>24</v>
@@ -5880,10 +5880,10 @@
         <v>70</v>
       </c>
       <c r="AO21">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AP21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ21">
         <v>10.5</v>
@@ -5892,46 +5892,46 @@
         <v>10</v>
       </c>
       <c r="AS21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AU21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV21">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AX21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ21">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BB21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC21">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE21">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG21">
         <v>4.4</v>
@@ -6020,7 +6020,7 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H22">
         <v>3.55</v>
@@ -6032,13 +6032,13 @@
         <v>3.8</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
         <v>2.38</v>
@@ -6050,16 +6050,16 @@
         <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S22">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="T22">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U22">
         <v>2.3</v>
@@ -6068,61 +6068,61 @@
         <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X22">
         <v>23</v>
       </c>
       <c r="Y22">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z22">
+        <v>32</v>
+      </c>
+      <c r="AA22">
+        <v>75</v>
+      </c>
+      <c r="AB22">
+        <v>12.5</v>
+      </c>
+      <c r="AC22">
+        <v>9.6</v>
+      </c>
+      <c r="AD22">
+        <v>16.5</v>
+      </c>
+      <c r="AE22">
+        <v>42</v>
+      </c>
+      <c r="AF22">
+        <v>15.5</v>
+      </c>
+      <c r="AG22">
+        <v>11.5</v>
+      </c>
+      <c r="AH22">
+        <v>17</v>
+      </c>
+      <c r="AI22">
+        <v>46</v>
+      </c>
+      <c r="AJ22">
+        <v>26</v>
+      </c>
+      <c r="AK22">
+        <v>21</v>
+      </c>
+      <c r="AL22">
+        <v>32</v>
+      </c>
+      <c r="AM22">
+        <v>80</v>
+      </c>
+      <c r="AN22">
+        <v>12.5</v>
+      </c>
+      <c r="AO22">
         <v>34</v>
-      </c>
-      <c r="AA22">
-        <v>80</v>
-      </c>
-      <c r="AB22">
-        <v>13.5</v>
-      </c>
-      <c r="AC22">
-        <v>11</v>
-      </c>
-      <c r="AD22">
-        <v>18</v>
-      </c>
-      <c r="AE22">
-        <v>46</v>
-      </c>
-      <c r="AF22">
-        <v>17</v>
-      </c>
-      <c r="AG22">
-        <v>12.5</v>
-      </c>
-      <c r="AH22">
-        <v>19</v>
-      </c>
-      <c r="AI22">
-        <v>50</v>
-      </c>
-      <c r="AJ22">
-        <v>28</v>
-      </c>
-      <c r="AK22">
-        <v>23</v>
-      </c>
-      <c r="AL22">
-        <v>36</v>
-      </c>
-      <c r="AM22">
-        <v>85</v>
-      </c>
-      <c r="AN22">
-        <v>13.5</v>
-      </c>
-      <c r="AO22">
-        <v>38</v>
       </c>
       <c r="AP22">
         <v>15</v>
@@ -6131,52 +6131,52 @@
         <v>13.5</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS22">
         <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU22">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV22">
         <v>12</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX22">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY22">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22">
         <v>12.5</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB22">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE22">
         <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6298,10 +6298,10 @@
         <v>1.47</v>
       </c>
       <c r="S23">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="T23">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="U23">
         <v>2.1</v>
@@ -6313,7 +6313,7 @@
         <v>2.4</v>
       </c>
       <c r="X23">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y23">
         <v>22</v>
@@ -6325,16 +6325,16 @@
         <v>170</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF23">
         <v>11.5</v>
@@ -6343,7 +6343,7 @@
         <v>11</v>
       </c>
       <c r="AH23">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI23">
         <v>85</v>
@@ -6358,7 +6358,7 @@
         <v>36</v>
       </c>
       <c r="AM23">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN23">
         <v>9.6</v>
@@ -6373,10 +6373,10 @@
         <v>17.5</v>
       </c>
       <c r="AR23">
+        <v>34</v>
+      </c>
+      <c r="AS23">
         <v>7.2</v>
-      </c>
-      <c r="AS23">
-        <v>8</v>
       </c>
       <c r="AT23">
         <v>8</v>
@@ -6388,37 +6388,37 @@
         <v>18.5</v>
       </c>
       <c r="AW23">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX23">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY23">
         <v>8.6</v>
       </c>
       <c r="AZ23">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA23">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC23">
         <v>14.5</v>
       </c>
       <c r="BD23">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE23">
+        <v>7</v>
+      </c>
+      <c r="BF23">
         <v>7.8</v>
       </c>
-      <c r="BF23">
-        <v>8</v>
-      </c>
       <c r="BG23">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6504,7 +6504,7 @@
         <v>1.5</v>
       </c>
       <c r="G24">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H24">
         <v>6.6</v>
@@ -6522,25 +6522,25 @@
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O24">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
         <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
         <v>1.61</v>
       </c>
       <c r="S24">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T24">
         <v>1.76</v>
@@ -6585,7 +6585,7 @@
         <v>11</v>
       </c>
       <c r="AH24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI24">
         <v>90</v>
@@ -6609,16 +6609,16 @@
         <v>100</v>
       </c>
       <c r="AP24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT24">
         <v>9.6</v>
@@ -6627,10 +6627,10 @@
         <v>10</v>
       </c>
       <c r="AV24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW24">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX24">
         <v>9.4</v>
@@ -6642,7 +6642,7 @@
         <v>4.1</v>
       </c>
       <c r="BA24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB24">
         <v>12.5</v>
@@ -6651,16 +6651,16 @@
         <v>13</v>
       </c>
       <c r="BD24">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE24">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF24">
         <v>4.7</v>
       </c>
       <c r="BG24">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH24">
         <v>5.1</v>
@@ -6752,7 +6752,7 @@
         <v>4.5</v>
       </c>
       <c r="I25">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J25">
         <v>4.4</v>
@@ -6776,13 +6776,13 @@
         <v>2.8</v>
       </c>
       <c r="Q25">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R25">
         <v>1.74</v>
       </c>
       <c r="S25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T25">
         <v>1.56</v>
@@ -6797,10 +6797,10 @@
         <v>2.28</v>
       </c>
       <c r="X25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y25">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z25">
         <v>50</v>
@@ -6809,52 +6809,52 @@
         <v>120</v>
       </c>
       <c r="AB25">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC25">
         <v>13.5</v>
       </c>
       <c r="AD25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF25">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG25">
         <v>12.5</v>
       </c>
       <c r="AH25">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI25">
         <v>55</v>
       </c>
       <c r="AJ25">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK25">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM25">
         <v>70</v>
       </c>
       <c r="AN25">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO25">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP25">
         <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR25">
         <v>1.01</v>
@@ -6863,43 +6863,43 @@
         <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU25">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW25">
         <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY25">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA25">
         <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC25">
         <v>12</v>
       </c>
       <c r="BD25">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BE25">
         <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BG25">
         <v>1.01</v>
@@ -6997,25 +6997,25 @@
         <v>2.82</v>
       </c>
       <c r="J26">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q26">
         <v>1.51</v>
@@ -7024,10 +7024,10 @@
         <v>1.66</v>
       </c>
       <c r="S26">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T26">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U26">
         <v>2.72</v>
@@ -7039,10 +7039,10 @@
         <v>1.62</v>
       </c>
       <c r="X26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y26">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Z26">
         <v>28</v>
@@ -7051,16 +7051,16 @@
         <v>42</v>
       </c>
       <c r="AB26">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC26">
         <v>12.5</v>
       </c>
       <c r="AD26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE26">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF26">
         <v>26</v>
@@ -7072,70 +7072,70 @@
         <v>17.5</v>
       </c>
       <c r="AI26">
+        <v>36</v>
+      </c>
+      <c r="AJ26">
+        <v>38</v>
+      </c>
+      <c r="AK26">
+        <v>29</v>
+      </c>
+      <c r="AL26">
+        <v>36</v>
+      </c>
+      <c r="AM26">
+        <v>65</v>
+      </c>
+      <c r="AN26">
+        <v>16</v>
+      </c>
+      <c r="AO26">
+        <v>17.5</v>
+      </c>
+      <c r="AP26">
+        <v>21</v>
+      </c>
+      <c r="AQ26">
+        <v>13</v>
+      </c>
+      <c r="AR26">
+        <v>16.5</v>
+      </c>
+      <c r="AS26">
         <v>32</v>
       </c>
-      <c r="AJ26">
-        <v>36</v>
-      </c>
-      <c r="AK26">
-        <v>28</v>
-      </c>
-      <c r="AL26">
-        <v>34</v>
-      </c>
-      <c r="AM26">
-        <v>60</v>
-      </c>
-      <c r="AN26">
-        <v>15</v>
-      </c>
-      <c r="AO26">
-        <v>15</v>
-      </c>
-      <c r="AP26">
-        <v>19</v>
-      </c>
-      <c r="AQ26">
+      <c r="AT26">
         <v>12.5</v>
       </c>
-      <c r="AR26">
-        <v>16</v>
-      </c>
-      <c r="AS26">
-        <v>1.01</v>
-      </c>
-      <c r="AT26">
-        <v>12</v>
-      </c>
       <c r="AU26">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV26">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW26">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX26">
         <v>17.5</v>
       </c>
       <c r="AY26">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26">
         <v>10.5</v>
       </c>
-      <c r="AZ26">
-        <v>12</v>
-      </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB26">
         <v>1.01</v>
       </c>
       <c r="BC26">
+        <v>17</v>
+      </c>
+      <c r="BD26">
         <v>20</v>
-      </c>
-      <c r="BD26">
-        <v>1.01</v>
       </c>
       <c r="BE26">
         <v>1.01</v>
@@ -7144,7 +7144,7 @@
         <v>9.6</v>
       </c>
       <c r="BG26">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH26">
         <v>5.4</v>
@@ -7233,37 +7233,37 @@
         <v>3.7</v>
       </c>
       <c r="H27">
+        <v>2.22</v>
+      </c>
+      <c r="I27">
         <v>2.26</v>
-      </c>
-      <c r="I27">
-        <v>2.3</v>
       </c>
       <c r="J27">
         <v>3.5</v>
       </c>
       <c r="K27">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M27">
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O27">
         <v>1.37</v>
       </c>
       <c r="P27">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R27">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S27">
         <v>3.9</v>
@@ -7275,28 +7275,28 @@
         <v>2.08</v>
       </c>
       <c r="V27">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W27">
         <v>1.37</v>
       </c>
       <c r="X27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y27">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z27">
         <v>13.5</v>
       </c>
       <c r="AA27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB27">
         <v>12.5</v>
       </c>
       <c r="AC27">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD27">
         <v>11.5</v>
@@ -7311,16 +7311,16 @@
         <v>15</v>
       </c>
       <c r="AH27">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI27">
+        <v>44</v>
+      </c>
+      <c r="AJ27">
+        <v>75</v>
+      </c>
+      <c r="AK27">
         <v>48</v>
-      </c>
-      <c r="AJ27">
-        <v>70</v>
-      </c>
-      <c r="AK27">
-        <v>46</v>
       </c>
       <c r="AL27">
         <v>60</v>
@@ -7329,7 +7329,7 @@
         <v>110</v>
       </c>
       <c r="AN27">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO27">
         <v>20</v>
@@ -7341,7 +7341,7 @@
         <v>8.6</v>
       </c>
       <c r="AR27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS27">
         <v>26</v>
@@ -7353,10 +7353,10 @@
         <v>7.2</v>
       </c>
       <c r="AV27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX27">
         <v>22</v>
@@ -7368,7 +7368,7 @@
         <v>17</v>
       </c>
       <c r="BA27">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB27">
         <v>60</v>
@@ -7410,7 +7410,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO27">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP27">
         <v>38</v>
@@ -7431,7 +7431,7 @@
         <v>3.85</v>
       </c>
       <c r="BV27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW27">
         <v>1.01</v>
@@ -7487,13 +7487,13 @@
         <v>3.6</v>
       </c>
       <c r="L28">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M28">
         <v>1.06</v>
       </c>
       <c r="N28">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O28">
         <v>1.3</v>
@@ -7505,10 +7505,10 @@
         <v>1.86</v>
       </c>
       <c r="R28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S28">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T28">
         <v>1.7</v>
@@ -7526,7 +7526,7 @@
         <v>18</v>
       </c>
       <c r="Y28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z28">
         <v>21</v>
@@ -7541,7 +7541,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD28">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE28">
         <v>32</v>
@@ -7562,7 +7562,7 @@
         <v>40</v>
       </c>
       <c r="AK28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL28">
         <v>44</v>
@@ -7571,10 +7571,10 @@
         <v>80</v>
       </c>
       <c r="AN28">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AO28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP28">
         <v>13.5</v>
@@ -7586,7 +7586,7 @@
         <v>17</v>
       </c>
       <c r="AS28">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT28">
         <v>10</v>
@@ -7598,7 +7598,7 @@
         <v>11</v>
       </c>
       <c r="AW28">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="AX28">
         <v>16</v>
@@ -7610,31 +7610,31 @@
         <v>14</v>
       </c>
       <c r="BA28">
+        <v>8.4</v>
+      </c>
+      <c r="BB28">
+        <v>8.4</v>
+      </c>
+      <c r="BC28">
         <v>7.6</v>
-      </c>
-      <c r="BB28">
-        <v>7.6</v>
-      </c>
-      <c r="BC28">
-        <v>7</v>
       </c>
       <c r="BD28">
         <v>32</v>
       </c>
       <c r="BE28">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF28">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BG28">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BH28">
         <v>3.55</v>
       </c>
       <c r="BI28">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ28">
         <v>10.5</v>
@@ -7643,7 +7643,7 @@
         <v>4.1</v>
       </c>
       <c r="BL28">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM28">
         <v>6.4</v>
@@ -7664,7 +7664,7 @@
         <v>36</v>
       </c>
       <c r="BS28">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BT28">
         <v>6.8</v>
@@ -7714,7 +7714,7 @@
         <v>1.87</v>
       </c>
       <c r="G29">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H29">
         <v>4.2</v>
@@ -7726,7 +7726,7 @@
         <v>3.55</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L29">
         <v>1.31</v>
@@ -7741,136 +7741,136 @@
         <v>1.3</v>
       </c>
       <c r="P29">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q29">
         <v>1.86</v>
       </c>
       <c r="R29">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S29">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="T29">
         <v>1.8</v>
       </c>
       <c r="U29">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V29">
         <v>1.26</v>
       </c>
       <c r="W29">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X29">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y29">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z29">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA29">
         <v>120</v>
       </c>
       <c r="AB29">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC29">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE29">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF29">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG29">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH29">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI29">
-        <v>740</v>
+        <v>80</v>
       </c>
       <c r="AJ29">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AK29">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL29">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AM29">
         <v>130</v>
       </c>
       <c r="AN29">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AO29">
-        <v>740</v>
+        <v>80</v>
       </c>
       <c r="AP29">
+        <v>10</v>
+      </c>
+      <c r="AQ29">
         <v>11</v>
       </c>
-      <c r="AQ29">
-        <v>11.5</v>
-      </c>
       <c r="AR29">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS29">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AT29">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU29">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV29">
         <v>13</v>
       </c>
       <c r="AW29">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AX29">
         <v>9</v>
       </c>
       <c r="AY29">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ29">
         <v>13.5</v>
       </c>
       <c r="BA29">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BB29">
+        <v>16.5</v>
+      </c>
+      <c r="BC29">
         <v>15.5</v>
       </c>
-      <c r="BC29">
-        <v>14.5</v>
-      </c>
       <c r="BD29">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE29">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BF29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG29">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7965,7 +7965,7 @@
         <v>4.3</v>
       </c>
       <c r="J30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K30">
         <v>3.85</v>
@@ -7983,16 +7983,16 @@
         <v>1.32</v>
       </c>
       <c r="P30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R30">
         <v>1.38</v>
       </c>
       <c r="S30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T30">
         <v>1.82</v>
@@ -8019,10 +8019,10 @@
         <v>90</v>
       </c>
       <c r="AB30">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30">
         <v>17</v>
@@ -8031,7 +8031,7 @@
         <v>55</v>
       </c>
       <c r="AF30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG30">
         <v>10.5</v>
@@ -8070,7 +8070,7 @@
         <v>26</v>
       </c>
       <c r="AS30">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT30">
         <v>8.800000000000001</v>
@@ -8100,7 +8100,7 @@
         <v>21</v>
       </c>
       <c r="BC30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD30">
         <v>32</v>
@@ -8109,7 +8109,7 @@
         <v>75</v>
       </c>
       <c r="BF30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG30">
         <v>44</v>
@@ -8130,7 +8130,7 @@
         <v>140</v>
       </c>
       <c r="BM30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN30">
         <v>4.7</v>
@@ -8139,7 +8139,7 @@
         <v>4.3</v>
       </c>
       <c r="BP30">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ30">
         <v>12.5</v>
@@ -8160,13 +8160,13 @@
         <v>36</v>
       </c>
       <c r="BW30">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX30">
         <v>46</v>
       </c>
       <c r="BY30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ30">
         <v>25</v>
@@ -8195,13 +8195,13 @@
         <v>184</v>
       </c>
       <c r="F31">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G31">
         <v>110</v>
       </c>
       <c r="H31">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I31">
         <v>110</v>
@@ -8243,10 +8243,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8437,7 +8437,7 @@
         <v>185</v>
       </c>
       <c r="F32">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="G32">
         <v>1.44</v>
@@ -8446,73 +8446,73 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J32">
         <v>4.6</v>
       </c>
       <c r="K32">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M32">
         <v>1.07</v>
       </c>
       <c r="N32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O32">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R32">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S32">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T32">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U32">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W32">
         <v>3.25</v>
       </c>
       <c r="X32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y32">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z32">
         <v>130</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="AB32">
         <v>6.8</v>
       </c>
       <c r="AC32">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD32">
         <v>55</v>
       </c>
       <c r="AE32">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AF32">
         <v>8.800000000000001</v>
@@ -8521,10 +8521,10 @@
         <v>11</v>
       </c>
       <c r="AH32">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI32">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AJ32">
         <v>14</v>
@@ -8548,61 +8548,61 @@
         <v>10.5</v>
       </c>
       <c r="AQ32">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR32">
+        <v>5.7</v>
+      </c>
+      <c r="AS32">
         <v>5.9</v>
-      </c>
-      <c r="AS32">
-        <v>6.2</v>
       </c>
       <c r="AT32">
         <v>5.7</v>
       </c>
       <c r="AU32">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV32">
         <v>32</v>
       </c>
       <c r="AW32">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX32">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY32">
         <v>9</v>
       </c>
       <c r="AZ32">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BA32">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC32">
         <v>15</v>
       </c>
       <c r="BD32">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE32">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BF32">
         <v>7.2</v>
       </c>
       <c r="BG32">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH32">
         <v>3.9</v>
       </c>
       <c r="BI32">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="BJ32">
         <v>16</v>
@@ -8620,7 +8620,7 @@
         <v>4.2</v>
       </c>
       <c r="BO32">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BP32">
         <v>11</v>
@@ -8629,7 +8629,7 @@
         <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
@@ -8647,7 +8647,7 @@
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
@@ -8921,10 +8921,10 @@
         <v>187</v>
       </c>
       <c r="F34">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G34">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H34">
         <v>3.8</v>
@@ -8942,43 +8942,43 @@
         <v>1.45</v>
       </c>
       <c r="M34">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N34">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O34">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P34">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q34">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R34">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S34">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T34">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U34">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V34">
         <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y34">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z34">
         <v>34</v>
@@ -8987,52 +8987,52 @@
         <v>110</v>
       </c>
       <c r="AB34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC34">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC34">
-        <v>9</v>
-      </c>
       <c r="AD34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE34">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF34">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG34">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH34">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI34">
         <v>100</v>
       </c>
       <c r="AJ34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK34">
         <v>32</v>
       </c>
       <c r="AL34">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM34">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO34">
         <v>110</v>
       </c>
       <c r="AP34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR34">
         <v>19.5</v>
@@ -9041,52 +9041,52 @@
         <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU34">
         <v>5.6</v>
       </c>
       <c r="AV34">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW34">
         <v>1.01</v>
       </c>
       <c r="AX34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY34">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA34">
         <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD34">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE34">
         <v>1.01</v>
       </c>
       <c r="BF34">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG34">
         <v>1.01</v>
       </c>
       <c r="BH34">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BI34">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="BJ34">
         <v>13</v>
@@ -9163,10 +9163,10 @@
         <v>188</v>
       </c>
       <c r="F35">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G35">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H35">
         <v>3.95</v>
@@ -9187,7 +9187,7 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O35">
         <v>1.39</v>
@@ -9196,10 +9196,10 @@
         <v>1.75</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S35">
         <v>3.9</v>
@@ -9214,7 +9214,7 @@
         <v>1.28</v>
       </c>
       <c r="W35">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X35">
         <v>14</v>
@@ -9229,7 +9229,7 @@
         <v>110</v>
       </c>
       <c r="AB35">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC35">
         <v>8.199999999999999</v>
@@ -9262,7 +9262,7 @@
         <v>46</v>
       </c>
       <c r="AM35">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN35">
         <v>21</v>
@@ -9280,7 +9280,7 @@
         <v>6.4</v>
       </c>
       <c r="AS35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT35">
         <v>7</v>
@@ -9292,7 +9292,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX35">
         <v>10.5</v>
@@ -9304,10 +9304,10 @@
         <v>17</v>
       </c>
       <c r="BA35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB35">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC35">
         <v>20</v>
@@ -9319,10 +9319,10 @@
         <v>7</v>
       </c>
       <c r="BF35">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH35">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="201">
   <si>
     <t>League</t>
   </si>
@@ -274,15 +274,15 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
     <t>Armenian Premier League</t>
   </si>
   <si>
-    <t>Lithuanian A Lyga</t>
-  </si>
-  <si>
-    <t>Polish Ekstraklasa</t>
-  </si>
-  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
@@ -295,18 +295,18 @@
     <t>Hungarian NB I</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
+    <t>Belgian Pro League</t>
   </si>
   <si>
     <t>Swiss Super League</t>
   </si>
   <si>
-    <t>Belgian Pro League</t>
-  </si>
-  <si>
     <t>French Ligue 1</t>
   </si>
   <si>
@@ -316,6 +316,9 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -367,6 +370,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -376,6 +382,9 @@
     <t>21:30:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -397,15 +406,15 @@
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>FK Banga Gargzdu</t>
+  </si>
+  <si>
+    <t>Rakow Czestochowa</t>
+  </si>
+  <si>
     <t>Alashkert</t>
   </si>
   <si>
-    <t>FK Banga Gargzdu</t>
-  </si>
-  <si>
-    <t>Rakow Czestochowa</t>
-  </si>
-  <si>
     <t>Al Sailiya</t>
   </si>
   <si>
@@ -430,52 +439,64 @@
     <t>Gyori</t>
   </si>
   <si>
+    <t>Al Draih</t>
+  </si>
+  <si>
+    <t>FC Copenhagen</t>
+  </si>
+  <si>
     <t>ES Setif</t>
   </si>
   <si>
-    <t>FC Copenhagen</t>
-  </si>
-  <si>
-    <t>Al Draih</t>
+    <t>Gent</t>
+  </si>
+  <si>
+    <t>Anderlecht</t>
+  </si>
+  <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
+    <t>FC Basel</t>
   </si>
   <si>
     <t>Lugano</t>
   </si>
   <si>
-    <t>Gent</t>
-  </si>
-  <si>
-    <t>Anderlecht</t>
-  </si>
-  <si>
-    <t>Lech Poznan</t>
-  </si>
-  <si>
-    <t>FC Basel</t>
-  </si>
-  <si>
     <t>Toulouse</t>
   </si>
   <si>
     <t>Hibernian</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
     <t>Univ Catolica (Ecu)</t>
   </si>
   <si>
-    <t>Real Sociedad</t>
+    <t>Rayo Zuliano</t>
   </si>
   <si>
     <t>JS El Biar</t>
   </si>
   <si>
+    <t>Estudiantes de Merida</t>
+  </si>
+  <si>
+    <t>Academia Anzoategui FC</t>
+  </si>
+  <si>
     <t>America de Cali S.A</t>
   </si>
   <si>
+    <t>CD Leones del Norte</t>
+  </si>
+  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
-    <t>CD Leones del Norte</t>
+    <t>Puerto Cabello</t>
   </si>
   <si>
     <t>Nautico PE</t>
@@ -499,15 +520,15 @@
     <t>Al-Kholood Club</t>
   </si>
   <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>Gornik Zabrze</t>
+  </si>
+  <si>
     <t>FC Van Yerevan</t>
   </si>
   <si>
-    <t>Panevezys</t>
-  </si>
-  <si>
-    <t>Gornik Zabrze</t>
-  </si>
-  <si>
     <t>Al Arabi (QAT)</t>
   </si>
   <si>
@@ -532,58 +553,70 @@
     <t>Ferencvaros</t>
   </si>
   <si>
+    <t>Al-Quadisiya (KSA)</t>
+  </si>
+  <si>
+    <t>FC Nordsjaelland</t>
+  </si>
+  <si>
     <t>ES Ben Aknoun</t>
   </si>
   <si>
-    <t>FC Nordsjaelland</t>
-  </si>
-  <si>
-    <t>Al-Quadisiya (KSA)</t>
+    <t>Oud-Heverlee Leuven</t>
+  </si>
+  <si>
+    <t>Kortrijk</t>
+  </si>
+  <si>
+    <t>Jagiellonia Bialystock</t>
+  </si>
+  <si>
+    <t>Sion</t>
   </si>
   <si>
     <t>Servette</t>
   </si>
   <si>
-    <t>Oud-Heverlee Leuven</t>
-  </si>
-  <si>
-    <t>Kortrijk</t>
-  </si>
-  <si>
-    <t>Jagiellonia Bialystock</t>
-  </si>
-  <si>
-    <t>Sion</t>
-  </si>
-  <si>
     <t>Lille</t>
   </si>
   <si>
     <t>Hearts</t>
   </si>
   <si>
+    <t>Celta Vigo</t>
+  </si>
+  <si>
     <t>Aucas</t>
   </si>
   <si>
-    <t>Celta Vigo</t>
+    <t>Carabobo FC</t>
   </si>
   <si>
     <t>Olympique Akbou</t>
   </si>
   <si>
+    <t>Universidad de Venezuela</t>
+  </si>
+  <si>
+    <t>Monagas</t>
+  </si>
+  <si>
     <t>Alianza FC Valledupar</t>
   </si>
   <si>
+    <t>Orense Sporting Club</t>
+  </si>
+  <si>
     <t>Cerro Porteno</t>
   </si>
   <si>
-    <t>Orense Sporting Club</t>
+    <t>Deportivo La Guaira</t>
   </si>
   <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>2026-09-02 09:54:29</t>
+    <t>2026-09-02 12:07:40</t>
   </si>
 </sst>
 </file>
@@ -915,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB35"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1165,70 +1198,70 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F2">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H2">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1240,25 +1273,25 @@
         <v>16</v>
       </c>
       <c r="AA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC2">
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1267,34 +1300,34 @@
         <v>50</v>
       </c>
       <c r="AJ2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AK2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR2">
         <v>11</v>
       </c>
       <c r="AS2">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1309,97 +1342,97 @@
         <v>21</v>
       </c>
       <c r="AX2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY2">
         <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
+        <v>30</v>
+      </c>
+      <c r="BB2">
+        <v>46</v>
+      </c>
+      <c r="BC2">
         <v>32</v>
       </c>
-      <c r="BB2">
+      <c r="BD2">
+        <v>40</v>
+      </c>
+      <c r="BE2">
         <v>50</v>
       </c>
-      <c r="BC2">
-        <v>34</v>
-      </c>
-      <c r="BD2">
-        <v>42</v>
-      </c>
-      <c r="BE2">
+      <c r="BF2">
+        <v>21</v>
+      </c>
+      <c r="BG2">
+        <v>9</v>
+      </c>
+      <c r="BH2">
+        <v>3.55</v>
+      </c>
+      <c r="BI2">
+        <v>2.54</v>
+      </c>
+      <c r="BJ2">
+        <v>10.5</v>
+      </c>
+      <c r="BK2">
+        <v>7.4</v>
+      </c>
+      <c r="BL2">
+        <v>640</v>
+      </c>
+      <c r="BM2">
         <v>7.2</v>
       </c>
-      <c r="BF2">
+      <c r="BN2">
+        <v>7</v>
+      </c>
+      <c r="BO2">
+        <v>3.7</v>
+      </c>
+      <c r="BP2">
         <v>38</v>
       </c>
-      <c r="BG2">
-        <v>15</v>
-      </c>
-      <c r="BH2">
-        <v>3.6</v>
-      </c>
-      <c r="BI2">
-        <v>2.52</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>3.55</v>
-      </c>
-      <c r="BL2">
-        <v>720</v>
-      </c>
-      <c r="BM2">
-        <v>4.7</v>
-      </c>
-      <c r="BN2">
-        <v>8.4</v>
-      </c>
-      <c r="BO2">
-        <v>5.2</v>
-      </c>
-      <c r="BP2">
-        <v>42</v>
-      </c>
       <c r="BQ2">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS2">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BT2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BU2">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BV2">
         <v>21</v>
       </c>
       <c r="BW2">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
         <v>42</v>
       </c>
       <c r="BY2">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1407,31 +1440,31 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
         <v>3.9</v>
@@ -1449,28 +1482,28 @@
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T3">
         <v>1.66</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
         <v>21</v>
@@ -1482,7 +1515,7 @@
         <v>22</v>
       </c>
       <c r="AA3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB3">
         <v>12.5</v>
@@ -1509,7 +1542,7 @@
         <v>40</v>
       </c>
       <c r="AJ3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK3">
         <v>27</v>
@@ -1527,7 +1560,7 @@
         <v>25</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
         <v>11.5</v>
@@ -1572,7 +1605,7 @@
         <v>29</v>
       </c>
       <c r="BE3">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BF3">
         <v>17</v>
@@ -1587,10 +1620,10 @@
         <v>3.25</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>120</v>
@@ -1599,10 +1632,10 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
         <v>23</v>
@@ -1611,16 +1644,16 @@
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
         <v>26</v>
@@ -1629,19 +1662,19 @@
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1649,142 +1682,142 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
         <v>2.56</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4">
         <v>16</v>
       </c>
       <c r="AA4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
         <v>12.5</v>
       </c>
       <c r="AE4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI4">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
         <v>50</v>
       </c>
-      <c r="AJ4">
+      <c r="AL4">
+        <v>70</v>
+      </c>
+      <c r="AM4">
+        <v>200</v>
+      </c>
+      <c r="AN4">
         <v>65</v>
       </c>
-      <c r="AK4">
-        <v>44</v>
-      </c>
-      <c r="AL4">
-        <v>60</v>
-      </c>
-      <c r="AM4">
-        <v>140</v>
-      </c>
-      <c r="AN4">
-        <v>46</v>
-      </c>
       <c r="AO4">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
         <v>10</v>
@@ -1793,49 +1826,49 @@
         <v>25</v>
       </c>
       <c r="AX4">
+        <v>18</v>
+      </c>
+      <c r="AY4">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4">
         <v>18.5</v>
       </c>
-      <c r="AY4">
-        <v>12</v>
-      </c>
-      <c r="AZ4">
-        <v>16.5</v>
-      </c>
       <c r="BA4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BC4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD4">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BH4">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -1844,46 +1877,46 @@
         <v>6.6</v>
       </c>
       <c r="BO4">
+        <v>4.7</v>
+      </c>
+      <c r="BP4">
+        <v>32</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>50</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
         <v>5.4</v>
       </c>
-      <c r="BP4">
-        <v>29</v>
-      </c>
-      <c r="BQ4">
-        <v>1.01</v>
-      </c>
-      <c r="BR4">
+      <c r="BU4">
+        <v>4</v>
+      </c>
+      <c r="BV4">
+        <v>23</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
         <v>44</v>
       </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
-      <c r="BT4">
-        <v>5.5</v>
-      </c>
-      <c r="BU4">
-        <v>4.6</v>
-      </c>
-      <c r="BV4">
-        <v>21</v>
-      </c>
-      <c r="BW4">
-        <v>1.01</v>
-      </c>
-      <c r="BX4">
-        <v>38</v>
-      </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1891,19 +1924,19 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
         <v>2.52</v>
@@ -1927,13 +1960,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
         <v>1.53</v>
@@ -1942,13 +1975,13 @@
         <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T5">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="V5">
         <v>1.47</v>
@@ -2014,7 +2047,7 @@
         <v>18</v>
       </c>
       <c r="AQ5">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AR5">
         <v>17</v>
@@ -2023,10 +2056,10 @@
         <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
         <v>10</v>
@@ -2041,7 +2074,7 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
@@ -2053,7 +2086,7 @@
         <v>16</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
@@ -2125,7 +2158,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2133,19 +2166,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
         <v>2.3</v>
@@ -2160,10 +2193,10 @@
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2172,22 +2205,22 @@
         <v>3.85</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
         <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
         <v>2.16</v>
@@ -2211,13 +2244,13 @@
         <v>80</v>
       </c>
       <c r="AB6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE6">
         <v>50</v>
@@ -2256,43 +2289,43 @@
         <v>12</v>
       </c>
       <c r="AQ6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
         <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW6">
         <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY6">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA6">
         <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD6">
         <v>1.01</v>
@@ -2307,22 +2340,22 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6">
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BL6">
         <v>130</v>
       </c>
       <c r="BM6">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BN6">
         <v>5.7</v>
@@ -2334,13 +2367,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BR6">
         <v>32</v>
       </c>
       <c r="BS6">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BT6">
         <v>8</v>
@@ -2352,22 +2385,22 @@
         <v>34</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BX6">
         <v>44</v>
       </c>
       <c r="BY6">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BZ6">
         <v>27</v>
       </c>
       <c r="CA6">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="CB6" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2375,22 +2408,22 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>2.88</v>
       </c>
       <c r="G7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>2.72</v>
@@ -2435,16 +2468,16 @@
         <v>1.99</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
         <v>19.5</v>
@@ -2486,7 +2519,7 @@
         <v>55</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN7">
         <v>36</v>
@@ -2609,7 +2642,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2617,241 +2650,241 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F8">
-        <v>1.17</v>
+        <v>1.79</v>
       </c>
       <c r="G8">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="H8">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
       <c r="Q8">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="S8">
-        <v>2.26</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="U8">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
+        <v>2.06</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8">
+        <v>1.01</v>
+      </c>
+      <c r="AR8">
+        <v>1.01</v>
+      </c>
+      <c r="AS8">
+        <v>1.01</v>
+      </c>
+      <c r="AT8">
+        <v>1.01</v>
+      </c>
+      <c r="AU8">
+        <v>1.01</v>
+      </c>
+      <c r="AV8">
+        <v>1.01</v>
+      </c>
+      <c r="AW8">
+        <v>1.01</v>
+      </c>
+      <c r="AX8">
+        <v>1.01</v>
+      </c>
+      <c r="AY8">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8">
+        <v>1.01</v>
+      </c>
+      <c r="BA8">
+        <v>1.01</v>
+      </c>
+      <c r="BB8">
+        <v>1.01</v>
+      </c>
+      <c r="BC8">
+        <v>1.01</v>
+      </c>
+      <c r="BD8">
+        <v>1.01</v>
+      </c>
+      <c r="BE8">
+        <v>1.01</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>3.7</v>
+      </c>
+      <c r="BI8">
+        <v>2.86</v>
+      </c>
+      <c r="BJ8">
+        <v>11.5</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>140</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
         <v>5.5</v>
       </c>
-      <c r="X8">
-        <v>36</v>
-      </c>
-      <c r="Y8">
-        <v>70</v>
-      </c>
-      <c r="Z8">
-        <v>260</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>11.5</v>
-      </c>
-      <c r="AC8">
-        <v>22</v>
-      </c>
-      <c r="AD8">
-        <v>90</v>
-      </c>
-      <c r="AE8">
-        <v>500</v>
-      </c>
-      <c r="AF8">
-        <v>9</v>
-      </c>
-      <c r="AG8">
-        <v>15</v>
-      </c>
-      <c r="AH8">
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>15.5</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>32</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>9.4</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>44</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
         <v>55</v>
       </c>
-      <c r="AI8">
-        <v>330</v>
-      </c>
-      <c r="AJ8">
-        <v>9.6</v>
-      </c>
-      <c r="AK8">
-        <v>17.5</v>
-      </c>
-      <c r="AL8">
-        <v>60</v>
-      </c>
-      <c r="AM8">
-        <v>320</v>
-      </c>
-      <c r="AN8">
-        <v>4.1</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>22</v>
-      </c>
-      <c r="AQ8">
-        <v>46</v>
-      </c>
-      <c r="AR8">
-        <v>170</v>
-      </c>
-      <c r="AS8">
-        <v>1.01</v>
-      </c>
-      <c r="AT8">
-        <v>7.6</v>
-      </c>
-      <c r="AU8">
-        <v>14.5</v>
-      </c>
-      <c r="AV8">
-        <v>55</v>
-      </c>
-      <c r="AW8">
-        <v>1.01</v>
-      </c>
-      <c r="AX8">
-        <v>6</v>
-      </c>
-      <c r="AY8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8">
-        <v>34</v>
-      </c>
-      <c r="BA8">
-        <v>210</v>
-      </c>
-      <c r="BB8">
-        <v>6.6</v>
-      </c>
-      <c r="BC8">
-        <v>11.5</v>
-      </c>
-      <c r="BD8">
-        <v>36</v>
-      </c>
-      <c r="BE8">
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>26</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
         <v>200</v>
-      </c>
-      <c r="BF8">
-        <v>2.98</v>
-      </c>
-      <c r="BG8">
-        <v>1.01</v>
-      </c>
-      <c r="BH8">
-        <v>5.4</v>
-      </c>
-      <c r="BI8">
-        <v>3.8</v>
-      </c>
-      <c r="BJ8">
-        <v>17</v>
-      </c>
-      <c r="BK8">
-        <v>11</v>
-      </c>
-      <c r="BL8">
-        <v>240</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>4.1</v>
-      </c>
-      <c r="BO8">
-        <v>2.98</v>
-      </c>
-      <c r="BP8">
-        <v>7</v>
-      </c>
-      <c r="BQ8">
-        <v>4.8</v>
-      </c>
-      <c r="BR8">
-        <v>28</v>
-      </c>
-      <c r="BS8">
-        <v>18</v>
-      </c>
-      <c r="BT8">
-        <v>23</v>
-      </c>
-      <c r="BU8">
-        <v>15</v>
-      </c>
-      <c r="BV8">
-        <v>200</v>
-      </c>
-      <c r="BW8">
-        <v>1.01</v>
-      </c>
-      <c r="BX8">
-        <v>150</v>
-      </c>
-      <c r="BY8">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8">
-        <v>9.6</v>
-      </c>
-      <c r="CA8">
-        <v>6.4</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2859,241 +2892,241 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="I9">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="U9">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V9">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS9">
         <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE9">
         <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI9">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK9">
         <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
+        <v>34</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>8</v>
+      </c>
+      <c r="BU9">
+        <v>5</v>
+      </c>
+      <c r="BV9">
         <v>32</v>
       </c>
-      <c r="BS9">
-        <v>1.01</v>
-      </c>
-      <c r="BT9">
-        <v>9.4</v>
-      </c>
-      <c r="BU9">
-        <v>1.01</v>
-      </c>
-      <c r="BV9">
-        <v>46</v>
-      </c>
       <c r="BW9">
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CA9">
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3101,241 +3134,241 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F10">
+        <v>1.18</v>
+      </c>
+      <c r="G10">
+        <v>1.22</v>
+      </c>
+      <c r="H10">
+        <v>17.5</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+      <c r="J10">
+        <v>7.6</v>
+      </c>
+      <c r="K10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.02</v>
+      </c>
+      <c r="N10">
+        <v>5.7</v>
+      </c>
+      <c r="O10">
+        <v>1.17</v>
+      </c>
+      <c r="P10">
+        <v>2.62</v>
+      </c>
+      <c r="Q10">
+        <v>1.5</v>
+      </c>
+      <c r="R10">
+        <v>1.65</v>
+      </c>
+      <c r="S10">
+        <v>2.12</v>
+      </c>
+      <c r="T10">
         <v>2.2</v>
       </c>
-      <c r="G10">
-        <v>2.38</v>
-      </c>
-      <c r="H10">
-        <v>3.25</v>
-      </c>
-      <c r="I10">
-        <v>3.65</v>
-      </c>
-      <c r="J10">
-        <v>3.55</v>
-      </c>
-      <c r="K10">
-        <v>4.3</v>
-      </c>
-      <c r="L10">
-        <v>1.31</v>
-      </c>
-      <c r="M10">
-        <v>1.06</v>
-      </c>
-      <c r="N10">
-        <v>3.95</v>
-      </c>
-      <c r="O10">
-        <v>1.29</v>
-      </c>
-      <c r="P10">
-        <v>2.04</v>
-      </c>
-      <c r="Q10">
-        <v>1.86</v>
-      </c>
-      <c r="R10">
-        <v>1.4</v>
-      </c>
-      <c r="S10">
-        <v>3.15</v>
-      </c>
-      <c r="T10">
-        <v>1.71</v>
-      </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>5.5</v>
       </c>
       <c r="X10">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="Y10">
+        <v>70</v>
+      </c>
+      <c r="Z10">
+        <v>260</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>11.5</v>
+      </c>
+      <c r="AC10">
+        <v>22</v>
+      </c>
+      <c r="AD10">
+        <v>90</v>
+      </c>
+      <c r="AE10">
+        <v>500</v>
+      </c>
+      <c r="AF10">
+        <v>9</v>
+      </c>
+      <c r="AG10">
+        <v>15</v>
+      </c>
+      <c r="AH10">
+        <v>55</v>
+      </c>
+      <c r="AI10">
+        <v>330</v>
+      </c>
+      <c r="AJ10">
+        <v>9.6</v>
+      </c>
+      <c r="AK10">
+        <v>17.5</v>
+      </c>
+      <c r="AL10">
+        <v>60</v>
+      </c>
+      <c r="AM10">
+        <v>320</v>
+      </c>
+      <c r="AN10">
+        <v>4.1</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>22</v>
+      </c>
+      <c r="AQ10">
+        <v>46</v>
+      </c>
+      <c r="AR10">
+        <v>170</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>8.6</v>
+      </c>
+      <c r="AU10">
+        <v>14.5</v>
+      </c>
+      <c r="AV10">
+        <v>55</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>6</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>34</v>
+      </c>
+      <c r="BA10">
+        <v>210</v>
+      </c>
+      <c r="BB10">
+        <v>6.6</v>
+      </c>
+      <c r="BC10">
+        <v>11.5</v>
+      </c>
+      <c r="BD10">
+        <v>36</v>
+      </c>
+      <c r="BE10">
+        <v>200</v>
+      </c>
+      <c r="BF10">
+        <v>2.98</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>5.4</v>
+      </c>
+      <c r="BI10">
+        <v>3.8</v>
+      </c>
+      <c r="BJ10">
         <v>17</v>
       </c>
-      <c r="Z10">
-        <v>30</v>
-      </c>
-      <c r="AA10">
-        <v>75</v>
-      </c>
-      <c r="AB10">
-        <v>13.5</v>
-      </c>
-      <c r="AC10">
-        <v>10</v>
-      </c>
-      <c r="AD10">
-        <v>17.5</v>
-      </c>
-      <c r="AE10">
-        <v>48</v>
-      </c>
-      <c r="AF10">
-        <v>18.5</v>
-      </c>
-      <c r="AG10">
-        <v>13.5</v>
-      </c>
-      <c r="AH10">
-        <v>21</v>
-      </c>
-      <c r="AI10">
-        <v>55</v>
-      </c>
-      <c r="AJ10">
-        <v>36</v>
-      </c>
-      <c r="AK10">
-        <v>29</v>
-      </c>
-      <c r="AL10">
-        <v>44</v>
-      </c>
-      <c r="AM10">
-        <v>100</v>
-      </c>
-      <c r="AN10">
-        <v>21</v>
-      </c>
-      <c r="AO10">
-        <v>42</v>
-      </c>
-      <c r="AP10">
-        <v>11.5</v>
-      </c>
-      <c r="AQ10">
-        <v>12.5</v>
-      </c>
-      <c r="AR10">
-        <v>21</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>8</v>
-      </c>
-      <c r="AU10">
-        <v>6.2</v>
-      </c>
-      <c r="AV10">
-        <v>10.5</v>
-      </c>
-      <c r="AW10">
-        <v>1.01</v>
-      </c>
-      <c r="AX10">
+      <c r="BK10">
         <v>11</v>
       </c>
-      <c r="AY10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ10">
-        <v>12</v>
-      </c>
-      <c r="BA10">
-        <v>34</v>
-      </c>
-      <c r="BB10">
-        <v>21</v>
-      </c>
-      <c r="BC10">
-        <v>17</v>
-      </c>
-      <c r="BD10">
-        <v>1.01</v>
-      </c>
-      <c r="BE10">
-        <v>1.01</v>
-      </c>
-      <c r="BF10">
-        <v>12</v>
-      </c>
-      <c r="BG10">
-        <v>1.01</v>
-      </c>
-      <c r="BH10">
-        <v>3.6</v>
-      </c>
-      <c r="BI10">
-        <v>3.25</v>
-      </c>
-      <c r="BJ10">
-        <v>11</v>
-      </c>
-      <c r="BK10">
-        <v>1.01</v>
-      </c>
       <c r="BL10">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="BM10">
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO10">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="BP10">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT10">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BU10">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BV10">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB10" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3343,25 +3376,25 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G11">
         <v>6.6</v>
       </c>
       <c r="H11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I11">
         <v>1.59</v>
@@ -3397,7 +3430,7 @@
         <v>2.16</v>
       </c>
       <c r="T11">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U11">
         <v>2.34</v>
@@ -3406,7 +3439,7 @@
         <v>2.68</v>
       </c>
       <c r="W11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X11">
         <v>38</v>
@@ -3415,19 +3448,19 @@
         <v>14</v>
       </c>
       <c r="Z11">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA11">
         <v>15.5</v>
       </c>
       <c r="AB11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC11">
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE11">
         <v>15</v>
@@ -3484,7 +3517,7 @@
         <v>9.6</v>
       </c>
       <c r="AW11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX11">
         <v>1.01</v>
@@ -3505,7 +3538,7 @@
         <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
         <v>1.01</v>
@@ -3577,7 +3610,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3585,34 +3618,34 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F12">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G12">
         <v>1.95</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12">
         <v>4.9</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3630,10 +3663,10 @@
         <v>2.04</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
         <v>3.05</v>
@@ -3651,112 +3684,112 @@
         <v>2.04</v>
       </c>
       <c r="X12">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA12">
         <v>120</v>
       </c>
       <c r="AB12">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE12">
         <v>65</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG12">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH12">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI12">
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK12">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AL12">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM12">
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP12">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR12">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AS12">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="AT12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
         <v>7.8</v>
       </c>
       <c r="AV12">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="AW12">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY12">
         <v>9</v>
       </c>
       <c r="AZ12">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="BA12">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB12">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BE12">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BF12">
         <v>10</v>
       </c>
       <c r="BG12">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3819,7 +3852,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3827,16 +3860,16 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F13">
         <v>1.4</v>
@@ -3848,22 +3881,22 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J13">
         <v>4.5</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L13">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O13">
         <v>1.34</v>
@@ -3881,13 +3914,13 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U13">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W13">
         <v>3.15</v>
@@ -3941,10 +3974,10 @@
         <v>290</v>
       </c>
       <c r="AN13">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO13">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
         <v>10.5</v>
@@ -3953,22 +3986,22 @@
         <v>20</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT13">
         <v>5.3</v>
       </c>
       <c r="AU13">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX13">
         <v>5.8</v>
@@ -3977,10 +4010,10 @@
         <v>8</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB13">
         <v>9</v>
@@ -3989,19 +4022,19 @@
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF13">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH13">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BI13">
         <v>2.8</v>
@@ -4061,7 +4094,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4069,16 +4102,16 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F14">
         <v>4.6</v>
@@ -4120,13 +4153,13 @@
         <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T14">
         <v>1.67</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
         <v>2.24</v>
@@ -4138,7 +4171,7 @@
         <v>24</v>
       </c>
       <c r="Y14">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z14">
         <v>12.5</v>
@@ -4150,7 +4183,7 @@
         <v>22</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
@@ -4165,7 +4198,7 @@
         <v>19</v>
       </c>
       <c r="AH14">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
         <v>30</v>
@@ -4207,7 +4240,7 @@
         <v>9</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW14">
         <v>15</v>
@@ -4228,10 +4261,10 @@
         <v>38</v>
       </c>
       <c r="BC14">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BD14">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BE14">
         <v>34</v>
@@ -4249,7 +4282,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK14">
         <v>6.8</v>
@@ -4303,7 +4336,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4311,16 +4344,16 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F15">
         <v>1.46</v>
@@ -4338,7 +4371,7 @@
         <v>4.5</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4362,7 +4395,7 @@
         <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="T15">
         <v>1.77</v>
@@ -4545,7 +4578,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4553,16 +4586,16 @@
         <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F16">
         <v>2.78</v>
@@ -4583,7 +4616,7 @@
         <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M16">
         <v>1.08</v>
@@ -4592,13 +4625,13 @@
         <v>3.3</v>
       </c>
       <c r="O16">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P16">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Q16">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>1.3</v>
@@ -4607,7 +4640,7 @@
         <v>3.8</v>
       </c>
       <c r="T16">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="U16">
         <v>2.06</v>
@@ -4616,7 +4649,7 @@
         <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X16">
         <v>14.5</v>
@@ -4634,13 +4667,13 @@
         <v>12.5</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16">
         <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF16">
         <v>23</v>
@@ -4649,7 +4682,7 @@
         <v>15</v>
       </c>
       <c r="AH16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI16">
         <v>55</v>
@@ -4679,19 +4712,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR16">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS16">
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16">
         <v>1.01</v>
@@ -4703,19 +4736,19 @@
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA16">
         <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC16">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE16">
         <v>1.01</v>
@@ -4730,7 +4763,7 @@
         <v>3.55</v>
       </c>
       <c r="BI16">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="BJ16">
         <v>11.5</v>
@@ -4787,7 +4820,7 @@
         <v>5</v>
       </c>
       <c r="CB16" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4795,31 +4828,31 @@
         <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F17">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G17">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H17">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
         <v>4.1</v>
@@ -4837,34 +4870,34 @@
         <v>1.25</v>
       </c>
       <c r="P17">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q17">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R17">
         <v>1.44</v>
       </c>
       <c r="S17">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T17">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X17">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Y17">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z17">
         <v>26</v>
@@ -4873,79 +4906,79 @@
         <v>55</v>
       </c>
       <c r="AB17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC17">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH17">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI17">
+        <v>46</v>
+      </c>
+      <c r="AJ17">
         <v>38</v>
       </c>
-      <c r="AJ17">
+      <c r="AK17">
+        <v>32</v>
+      </c>
+      <c r="AL17">
         <v>42</v>
-      </c>
-      <c r="AK17">
-        <v>29</v>
-      </c>
-      <c r="AL17">
-        <v>36</v>
       </c>
       <c r="AM17">
         <v>75</v>
       </c>
       <c r="AN17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP17">
         <v>13.5</v>
       </c>
       <c r="AQ17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS17">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
+        <v>10.5</v>
+      </c>
+      <c r="AU17">
+        <v>7.2</v>
+      </c>
+      <c r="AV17">
         <v>11</v>
       </c>
-      <c r="AU17">
-        <v>7.6</v>
-      </c>
-      <c r="AV17">
-        <v>10.5</v>
-      </c>
       <c r="AW17">
         <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
@@ -4954,19 +4987,19 @@
         <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD17">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BH17">
         <v>4.5</v>
@@ -4987,7 +5020,7 @@
         <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO17">
         <v>4.4</v>
@@ -5029,7 +5062,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5037,34 +5070,34 @@
         <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F18">
         <v>3.95</v>
       </c>
       <c r="G18">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H18">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I18">
         <v>1.95</v>
       </c>
       <c r="J18">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5073,34 +5106,34 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O18">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P18">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R18">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="T18">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U18">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
         <v>2.04</v>
       </c>
       <c r="W18">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5211,10 +5244,10 @@
         <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BI18">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BJ18">
         <v>11</v>
@@ -5223,7 +5256,7 @@
         <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM18">
         <v>1.01</v>
@@ -5232,305 +5265,305 @@
         <v>9.6</v>
       </c>
       <c r="BO18">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY18">
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F19">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="G19">
+        <v>6.6</v>
+      </c>
+      <c r="H19">
+        <v>1.52</v>
+      </c>
+      <c r="I19">
+        <v>1.62</v>
+      </c>
+      <c r="J19">
+        <v>4.7</v>
+      </c>
+      <c r="K19">
+        <v>6</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>5.7</v>
+      </c>
+      <c r="O19">
+        <v>1.18</v>
+      </c>
+      <c r="P19">
+        <v>2.62</v>
+      </c>
+      <c r="Q19">
+        <v>1.52</v>
+      </c>
+      <c r="R19">
+        <v>1.64</v>
+      </c>
+      <c r="S19">
+        <v>2.28</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>2.62</v>
+      </c>
+      <c r="W19">
+        <v>1.17</v>
+      </c>
+      <c r="X19">
+        <v>34</v>
+      </c>
+      <c r="Y19">
+        <v>15</v>
+      </c>
+      <c r="Z19">
+        <v>14</v>
+      </c>
+      <c r="AA19">
+        <v>18.5</v>
+      </c>
+      <c r="AB19">
+        <v>36</v>
+      </c>
+      <c r="AC19">
+        <v>14.5</v>
+      </c>
+      <c r="AD19">
+        <v>13</v>
+      </c>
+      <c r="AE19">
+        <v>18.5</v>
+      </c>
+      <c r="AF19">
+        <v>70</v>
+      </c>
+      <c r="AG19">
+        <v>32</v>
+      </c>
+      <c r="AH19">
+        <v>25</v>
+      </c>
+      <c r="AI19">
+        <v>34</v>
+      </c>
+      <c r="AJ19">
+        <v>160</v>
+      </c>
+      <c r="AK19">
+        <v>80</v>
+      </c>
+      <c r="AL19">
+        <v>70</v>
+      </c>
+      <c r="AM19">
+        <v>85</v>
+      </c>
+      <c r="AN19">
+        <v>70</v>
+      </c>
+      <c r="AO19">
+        <v>5.9</v>
+      </c>
+      <c r="AP19">
+        <v>19.5</v>
+      </c>
+      <c r="AQ19">
+        <v>9</v>
+      </c>
+      <c r="AR19">
+        <v>8.6</v>
+      </c>
+      <c r="AS19">
+        <v>11</v>
+      </c>
+      <c r="AT19">
+        <v>20</v>
+      </c>
+      <c r="AU19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV19">
+        <v>7.8</v>
+      </c>
+      <c r="AW19">
+        <v>11</v>
+      </c>
+      <c r="AX19">
+        <v>4.5</v>
+      </c>
+      <c r="AY19">
+        <v>18</v>
+      </c>
+      <c r="AZ19">
+        <v>14.5</v>
+      </c>
+      <c r="BA19">
+        <v>20</v>
+      </c>
+      <c r="BB19">
+        <v>4.6</v>
+      </c>
+      <c r="BC19">
+        <v>4.5</v>
+      </c>
+      <c r="BD19">
+        <v>4.5</v>
+      </c>
+      <c r="BE19">
+        <v>4.5</v>
+      </c>
+      <c r="BF19">
+        <v>4.5</v>
+      </c>
+      <c r="BG19">
+        <v>4.4</v>
+      </c>
+      <c r="BH19">
+        <v>5.4</v>
+      </c>
+      <c r="BI19">
+        <v>3.55</v>
+      </c>
+      <c r="BJ19">
+        <v>12</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
         <v>110</v>
       </c>
-      <c r="H19">
-        <v>1.1</v>
-      </c>
-      <c r="I19">
-        <v>110</v>
-      </c>
-      <c r="J19">
-        <v>1.24</v>
-      </c>
-      <c r="K19">
-        <v>320</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>1.09</v>
-      </c>
-      <c r="O19">
-        <v>1.02</v>
-      </c>
-      <c r="P19">
-        <v>1.09</v>
-      </c>
-      <c r="Q19">
-        <v>1.43</v>
-      </c>
-      <c r="R19">
-        <v>1.08</v>
-      </c>
-      <c r="S19">
-        <v>1.44</v>
-      </c>
-      <c r="T19">
-        <v>1.01</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.1</v>
-      </c>
-      <c r="W19">
-        <v>1.1</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.01</v>
-      </c>
-      <c r="AQ19">
-        <v>1.01</v>
-      </c>
-      <c r="AR19">
-        <v>1.01</v>
-      </c>
-      <c r="AS19">
-        <v>1.01</v>
-      </c>
-      <c r="AT19">
-        <v>1.01</v>
-      </c>
-      <c r="AU19">
-        <v>1.01</v>
-      </c>
-      <c r="AV19">
-        <v>1.01</v>
-      </c>
-      <c r="AW19">
-        <v>1.01</v>
-      </c>
-      <c r="AX19">
-        <v>1.01</v>
-      </c>
-      <c r="AY19">
-        <v>1.01</v>
-      </c>
-      <c r="AZ19">
-        <v>1.01</v>
-      </c>
-      <c r="BA19">
-        <v>1.01</v>
-      </c>
-      <c r="BB19">
-        <v>1.01</v>
-      </c>
-      <c r="BC19">
-        <v>1.01</v>
-      </c>
-      <c r="BD19">
-        <v>1.01</v>
-      </c>
-      <c r="BE19">
-        <v>1.01</v>
-      </c>
-      <c r="BF19">
-        <v>1.01</v>
-      </c>
-      <c r="BG19">
-        <v>1.01</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
       <c r="BM19">
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO19">
         <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ19">
         <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F20">
         <v>2.18</v>
@@ -5539,7 +5572,7 @@
         <v>2.24</v>
       </c>
       <c r="H20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I20">
         <v>3.3</v>
@@ -5551,31 +5584,31 @@
         <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M20">
         <v>1.03</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O20">
         <v>1.17</v>
       </c>
       <c r="P20">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q20">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R20">
         <v>1.71</v>
       </c>
       <c r="S20">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U20">
         <v>2.74</v>
@@ -5584,16 +5617,16 @@
         <v>1.43</v>
       </c>
       <c r="W20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X20">
         <v>28</v>
       </c>
       <c r="Y20">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="Z20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA20">
         <v>60</v>
@@ -5611,16 +5644,16 @@
         <v>30</v>
       </c>
       <c r="AF20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG20">
         <v>12</v>
       </c>
       <c r="AH20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI20">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AJ20">
         <v>32</v>
@@ -5629,19 +5662,19 @@
         <v>20</v>
       </c>
       <c r="AL20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM20">
         <v>55</v>
       </c>
       <c r="AN20">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO20">
         <v>18.5</v>
       </c>
       <c r="AP20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ20">
         <v>18.5</v>
@@ -5650,7 +5683,7 @@
         <v>25</v>
       </c>
       <c r="AS20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT20">
         <v>14.5</v>
@@ -5689,16 +5722,16 @@
         <v>42</v>
       </c>
       <c r="BF20">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH20">
         <v>5.4</v>
       </c>
       <c r="BI20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ20">
         <v>9.6</v>
@@ -5713,10 +5746,10 @@
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
         <v>16</v>
@@ -5737,7 +5770,7 @@
         <v>5.6</v>
       </c>
       <c r="BV20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
@@ -5749,72 +5782,72 @@
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F21">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="G21">
-        <v>6.6</v>
+        <v>110</v>
       </c>
       <c r="H21">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="I21">
-        <v>1.61</v>
+        <v>110</v>
       </c>
       <c r="J21">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="K21">
-        <v>5.9</v>
+        <v>320</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>1.09</v>
+      </c>
+      <c r="O21">
         <v>1.02</v>
       </c>
-      <c r="N21">
-        <v>5.7</v>
-      </c>
-      <c r="O21">
-        <v>1.17</v>
-      </c>
       <c r="P21">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="Q21">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="R21">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="S21">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5823,181 +5856,181 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.64</v>
+        <v>1.1</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
         <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
         <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
         <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
         <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
         <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6005,178 +6038,178 @@
         <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="G22">
+        <v>1.72</v>
+      </c>
+      <c r="H22">
+        <v>5.7</v>
+      </c>
+      <c r="I22">
+        <v>6.2</v>
+      </c>
+      <c r="J22">
+        <v>4.1</v>
+      </c>
+      <c r="K22">
+        <v>4.4</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.06</v>
+      </c>
+      <c r="N22">
+        <v>4.2</v>
+      </c>
+      <c r="O22">
+        <v>1.25</v>
+      </c>
+      <c r="P22">
         <v>2.1</v>
       </c>
-      <c r="H22">
-        <v>3.55</v>
-      </c>
-      <c r="I22">
-        <v>3.95</v>
-      </c>
-      <c r="J22">
-        <v>3.8</v>
-      </c>
-      <c r="K22">
-        <v>4.2</v>
-      </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.05</v>
-      </c>
-      <c r="N22">
-        <v>2.38</v>
-      </c>
-      <c r="O22">
-        <v>1.22</v>
-      </c>
-      <c r="P22">
-        <v>2.2</v>
-      </c>
       <c r="Q22">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="R22">
         <v>1.47</v>
       </c>
       <c r="S22">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T22">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="W22">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="X22">
+        <v>20</v>
+      </c>
+      <c r="Y22">
         <v>23</v>
       </c>
-      <c r="Y22">
+      <c r="Z22">
+        <v>55</v>
+      </c>
+      <c r="AA22">
+        <v>170</v>
+      </c>
+      <c r="AB22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>24</v>
+      </c>
+      <c r="AE22">
+        <v>90</v>
+      </c>
+      <c r="AF22">
+        <v>11.5</v>
+      </c>
+      <c r="AG22">
+        <v>11</v>
+      </c>
+      <c r="AH22">
+        <v>21</v>
+      </c>
+      <c r="AI22">
+        <v>85</v>
+      </c>
+      <c r="AJ22">
         <v>18</v>
       </c>
-      <c r="Z22">
-        <v>32</v>
-      </c>
-      <c r="AA22">
-        <v>75</v>
-      </c>
-      <c r="AB22">
-        <v>12.5</v>
-      </c>
-      <c r="AC22">
+      <c r="AK22">
+        <v>18</v>
+      </c>
+      <c r="AL22">
+        <v>40</v>
+      </c>
+      <c r="AM22">
+        <v>120</v>
+      </c>
+      <c r="AN22">
         <v>9.6</v>
       </c>
-      <c r="AD22">
-        <v>16.5</v>
-      </c>
-      <c r="AE22">
-        <v>42</v>
-      </c>
-      <c r="AF22">
-        <v>15.5</v>
-      </c>
-      <c r="AG22">
-        <v>11.5</v>
-      </c>
-      <c r="AH22">
-        <v>17</v>
-      </c>
-      <c r="AI22">
-        <v>46</v>
-      </c>
-      <c r="AJ22">
-        <v>26</v>
-      </c>
-      <c r="AK22">
-        <v>21</v>
-      </c>
-      <c r="AL22">
-        <v>32</v>
-      </c>
-      <c r="AM22">
-        <v>80</v>
-      </c>
-      <c r="AN22">
-        <v>12.5</v>
-      </c>
       <c r="AO22">
+        <v>100</v>
+      </c>
+      <c r="AP22">
+        <v>14.5</v>
+      </c>
+      <c r="AQ22">
+        <v>16</v>
+      </c>
+      <c r="AR22">
         <v>34</v>
       </c>
-      <c r="AP22">
-        <v>15</v>
-      </c>
-      <c r="AQ22">
-        <v>13.5</v>
-      </c>
-      <c r="AR22">
-        <v>22</v>
-      </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT22">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>19</v>
+      </c>
+      <c r="AW22">
+        <v>7.2</v>
+      </c>
+      <c r="AX22">
+        <v>9</v>
+      </c>
+      <c r="AY22">
+        <v>8.6</v>
+      </c>
+      <c r="AZ22">
+        <v>5.7</v>
+      </c>
+      <c r="BA22">
+        <v>7.2</v>
+      </c>
+      <c r="BB22">
+        <v>14</v>
+      </c>
+      <c r="BC22">
+        <v>14.5</v>
+      </c>
+      <c r="BD22">
+        <v>6.4</v>
+      </c>
+      <c r="BE22">
+        <v>7.2</v>
+      </c>
+      <c r="BF22">
         <v>7.8</v>
       </c>
-      <c r="AV22">
-        <v>12</v>
-      </c>
-      <c r="AW22">
-        <v>30</v>
-      </c>
-      <c r="AX22">
-        <v>12.5</v>
-      </c>
-      <c r="AY22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22">
-        <v>12.5</v>
-      </c>
-      <c r="BA22">
-        <v>34</v>
-      </c>
-      <c r="BB22">
-        <v>20</v>
-      </c>
-      <c r="BC22">
-        <v>17</v>
-      </c>
-      <c r="BD22">
-        <v>23</v>
-      </c>
-      <c r="BE22">
-        <v>1.01</v>
-      </c>
-      <c r="BF22">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG22">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6239,117 +6272,117 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="F23">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="G23">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="H23">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I23">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="O23">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q23">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="S23">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
         <v>1.76</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W23">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="X23">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Y23">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="Z23">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AA23">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AB23">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AC23">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AD23">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AE23">
+        <v>110</v>
+      </c>
+      <c r="AF23">
+        <v>13.5</v>
+      </c>
+      <c r="AG23">
+        <v>12.5</v>
+      </c>
+      <c r="AH23">
+        <v>25</v>
+      </c>
+      <c r="AI23">
         <v>90</v>
       </c>
-      <c r="AF23">
-        <v>11.5</v>
-      </c>
-      <c r="AG23">
-        <v>11</v>
-      </c>
-      <c r="AH23">
-        <v>23</v>
-      </c>
-      <c r="AI23">
-        <v>85</v>
-      </c>
       <c r="AJ23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK23">
         <v>18</v>
@@ -6358,560 +6391,560 @@
         <v>36</v>
       </c>
       <c r="AM23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN23">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO23">
         <v>100</v>
       </c>
       <c r="AP23">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AR23">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="AS23">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV23">
         <v>18.5</v>
       </c>
       <c r="AW23">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AX23">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY23">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ23">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="BA23">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB23">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC23">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD23">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE23">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BF23">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG23">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU23">
         <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F24">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="G24">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="H24">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="I24">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="J24">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K24">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R24">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="S24">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="T24">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="U24">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="W24">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="X24">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z24">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AA24">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AB24">
+        <v>16.5</v>
+      </c>
+      <c r="AC24">
         <v>13.5</v>
       </c>
-      <c r="AC24">
-        <v>14</v>
-      </c>
       <c r="AD24">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AE24">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AF24">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG24">
+        <v>12.5</v>
+      </c>
+      <c r="AH24">
+        <v>19.5</v>
+      </c>
+      <c r="AI24">
+        <v>55</v>
+      </c>
+      <c r="AJ24">
+        <v>22</v>
+      </c>
+      <c r="AK24">
+        <v>18.5</v>
+      </c>
+      <c r="AL24">
+        <v>29</v>
+      </c>
+      <c r="AM24">
+        <v>70</v>
+      </c>
+      <c r="AN24">
+        <v>7.2</v>
+      </c>
+      <c r="AO24">
+        <v>42</v>
+      </c>
+      <c r="AP24">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24">
+        <v>20</v>
+      </c>
+      <c r="AR24">
+        <v>1.01</v>
+      </c>
+      <c r="AS24">
+        <v>1.01</v>
+      </c>
+      <c r="AT24">
         <v>11</v>
-      </c>
-      <c r="AH24">
-        <v>25</v>
-      </c>
-      <c r="AI24">
-        <v>90</v>
-      </c>
-      <c r="AJ24">
-        <v>17</v>
-      </c>
-      <c r="AK24">
-        <v>18</v>
-      </c>
-      <c r="AL24">
-        <v>36</v>
-      </c>
-      <c r="AM24">
-        <v>110</v>
-      </c>
-      <c r="AN24">
-        <v>7</v>
-      </c>
-      <c r="AO24">
-        <v>100</v>
-      </c>
-      <c r="AP24">
-        <v>4.3</v>
-      </c>
-      <c r="AQ24">
-        <v>4.3</v>
-      </c>
-      <c r="AR24">
-        <v>4.7</v>
-      </c>
-      <c r="AS24">
-        <v>4.9</v>
-      </c>
-      <c r="AT24">
-        <v>9.6</v>
       </c>
       <c r="AU24">
         <v>10</v>
       </c>
       <c r="AV24">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AW24">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY24">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ24">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BA24">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD24">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BE24">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG24">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BI24">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BJ24">
+        <v>10.5</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>85</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>5.5</v>
+      </c>
+      <c r="BO24">
+        <v>3.9</v>
+      </c>
+      <c r="BP24">
         <v>12</v>
       </c>
-      <c r="BK24">
-        <v>1.01</v>
-      </c>
-      <c r="BL24">
-        <v>130</v>
-      </c>
-      <c r="BM24">
-        <v>1.01</v>
-      </c>
-      <c r="BN24">
-        <v>5.1</v>
-      </c>
-      <c r="BO24">
-        <v>3.35</v>
-      </c>
-      <c r="BP24">
-        <v>11</v>
-      </c>
       <c r="BQ24">
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BS24">
         <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU24">
         <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BY24">
         <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CA24">
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F25">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="G25">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="H25">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="I25">
-        <v>5.3</v>
+        <v>2.82</v>
       </c>
       <c r="J25">
+        <v>3.95</v>
+      </c>
+      <c r="K25">
         <v>4.4</v>
       </c>
-      <c r="K25">
-        <v>5.1</v>
-      </c>
       <c r="L25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M25">
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O25">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="Q25">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R25">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="S25">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T25">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="U25">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="V25">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="W25">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="X25">
+        <v>34</v>
+      </c>
+      <c r="Y25">
+        <v>22</v>
+      </c>
+      <c r="Z25">
+        <v>28</v>
+      </c>
+      <c r="AA25">
+        <v>48</v>
+      </c>
+      <c r="AB25">
+        <v>21</v>
+      </c>
+      <c r="AC25">
+        <v>12.5</v>
+      </c>
+      <c r="AD25">
+        <v>16</v>
+      </c>
+      <c r="AE25">
+        <v>32</v>
+      </c>
+      <c r="AF25">
+        <v>26</v>
+      </c>
+      <c r="AG25">
+        <v>15.5</v>
+      </c>
+      <c r="AH25">
+        <v>17.5</v>
+      </c>
+      <c r="AI25">
         <v>36</v>
       </c>
-      <c r="Y25">
-        <v>32</v>
-      </c>
-      <c r="Z25">
-        <v>50</v>
-      </c>
-      <c r="AA25">
-        <v>120</v>
-      </c>
-      <c r="AB25">
+      <c r="AJ25">
+        <v>44</v>
+      </c>
+      <c r="AK25">
+        <v>29</v>
+      </c>
+      <c r="AL25">
+        <v>36</v>
+      </c>
+      <c r="AM25">
+        <v>65</v>
+      </c>
+      <c r="AN25">
+        <v>16</v>
+      </c>
+      <c r="AO25">
+        <v>17.5</v>
+      </c>
+      <c r="AP25">
+        <v>21</v>
+      </c>
+      <c r="AQ25">
+        <v>13</v>
+      </c>
+      <c r="AR25">
         <v>16.5</v>
       </c>
-      <c r="AC25">
-        <v>13.5</v>
-      </c>
-      <c r="AD25">
-        <v>23</v>
-      </c>
-      <c r="AE25">
-        <v>60</v>
-      </c>
-      <c r="AF25">
-        <v>16.5</v>
-      </c>
-      <c r="AG25">
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
         <v>12.5</v>
       </c>
-      <c r="AH25">
-        <v>19.5</v>
-      </c>
-      <c r="AI25">
-        <v>55</v>
-      </c>
-      <c r="AJ25">
-        <v>22</v>
-      </c>
-      <c r="AK25">
-        <v>18.5</v>
-      </c>
-      <c r="AL25">
-        <v>29</v>
-      </c>
-      <c r="AM25">
-        <v>70</v>
-      </c>
-      <c r="AN25">
-        <v>7.2</v>
-      </c>
-      <c r="AO25">
-        <v>42</v>
-      </c>
-      <c r="AP25">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25">
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
+        <v>9.6</v>
+      </c>
+      <c r="AW25">
+        <v>18</v>
+      </c>
+      <c r="AX25">
+        <v>17.5</v>
+      </c>
+      <c r="AY25">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25">
+        <v>10.5</v>
+      </c>
+      <c r="BA25">
+        <v>21</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>17</v>
+      </c>
+      <c r="BD25">
         <v>20</v>
       </c>
-      <c r="AR25">
-        <v>1.01</v>
-      </c>
-      <c r="AS25">
-        <v>1.01</v>
-      </c>
-      <c r="AT25">
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
         <v>11</v>
       </c>
-      <c r="AU25">
-        <v>9</v>
-      </c>
-      <c r="AV25">
-        <v>15</v>
-      </c>
-      <c r="AW25">
-        <v>1.01</v>
-      </c>
-      <c r="AX25">
+      <c r="BG25">
         <v>10.5</v>
       </c>
-      <c r="AY25">
-        <v>8.4</v>
-      </c>
-      <c r="AZ25">
-        <v>12.5</v>
-      </c>
-      <c r="BA25">
-        <v>1.01</v>
-      </c>
-      <c r="BB25">
-        <v>14</v>
-      </c>
-      <c r="BC25">
-        <v>12</v>
-      </c>
-      <c r="BD25">
-        <v>18.5</v>
-      </c>
-      <c r="BE25">
-        <v>1.01</v>
-      </c>
-      <c r="BF25">
-        <v>5</v>
-      </c>
-      <c r="BG25">
-        <v>1.01</v>
-      </c>
       <c r="BH25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI25">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BJ25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK25">
         <v>1.01</v>
@@ -6923,291 +6956,291 @@
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BO25">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP25">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
+        <v>28</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>7.6</v>
+      </c>
+      <c r="BU25">
+        <v>4.8</v>
+      </c>
+      <c r="BV25">
         <v>22</v>
       </c>
-      <c r="BS25">
-        <v>1.01</v>
-      </c>
-      <c r="BT25">
-        <v>10.5</v>
-      </c>
-      <c r="BU25">
-        <v>1.01</v>
-      </c>
-      <c r="BV25">
-        <v>38</v>
-      </c>
       <c r="BW25">
         <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F26">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="H26">
-        <v>2.66</v>
+        <v>3.65</v>
       </c>
       <c r="I26">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K26">
+        <v>4.2</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.05</v>
+      </c>
+      <c r="N26">
         <v>4.6</v>
       </c>
-      <c r="L26">
+      <c r="O26">
         <v>1.23</v>
       </c>
-      <c r="M26">
-        <v>1.01</v>
-      </c>
-      <c r="N26">
-        <v>5.8</v>
-      </c>
-      <c r="O26">
-        <v>1.18</v>
-      </c>
       <c r="P26">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="S26">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="T26">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="U26">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="X26">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Y26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z26">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA26">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AB26">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AC26">
+        <v>11</v>
+      </c>
+      <c r="AD26">
+        <v>18.5</v>
+      </c>
+      <c r="AE26">
+        <v>48</v>
+      </c>
+      <c r="AF26">
+        <v>17</v>
+      </c>
+      <c r="AG26">
         <v>12.5</v>
       </c>
-      <c r="AD26">
-        <v>16</v>
-      </c>
-      <c r="AE26">
-        <v>32</v>
-      </c>
-      <c r="AF26">
-        <v>26</v>
-      </c>
-      <c r="AG26">
-        <v>15.5</v>
-      </c>
       <c r="AH26">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI26">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AJ26">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AK26">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AL26">
         <v>36</v>
       </c>
       <c r="AM26">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AN26">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AO26">
-        <v>17.5</v>
+        <v>38</v>
       </c>
       <c r="AP26">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AQ26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR26">
+        <v>1.01</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>10</v>
+      </c>
+      <c r="AU26">
+        <v>7.8</v>
+      </c>
+      <c r="AV26">
+        <v>12</v>
+      </c>
+      <c r="AW26">
+        <v>1.01</v>
+      </c>
+      <c r="AX26">
+        <v>12</v>
+      </c>
+      <c r="AY26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26">
+        <v>12.5</v>
+      </c>
+      <c r="BA26">
+        <v>34</v>
+      </c>
+      <c r="BB26">
+        <v>20</v>
+      </c>
+      <c r="BC26">
         <v>16.5</v>
       </c>
-      <c r="AS26">
-        <v>32</v>
-      </c>
-      <c r="AT26">
-        <v>12.5</v>
-      </c>
-      <c r="AU26">
-        <v>7.6</v>
-      </c>
-      <c r="AV26">
-        <v>9.6</v>
-      </c>
-      <c r="AW26">
-        <v>18</v>
-      </c>
-      <c r="AX26">
-        <v>17.5</v>
-      </c>
-      <c r="AY26">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26">
-        <v>10.5</v>
-      </c>
-      <c r="BA26">
-        <v>21</v>
-      </c>
-      <c r="BB26">
-        <v>1.01</v>
-      </c>
-      <c r="BC26">
-        <v>17</v>
-      </c>
       <c r="BD26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE26">
         <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG26">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
         <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
         <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7215,19 +7248,19 @@
         <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E27" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F27">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G27">
         <v>3.7</v>
@@ -7239,7 +7272,7 @@
         <v>2.26</v>
       </c>
       <c r="J27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7251,7 +7284,7 @@
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
         <v>1.37</v>
@@ -7260,10 +7293,10 @@
         <v>1.85</v>
       </c>
       <c r="Q27">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
         <v>3.9</v>
@@ -7275,13 +7308,13 @@
         <v>2.08</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W27">
         <v>1.37</v>
       </c>
       <c r="X27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y27">
         <v>9.199999999999999</v>
@@ -7299,10 +7332,10 @@
         <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE27">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF27">
         <v>25</v>
@@ -7311,16 +7344,16 @@
         <v>15</v>
       </c>
       <c r="AH27">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI27">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ27">
         <v>75</v>
       </c>
       <c r="AK27">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL27">
         <v>60</v>
@@ -7329,10 +7362,10 @@
         <v>110</v>
       </c>
       <c r="AN27">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO27">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP27">
         <v>11.5</v>
@@ -7368,7 +7401,7 @@
         <v>17</v>
       </c>
       <c r="BA27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB27">
         <v>60</v>
@@ -7383,7 +7416,7 @@
         <v>40</v>
       </c>
       <c r="BF27">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BG27">
         <v>17.5</v>
@@ -7449,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7457,37 +7490,37 @@
         <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F28">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G28">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H28">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I28">
         <v>2.96</v>
       </c>
       <c r="J28">
+        <v>3.4</v>
+      </c>
+      <c r="K28">
         <v>3.5</v>
       </c>
-      <c r="K28">
-        <v>3.6</v>
-      </c>
       <c r="L28">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M28">
         <v>1.06</v>
@@ -7502,7 +7535,7 @@
         <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R28">
         <v>1.39</v>
@@ -7514,13 +7547,13 @@
         <v>1.7</v>
       </c>
       <c r="U28">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V28">
         <v>1.51</v>
       </c>
       <c r="W28">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X28">
         <v>18</v>
@@ -7577,7 +7610,7 @@
         <v>30</v>
       </c>
       <c r="AP28">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ28">
         <v>10.5</v>
@@ -7610,7 +7643,7 @@
         <v>14</v>
       </c>
       <c r="BA28">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BB28">
         <v>8.4</v>
@@ -7691,526 +7724,526 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>2.02</v>
+      </c>
+      <c r="H29">
+        <v>4.1</v>
+      </c>
+      <c r="I29">
+        <v>4.3</v>
+      </c>
+      <c r="J29">
+        <v>3.75</v>
+      </c>
+      <c r="K29">
+        <v>3.85</v>
+      </c>
+      <c r="L29">
+        <v>1.42</v>
+      </c>
+      <c r="M29">
+        <v>1.07</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29">
+        <v>1.31</v>
+      </c>
+      <c r="P29">
+        <v>2.02</v>
+      </c>
+      <c r="Q29">
+        <v>1.96</v>
+      </c>
+      <c r="R29">
+        <v>1.39</v>
+      </c>
+      <c r="S29">
+        <v>3.45</v>
+      </c>
+      <c r="T29">
+        <v>1.81</v>
+      </c>
+      <c r="U29">
+        <v>2.16</v>
+      </c>
+      <c r="V29">
+        <v>1.31</v>
+      </c>
+      <c r="W29">
+        <v>1.98</v>
+      </c>
+      <c r="X29">
+        <v>15</v>
+      </c>
+      <c r="Y29">
+        <v>15.5</v>
+      </c>
+      <c r="Z29">
+        <v>30</v>
+      </c>
+      <c r="AA29">
+        <v>90</v>
+      </c>
+      <c r="AB29">
+        <v>9.6</v>
+      </c>
+      <c r="AC29">
+        <v>8.4</v>
+      </c>
+      <c r="AD29">
+        <v>17</v>
+      </c>
+      <c r="AE29">
+        <v>55</v>
+      </c>
+      <c r="AF29">
+        <v>12.5</v>
+      </c>
+      <c r="AG29">
+        <v>10.5</v>
+      </c>
+      <c r="AH29">
+        <v>18.5</v>
+      </c>
+      <c r="AI29">
+        <v>60</v>
+      </c>
+      <c r="AJ29">
+        <v>24</v>
+      </c>
+      <c r="AK29">
+        <v>21</v>
+      </c>
+      <c r="AL29">
+        <v>36</v>
+      </c>
+      <c r="AM29">
+        <v>100</v>
+      </c>
+      <c r="AN29">
+        <v>14</v>
+      </c>
+      <c r="AO29">
+        <v>55</v>
+      </c>
+      <c r="AP29">
+        <v>13.5</v>
+      </c>
+      <c r="AQ29">
+        <v>14</v>
+      </c>
+      <c r="AR29">
+        <v>26</v>
+      </c>
+      <c r="AS29">
+        <v>70</v>
+      </c>
+      <c r="AT29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>15</v>
+      </c>
+      <c r="AW29">
+        <v>44</v>
+      </c>
+      <c r="AX29">
+        <v>11</v>
+      </c>
+      <c r="AY29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29">
+        <v>17</v>
+      </c>
+      <c r="BA29">
+        <v>50</v>
+      </c>
+      <c r="BB29">
+        <v>21</v>
+      </c>
+      <c r="BC29">
+        <v>18.5</v>
+      </c>
+      <c r="BD29">
+        <v>32</v>
+      </c>
+      <c r="BE29">
         <v>80</v>
       </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" t="s">
-        <v>182</v>
-      </c>
-      <c r="F29">
-        <v>1.87</v>
-      </c>
-      <c r="G29">
-        <v>2.06</v>
-      </c>
-      <c r="H29">
+      <c r="BF29">
+        <v>12.5</v>
+      </c>
+      <c r="BG29">
+        <v>44</v>
+      </c>
+      <c r="BH29">
+        <v>3.45</v>
+      </c>
+      <c r="BI29">
+        <v>3.1</v>
+      </c>
+      <c r="BJ29">
+        <v>12.5</v>
+      </c>
+      <c r="BK29">
+        <v>8.6</v>
+      </c>
+      <c r="BL29">
+        <v>140</v>
+      </c>
+      <c r="BM29">
+        <v>10.5</v>
+      </c>
+      <c r="BN29">
+        <v>4.7</v>
+      </c>
+      <c r="BO29">
         <v>4.2</v>
       </c>
-      <c r="I29">
-        <v>4.8</v>
-      </c>
-      <c r="J29">
-        <v>3.55</v>
-      </c>
-      <c r="K29">
-        <v>3.95</v>
-      </c>
-      <c r="L29">
-        <v>1.31</v>
-      </c>
-      <c r="M29">
-        <v>1.05</v>
-      </c>
-      <c r="N29">
-        <v>2.82</v>
-      </c>
-      <c r="O29">
-        <v>1.3</v>
-      </c>
-      <c r="P29">
-        <v>1.84</v>
-      </c>
-      <c r="Q29">
-        <v>1.86</v>
-      </c>
-      <c r="R29">
-        <v>1.23</v>
-      </c>
-      <c r="S29">
-        <v>3.35</v>
-      </c>
-      <c r="T29">
-        <v>1.8</v>
-      </c>
-      <c r="U29">
-        <v>2</v>
-      </c>
-      <c r="V29">
-        <v>1.26</v>
-      </c>
-      <c r="W29">
-        <v>1.94</v>
-      </c>
-      <c r="X29">
-        <v>17</v>
-      </c>
-      <c r="Y29">
-        <v>19</v>
-      </c>
-      <c r="Z29">
-        <v>40</v>
-      </c>
-      <c r="AA29">
-        <v>120</v>
-      </c>
-      <c r="AB29">
-        <v>11</v>
-      </c>
-      <c r="AC29">
-        <v>10</v>
-      </c>
-      <c r="AD29">
-        <v>22</v>
-      </c>
-      <c r="AE29">
-        <v>70</v>
-      </c>
-      <c r="AF29">
-        <v>15</v>
-      </c>
-      <c r="AG29">
-        <v>13</v>
-      </c>
-      <c r="AH29">
-        <v>23</v>
-      </c>
-      <c r="AI29">
-        <v>80</v>
-      </c>
-      <c r="AJ29">
-        <v>28</v>
-      </c>
-      <c r="AK29">
-        <v>26</v>
-      </c>
-      <c r="AL29">
+      <c r="BP29">
+        <v>14.5</v>
+      </c>
+      <c r="BQ29">
+        <v>12.5</v>
+      </c>
+      <c r="BR29">
+        <v>29</v>
+      </c>
+      <c r="BS29">
+        <v>8.4</v>
+      </c>
+      <c r="BT29">
+        <v>7.6</v>
+      </c>
+      <c r="BU29">
+        <v>6.6</v>
+      </c>
+      <c r="BV29">
+        <v>36</v>
+      </c>
+      <c r="BW29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX29">
         <v>46</v>
       </c>
-      <c r="AM29">
-        <v>130</v>
-      </c>
-      <c r="AN29">
+      <c r="BY29">
+        <v>9.6</v>
+      </c>
+      <c r="BZ29">
+        <v>25</v>
+      </c>
+      <c r="CA29">
         <v>17.5</v>
       </c>
-      <c r="AO29">
-        <v>80</v>
-      </c>
-      <c r="AP29">
-        <v>10</v>
-      </c>
-      <c r="AQ29">
-        <v>11</v>
-      </c>
-      <c r="AR29">
-        <v>6.6</v>
-      </c>
-      <c r="AS29">
-        <v>4.3</v>
-      </c>
-      <c r="AT29">
-        <v>6.6</v>
-      </c>
-      <c r="AU29">
-        <v>6.2</v>
-      </c>
-      <c r="AV29">
-        <v>13</v>
-      </c>
-      <c r="AW29">
-        <v>4.2</v>
-      </c>
-      <c r="AX29">
-        <v>9</v>
-      </c>
-      <c r="AY29">
-        <v>7.8</v>
-      </c>
-      <c r="AZ29">
-        <v>13.5</v>
-      </c>
-      <c r="BA29">
-        <v>4.2</v>
-      </c>
-      <c r="BB29">
-        <v>16.5</v>
-      </c>
-      <c r="BC29">
-        <v>15.5</v>
-      </c>
-      <c r="BD29">
-        <v>4.8</v>
-      </c>
-      <c r="BE29">
-        <v>4.2</v>
-      </c>
-      <c r="BF29">
-        <v>10.5</v>
-      </c>
-      <c r="BG29">
-        <v>4.2</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.01</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.01</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>1.01</v>
-      </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.01</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>1.01</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>1.01</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>1.01</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>1.01</v>
-      </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
-        <v>1.01</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>1.01</v>
-      </c>
       <c r="CB29" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="G30">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I30">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K30">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L30">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="O30">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P30">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="Q30">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="R30">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="S30">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T30">
         <v>1.82</v>
       </c>
       <c r="U30">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="W30">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X30">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Y30">
+        <v>19</v>
+      </c>
+      <c r="Z30">
+        <v>40</v>
+      </c>
+      <c r="AA30">
+        <v>120</v>
+      </c>
+      <c r="AB30">
+        <v>11</v>
+      </c>
+      <c r="AC30">
+        <v>10</v>
+      </c>
+      <c r="AD30">
+        <v>22</v>
+      </c>
+      <c r="AE30">
+        <v>70</v>
+      </c>
+      <c r="AF30">
+        <v>15</v>
+      </c>
+      <c r="AG30">
+        <v>13</v>
+      </c>
+      <c r="AH30">
+        <v>23</v>
+      </c>
+      <c r="AI30">
+        <v>80</v>
+      </c>
+      <c r="AJ30">
+        <v>28</v>
+      </c>
+      <c r="AK30">
+        <v>26</v>
+      </c>
+      <c r="AL30">
+        <v>46</v>
+      </c>
+      <c r="AM30">
+        <v>130</v>
+      </c>
+      <c r="AN30">
+        <v>17.5</v>
+      </c>
+      <c r="AO30">
+        <v>80</v>
+      </c>
+      <c r="AP30">
+        <v>10</v>
+      </c>
+      <c r="AQ30">
+        <v>11</v>
+      </c>
+      <c r="AR30">
+        <v>6.6</v>
+      </c>
+      <c r="AS30">
+        <v>4.3</v>
+      </c>
+      <c r="AT30">
+        <v>6.6</v>
+      </c>
+      <c r="AU30">
+        <v>6.2</v>
+      </c>
+      <c r="AV30">
+        <v>13</v>
+      </c>
+      <c r="AW30">
+        <v>4.2</v>
+      </c>
+      <c r="AX30">
+        <v>9</v>
+      </c>
+      <c r="AY30">
+        <v>7.8</v>
+      </c>
+      <c r="AZ30">
+        <v>13.5</v>
+      </c>
+      <c r="BA30">
+        <v>4.2</v>
+      </c>
+      <c r="BB30">
+        <v>16.5</v>
+      </c>
+      <c r="BC30">
         <v>15.5</v>
       </c>
-      <c r="Z30">
-        <v>30</v>
-      </c>
-      <c r="AA30">
-        <v>90</v>
-      </c>
-      <c r="AB30">
-        <v>9.6</v>
-      </c>
-      <c r="AC30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD30">
-        <v>17</v>
-      </c>
-      <c r="AE30">
-        <v>55</v>
-      </c>
-      <c r="AF30">
-        <v>12.5</v>
-      </c>
-      <c r="AG30">
+      <c r="BD30">
+        <v>4.8</v>
+      </c>
+      <c r="BE30">
+        <v>4.2</v>
+      </c>
+      <c r="BF30">
         <v>10.5</v>
       </c>
-      <c r="AH30">
-        <v>18.5</v>
-      </c>
-      <c r="AI30">
-        <v>60</v>
-      </c>
-      <c r="AJ30">
-        <v>24</v>
-      </c>
-      <c r="AK30">
-        <v>21</v>
-      </c>
-      <c r="AL30">
-        <v>36</v>
-      </c>
-      <c r="AM30">
-        <v>100</v>
-      </c>
-      <c r="AN30">
-        <v>14.5</v>
-      </c>
-      <c r="AO30">
-        <v>55</v>
-      </c>
-      <c r="AP30">
-        <v>13.5</v>
-      </c>
-      <c r="AQ30">
-        <v>14</v>
-      </c>
-      <c r="AR30">
-        <v>26</v>
-      </c>
-      <c r="AS30">
-        <v>70</v>
-      </c>
-      <c r="AT30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU30">
-        <v>7.6</v>
-      </c>
-      <c r="AV30">
-        <v>15</v>
-      </c>
-      <c r="AW30">
-        <v>44</v>
-      </c>
-      <c r="AX30">
-        <v>11</v>
-      </c>
-      <c r="AY30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ30">
-        <v>17</v>
-      </c>
-      <c r="BA30">
-        <v>50</v>
-      </c>
-      <c r="BB30">
-        <v>21</v>
-      </c>
-      <c r="BC30">
-        <v>18.5</v>
-      </c>
-      <c r="BD30">
-        <v>32</v>
-      </c>
-      <c r="BE30">
-        <v>75</v>
-      </c>
-      <c r="BF30">
-        <v>12.5</v>
-      </c>
       <c r="BG30">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="BH30">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F31">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="G31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="I31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="K31">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8219,23 +8252,23 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="O31">
+        <v>1.28</v>
+      </c>
+      <c r="P31">
+        <v>1.24</v>
+      </c>
+      <c r="Q31">
+        <v>1.01</v>
+      </c>
+      <c r="R31">
+        <v>1.18</v>
+      </c>
+      <c r="S31">
         <v>1.02</v>
       </c>
-      <c r="P31">
-        <v>1.09</v>
-      </c>
-      <c r="Q31">
-        <v>1.47</v>
-      </c>
-      <c r="R31">
-        <v>1.08</v>
-      </c>
-      <c r="S31">
-        <v>1.48</v>
-      </c>
       <c r="T31">
         <v>1.01</v>
       </c>
@@ -8243,10 +8276,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8417,249 +8450,249 @@
         <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F32">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="G32">
-        <v>1.44</v>
+        <v>110</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>1.12</v>
       </c>
       <c r="I32">
-        <v>12.5</v>
+        <v>110</v>
       </c>
       <c r="J32">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="L32">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="O32">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P32">
-        <v>1.85</v>
+        <v>1.09</v>
       </c>
       <c r="Q32">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="R32">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="S32">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="T32">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W32">
-        <v>3.25</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
         <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
         <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
         <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8667,34 +8700,34 @@
         <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
         <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E33" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8703,22 +8736,22 @@
         <v>1.01</v>
       </c>
       <c r="N33">
+        <v>1.24</v>
+      </c>
+      <c r="O33">
         <v>1.26</v>
       </c>
-      <c r="O33">
-        <v>1.33</v>
-      </c>
       <c r="P33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q33">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="R33">
         <v>1.18</v>
       </c>
       <c r="S33">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
         <v>1.01</v>
@@ -8901,491 +8934,1459 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
         <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F34">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="G34">
-        <v>2.34</v>
+        <v>100</v>
       </c>
       <c r="H34">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="I34">
-        <v>4.3</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="K34">
-        <v>3.4</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N34">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="O34">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="P34">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q34">
-        <v>2.36</v>
+        <v>1.31</v>
       </c>
       <c r="R34">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S34">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="T34">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="U34">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W34">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y34">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z34">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA34">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB34">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC34">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD34">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE34">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF34">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH34">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI34">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK34">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL34">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34">
+        <v>1.01</v>
+      </c>
+      <c r="AR34">
+        <v>1.01</v>
+      </c>
+      <c r="AS34">
+        <v>1.01</v>
+      </c>
+      <c r="AT34">
+        <v>1.01</v>
+      </c>
+      <c r="AU34">
+        <v>1.01</v>
+      </c>
+      <c r="AV34">
+        <v>1.01</v>
+      </c>
+      <c r="AW34">
+        <v>1.01</v>
+      </c>
+      <c r="AX34">
+        <v>1.01</v>
+      </c>
+      <c r="AY34">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34">
+        <v>1.01</v>
+      </c>
+      <c r="BA34">
+        <v>1.01</v>
+      </c>
+      <c r="BB34">
+        <v>1.01</v>
+      </c>
+      <c r="BC34">
+        <v>1.01</v>
+      </c>
+      <c r="BD34">
+        <v>1.01</v>
+      </c>
+      <c r="BE34">
+        <v>1.01</v>
+      </c>
+      <c r="BF34">
+        <v>1.01</v>
+      </c>
+      <c r="BG34">
+        <v>1.01</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.01</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.01</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.01</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.01</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.01</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.01</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.01</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.01</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="s">
         <v>200</v>
-      </c>
-      <c r="AN34">
-        <v>34</v>
-      </c>
-      <c r="AO34">
-        <v>110</v>
-      </c>
-      <c r="AP34">
-        <v>7.6</v>
-      </c>
-      <c r="AQ34">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR34">
-        <v>19.5</v>
-      </c>
-      <c r="AS34">
-        <v>1.01</v>
-      </c>
-      <c r="AT34">
-        <v>6.6</v>
-      </c>
-      <c r="AU34">
-        <v>5.6</v>
-      </c>
-      <c r="AV34">
-        <v>12</v>
-      </c>
-      <c r="AW34">
-        <v>1.01</v>
-      </c>
-      <c r="AX34">
-        <v>9.4</v>
-      </c>
-      <c r="AY34">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ34">
-        <v>18.5</v>
-      </c>
-      <c r="BA34">
-        <v>1.01</v>
-      </c>
-      <c r="BB34">
-        <v>1.01</v>
-      </c>
-      <c r="BC34">
-        <v>21</v>
-      </c>
-      <c r="BD34">
-        <v>1.01</v>
-      </c>
-      <c r="BE34">
-        <v>1.01</v>
-      </c>
-      <c r="BF34">
-        <v>1.01</v>
-      </c>
-      <c r="BG34">
-        <v>1.01</v>
-      </c>
-      <c r="BH34">
-        <v>3.25</v>
-      </c>
-      <c r="BI34">
-        <v>2.3</v>
-      </c>
-      <c r="BJ34">
-        <v>13</v>
-      </c>
-      <c r="BK34">
-        <v>1.01</v>
-      </c>
-      <c r="BL34">
-        <v>230</v>
-      </c>
-      <c r="BM34">
-        <v>1.01</v>
-      </c>
-      <c r="BN34">
-        <v>5.7</v>
-      </c>
-      <c r="BO34">
-        <v>3.75</v>
-      </c>
-      <c r="BP34">
-        <v>23</v>
-      </c>
-      <c r="BQ34">
-        <v>1.01</v>
-      </c>
-      <c r="BR34">
-        <v>48</v>
-      </c>
-      <c r="BS34">
-        <v>1.01</v>
-      </c>
-      <c r="BT34">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU34">
-        <v>5.2</v>
-      </c>
-      <c r="BV34">
-        <v>46</v>
-      </c>
-      <c r="BW34">
-        <v>1.01</v>
-      </c>
-      <c r="BX34">
-        <v>70</v>
-      </c>
-      <c r="BY34">
-        <v>1.01</v>
-      </c>
-      <c r="BZ34">
-        <v>55</v>
-      </c>
-      <c r="CA34">
-        <v>1.01</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
         <v>120</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F35">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="G35">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="H35">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="I35">
+        <v>12.5</v>
+      </c>
+      <c r="J35">
         <v>4.6</v>
       </c>
-      <c r="J35">
-        <v>3.3</v>
-      </c>
       <c r="K35">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L35">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M35">
         <v>1.08</v>
       </c>
       <c r="N35">
+        <v>3.5</v>
+      </c>
+      <c r="O35">
+        <v>1.35</v>
+      </c>
+      <c r="P35">
+        <v>1.85</v>
+      </c>
+      <c r="Q35">
+        <v>2.04</v>
+      </c>
+      <c r="R35">
+        <v>1.32</v>
+      </c>
+      <c r="S35">
+        <v>3.6</v>
+      </c>
+      <c r="T35">
+        <v>2.36</v>
+      </c>
+      <c r="U35">
+        <v>1.65</v>
+      </c>
+      <c r="V35">
+        <v>1.09</v>
+      </c>
+      <c r="W35">
+        <v>3.2</v>
+      </c>
+      <c r="X35">
+        <v>18</v>
+      </c>
+      <c r="Y35">
+        <v>36</v>
+      </c>
+      <c r="Z35">
+        <v>130</v>
+      </c>
+      <c r="AA35">
+        <v>650</v>
+      </c>
+      <c r="AB35">
+        <v>7.8</v>
+      </c>
+      <c r="AC35">
+        <v>14</v>
+      </c>
+      <c r="AD35">
+        <v>55</v>
+      </c>
+      <c r="AE35">
+        <v>300</v>
+      </c>
+      <c r="AF35">
+        <v>7.6</v>
+      </c>
+      <c r="AG35">
+        <v>12.5</v>
+      </c>
+      <c r="AH35">
+        <v>42</v>
+      </c>
+      <c r="AI35">
+        <v>250</v>
+      </c>
+      <c r="AJ35">
+        <v>14</v>
+      </c>
+      <c r="AK35">
+        <v>21</v>
+      </c>
+      <c r="AL35">
+        <v>65</v>
+      </c>
+      <c r="AM35">
+        <v>310</v>
+      </c>
+      <c r="AN35">
+        <v>8.6</v>
+      </c>
+      <c r="AO35">
+        <v>540</v>
+      </c>
+      <c r="AP35">
+        <v>10.5</v>
+      </c>
+      <c r="AQ35">
+        <v>20</v>
+      </c>
+      <c r="AR35">
+        <v>5</v>
+      </c>
+      <c r="AS35">
+        <v>5.1</v>
+      </c>
+      <c r="AT35">
+        <v>5.8</v>
+      </c>
+      <c r="AU35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV35">
+        <v>4.7</v>
+      </c>
+      <c r="AW35">
+        <v>5.1</v>
+      </c>
+      <c r="AX35">
+        <v>6.4</v>
+      </c>
+      <c r="AY35">
+        <v>9</v>
+      </c>
+      <c r="AZ35">
+        <v>4.6</v>
+      </c>
+      <c r="BA35">
+        <v>5.1</v>
+      </c>
+      <c r="BB35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC35">
+        <v>14.5</v>
+      </c>
+      <c r="BD35">
+        <v>4.8</v>
+      </c>
+      <c r="BE35">
+        <v>5.1</v>
+      </c>
+      <c r="BF35">
+        <v>6.2</v>
+      </c>
+      <c r="BG35">
+        <v>5.1</v>
+      </c>
+      <c r="BH35">
+        <v>3.9</v>
+      </c>
+      <c r="BI35">
+        <v>3</v>
+      </c>
+      <c r="BJ35">
+        <v>16</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>280</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>4.2</v>
+      </c>
+      <c r="BO35">
+        <v>2.88</v>
+      </c>
+      <c r="BP35">
+        <v>11</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>36</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>16</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>140</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>130</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>23</v>
+      </c>
+      <c r="CA35">
+        <v>1.01</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36">
+        <v>2.02</v>
+      </c>
+      <c r="G36">
+        <v>2.14</v>
+      </c>
+      <c r="H36">
+        <v>4.3</v>
+      </c>
+      <c r="I36">
+        <v>4.9</v>
+      </c>
+      <c r="J36">
+        <v>3.2</v>
+      </c>
+      <c r="K36">
+        <v>3.55</v>
+      </c>
+      <c r="L36">
+        <v>1.45</v>
+      </c>
+      <c r="M36">
+        <v>1.1</v>
+      </c>
+      <c r="N36">
+        <v>2.84</v>
+      </c>
+      <c r="O36">
+        <v>1.46</v>
+      </c>
+      <c r="P36">
+        <v>1.61</v>
+      </c>
+      <c r="Q36">
+        <v>2.34</v>
+      </c>
+      <c r="R36">
+        <v>1.21</v>
+      </c>
+      <c r="S36">
+        <v>4.1</v>
+      </c>
+      <c r="T36">
+        <v>1.87</v>
+      </c>
+      <c r="U36">
+        <v>1.68</v>
+      </c>
+      <c r="V36">
+        <v>1.25</v>
+      </c>
+      <c r="W36">
+        <v>1.87</v>
+      </c>
+      <c r="X36">
+        <v>12.5</v>
+      </c>
+      <c r="Y36">
+        <v>16</v>
+      </c>
+      <c r="Z36">
+        <v>38</v>
+      </c>
+      <c r="AA36">
+        <v>140</v>
+      </c>
+      <c r="AB36">
+        <v>8.6</v>
+      </c>
+      <c r="AC36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD36">
+        <v>24</v>
+      </c>
+      <c r="AE36">
+        <v>90</v>
+      </c>
+      <c r="AF36">
+        <v>14</v>
+      </c>
+      <c r="AG36">
+        <v>13</v>
+      </c>
+      <c r="AH36">
+        <v>29</v>
+      </c>
+      <c r="AI36">
+        <v>110</v>
+      </c>
+      <c r="AJ36">
+        <v>34</v>
+      </c>
+      <c r="AK36">
+        <v>34</v>
+      </c>
+      <c r="AL36">
+        <v>65</v>
+      </c>
+      <c r="AM36">
+        <v>210</v>
+      </c>
+      <c r="AN36">
+        <v>30</v>
+      </c>
+      <c r="AO36">
+        <v>130</v>
+      </c>
+      <c r="AP36">
+        <v>7.6</v>
+      </c>
+      <c r="AQ36">
+        <v>9.6</v>
+      </c>
+      <c r="AR36">
+        <v>1.01</v>
+      </c>
+      <c r="AS36">
+        <v>1.01</v>
+      </c>
+      <c r="AT36">
+        <v>5.4</v>
+      </c>
+      <c r="AU36">
+        <v>5.7</v>
+      </c>
+      <c r="AV36">
+        <v>14</v>
+      </c>
+      <c r="AW36">
+        <v>1.01</v>
+      </c>
+      <c r="AX36">
+        <v>8.4</v>
+      </c>
+      <c r="AY36">
+        <v>7.8</v>
+      </c>
+      <c r="AZ36">
+        <v>17</v>
+      </c>
+      <c r="BA36">
+        <v>1.01</v>
+      </c>
+      <c r="BB36">
+        <v>19.5</v>
+      </c>
+      <c r="BC36">
+        <v>19</v>
+      </c>
+      <c r="BD36">
+        <v>1.01</v>
+      </c>
+      <c r="BE36">
+        <v>1.01</v>
+      </c>
+      <c r="BF36">
+        <v>17.5</v>
+      </c>
+      <c r="BG36">
+        <v>1.01</v>
+      </c>
+      <c r="BH36">
+        <v>3.25</v>
+      </c>
+      <c r="BI36">
+        <v>2.32</v>
+      </c>
+      <c r="BJ36">
+        <v>13.5</v>
+      </c>
+      <c r="BK36">
+        <v>1.01</v>
+      </c>
+      <c r="BL36">
+        <v>230</v>
+      </c>
+      <c r="BM36">
+        <v>1.01</v>
+      </c>
+      <c r="BN36">
+        <v>5.5</v>
+      </c>
+      <c r="BO36">
+        <v>3.6</v>
+      </c>
+      <c r="BP36">
+        <v>21</v>
+      </c>
+      <c r="BQ36">
+        <v>1.01</v>
+      </c>
+      <c r="BR36">
+        <v>48</v>
+      </c>
+      <c r="BS36">
+        <v>1.01</v>
+      </c>
+      <c r="BT36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU36">
+        <v>5.5</v>
+      </c>
+      <c r="BV36">
+        <v>50</v>
+      </c>
+      <c r="BW36">
+        <v>1.01</v>
+      </c>
+      <c r="BX36">
+        <v>75</v>
+      </c>
+      <c r="BY36">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36">
+        <v>50</v>
+      </c>
+      <c r="CA36">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.01</v>
+      </c>
+      <c r="N37">
+        <v>1.26</v>
+      </c>
+      <c r="O37">
+        <v>1.33</v>
+      </c>
+      <c r="P37">
+        <v>1.25</v>
+      </c>
+      <c r="Q37">
+        <v>1.33</v>
+      </c>
+      <c r="R37">
+        <v>1.18</v>
+      </c>
+      <c r="S37">
+        <v>1.34</v>
+      </c>
+      <c r="T37">
+        <v>1.01</v>
+      </c>
+      <c r="U37">
+        <v>1.01</v>
+      </c>
+      <c r="V37">
+        <v>1.01</v>
+      </c>
+      <c r="W37">
+        <v>1.01</v>
+      </c>
+      <c r="X37">
+        <v>1000</v>
+      </c>
+      <c r="Y37">
+        <v>1000</v>
+      </c>
+      <c r="Z37">
+        <v>1000</v>
+      </c>
+      <c r="AA37">
+        <v>1000</v>
+      </c>
+      <c r="AB37">
+        <v>1000</v>
+      </c>
+      <c r="AC37">
+        <v>1000</v>
+      </c>
+      <c r="AD37">
+        <v>1000</v>
+      </c>
+      <c r="AE37">
+        <v>1000</v>
+      </c>
+      <c r="AF37">
+        <v>1000</v>
+      </c>
+      <c r="AG37">
+        <v>1000</v>
+      </c>
+      <c r="AH37">
+        <v>1000</v>
+      </c>
+      <c r="AI37">
+        <v>1000</v>
+      </c>
+      <c r="AJ37">
+        <v>1000</v>
+      </c>
+      <c r="AK37">
+        <v>1000</v>
+      </c>
+      <c r="AL37">
+        <v>1000</v>
+      </c>
+      <c r="AM37">
+        <v>1000</v>
+      </c>
+      <c r="AN37">
+        <v>1000</v>
+      </c>
+      <c r="AO37">
+        <v>1000</v>
+      </c>
+      <c r="AP37">
+        <v>1.01</v>
+      </c>
+      <c r="AQ37">
+        <v>1.01</v>
+      </c>
+      <c r="AR37">
+        <v>1.01</v>
+      </c>
+      <c r="AS37">
+        <v>1.01</v>
+      </c>
+      <c r="AT37">
+        <v>1.01</v>
+      </c>
+      <c r="AU37">
+        <v>1.01</v>
+      </c>
+      <c r="AV37">
+        <v>1.01</v>
+      </c>
+      <c r="AW37">
+        <v>1.01</v>
+      </c>
+      <c r="AX37">
+        <v>1.01</v>
+      </c>
+      <c r="AY37">
+        <v>1.01</v>
+      </c>
+      <c r="AZ37">
+        <v>1.01</v>
+      </c>
+      <c r="BA37">
+        <v>1.01</v>
+      </c>
+      <c r="BB37">
+        <v>1.01</v>
+      </c>
+      <c r="BC37">
+        <v>1.01</v>
+      </c>
+      <c r="BD37">
+        <v>1.01</v>
+      </c>
+      <c r="BE37">
+        <v>1.01</v>
+      </c>
+      <c r="BF37">
+        <v>1.01</v>
+      </c>
+      <c r="BG37">
+        <v>1.01</v>
+      </c>
+      <c r="BH37">
+        <v>1000</v>
+      </c>
+      <c r="BI37">
+        <v>1.01</v>
+      </c>
+      <c r="BJ37">
+        <v>1000</v>
+      </c>
+      <c r="BK37">
+        <v>1.01</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>1.01</v>
+      </c>
+      <c r="BN37">
+        <v>1000</v>
+      </c>
+      <c r="BO37">
+        <v>1.01</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>1.01</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>1.01</v>
+      </c>
+      <c r="BT37">
+        <v>1000</v>
+      </c>
+      <c r="BU37">
+        <v>1.01</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>1.01</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38">
+        <v>1.08</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38">
+        <v>1.08</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
+        <v>1.08</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>1.01</v>
+      </c>
+      <c r="M38">
+        <v>1.01</v>
+      </c>
+      <c r="N38">
+        <v>1.01</v>
+      </c>
+      <c r="O38">
+        <v>1.01</v>
+      </c>
+      <c r="P38">
+        <v>1.24</v>
+      </c>
+      <c r="Q38">
+        <v>1.01</v>
+      </c>
+      <c r="R38">
+        <v>1.18</v>
+      </c>
+      <c r="S38">
+        <v>1.02</v>
+      </c>
+      <c r="T38">
+        <v>1.01</v>
+      </c>
+      <c r="U38">
+        <v>1.01</v>
+      </c>
+      <c r="V38">
+        <v>1.01</v>
+      </c>
+      <c r="W38">
+        <v>1.01</v>
+      </c>
+      <c r="X38">
+        <v>1000</v>
+      </c>
+      <c r="Y38">
+        <v>1000</v>
+      </c>
+      <c r="Z38">
+        <v>1000</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
+        <v>1000</v>
+      </c>
+      <c r="AC38">
+        <v>1000</v>
+      </c>
+      <c r="AD38">
+        <v>1000</v>
+      </c>
+      <c r="AE38">
+        <v>1000</v>
+      </c>
+      <c r="AF38">
+        <v>1000</v>
+      </c>
+      <c r="AG38">
+        <v>1000</v>
+      </c>
+      <c r="AH38">
+        <v>1000</v>
+      </c>
+      <c r="AI38">
+        <v>1000</v>
+      </c>
+      <c r="AJ38">
+        <v>1000</v>
+      </c>
+      <c r="AK38">
+        <v>1000</v>
+      </c>
+      <c r="AL38">
+        <v>1000</v>
+      </c>
+      <c r="AM38">
+        <v>1000</v>
+      </c>
+      <c r="AN38">
+        <v>1000</v>
+      </c>
+      <c r="AO38">
+        <v>1000</v>
+      </c>
+      <c r="AP38">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38">
+        <v>1.01</v>
+      </c>
+      <c r="AR38">
+        <v>1.01</v>
+      </c>
+      <c r="AS38">
+        <v>1.01</v>
+      </c>
+      <c r="AT38">
+        <v>1.01</v>
+      </c>
+      <c r="AU38">
+        <v>1.01</v>
+      </c>
+      <c r="AV38">
+        <v>1.01</v>
+      </c>
+      <c r="AW38">
+        <v>1.01</v>
+      </c>
+      <c r="AX38">
+        <v>1.01</v>
+      </c>
+      <c r="AY38">
+        <v>1.01</v>
+      </c>
+      <c r="AZ38">
+        <v>1.01</v>
+      </c>
+      <c r="BA38">
+        <v>1.01</v>
+      </c>
+      <c r="BB38">
+        <v>1.01</v>
+      </c>
+      <c r="BC38">
+        <v>1.01</v>
+      </c>
+      <c r="BD38">
+        <v>1.01</v>
+      </c>
+      <c r="BE38">
+        <v>1.01</v>
+      </c>
+      <c r="BF38">
+        <v>1.01</v>
+      </c>
+      <c r="BG38">
+        <v>1.01</v>
+      </c>
+      <c r="BH38">
+        <v>1000</v>
+      </c>
+      <c r="BI38">
+        <v>1.01</v>
+      </c>
+      <c r="BJ38">
+        <v>1000</v>
+      </c>
+      <c r="BK38">
+        <v>1.01</v>
+      </c>
+      <c r="BL38">
+        <v>1000</v>
+      </c>
+      <c r="BM38">
+        <v>1.01</v>
+      </c>
+      <c r="BN38">
+        <v>1000</v>
+      </c>
+      <c r="BO38">
+        <v>1.01</v>
+      </c>
+      <c r="BP38">
+        <v>1000</v>
+      </c>
+      <c r="BQ38">
+        <v>1.01</v>
+      </c>
+      <c r="BR38">
+        <v>1000</v>
+      </c>
+      <c r="BS38">
+        <v>1.01</v>
+      </c>
+      <c r="BT38">
+        <v>1000</v>
+      </c>
+      <c r="BU38">
+        <v>1.01</v>
+      </c>
+      <c r="BV38">
+        <v>1000</v>
+      </c>
+      <c r="BW38">
+        <v>1.01</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>1.01</v>
+      </c>
+      <c r="BZ38">
+        <v>1000</v>
+      </c>
+      <c r="CA38">
+        <v>1.01</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s">
+        <v>199</v>
+      </c>
+      <c r="F39">
+        <v>2.02</v>
+      </c>
+      <c r="G39">
+        <v>2.18</v>
+      </c>
+      <c r="H39">
+        <v>3.95</v>
+      </c>
+      <c r="I39">
+        <v>4.5</v>
+      </c>
+      <c r="J39">
+        <v>3.3</v>
+      </c>
+      <c r="K39">
+        <v>3.65</v>
+      </c>
+      <c r="L39">
+        <v>1.4</v>
+      </c>
+      <c r="M39">
+        <v>1.08</v>
+      </c>
+      <c r="N39">
         <v>3.15</v>
       </c>
-      <c r="O35">
+      <c r="O39">
         <v>1.39</v>
       </c>
-      <c r="P35">
+      <c r="P39">
         <v>1.75</v>
       </c>
-      <c r="Q35">
-        <v>2.1</v>
-      </c>
-      <c r="R35">
+      <c r="Q39">
+        <v>2</v>
+      </c>
+      <c r="R39">
+        <v>1.27</v>
+      </c>
+      <c r="S39">
+        <v>3.8</v>
+      </c>
+      <c r="T39">
+        <v>1.79</v>
+      </c>
+      <c r="U39">
+        <v>1.92</v>
+      </c>
+      <c r="V39">
         <v>1.28</v>
       </c>
-      <c r="S35">
-        <v>3.9</v>
-      </c>
-      <c r="T35">
-        <v>1.87</v>
-      </c>
-      <c r="U35">
-        <v>1.96</v>
-      </c>
-      <c r="V35">
-        <v>1.28</v>
-      </c>
-      <c r="W35">
+      <c r="W39">
         <v>1.85</v>
       </c>
-      <c r="X35">
+      <c r="X39">
         <v>14</v>
       </c>
-      <c r="Y35">
-        <v>14</v>
-      </c>
-      <c r="Z35">
-        <v>32</v>
-      </c>
-      <c r="AA35">
+      <c r="Y39">
+        <v>15.5</v>
+      </c>
+      <c r="Z39">
+        <v>36</v>
+      </c>
+      <c r="AA39">
         <v>110</v>
       </c>
-      <c r="AB35">
+      <c r="AB39">
         <v>9.4</v>
       </c>
-      <c r="AC35">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD35">
-        <v>18</v>
-      </c>
-      <c r="AE35">
+      <c r="AC39">
+        <v>9</v>
+      </c>
+      <c r="AD39">
+        <v>20</v>
+      </c>
+      <c r="AE39">
         <v>70</v>
       </c>
-      <c r="AF35">
-        <v>13.5</v>
-      </c>
-      <c r="AG35">
-        <v>11.5</v>
-      </c>
-      <c r="AH35">
-        <v>21</v>
-      </c>
-      <c r="AI35">
-        <v>75</v>
-      </c>
-      <c r="AJ35">
-        <v>28</v>
-      </c>
-      <c r="AK35">
-        <v>26</v>
-      </c>
-      <c r="AL35">
-        <v>46</v>
-      </c>
-      <c r="AM35">
-        <v>140</v>
-      </c>
-      <c r="AN35">
-        <v>21</v>
-      </c>
-      <c r="AO35">
-        <v>75</v>
-      </c>
-      <c r="AP35">
+      <c r="AF39">
+        <v>14.5</v>
+      </c>
+      <c r="AG39">
+        <v>12.5</v>
+      </c>
+      <c r="AH39">
+        <v>23</v>
+      </c>
+      <c r="AI39">
+        <v>80</v>
+      </c>
+      <c r="AJ39">
+        <v>30</v>
+      </c>
+      <c r="AK39">
+        <v>29</v>
+      </c>
+      <c r="AL39">
+        <v>50</v>
+      </c>
+      <c r="AM39">
+        <v>150</v>
+      </c>
+      <c r="AN39">
+        <v>23</v>
+      </c>
+      <c r="AO39">
+        <v>85</v>
+      </c>
+      <c r="AP39">
         <v>10</v>
       </c>
-      <c r="AQ35">
-        <v>11</v>
-      </c>
-      <c r="AR35">
-        <v>6.4</v>
-      </c>
-      <c r="AS35">
+      <c r="AQ39">
+        <v>10</v>
+      </c>
+      <c r="AR39">
+        <v>4.9</v>
+      </c>
+      <c r="AS39">
+        <v>5</v>
+      </c>
+      <c r="AT39">
         <v>7</v>
       </c>
-      <c r="AT35">
-        <v>7</v>
-      </c>
-      <c r="AU35">
+      <c r="AU39">
         <v>6.6</v>
       </c>
-      <c r="AV35">
-        <v>14.5</v>
-      </c>
-      <c r="AW35">
-        <v>6.8</v>
-      </c>
-      <c r="AX35">
-        <v>10.5</v>
-      </c>
-      <c r="AY35">
+      <c r="AV39">
+        <v>13</v>
+      </c>
+      <c r="AW39">
+        <v>4.8</v>
+      </c>
+      <c r="AX39">
+        <v>9.6</v>
+      </c>
+      <c r="AY39">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ35">
+      <c r="AZ39">
         <v>17</v>
       </c>
-      <c r="BA35">
-        <v>6.8</v>
-      </c>
-      <c r="BB35">
-        <v>6.4</v>
-      </c>
-      <c r="BC35">
+      <c r="BA39">
+        <v>4.9</v>
+      </c>
+      <c r="BB39">
         <v>20</v>
       </c>
-      <c r="BD35">
-        <v>6.4</v>
-      </c>
-      <c r="BE35">
-        <v>7</v>
-      </c>
-      <c r="BF35">
+      <c r="BC39">
+        <v>18.5</v>
+      </c>
+      <c r="BD39">
+        <v>4.7</v>
+      </c>
+      <c r="BE39">
+        <v>5</v>
+      </c>
+      <c r="BF39">
         <v>17</v>
       </c>
-      <c r="BG35">
-        <v>6.8</v>
-      </c>
-      <c r="BH35">
-        <v>1000</v>
-      </c>
-      <c r="BI35">
-        <v>1.01</v>
-      </c>
-      <c r="BJ35">
-        <v>1000</v>
-      </c>
-      <c r="BK35">
-        <v>1.01</v>
-      </c>
-      <c r="BL35">
-        <v>1000</v>
-      </c>
-      <c r="BM35">
-        <v>1.01</v>
-      </c>
-      <c r="BN35">
-        <v>1000</v>
-      </c>
-      <c r="BO35">
-        <v>1.01</v>
-      </c>
-      <c r="BP35">
-        <v>1000</v>
-      </c>
-      <c r="BQ35">
-        <v>1.01</v>
-      </c>
-      <c r="BR35">
-        <v>1000</v>
-      </c>
-      <c r="BS35">
-        <v>1.01</v>
-      </c>
-      <c r="BT35">
-        <v>1000</v>
-      </c>
-      <c r="BU35">
-        <v>1.01</v>
-      </c>
-      <c r="BV35">
-        <v>1000</v>
-      </c>
-      <c r="BW35">
-        <v>1.01</v>
-      </c>
-      <c r="BX35">
-        <v>1000</v>
-      </c>
-      <c r="BY35">
-        <v>1.01</v>
-      </c>
-      <c r="BZ35">
-        <v>1000</v>
-      </c>
-      <c r="CA35">
-        <v>1.01</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>189</v>
+      <c r="BG39">
+        <v>4.9</v>
+      </c>
+      <c r="BH39">
+        <v>1000</v>
+      </c>
+      <c r="BI39">
+        <v>1.01</v>
+      </c>
+      <c r="BJ39">
+        <v>1000</v>
+      </c>
+      <c r="BK39">
+        <v>1.01</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>1.01</v>
+      </c>
+      <c r="BN39">
+        <v>1000</v>
+      </c>
+      <c r="BO39">
+        <v>1.01</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>1.01</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>1.01</v>
+      </c>
+      <c r="BT39">
+        <v>1000</v>
+      </c>
+      <c r="BU39">
+        <v>1.01</v>
+      </c>
+      <c r="BV39">
+        <v>1000</v>
+      </c>
+      <c r="BW39">
+        <v>1.01</v>
+      </c>
+      <c r="BX39">
+        <v>1000</v>
+      </c>
+      <c r="BY39">
+        <v>1.01</v>
+      </c>
+      <c r="BZ39">
+        <v>1000</v>
+      </c>
+      <c r="CA39">
+        <v>1.01</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -631,7 +631,7 @@
     <t>Trujillanos</t>
   </si>
   <si>
-    <t>2026-09-02 19:20:28</t>
+    <t>2026-09-02 21:36:11</t>
   </si>
 </sst>
 </file>
@@ -1225,226 +1225,226 @@
         <v>165</v>
       </c>
       <c r="F2">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>2.04</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>2.64</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="W2">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="Z2">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AF2">
+        <v>44</v>
+      </c>
+      <c r="AG2">
+        <v>30</v>
+      </c>
+      <c r="AH2">
+        <v>46</v>
+      </c>
+      <c r="AI2">
+        <v>110</v>
+      </c>
+      <c r="AJ2">
+        <v>200</v>
+      </c>
+      <c r="AK2">
+        <v>150</v>
+      </c>
+      <c r="AL2">
+        <v>220</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>410</v>
+      </c>
+      <c r="AO2">
         <v>38</v>
       </c>
-      <c r="AG2">
-        <v>17.5</v>
-      </c>
-      <c r="AH2">
-        <v>23</v>
-      </c>
-      <c r="AI2">
-        <v>48</v>
-      </c>
-      <c r="AJ2">
-        <v>120</v>
-      </c>
-      <c r="AK2">
-        <v>55</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>80</v>
-      </c>
-      <c r="AO2">
-        <v>16.5</v>
-      </c>
       <c r="AP2">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
+        <v>5.1</v>
+      </c>
+      <c r="AR2">
         <v>8.4</v>
-      </c>
-      <c r="AR2">
-        <v>10.5</v>
       </c>
       <c r="AS2">
         <v>21</v>
       </c>
       <c r="AT2">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>30</v>
+      </c>
+      <c r="AX2">
+        <v>32</v>
+      </c>
+      <c r="AY2">
+        <v>21</v>
+      </c>
+      <c r="AZ2">
+        <v>30</v>
+      </c>
+      <c r="BA2">
+        <v>80</v>
+      </c>
+      <c r="BB2">
+        <v>120</v>
+      </c>
+      <c r="BC2">
+        <v>95</v>
+      </c>
+      <c r="BD2">
+        <v>150</v>
+      </c>
+      <c r="BE2">
+        <v>240</v>
+      </c>
+      <c r="BF2">
+        <v>110</v>
+      </c>
+      <c r="BG2">
+        <v>30</v>
+      </c>
+      <c r="BH2">
+        <v>1.6</v>
+      </c>
+      <c r="BI2">
+        <v>1.52</v>
+      </c>
+      <c r="BJ2">
+        <v>48</v>
+      </c>
+      <c r="BK2">
+        <v>34</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>11</v>
+      </c>
+      <c r="BN2">
+        <v>12</v>
+      </c>
+      <c r="BO2">
         <v>9.4</v>
       </c>
-      <c r="AW2">
-        <v>19.5</v>
-      </c>
-      <c r="AX2">
-        <v>26</v>
-      </c>
-      <c r="AY2">
-        <v>15</v>
-      </c>
-      <c r="AZ2">
-        <v>16.5</v>
-      </c>
-      <c r="BA2">
-        <v>32</v>
-      </c>
-      <c r="BB2">
-        <v>55</v>
-      </c>
-      <c r="BC2">
-        <v>36</v>
-      </c>
-      <c r="BD2">
-        <v>42</v>
-      </c>
-      <c r="BE2">
-        <v>80</v>
-      </c>
-      <c r="BF2">
+      <c r="BP2">
+        <v>210</v>
+      </c>
+      <c r="BQ2">
+        <v>120</v>
+      </c>
+      <c r="BR2">
+        <v>800</v>
+      </c>
+      <c r="BS2">
+        <v>11.5</v>
+      </c>
+      <c r="BT2">
+        <v>5.4</v>
+      </c>
+      <c r="BU2">
+        <v>4.8</v>
+      </c>
+      <c r="BV2">
+        <v>60</v>
+      </c>
+      <c r="BW2">
         <v>38</v>
       </c>
-      <c r="BG2">
-        <v>14</v>
-      </c>
-      <c r="BH2">
-        <v>3.9</v>
-      </c>
-      <c r="BI2">
-        <v>3.05</v>
-      </c>
-      <c r="BJ2">
-        <v>12</v>
-      </c>
-      <c r="BK2">
-        <v>5.3</v>
-      </c>
-      <c r="BL2">
-        <v>160</v>
-      </c>
-      <c r="BM2">
-        <v>5.9</v>
-      </c>
-      <c r="BN2">
-        <v>9</v>
-      </c>
-      <c r="BO2">
-        <v>6.2</v>
-      </c>
-      <c r="BP2">
-        <v>44</v>
-      </c>
-      <c r="BQ2">
-        <v>5.4</v>
-      </c>
-      <c r="BR2">
-        <v>55</v>
-      </c>
-      <c r="BS2">
-        <v>5.5</v>
-      </c>
-      <c r="BT2">
-        <v>4.7</v>
-      </c>
-      <c r="BU2">
-        <v>4.3</v>
-      </c>
-      <c r="BV2">
-        <v>17</v>
-      </c>
-      <c r="BW2">
-        <v>5.6</v>
-      </c>
       <c r="BX2">
-        <v>30</v>
+        <v>450</v>
       </c>
       <c r="BY2">
-        <v>5.1</v>
+        <v>150</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>560</v>
       </c>
       <c r="CA2">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="s">
         <v>205</v>
@@ -1467,22 +1467,22 @@
         <v>166</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="H3">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="I3">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.37</v>
@@ -1506,49 +1506,49 @@
         <v>1.45</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="W3">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH3">
         <v>16</v>
@@ -1557,22 +1557,22 @@
         <v>36</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO3">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AP3">
         <v>15.5</v>
@@ -1581,16 +1581,16 @@
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>10.5</v>
@@ -1599,13 +1599,13 @@
         <v>21</v>
       </c>
       <c r="AX3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY3">
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3">
         <v>30</v>
@@ -1614,79 +1614,79 @@
         <v>40</v>
       </c>
       <c r="BC3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD3">
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BF3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BG3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3">
         <v>9</v>
       </c>
       <c r="BK3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>120</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>23</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BW3">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>205</v>
@@ -1709,16 +1709,16 @@
         <v>167</v>
       </c>
       <c r="F4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H4">
+        <v>2.32</v>
+      </c>
+      <c r="I4">
         <v>2.36</v>
-      </c>
-      <c r="I4">
-        <v>2.4</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1727,7 +1727,7 @@
         <v>3.2</v>
       </c>
       <c r="L4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M4">
         <v>1.13</v>
@@ -1736,40 +1736,40 @@
         <v>2.66</v>
       </c>
       <c r="O4">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q4">
         <v>2.78</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
         <v>5.9</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X4">
         <v>8.6</v>
       </c>
       <c r="Y4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA4">
         <v>34</v>
@@ -1787,10 +1787,10 @@
         <v>34</v>
       </c>
       <c r="AF4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH4">
         <v>25</v>
@@ -1799,19 +1799,19 @@
         <v>65</v>
       </c>
       <c r="AJ4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL4">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM4">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AO4">
         <v>36</v>
@@ -1820,10 +1820,10 @@
         <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS4">
         <v>29</v>
@@ -1835,7 +1835,7 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
         <v>29</v>
@@ -1844,7 +1844,7 @@
         <v>22</v>
       </c>
       <c r="AY4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ4">
         <v>21</v>
@@ -1853,19 +1853,19 @@
         <v>50</v>
       </c>
       <c r="BB4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BC4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BE4">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="BF4">
-        <v>75</v>
+        <v>14.5</v>
       </c>
       <c r="BG4">
         <v>30</v>
@@ -1874,19 +1874,19 @@
         <v>2.66</v>
       </c>
       <c r="BI4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4">
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4">
         <v>220</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>7.2</v>
@@ -1895,16 +1895,16 @@
         <v>5.9</v>
       </c>
       <c r="BP4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BQ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR4">
+        <v>65</v>
+      </c>
+      <c r="BS4">
         <v>10.5</v>
-      </c>
-      <c r="BR4">
-        <v>60</v>
-      </c>
-      <c r="BS4">
-        <v>11</v>
       </c>
       <c r="BT4">
         <v>5</v>
@@ -1913,22 +1913,22 @@
         <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>60</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>205</v>
@@ -2211,7 +2211,7 @@
         <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2250,13 +2250,13 @@
         <v>16</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
         <v>28</v>
       </c>
       <c r="AA6">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AB6">
         <v>11</v>
@@ -2292,7 +2292,7 @@
         <v>36</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6">
         <v>17.5</v>
@@ -2307,10 +2307,10 @@
         <v>11</v>
       </c>
       <c r="AR6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT6">
         <v>8.199999999999999</v>
@@ -2322,7 +2322,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2334,25 +2334,25 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BB6">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="BC6">
         <v>17</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF6">
         <v>13</v>
       </c>
       <c r="BG6">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BH6">
         <v>3.95</v>
@@ -2435,13 +2435,13 @@
         <v>170</v>
       </c>
       <c r="F7">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I7">
         <v>2.7</v>
@@ -2450,22 +2450,22 @@
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2480,19 +2480,19 @@
         <v>1.83</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W7">
         <v>1.42</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7">
         <v>17</v>
@@ -2564,7 +2564,7 @@
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AX7">
         <v>15.5</v>
@@ -2576,7 +2576,7 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB7">
         <v>36</v>
@@ -2588,13 +2588,13 @@
         <v>36</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
         <v>26</v>
       </c>
       <c r="BG7">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2677,10 +2677,10 @@
         <v>171</v>
       </c>
       <c r="F8">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G8">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="H8">
         <v>4.6</v>
@@ -2692,7 +2692,7 @@
         <v>3.6</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.31</v>
@@ -2701,7 +2701,7 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O8">
         <v>1.28</v>
@@ -2731,121 +2731,121 @@
         <v>2.06</v>
       </c>
       <c r="X8">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="Y8">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AA8">
         <v>900</v>
       </c>
       <c r="AB8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AE8">
         <v>700</v>
       </c>
       <c r="AF8">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK8">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL8">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM8">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
         <v>290</v>
       </c>
       <c r="AP8">
-        <v>1.43</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8">
-        <v>1.41</v>
+        <v>13</v>
       </c>
       <c r="AR8">
-        <v>1.39</v>
+        <v>6.8</v>
       </c>
       <c r="AS8">
-        <v>1.43</v>
+        <v>7.8</v>
       </c>
       <c r="AT8">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="AU8">
-        <v>1.39</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>1.42</v>
+        <v>14</v>
       </c>
       <c r="AW8">
-        <v>1.43</v>
+        <v>7.4</v>
       </c>
       <c r="AX8">
-        <v>1.39</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8">
-        <v>1.38</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8">
-        <v>1.41</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>1.43</v>
+        <v>7.6</v>
       </c>
       <c r="BB8">
-        <v>1.42</v>
+        <v>15.5</v>
       </c>
       <c r="BC8">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="BD8">
-        <v>1.38</v>
+        <v>6.6</v>
       </c>
       <c r="BE8">
-        <v>1.43</v>
+        <v>7.8</v>
       </c>
       <c r="BF8">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI8">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
         <v>1.01</v>
@@ -2857,7 +2857,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO8">
         <v>1.01</v>
@@ -2875,13 +2875,13 @@
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU8">
         <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
@@ -2893,7 +2893,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -2919,7 +2919,7 @@
         <v>172</v>
       </c>
       <c r="F9">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G9">
         <v>2.48</v>
@@ -2931,7 +2931,7 @@
         <v>3.35</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
         <v>3.75</v>
@@ -2964,7 +2964,7 @@
         <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
         <v>1.43</v>
@@ -3075,10 +3075,10 @@
         <v>5.2</v>
       </c>
       <c r="BF9">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG9">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BH9">
         <v>3.6</v>
@@ -3164,19 +3164,19 @@
         <v>1.18</v>
       </c>
       <c r="G10">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="H10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I10">
         <v>23</v>
       </c>
       <c r="J10">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="K10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3188,7 +3188,7 @@
         <v>6.6</v>
       </c>
       <c r="O10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
         <v>2.92</v>
@@ -3212,7 +3212,7 @@
         <v>1.04</v>
       </c>
       <c r="W10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="X10">
         <v>40</v>
@@ -3233,7 +3233,7 @@
         <v>23</v>
       </c>
       <c r="AD10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
         <v>360</v>
@@ -3269,58 +3269,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR10">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AS10">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AU10">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="AV10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW10">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX10">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AZ10">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BA10">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BB10">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BC10">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="BD10">
+        <v>6.4</v>
+      </c>
+      <c r="BE10">
         <v>7.2</v>
       </c>
-      <c r="BE10">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF10">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="BG10">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3406,13 +3406,13 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H11">
         <v>1.6</v>
       </c>
       <c r="I11">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>3</v>
@@ -3427,13 +3427,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q11">
         <v>1.22</v>
@@ -3445,16 +3445,16 @@
         <v>1.63</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>500</v>
@@ -3511,58 +3511,58 @@
         <v>500</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF11">
         <v>1.55</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3887,16 +3887,16 @@
         <v>176</v>
       </c>
       <c r="F13">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G13">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -3935,10 +3935,10 @@
         <v>2.12</v>
       </c>
       <c r="V13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X13">
         <v>17</v>
@@ -3989,7 +3989,7 @@
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO13">
         <v>75</v>
@@ -4138,7 +4138,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J14">
         <v>4.6</v>
@@ -4147,7 +4147,7 @@
         <v>5.1</v>
       </c>
       <c r="L14">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M14">
         <v>1.07</v>
@@ -4156,13 +4156,13 @@
         <v>3.5</v>
       </c>
       <c r="O14">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P14">
         <v>1.85</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>1.32</v>
@@ -4171,10 +4171,10 @@
         <v>3.7</v>
       </c>
       <c r="T14">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V14">
         <v>1.08</v>
@@ -4186,16 +4186,16 @@
         <v>16.5</v>
       </c>
       <c r="Y14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z14">
         <v>120</v>
       </c>
       <c r="AA14">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="AB14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC14">
         <v>11.5</v>
@@ -4210,7 +4210,7 @@
         <v>7.4</v>
       </c>
       <c r="AG14">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH14">
         <v>40</v>
@@ -4243,10 +4243,10 @@
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS14">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT14">
         <v>5.9</v>
@@ -4258,7 +4258,7 @@
         <v>32</v>
       </c>
       <c r="AW14">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX14">
         <v>5.8</v>
@@ -4267,10 +4267,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA14">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB14">
         <v>9</v>
@@ -4279,16 +4279,16 @@
         <v>15.5</v>
       </c>
       <c r="BD14">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF14">
         <v>7.4</v>
       </c>
       <c r="BG14">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH14">
         <v>3.4</v>
@@ -4297,13 +4297,13 @@
         <v>2.8</v>
       </c>
       <c r="BJ14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK14">
         <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="BM14">
         <v>1.01</v>
@@ -4345,7 +4345,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA14">
         <v>1.01</v>
@@ -4374,13 +4374,13 @@
         <v>4.7</v>
       </c>
       <c r="G15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H15">
         <v>1.75</v>
       </c>
       <c r="I15">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J15">
         <v>4.4</v>
@@ -4389,13 +4389,13 @@
         <v>4.5</v>
       </c>
       <c r="L15">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M15">
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O15">
         <v>1.21</v>
@@ -4410,19 +4410,19 @@
         <v>1.58</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
         <v>1.69</v>
       </c>
       <c r="U15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
         <v>2.28</v>
       </c>
       <c r="W15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X15">
         <v>25</v>
@@ -4434,10 +4434,10 @@
         <v>12.5</v>
       </c>
       <c r="AA15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC15">
         <v>10.5</v>
@@ -4446,10 +4446,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG15">
         <v>19</v>
@@ -4476,7 +4476,7 @@
         <v>44</v>
       </c>
       <c r="AO15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP15">
         <v>20</v>
@@ -4527,7 +4527,7 @@
         <v>60</v>
       </c>
       <c r="BF15">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BG15">
         <v>7.4</v>
@@ -4536,7 +4536,7 @@
         <v>4.8</v>
       </c>
       <c r="BI15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15">
         <v>9.199999999999999</v>
@@ -4587,7 +4587,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="CA15">
         <v>10</v>
@@ -4622,7 +4622,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>5.1</v>
@@ -4637,19 +4637,19 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O16">
         <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
         <v>1.71</v>
       </c>
       <c r="R16">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
         <v>2.8</v>
@@ -4658,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="U16">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W16">
         <v>3.25</v>
@@ -4691,7 +4691,7 @@
         <v>150</v>
       </c>
       <c r="AF16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10.5</v>
@@ -4703,7 +4703,7 @@
         <v>130</v>
       </c>
       <c r="AJ16">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="AK16">
         <v>65</v>
@@ -4715,7 +4715,7 @@
         <v>160</v>
       </c>
       <c r="AN16">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AO16">
         <v>190</v>
@@ -4727,10 +4727,10 @@
         <v>23</v>
       </c>
       <c r="AR16">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS16">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT16">
         <v>7.8</v>
@@ -4742,7 +4742,7 @@
         <v>25</v>
       </c>
       <c r="AW16">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX16">
         <v>7.4</v>
@@ -4754,22 +4754,22 @@
         <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD16">
         <v>30</v>
       </c>
       <c r="BE16">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG16">
         <v>15</v>
@@ -4858,7 +4858,7 @@
         <v>2.72</v>
       </c>
       <c r="G17">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H17">
         <v>2.74</v>
@@ -4906,7 +4906,7 @@
         <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X17">
         <v>15</v>
@@ -4984,7 +4984,7 @@
         <v>11</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX17">
         <v>14</v>
@@ -4996,25 +4996,25 @@
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF17">
-        <v>1.86</v>
+        <v>6.6</v>
       </c>
       <c r="BG17">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH17">
         <v>3.9</v>
@@ -5100,7 +5100,7 @@
         <v>2.58</v>
       </c>
       <c r="G18">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H18">
         <v>2.68</v>
@@ -5139,10 +5139,10 @@
         <v>2.84</v>
       </c>
       <c r="T18">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U18">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V18">
         <v>1.51</v>
@@ -5214,7 +5214,7 @@
         <v>17.5</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT18">
         <v>11</v>
@@ -5247,10 +5247,10 @@
         <v>14.5</v>
       </c>
       <c r="BD18">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18">
         <v>15.5</v>
@@ -5408,10 +5408,10 @@
         <v>500</v>
       </c>
       <c r="AC19">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AD19">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE19">
         <v>25</v>
@@ -5447,52 +5447,52 @@
         <v>11.5</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AS19">
         <v>14.5</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AU19">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AY19">
         <v>12.5</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA19">
         <v>19</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BD19">
         <v>2.5</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BF19">
         <v>5.3</v>
@@ -5581,22 +5581,22 @@
         <v>183</v>
       </c>
       <c r="F20">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G20">
         <v>6.6</v>
       </c>
       <c r="H20">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I20">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J20">
         <v>4.6</v>
       </c>
       <c r="K20">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5614,22 +5614,22 @@
         <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S20">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T20">
         <v>1.6</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="V20">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="W20">
         <v>1.18</v>
@@ -5653,16 +5653,16 @@
         <v>14</v>
       </c>
       <c r="AD20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE20">
         <v>18.5</v>
       </c>
       <c r="AF20">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG20">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH20">
         <v>24</v>
@@ -5671,7 +5671,7 @@
         <v>34</v>
       </c>
       <c r="AJ20">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK20">
         <v>75</v>
@@ -5686,7 +5686,7 @@
         <v>70</v>
       </c>
       <c r="AO20">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AP20">
         <v>21</v>
@@ -5701,7 +5701,7 @@
         <v>13</v>
       </c>
       <c r="AT20">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5713,10 +5713,10 @@
         <v>13.5</v>
       </c>
       <c r="AX20">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AY20">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AZ20">
         <v>17.5</v>
@@ -5725,19 +5725,19 @@
         <v>14.5</v>
       </c>
       <c r="BB20">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC20">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD20">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE20">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF20">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BG20">
         <v>5.7</v>
@@ -5829,58 +5829,58 @@
         <v>2.2</v>
       </c>
       <c r="H21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J21">
         <v>4.1</v>
       </c>
       <c r="K21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M21">
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P21">
         <v>3</v>
       </c>
       <c r="Q21">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R21">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S21">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T21">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U21">
         <v>2.92</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X21">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="Y21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z21">
         <v>32</v>
@@ -5889,31 +5889,31 @@
         <v>60</v>
       </c>
       <c r="AB21">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC21">
         <v>11</v>
       </c>
       <c r="AD21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE21">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AF21">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG21">
         <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI21">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AJ21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK21">
         <v>19.5</v>
@@ -5922,19 +5922,19 @@
         <v>25</v>
       </c>
       <c r="AM21">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AN21">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO21">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AP21">
         <v>29</v>
       </c>
       <c r="AQ21">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR21">
         <v>26</v>
@@ -5943,10 +5943,10 @@
         <v>44</v>
       </c>
       <c r="AT21">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AU21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV21">
         <v>13</v>
@@ -5955,16 +5955,16 @@
         <v>26</v>
       </c>
       <c r="AX21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY21">
         <v>10.5</v>
       </c>
       <c r="AZ21">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB21">
         <v>26</v>
@@ -5973,31 +5973,31 @@
         <v>17</v>
       </c>
       <c r="BD21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE21">
         <v>40</v>
       </c>
       <c r="BF21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG21">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH21">
         <v>5.4</v>
       </c>
       <c r="BI21">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BJ21">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK21">
         <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM21">
         <v>1.01</v>
@@ -6006,7 +6006,7 @@
         <v>6.4</v>
       </c>
       <c r="BO21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP21">
         <v>16</v>
@@ -6015,7 +6015,7 @@
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS21">
         <v>1.01</v>
@@ -6027,19 +6027,19 @@
         <v>5.6</v>
       </c>
       <c r="BV21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW21">
         <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BY21">
         <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA21">
         <v>1.01</v>
@@ -6071,7 +6071,7 @@
         <v>1.87</v>
       </c>
       <c r="H22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I22">
         <v>6.6</v>
@@ -6089,7 +6089,7 @@
         <v>1.1</v>
       </c>
       <c r="N22">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O22">
         <v>1.45</v>
@@ -6098,7 +6098,7 @@
         <v>1.61</v>
       </c>
       <c r="Q22">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R22">
         <v>1.22</v>
@@ -6107,10 +6107,10 @@
         <v>4.5</v>
       </c>
       <c r="T22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U22">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V22">
         <v>1.18</v>
@@ -6119,7 +6119,7 @@
         <v>2.16</v>
       </c>
       <c r="X22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y22">
         <v>16</v>
@@ -6131,7 +6131,7 @@
         <v>900</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC22">
         <v>8.6</v>
@@ -6170,7 +6170,7 @@
         <v>18.5</v>
       </c>
       <c r="AO22">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AP22">
         <v>8</v>
@@ -6179,10 +6179,10 @@
         <v>11.5</v>
       </c>
       <c r="AR22">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AS22">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT22">
         <v>5.7</v>
@@ -6194,7 +6194,7 @@
         <v>18</v>
       </c>
       <c r="AW22">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="AX22">
         <v>7.6</v>
@@ -6206,7 +6206,7 @@
         <v>19</v>
       </c>
       <c r="BA22">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22">
         <v>15</v>
@@ -6218,13 +6218,13 @@
         <v>34</v>
       </c>
       <c r="BE22">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF22">
         <v>13.5</v>
       </c>
       <c r="BG22">
-        <v>1.55</v>
+        <v>9.4</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6307,13 +6307,13 @@
         <v>186</v>
       </c>
       <c r="F23">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G23">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H23">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I23">
         <v>6.6</v>
@@ -6322,7 +6322,7 @@
         <v>4.2</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6331,7 +6331,7 @@
         <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O23">
         <v>1.26</v>
@@ -6340,7 +6340,7 @@
         <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R23">
         <v>1.47</v>
@@ -6355,10 +6355,10 @@
         <v>2.08</v>
       </c>
       <c r="V23">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W23">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X23">
         <v>22</v>
@@ -6370,7 +6370,7 @@
         <v>50</v>
       </c>
       <c r="AA23">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB23">
         <v>9.800000000000001</v>
@@ -6394,7 +6394,7 @@
         <v>20</v>
       </c>
       <c r="AI23">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AJ23">
         <v>16.5</v>
@@ -6412,7 +6412,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO23">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AP23">
         <v>16</v>
@@ -6463,7 +6463,7 @@
         <v>13</v>
       </c>
       <c r="BF23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG23">
         <v>14</v>
@@ -6552,13 +6552,13 @@
         <v>1.52</v>
       </c>
       <c r="G24">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H24">
         <v>6.6</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J24">
         <v>4.8</v>
@@ -6609,7 +6609,7 @@
         <v>34</v>
       </c>
       <c r="Z24">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AA24">
         <v>200</v>
@@ -6651,7 +6651,7 @@
         <v>320</v>
       </c>
       <c r="AN24">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AO24">
         <v>80</v>
@@ -6666,7 +6666,7 @@
         <v>50</v>
       </c>
       <c r="AS24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT24">
         <v>10</v>
@@ -6711,7 +6711,7 @@
         <v>55</v>
       </c>
       <c r="BH24">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI24">
         <v>3.4</v>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM24">
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO24">
         <v>3.35</v>
@@ -6741,7 +6741,7 @@
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS24">
         <v>1.01</v>
@@ -6759,7 +6759,7 @@
         <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY24">
         <v>1.01</v>
@@ -6797,16 +6797,16 @@
         <v>1.85</v>
       </c>
       <c r="H25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I25">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J25">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K25">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L25">
         <v>1.25</v>
@@ -6815,37 +6815,37 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O25">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P25">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q25">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R25">
         <v>1.75</v>
       </c>
       <c r="S25">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T25">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V25">
         <v>1.27</v>
       </c>
       <c r="W25">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y25">
         <v>26</v>
@@ -6872,7 +6872,7 @@
         <v>16.5</v>
       </c>
       <c r="AG25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH25">
         <v>16</v>
@@ -6899,7 +6899,7 @@
         <v>32</v>
       </c>
       <c r="AP25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ25">
         <v>21</v>
@@ -6908,7 +6908,7 @@
         <v>20</v>
       </c>
       <c r="AS25">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT25">
         <v>12</v>
@@ -6920,7 +6920,7 @@
         <v>14</v>
       </c>
       <c r="AW25">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX25">
         <v>10.5</v>
@@ -6932,7 +6932,7 @@
         <v>12.5</v>
       </c>
       <c r="BA25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB25">
         <v>17</v>
@@ -6950,10 +6950,10 @@
         <v>6</v>
       </c>
       <c r="BG25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI25">
         <v>3.9</v>
@@ -6974,7 +6974,7 @@
         <v>5.7</v>
       </c>
       <c r="BO25">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP25">
         <v>13</v>
@@ -6989,7 +6989,7 @@
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU25">
         <v>1.01</v>
@@ -7010,7 +7010,7 @@
         <v>14.5</v>
       </c>
       <c r="CA25">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>205</v>
@@ -7036,61 +7036,61 @@
         <v>2.52</v>
       </c>
       <c r="G26">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H26">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I26">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J26">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K26">
         <v>4.2</v>
       </c>
       <c r="L26">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M26">
         <v>1.03</v>
       </c>
       <c r="N26">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O26">
         <v>1.17</v>
       </c>
       <c r="P26">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="Q26">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R26">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S26">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U26">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X26">
         <v>32</v>
       </c>
       <c r="Y26">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Z26">
         <v>28</v>
@@ -7099,7 +7099,7 @@
         <v>42</v>
       </c>
       <c r="AB26">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC26">
         <v>10.5</v>
@@ -7108,10 +7108,10 @@
         <v>14</v>
       </c>
       <c r="AE26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF26">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG26">
         <v>13</v>
@@ -7129,13 +7129,13 @@
         <v>24</v>
       </c>
       <c r="AL26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM26">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AN26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO26">
         <v>15.5</v>
@@ -7153,10 +7153,10 @@
         <v>18</v>
       </c>
       <c r="AT26">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AU26">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV26">
         <v>9.6</v>
@@ -7168,7 +7168,7 @@
         <v>18</v>
       </c>
       <c r="AY26">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26">
         <v>10</v>
@@ -7180,13 +7180,13 @@
         <v>18</v>
       </c>
       <c r="BC26">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD26">
         <v>20</v>
       </c>
       <c r="BE26">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF26">
         <v>10.5</v>
@@ -7195,10 +7195,10 @@
         <v>11</v>
       </c>
       <c r="BH26">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BI26">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26">
         <v>10</v>
@@ -7207,13 +7207,13 @@
         <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM26">
         <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO26">
         <v>4.6</v>
@@ -7225,7 +7225,7 @@
         <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS26">
         <v>1.01</v>
@@ -7234,7 +7234,7 @@
         <v>7.6</v>
       </c>
       <c r="BU26">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV26">
         <v>22</v>
@@ -7243,13 +7243,13 @@
         <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY26">
         <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA26">
         <v>1.01</v>
@@ -7278,7 +7278,7 @@
         <v>1.97</v>
       </c>
       <c r="G27">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H27">
         <v>3.65</v>
@@ -7293,16 +7293,16 @@
         <v>4.3</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M27">
         <v>1.03</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P27">
         <v>2.48</v>
@@ -7311,22 +7311,22 @@
         <v>1.63</v>
       </c>
       <c r="R27">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S27">
         <v>2.54</v>
       </c>
       <c r="T27">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X27">
         <v>23</v>
@@ -7362,7 +7362,7 @@
         <v>16.5</v>
       </c>
       <c r="AI27">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ27">
         <v>25</v>
@@ -7392,7 +7392,7 @@
         <v>14.5</v>
       </c>
       <c r="AS27">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT27">
         <v>10</v>
@@ -7404,7 +7404,7 @@
         <v>13</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX27">
         <v>12</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="BA27">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BB27">
         <v>20</v>
@@ -7425,7 +7425,7 @@
         <v>16.5</v>
       </c>
       <c r="BD27">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BE27">
         <v>30</v>
@@ -7434,7 +7434,7 @@
         <v>8.4</v>
       </c>
       <c r="BG27">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7517,25 +7517,25 @@
         <v>191</v>
       </c>
       <c r="F28">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G28">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H28">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="I28">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K28">
         <v>3.55</v>
       </c>
       <c r="L28">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M28">
         <v>1.08</v>
@@ -7559,100 +7559,100 @@
         <v>3.85</v>
       </c>
       <c r="T28">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V28">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="W28">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X28">
         <v>13</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA28">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB28">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD28">
         <v>11</v>
       </c>
       <c r="AE28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH28">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI28">
         <v>42</v>
       </c>
       <c r="AJ28">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK28">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL28">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM28">
         <v>110</v>
       </c>
       <c r="AN28">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO28">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AP28">
         <v>11.5</v>
       </c>
       <c r="AQ28">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR28">
         <v>12</v>
       </c>
       <c r="AS28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU28">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV28">
         <v>10</v>
       </c>
       <c r="AW28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX28">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ28">
         <v>17</v>
@@ -7661,10 +7661,10 @@
         <v>36</v>
       </c>
       <c r="BB28">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC28">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD28">
         <v>50</v>
@@ -7673,64 +7673,64 @@
         <v>55</v>
       </c>
       <c r="BF28">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BG28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH28">
         <v>3.75</v>
       </c>
       <c r="BI28">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ28">
         <v>9.800000000000001</v>
       </c>
       <c r="BK28">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL28">
         <v>160</v>
       </c>
       <c r="BM28">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN28">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BP28">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BQ28">
+        <v>7.2</v>
+      </c>
+      <c r="BR28">
+        <v>55</v>
+      </c>
+      <c r="BS28">
         <v>7.4</v>
       </c>
-      <c r="BR28">
-        <v>42</v>
-      </c>
-      <c r="BS28">
-        <v>8</v>
-      </c>
       <c r="BT28">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BU28">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV28">
         <v>17</v>
       </c>
       <c r="BW28">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="BX28">
         <v>32</v>
       </c>
       <c r="BY28">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7759,16 +7759,16 @@
         <v>192</v>
       </c>
       <c r="F29">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G29">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H29">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I29">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J29">
         <v>3.5</v>
@@ -7777,13 +7777,13 @@
         <v>3.55</v>
       </c>
       <c r="L29">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O29">
         <v>1.3</v>
@@ -7813,7 +7813,7 @@
         <v>1.58</v>
       </c>
       <c r="X29">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y29">
         <v>13</v>
@@ -7834,37 +7834,37 @@
         <v>12</v>
       </c>
       <c r="AE29">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF29">
         <v>19</v>
       </c>
       <c r="AG29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH29">
         <v>16</v>
       </c>
       <c r="AI29">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ29">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK29">
-        <v>530</v>
+        <v>28</v>
       </c>
       <c r="AL29">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM29">
         <v>85</v>
       </c>
       <c r="AN29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP29">
         <v>14.5</v>
@@ -7888,7 +7888,7 @@
         <v>11</v>
       </c>
       <c r="AW29">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AX29">
         <v>16.5</v>
@@ -7897,13 +7897,13 @@
         <v>11</v>
       </c>
       <c r="AZ29">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA29">
         <v>34</v>
       </c>
       <c r="BB29">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC29">
         <v>24</v>
@@ -7915,13 +7915,13 @@
         <v>60</v>
       </c>
       <c r="BF29">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH29">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI29">
         <v>3.25</v>
@@ -7936,7 +7936,7 @@
         <v>120</v>
       </c>
       <c r="BM29">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN29">
         <v>6.6</v>
@@ -7954,7 +7954,7 @@
         <v>36</v>
       </c>
       <c r="BS29">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BT29">
         <v>6.8</v>
@@ -7963,16 +7963,16 @@
         <v>4.7</v>
       </c>
       <c r="BV29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW29">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX29">
         <v>38</v>
       </c>
       <c r="BY29">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8001,13 +8001,13 @@
         <v>193</v>
       </c>
       <c r="F30">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G30">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="H30">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I30">
         <v>4.4</v>
@@ -8052,7 +8052,7 @@
         <v>1.29</v>
       </c>
       <c r="W30">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X30">
         <v>14.5</v>
@@ -8100,7 +8100,7 @@
         <v>36</v>
       </c>
       <c r="AM30">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN30">
         <v>13.5</v>
@@ -8142,7 +8142,7 @@
         <v>17</v>
       </c>
       <c r="BA30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB30">
         <v>21</v>
@@ -8163,22 +8163,22 @@
         <v>48</v>
       </c>
       <c r="BH30">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BI30">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ30">
         <v>10</v>
       </c>
       <c r="BK30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL30">
         <v>150</v>
       </c>
       <c r="BM30">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BN30">
         <v>4.5</v>
@@ -8187,16 +8187,16 @@
         <v>4.1</v>
       </c>
       <c r="BP30">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BQ30">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR30">
         <v>28</v>
       </c>
       <c r="BS30">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BT30">
         <v>7.4</v>
@@ -8208,13 +8208,13 @@
         <v>36</v>
       </c>
       <c r="BW30">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BX30">
         <v>46</v>
       </c>
       <c r="BY30">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ30">
         <v>25</v>
@@ -8252,7 +8252,7 @@
         <v>4</v>
       </c>
       <c r="I31">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J31">
         <v>3.4</v>
@@ -8267,7 +8267,7 @@
         <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O31">
         <v>1.33</v>
@@ -8291,22 +8291,22 @@
         <v>2.04</v>
       </c>
       <c r="V31">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W31">
         <v>1.92</v>
       </c>
       <c r="X31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z31">
         <v>32</v>
       </c>
       <c r="AA31">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB31">
         <v>11.5</v>
@@ -8360,7 +8360,7 @@
         <v>24</v>
       </c>
       <c r="AS31">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT31">
         <v>7.8</v>
@@ -8396,7 +8396,7 @@
         <v>27</v>
       </c>
       <c r="BE31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF31">
         <v>13</v>
@@ -8509,7 +8509,7 @@
         <v>1.06</v>
       </c>
       <c r="N32">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O32">
         <v>1.31</v>
@@ -8518,7 +8518,7 @@
         <v>1.85</v>
       </c>
       <c r="Q32">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R32">
         <v>1.32</v>
@@ -8533,7 +8533,7 @@
         <v>1.68</v>
       </c>
       <c r="V32">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="W32">
         <v>1.1</v>
@@ -8578,7 +8578,7 @@
         <v>500</v>
       </c>
       <c r="AK32">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AL32">
         <v>190</v>
@@ -8590,10 +8590,10 @@
         <v>390</v>
       </c>
       <c r="AO32">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP32">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AQ32">
         <v>3.9</v>
@@ -8602,46 +8602,46 @@
         <v>4.1</v>
       </c>
       <c r="AS32">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU32">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AV32">
         <v>4.7</v>
       </c>
       <c r="AW32">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX32">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY32">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AZ32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA32">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC32">
         <v>8</v>
       </c>
-      <c r="BC32">
-        <v>7.8</v>
-      </c>
       <c r="BD32">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE32">
         <v>8</v>
       </c>
       <c r="BF32">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG32">
         <v>4.2</v>
@@ -8739,7 +8739,7 @@
         <v>110</v>
       </c>
       <c r="J33">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="K33">
         <v>280</v>
@@ -8748,25 +8748,25 @@
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N33">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O33">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="P33">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q33">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R33">
         <v>1.08</v>
       </c>
       <c r="S33">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="T33">
         <v>1.05</v>
@@ -8775,10 +8775,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -8883,7 +8883,7 @@
         <v>2.5</v>
       </c>
       <c r="BF33">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="BG33">
         <v>1.55</v>
@@ -9005,7 +9005,7 @@
         <v>1.93</v>
       </c>
       <c r="R34">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S34">
         <v>3.05</v>
@@ -9077,37 +9077,37 @@
         <v>36</v>
       </c>
       <c r="AP34">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ34">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR34">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="AS34">
         <v>4.9</v>
       </c>
       <c r="AT34">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="AU34">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="AV34">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AW34">
         <v>4.7</v>
       </c>
       <c r="AX34">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AY34">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ34">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BA34">
         <v>4.9</v>
@@ -9125,7 +9125,7 @@
         <v>5.1</v>
       </c>
       <c r="BF34">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BG34">
         <v>4.7</v>
@@ -9223,7 +9223,7 @@
         <v>12.5</v>
       </c>
       <c r="J35">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K35">
         <v>5.1</v>
@@ -9265,28 +9265,28 @@
         <v>3.4</v>
       </c>
       <c r="X35">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z35">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA35">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB35">
         <v>6.8</v>
       </c>
       <c r="AC35">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD35">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE35">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AF35">
         <v>7.4</v>
@@ -9295,82 +9295,82 @@
         <v>10.5</v>
       </c>
       <c r="AH35">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI35">
         <v>250</v>
       </c>
       <c r="AJ35">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AK35">
         <v>18</v>
       </c>
       <c r="AL35">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AM35">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN35">
         <v>8.6</v>
       </c>
       <c r="AO35">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AP35">
         <v>12.5</v>
       </c>
       <c r="AQ35">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AR35">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS35">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT35">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU35">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV35">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AW35">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX35">
         <v>6.4</v>
       </c>
       <c r="AY35">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BA35">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BB35">
         <v>10</v>
       </c>
       <c r="BC35">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD35">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BE35">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF35">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG35">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9453,22 +9453,22 @@
         <v>199</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G36">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H36">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I36">
         <v>4.8</v>
       </c>
       <c r="J36">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K36">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L36">
         <v>1.44</v>
@@ -9477,16 +9477,16 @@
         <v>1.1</v>
       </c>
       <c r="N36">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="O36">
         <v>1.46</v>
       </c>
       <c r="P36">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q36">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R36">
         <v>1.26</v>
@@ -9504,7 +9504,7 @@
         <v>1.26</v>
       </c>
       <c r="W36">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X36">
         <v>11</v>
@@ -9513,7 +9513,7 @@
         <v>16</v>
       </c>
       <c r="Z36">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AA36">
         <v>900</v>
@@ -9531,10 +9531,10 @@
         <v>370</v>
       </c>
       <c r="AF36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG36">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH36">
         <v>26</v>
@@ -9543,19 +9543,19 @@
         <v>500</v>
       </c>
       <c r="AJ36">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK36">
         <v>34</v>
       </c>
       <c r="AL36">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AM36">
         <v>580</v>
       </c>
       <c r="AN36">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AO36">
         <v>500</v>
@@ -9570,7 +9570,7 @@
         <v>11.5</v>
       </c>
       <c r="AS36">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT36">
         <v>6</v>
@@ -9582,7 +9582,7 @@
         <v>16.5</v>
       </c>
       <c r="AW36">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX36">
         <v>9.6</v>
@@ -9594,25 +9594,25 @@
         <v>20</v>
       </c>
       <c r="BA36">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB36">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BC36">
         <v>14.5</v>
       </c>
       <c r="BD36">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE36">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF36">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG36">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH36">
         <v>3.2</v>
@@ -9704,7 +9704,7 @@
         <v>1.86</v>
       </c>
       <c r="I37">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J37">
         <v>3.15</v>
@@ -9737,13 +9737,13 @@
         <v>2.78</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W37">
         <v>1.22</v>
@@ -9964,7 +9964,7 @@
         <v>3.45</v>
       </c>
       <c r="O38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P38">
         <v>1.83</v>
@@ -10179,25 +10179,25 @@
         <v>202</v>
       </c>
       <c r="F39">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G39">
         <v>2.44</v>
       </c>
       <c r="H39">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I39">
         <v>4.4</v>
       </c>
       <c r="J39">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L39">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M39">
         <v>1.01</v>
@@ -10212,7 +10212,7 @@
         <v>1.53</v>
       </c>
       <c r="Q39">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R39">
         <v>1.18</v>
@@ -10287,37 +10287,37 @@
         <v>100</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS39">
         <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW39">
         <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA39">
         <v>1.01</v>
@@ -10335,7 +10335,7 @@
         <v>1.01</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG39">
         <v>1.01</v>
@@ -10362,7 +10362,7 @@
         <v>5.5</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP39">
         <v>22</v>
@@ -10380,7 +10380,7 @@
         <v>8</v>
       </c>
       <c r="BU39">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV39">
         <v>44</v>
@@ -10421,7 +10421,7 @@
         <v>203</v>
       </c>
       <c r="F40">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G40">
         <v>2.16</v>
@@ -10439,7 +10439,7 @@
         <v>3.65</v>
       </c>
       <c r="L40">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M40">
         <v>1.08</v>
@@ -10457,13 +10457,13 @@
         <v>2.1</v>
       </c>
       <c r="R40">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S40">
         <v>3.9</v>
       </c>
       <c r="T40">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U40">
         <v>1.95</v>
@@ -10487,7 +10487,7 @@
         <v>110</v>
       </c>
       <c r="AB40">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC40">
         <v>8.199999999999999</v>
@@ -10535,10 +10535,10 @@
         <v>10.5</v>
       </c>
       <c r="AR40">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS40">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT40">
         <v>7</v>
@@ -10550,7 +10550,7 @@
         <v>13</v>
       </c>
       <c r="AW40">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX40">
         <v>9.6</v>
@@ -10562,7 +10562,7 @@
         <v>17</v>
       </c>
       <c r="BA40">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB40">
         <v>19.5</v>
@@ -10571,16 +10571,16 @@
         <v>18.5</v>
       </c>
       <c r="BD40">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE40">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF40">
         <v>16</v>
       </c>
       <c r="BG40">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10663,13 +10663,13 @@
         <v>204</v>
       </c>
       <c r="F41">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="G41">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="H41">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I41">
         <v>9.199999999999999</v>
@@ -10678,7 +10678,7 @@
         <v>3.45</v>
       </c>
       <c r="K41">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L41">
         <v>1.32</v>
@@ -10714,7 +10714,7 @@
         <v>1.12</v>
       </c>
       <c r="W41">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X41">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -601,7 +601,7 @@
     <t>Trujillanos</t>
   </si>
   <si>
-    <t>2026-09-03 02:04:24</t>
+    <t>2026-09-03 04:19:52</t>
   </si>
 </sst>
 </file>
@@ -1195,13 +1195,13 @@
         <v>158</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
         <v>2.5</v>
       </c>
       <c r="H2">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I2">
         <v>3.05</v>
@@ -1210,13 +1210,13 @@
         <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>5.7</v>
@@ -1225,34 +1225,34 @@
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q2">
         <v>1.56</v>
       </c>
       <c r="R2">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S2">
         <v>2.4</v>
       </c>
       <c r="T2">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V2">
         <v>1.48</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
         <v>32</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>29</v>
@@ -1261,16 +1261,16 @@
         <v>55</v>
       </c>
       <c r="AB2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC2">
         <v>10</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF2">
         <v>24</v>
@@ -1279,7 +1279,7 @@
         <v>15</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
         <v>40</v>
@@ -1300,10 +1300,10 @@
         <v>13</v>
       </c>
       <c r="AO2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -1315,7 +1315,7 @@
         <v>30</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU2">
         <v>8.800000000000001</v>
@@ -1327,7 +1327,7 @@
         <v>21</v>
       </c>
       <c r="AX2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
@@ -1336,10 +1336,10 @@
         <v>13</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2">
         <v>17.5</v>
@@ -1348,7 +1348,7 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
@@ -1384,7 +1384,7 @@
         <v>19</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>28</v>
@@ -1437,40 +1437,40 @@
         <v>159</v>
       </c>
       <c r="F3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
         <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.39</v>
@@ -1479,43 +1479,43 @@
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z3">
         <v>27</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
         <v>9.4</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1524,7 +1524,7 @@
         <v>17</v>
       </c>
       <c r="AI3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>32</v>
@@ -1545,31 +1545,31 @@
         <v>46</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>9.4</v>
@@ -1578,85 +1578,85 @@
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="BB3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BL3">
         <v>130</v>
       </c>
       <c r="BM3">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BN3">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BR3">
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT3">
         <v>7</v>
       </c>
       <c r="BU3">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX3">
         <v>44</v>
       </c>
       <c r="BY3">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BZ3">
         <v>27</v>
       </c>
       <c r="CA3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="s">
         <v>195</v>
@@ -1679,16 +1679,16 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J4">
         <v>3.3</v>
@@ -1700,10 +1700,10 @@
         <v>1.49</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.4</v>
@@ -1712,31 +1712,31 @@
         <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
         <v>15.5</v>
@@ -1754,7 +1754,7 @@
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF4">
         <v>23</v>
@@ -1763,16 +1763,16 @@
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>150</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AL4">
         <v>70</v>
@@ -1784,25 +1784,25 @@
         <v>55</v>
       </c>
       <c r="AO4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AT4">
         <v>10</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>10</v>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
       <c r="BA4">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB4">
         <v>36</v>
@@ -1832,7 +1832,7 @@
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
         <v>26</v>
@@ -1841,7 +1841,7 @@
         <v>21</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
         <v>2.62</v>
@@ -1865,7 +1865,7 @@
         <v>5.6</v>
       </c>
       <c r="BP4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
@@ -1895,7 +1895,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1924,19 +1924,19 @@
         <v>1.2</v>
       </c>
       <c r="G5">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="H5">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="K5">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="L5">
         <v>1.25</v>
@@ -1945,34 +1945,34 @@
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
         <v>2.92</v>
       </c>
       <c r="Q5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R5">
         <v>1.77</v>
       </c>
       <c r="S5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T5">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W5">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="X5">
         <v>38</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
         <v>24</v>
@@ -1999,16 +1999,16 @@
         <v>360</v>
       </c>
       <c r="AF5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI5">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AJ5">
         <v>8.6</v>
@@ -2023,79 +2023,79 @@
         <v>240</v>
       </c>
       <c r="AN5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
+        <v>6.8</v>
+      </c>
+      <c r="AQ5">
         <v>7.4</v>
       </c>
-      <c r="AQ5">
-        <v>7.8</v>
-      </c>
       <c r="AR5">
+        <v>8</v>
+      </c>
+      <c r="AS5">
         <v>8.4</v>
       </c>
-      <c r="AS5">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AT5">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AU5">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="BC5">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BG5">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BI5">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM5">
         <v>1.01</v>
@@ -2104,16 +2104,16 @@
         <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>7.2</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
@@ -2125,19 +2125,19 @@
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -2163,76 +2163,76 @@
         <v>162</v>
       </c>
       <c r="F6">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H6">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="I6">
-        <v>9.4</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>1.32</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
         <v>1.2</v>
       </c>
       <c r="P6">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q6">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="R6">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
-        <v>1.2</v>
+        <v>2.36</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U6">
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="X6">
         <v>500</v>
       </c>
       <c r="Y6">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA6">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC6">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>500</v>
@@ -2244,16 +2244,16 @@
         <v>500</v>
       </c>
       <c r="AG6">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AI6">
         <v>500</v>
       </c>
       <c r="AJ6">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK6">
         <v>500</v>
@@ -2262,124 +2262,124 @@
         <v>500</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AP6">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6">
-        <v>1.16</v>
+        <v>5.5</v>
       </c>
       <c r="AR6">
-        <v>1.14</v>
+        <v>7</v>
       </c>
       <c r="AS6">
-        <v>1.15</v>
+        <v>5.5</v>
       </c>
       <c r="AT6">
-        <v>1.16</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>1.13</v>
+        <v>4.8</v>
       </c>
       <c r="AW6">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AX6">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AY6">
-        <v>1.14</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6">
-        <v>1.14</v>
+        <v>1.96</v>
       </c>
       <c r="BA6">
-        <v>1.15</v>
+        <v>5.5</v>
       </c>
       <c r="BB6">
-        <v>1.15</v>
+        <v>5.5</v>
       </c>
       <c r="BC6">
-        <v>1.15</v>
+        <v>2.18</v>
       </c>
       <c r="BD6">
-        <v>1.16</v>
+        <v>5.5</v>
       </c>
       <c r="BE6">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="BF6">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="BG6">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2405,7 +2405,7 @@
         <v>163</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G7">
         <v>1.9</v>
@@ -2414,7 +2414,7 @@
         <v>4.5</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
         <v>3.75</v>
@@ -2423,46 +2423,46 @@
         <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="R7">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U7">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X7">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
         <v>42</v>
@@ -2471,16 +2471,16 @@
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>19</v>
       </c>
       <c r="AE7">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AF7">
         <v>12.5</v>
@@ -2489,7 +2489,7 @@
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI7">
         <v>700</v>
@@ -2498,85 +2498,85 @@
         <v>22</v>
       </c>
       <c r="AK7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL7">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO7">
-        <v>290</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AQ7">
+        <v>14.5</v>
+      </c>
+      <c r="AR7">
+        <v>14</v>
+      </c>
+      <c r="AS7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU7">
+        <v>7.2</v>
+      </c>
+      <c r="AV7">
+        <v>15</v>
+      </c>
+      <c r="AW7">
+        <v>38</v>
+      </c>
+      <c r="AX7">
+        <v>10</v>
+      </c>
+      <c r="AY7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>15.5</v>
+      </c>
+      <c r="BA7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB7">
+        <v>18</v>
+      </c>
+      <c r="BC7">
+        <v>17</v>
+      </c>
+      <c r="BD7">
         <v>13</v>
       </c>
-      <c r="AR7">
-        <v>8.4</v>
-      </c>
-      <c r="AS7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT7">
-        <v>7.8</v>
-      </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>14</v>
-      </c>
-      <c r="AW7">
+      <c r="BE7">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY7">
-        <v>7.6</v>
-      </c>
-      <c r="AZ7">
-        <v>13</v>
-      </c>
-      <c r="BA7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB7">
-        <v>15.5</v>
-      </c>
-      <c r="BC7">
-        <v>14</v>
-      </c>
-      <c r="BD7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE7">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF7">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG7">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BH7">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI7">
         <v>3</v>
       </c>
       <c r="BJ7">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL7">
         <v>130</v>
@@ -2585,16 +2585,16 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
         <v>26</v>
@@ -2615,13 +2615,13 @@
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2647,25 +2647,25 @@
         <v>164</v>
       </c>
       <c r="F8">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="G8">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="I8">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2680,7 +2680,7 @@
         <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R8">
         <v>1.46</v>
@@ -2692,133 +2692,133 @@
         <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
+        <v>21</v>
+      </c>
+      <c r="Y8">
+        <v>17</v>
+      </c>
+      <c r="Z8">
+        <v>26</v>
+      </c>
+      <c r="AA8">
+        <v>55</v>
+      </c>
+      <c r="AB8">
+        <v>15.5</v>
+      </c>
+      <c r="AC8">
+        <v>8.4</v>
+      </c>
+      <c r="AD8">
+        <v>15</v>
+      </c>
+      <c r="AE8">
+        <v>38</v>
+      </c>
+      <c r="AF8">
         <v>22</v>
       </c>
-      <c r="Y8">
-        <v>18</v>
-      </c>
-      <c r="Z8">
-        <v>29</v>
-      </c>
-      <c r="AA8">
-        <v>65</v>
-      </c>
-      <c r="AB8">
-        <v>14.5</v>
-      </c>
-      <c r="AC8">
-        <v>8.6</v>
-      </c>
-      <c r="AD8">
-        <v>14</v>
-      </c>
-      <c r="AE8">
-        <v>42</v>
-      </c>
-      <c r="AF8">
-        <v>21</v>
-      </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
         <v>19</v>
       </c>
       <c r="AI8">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM8">
         <v>85</v>
       </c>
       <c r="AN8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO8">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AP8">
         <v>15.5</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
+        <v>19</v>
+      </c>
+      <c r="AS8">
         <v>20</v>
-      </c>
-      <c r="AS8">
-        <v>5.3</v>
       </c>
       <c r="AT8">
         <v>11</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW8">
+        <v>24</v>
+      </c>
+      <c r="AX8">
         <v>16</v>
       </c>
-      <c r="AX8">
-        <v>15</v>
-      </c>
       <c r="AY8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BB8">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE8">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BF8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG8">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BH8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL8">
         <v>110</v>
@@ -2827,43 +2827,43 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS8">
         <v>1.02</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -2898,7 +2898,7 @@
         <v>1.54</v>
       </c>
       <c r="I9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J9">
         <v>4.8</v>
@@ -2913,7 +2913,7 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O9">
         <v>1.16</v>
@@ -2922,7 +2922,7 @@
         <v>2.82</v>
       </c>
       <c r="Q9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R9">
         <v>1.74</v>
@@ -2937,10 +2937,10 @@
         <v>2.36</v>
       </c>
       <c r="V9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="W9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X9">
         <v>32</v>
@@ -2964,13 +2964,13 @@
         <v>11</v>
       </c>
       <c r="AE9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF9">
         <v>270</v>
       </c>
       <c r="AG9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH9">
         <v>24</v>
@@ -2997,7 +2997,7 @@
         <v>5.5</v>
       </c>
       <c r="AP9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ9">
         <v>12</v>
@@ -3033,7 +3033,7 @@
         <v>20</v>
       </c>
       <c r="BB9">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BC9">
         <v>44</v>
@@ -3045,7 +3045,7 @@
         <v>50</v>
       </c>
       <c r="BF9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG9">
         <v>4.9</v>
@@ -3057,10 +3057,10 @@
         <v>3.75</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL9">
         <v>100</v>
@@ -3069,7 +3069,7 @@
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BO9">
         <v>6.6</v>
@@ -3087,13 +3087,13 @@
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BU9">
         <v>4.1</v>
       </c>
       <c r="BV9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW9">
         <v>6</v>
@@ -3108,7 +3108,7 @@
         <v>13.5</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>195</v>
@@ -3131,16 +3131,16 @@
         <v>166</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H10">
         <v>5.2</v>
       </c>
       <c r="I10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J10">
         <v>4.1</v>
@@ -3152,7 +3152,7 @@
         <v>1.4</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
         <v>4.4</v>
@@ -3164,7 +3164,7 @@
         <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R10">
         <v>1.43</v>
@@ -3173,7 +3173,7 @@
         <v>3.15</v>
       </c>
       <c r="T10">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
         <v>2.08</v>
@@ -3182,7 +3182,7 @@
         <v>1.21</v>
       </c>
       <c r="W10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X10">
         <v>17</v>
@@ -3194,10 +3194,10 @@
         <v>44</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
         <v>10.5</v>
@@ -3206,7 +3206,7 @@
         <v>24</v>
       </c>
       <c r="AE10">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -3221,13 +3221,13 @@
         <v>75</v>
       </c>
       <c r="AJ10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM10">
         <v>110</v>
@@ -3251,25 +3251,25 @@
         <v>85</v>
       </c>
       <c r="AT10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW10">
         <v>50</v>
       </c>
       <c r="AX10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA10">
         <v>50</v>
@@ -3287,70 +3287,70 @@
         <v>70</v>
       </c>
       <c r="BF10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG10">
         <v>55</v>
       </c>
       <c r="BH10">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BI10">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL10">
         <v>140</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX10">
         <v>60</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
         <v>22</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
         <v>195</v>
@@ -3373,19 +3373,19 @@
         <v>167</v>
       </c>
       <c r="F11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G11">
         <v>2.92</v>
       </c>
       <c r="H11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I11">
         <v>2.94</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
         <v>3.5</v>
@@ -3400,7 +3400,7 @@
         <v>3.55</v>
       </c>
       <c r="O11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
         <v>1.84</v>
@@ -3409,16 +3409,16 @@
         <v>2.08</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
         <v>3.75</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V11">
         <v>1.52</v>
@@ -3451,7 +3451,7 @@
         <v>40</v>
       </c>
       <c r="AF11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -3538,28 +3538,28 @@
         <v>3.65</v>
       </c>
       <c r="BI11">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11">
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BL11">
         <v>150</v>
       </c>
       <c r="BM11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN11">
         <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ11">
         <v>4.7</v>
@@ -3568,7 +3568,7 @@
         <v>42</v>
       </c>
       <c r="BS11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT11">
         <v>6.6</v>
@@ -3586,13 +3586,13 @@
         <v>42</v>
       </c>
       <c r="BY11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ11">
         <v>36</v>
       </c>
       <c r="CA11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="s">
         <v>195</v>
@@ -3615,22 +3615,22 @@
         <v>168</v>
       </c>
       <c r="F12">
+        <v>1.41</v>
+      </c>
+      <c r="G12">
         <v>1.44</v>
       </c>
-      <c r="G12">
-        <v>1.48</v>
-      </c>
       <c r="H12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="J12">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L12">
         <v>1.34</v>
@@ -3639,40 +3639,40 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q12">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
         <v>1.49</v>
       </c>
       <c r="S12">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U12">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="V12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W12">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="X12">
         <v>23</v>
       </c>
       <c r="Y12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z12">
         <v>85</v>
@@ -3681,10 +3681,10 @@
         <v>320</v>
       </c>
       <c r="AB12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD12">
         <v>36</v>
@@ -3693,7 +3693,7 @@
         <v>180</v>
       </c>
       <c r="AF12">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
@@ -3705,22 +3705,22 @@
         <v>130</v>
       </c>
       <c r="AJ12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK12">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>160</v>
+        <v>510</v>
       </c>
       <c r="AN12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO12">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP12">
         <v>18</v>
@@ -3732,19 +3732,19 @@
         <v>55</v>
       </c>
       <c r="AS12">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU12">
         <v>10</v>
       </c>
       <c r="AV12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AX12">
         <v>7.6</v>
@@ -3753,7 +3753,7 @@
         <v>9</v>
       </c>
       <c r="AZ12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA12">
         <v>55</v>
@@ -3765,16 +3765,16 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF12">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BH12">
         <v>4.6</v>
@@ -3783,13 +3783,13 @@
         <v>3.1</v>
       </c>
       <c r="BJ12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM12">
         <v>1.01</v>
@@ -3798,34 +3798,34 @@
         <v>4.6</v>
       </c>
       <c r="BO12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP12">
         <v>10.5</v>
       </c>
       <c r="BQ12">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS12">
         <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BU12">
         <v>1.01</v>
       </c>
       <c r="BV12">
+        <v>90</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
         <v>85</v>
-      </c>
-      <c r="BW12">
-        <v>1.01</v>
-      </c>
-      <c r="BX12">
-        <v>80</v>
       </c>
       <c r="BY12">
         <v>1.01</v>
@@ -3834,7 +3834,7 @@
         <v>17.5</v>
       </c>
       <c r="CA12">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
         <v>195</v>
@@ -3857,16 +3857,16 @@
         <v>169</v>
       </c>
       <c r="F13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G13">
         <v>1.41</v>
       </c>
       <c r="H13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J13">
         <v>4.9</v>
@@ -3887,31 +3887,31 @@
         <v>1.36</v>
       </c>
       <c r="P13">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
         <v>2.1</v>
       </c>
       <c r="R13">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13">
         <v>3.9</v>
       </c>
       <c r="T13">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W13">
         <v>3.4</v>
       </c>
       <c r="X13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y13">
         <v>32</v>
@@ -3920,7 +3920,7 @@
         <v>110</v>
       </c>
       <c r="AA13">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="AB13">
         <v>6.4</v>
@@ -3929,7 +3929,7 @@
         <v>11.5</v>
       </c>
       <c r="AD13">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE13">
         <v>290</v>
@@ -3944,25 +3944,25 @@
         <v>40</v>
       </c>
       <c r="AI13">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AJ13">
         <v>11</v>
       </c>
       <c r="AK13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL13">
         <v>60</v>
       </c>
       <c r="AM13">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AN13">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO13">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="AP13">
         <v>12</v>
@@ -3971,10 +3971,10 @@
         <v>26</v>
       </c>
       <c r="AR13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT13">
         <v>5.8</v>
@@ -3983,10 +3983,10 @@
         <v>10</v>
       </c>
       <c r="AV13">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AW13">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX13">
         <v>6.2</v>
@@ -3998,7 +3998,7 @@
         <v>32</v>
       </c>
       <c r="BA13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB13">
         <v>9.800000000000001</v>
@@ -4010,43 +4010,43 @@
         <v>46</v>
       </c>
       <c r="BE13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF13">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG13">
         <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI13">
         <v>2.78</v>
       </c>
       <c r="BJ13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BL13">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BO13">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BP13">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR13">
         <v>36</v>
@@ -4055,13 +4055,13 @@
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BV13">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BW13">
         <v>1.01</v>
@@ -4099,19 +4099,19 @@
         <v>170</v>
       </c>
       <c r="F14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G14">
         <v>4.9</v>
       </c>
       <c r="H14">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I14">
         <v>1.77</v>
       </c>
       <c r="J14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
         <v>4.5</v>
@@ -4123,19 +4123,19 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O14">
         <v>1.21</v>
       </c>
       <c r="P14">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q14">
         <v>1.66</v>
       </c>
       <c r="R14">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S14">
         <v>2.68</v>
@@ -4144,31 +4144,31 @@
         <v>1.69</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
         <v>2.28</v>
       </c>
       <c r="W14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z14">
         <v>12.5</v>
       </c>
       <c r="AA14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AB14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14">
         <v>9.800000000000001</v>
@@ -4180,13 +4180,13 @@
         <v>40</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH14">
         <v>17.5</v>
       </c>
       <c r="AI14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ14">
         <v>110</v>
@@ -4204,7 +4204,7 @@
         <v>44</v>
       </c>
       <c r="AO14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP14">
         <v>20</v>
@@ -4222,28 +4222,28 @@
         <v>20</v>
       </c>
       <c r="AU14">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW14">
         <v>14.5</v>
       </c>
       <c r="AX14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY14">
         <v>17</v>
       </c>
       <c r="AZ14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA14">
         <v>24</v>
       </c>
       <c r="BB14">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BC14">
         <v>38</v>
@@ -4252,13 +4252,13 @@
         <v>44</v>
       </c>
       <c r="BE14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF14">
         <v>34</v>
       </c>
       <c r="BG14">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH14">
         <v>4.8</v>
@@ -4270,7 +4270,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL14">
         <v>110</v>
@@ -4279,7 +4279,7 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO14">
         <v>1.01</v>
@@ -4297,7 +4297,7 @@
         <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU14">
         <v>4.2</v>
@@ -4306,10 +4306,10 @@
         <v>11.5</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BY14">
         <v>1.01</v>
@@ -4341,22 +4341,22 @@
         <v>171</v>
       </c>
       <c r="F15">
+        <v>4.2</v>
+      </c>
+      <c r="G15">
+        <v>4.6</v>
+      </c>
+      <c r="H15">
+        <v>1.81</v>
+      </c>
+      <c r="I15">
+        <v>1.89</v>
+      </c>
+      <c r="J15">
         <v>4</v>
       </c>
-      <c r="G15">
-        <v>4.5</v>
-      </c>
-      <c r="H15">
-        <v>1.83</v>
-      </c>
-      <c r="I15">
-        <v>1.94</v>
-      </c>
-      <c r="J15">
-        <v>4.1</v>
-      </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.29</v>
@@ -4365,7 +4365,7 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O15">
         <v>1.19</v>
@@ -4374,133 +4374,133 @@
         <v>2.56</v>
       </c>
       <c r="Q15">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
         <v>1.62</v>
       </c>
       <c r="S15">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T15">
         <v>1.49</v>
       </c>
       <c r="U15">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="W15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X15">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="Y15">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Z15">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AA15">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AB15">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AC15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AF15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AG15">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AH15">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AI15">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="AJ15">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK15">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AL15">
         <v>150</v>
       </c>
       <c r="AM15">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN15">
-        <v>300</v>
+        <v>42</v>
       </c>
       <c r="AO15">
+        <v>8.4</v>
+      </c>
+      <c r="AP15">
+        <v>21</v>
+      </c>
+      <c r="AQ15">
+        <v>11</v>
+      </c>
+      <c r="AR15">
         <v>11.5</v>
       </c>
-      <c r="AP15">
-        <v>2.36</v>
-      </c>
-      <c r="AQ15">
-        <v>2.06</v>
-      </c>
-      <c r="AR15">
-        <v>2.22</v>
-      </c>
       <c r="AS15">
+        <v>17.5</v>
+      </c>
+      <c r="AT15">
+        <v>18.5</v>
+      </c>
+      <c r="AU15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15">
+        <v>9</v>
+      </c>
+      <c r="AW15">
         <v>14.5</v>
       </c>
-      <c r="AT15">
-        <v>2.18</v>
-      </c>
-      <c r="AU15">
-        <v>6.6</v>
-      </c>
-      <c r="AV15">
-        <v>2</v>
-      </c>
-      <c r="AW15">
-        <v>2.16</v>
-      </c>
       <c r="AX15">
-        <v>2.24</v>
+        <v>29</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AZ15">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BA15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB15">
-        <v>2.3</v>
+        <v>55</v>
       </c>
       <c r="BC15">
-        <v>2.28</v>
+        <v>36</v>
       </c>
       <c r="BD15">
-        <v>2.5</v>
+        <v>36</v>
       </c>
       <c r="BE15">
-        <v>2.3</v>
+        <v>50</v>
       </c>
       <c r="BF15">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BG15">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH15">
         <v>5.2</v>
@@ -4509,7 +4509,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK15">
         <v>3.25</v>
@@ -4518,49 +4518,49 @@
         <v>95</v>
       </c>
       <c r="BM15">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO15">
         <v>6</v>
       </c>
       <c r="BP15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW15">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BX15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ15">
         <v>17.5</v>
       </c>
       <c r="CA15">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="CB15" t="s">
         <v>195</v>
@@ -4583,19 +4583,19 @@
         <v>172</v>
       </c>
       <c r="F16">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G16">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H16">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K16">
         <v>3.8</v>
@@ -4607,46 +4607,46 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q16">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S16">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="T16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X16">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y16">
         <v>14</v>
       </c>
       <c r="Z16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA16">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AB16">
         <v>13.5</v>
@@ -4658,7 +4658,7 @@
         <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AF16">
         <v>19</v>
@@ -4670,16 +4670,16 @@
         <v>16.5</v>
       </c>
       <c r="AI16">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK16">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AL16">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AM16">
         <v>200</v>
@@ -4691,115 +4691,115 @@
         <v>22</v>
       </c>
       <c r="AP16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS16">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AT16">
         <v>11</v>
       </c>
       <c r="AU16">
+        <v>7</v>
+      </c>
+      <c r="AV16">
+        <v>10.5</v>
+      </c>
+      <c r="AW16">
+        <v>22</v>
+      </c>
+      <c r="AX16">
+        <v>16</v>
+      </c>
+      <c r="AY16">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16">
+        <v>13</v>
+      </c>
+      <c r="BA16">
+        <v>27</v>
+      </c>
+      <c r="BB16">
+        <v>25</v>
+      </c>
+      <c r="BC16">
+        <v>20</v>
+      </c>
+      <c r="BD16">
+        <v>27</v>
+      </c>
+      <c r="BE16">
+        <v>55</v>
+      </c>
+      <c r="BF16">
+        <v>16.5</v>
+      </c>
+      <c r="BG16">
+        <v>18</v>
+      </c>
+      <c r="BH16">
+        <v>4.5</v>
+      </c>
+      <c r="BI16">
+        <v>3</v>
+      </c>
+      <c r="BJ16">
+        <v>11</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>110</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>7</v>
+      </c>
+      <c r="BO16">
+        <v>4.4</v>
+      </c>
+      <c r="BP16">
+        <v>23</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>34</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
         <v>7.2</v>
       </c>
-      <c r="AV16">
-        <v>11</v>
-      </c>
-      <c r="AW16">
-        <v>13</v>
-      </c>
-      <c r="AX16">
-        <v>15</v>
-      </c>
-      <c r="AY16">
-        <v>10</v>
-      </c>
-      <c r="AZ16">
-        <v>13.5</v>
-      </c>
-      <c r="BA16">
-        <v>30</v>
-      </c>
-      <c r="BB16">
-        <v>30</v>
-      </c>
-      <c r="BC16">
-        <v>14.5</v>
-      </c>
-      <c r="BD16">
-        <v>7.6</v>
-      </c>
-      <c r="BE16">
-        <v>8.6</v>
-      </c>
-      <c r="BF16">
-        <v>15.5</v>
-      </c>
-      <c r="BG16">
-        <v>18.5</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.01</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.01</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.01</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.01</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -4825,7 +4825,7 @@
         <v>173</v>
       </c>
       <c r="F17">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G17">
         <v>1.87</v>
@@ -4834,16 +4834,16 @@
         <v>5.5</v>
       </c>
       <c r="I17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J17">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M17">
         <v>1.1</v>
@@ -4858,7 +4858,7 @@
         <v>1.64</v>
       </c>
       <c r="Q17">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
         <v>1.22</v>
@@ -4870,7 +4870,7 @@
         <v>2.16</v>
       </c>
       <c r="U17">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
         <v>1.2</v>
@@ -4882,7 +4882,7 @@
         <v>10.5</v>
       </c>
       <c r="Y17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z17">
         <v>48</v>
@@ -4912,7 +4912,7 @@
         <v>27</v>
       </c>
       <c r="AI17">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="AJ17">
         <v>21</v>
@@ -4927,7 +4927,7 @@
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO17">
         <v>700</v>
@@ -4939,10 +4939,10 @@
         <v>11.5</v>
       </c>
       <c r="AR17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT17">
         <v>5.7</v>
@@ -4954,7 +4954,7 @@
         <v>18</v>
       </c>
       <c r="AW17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX17">
         <v>7.6</v>
@@ -4963,10 +4963,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB17">
         <v>15</v>
@@ -4978,73 +4978,73 @@
         <v>34</v>
       </c>
       <c r="BE17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF17">
         <v>13.5</v>
       </c>
       <c r="BG17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="CB17" t="s">
         <v>195</v>
@@ -5067,16 +5067,16 @@
         <v>174</v>
       </c>
       <c r="F18">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G18">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H18">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J18">
         <v>4.1</v>
@@ -5097,43 +5097,43 @@
         <v>1.15</v>
       </c>
       <c r="P18">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R18">
         <v>1.82</v>
       </c>
       <c r="S18">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T18">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U18">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V18">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X18">
         <v>32</v>
       </c>
       <c r="Y18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z18">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AA18">
         <v>60</v>
       </c>
       <c r="AB18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC18">
         <v>11</v>
@@ -5142,7 +5142,7 @@
         <v>14.5</v>
       </c>
       <c r="AE18">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="AF18">
         <v>19.5</v>
@@ -5151,10 +5151,10 @@
         <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ18">
         <v>29</v>
@@ -5181,7 +5181,7 @@
         <v>21</v>
       </c>
       <c r="AR18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS18">
         <v>48</v>
@@ -5190,13 +5190,13 @@
         <v>16.5</v>
       </c>
       <c r="AU18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX18">
         <v>17.5</v>
@@ -5211,10 +5211,10 @@
         <v>28</v>
       </c>
       <c r="BB18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC18">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD18">
         <v>21</v>
@@ -5223,7 +5223,7 @@
         <v>38</v>
       </c>
       <c r="BF18">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG18">
         <v>15</v>
@@ -5241,7 +5241,7 @@
         <v>6.4</v>
       </c>
       <c r="BL18">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BM18">
         <v>1.01</v>
@@ -5309,55 +5309,55 @@
         <v>175</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G19">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H19">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="I19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J19">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K19">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M19">
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O19">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q19">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R19">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="S19">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="T19">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U19">
         <v>2.28</v>
       </c>
       <c r="V19">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W19">
         <v>1.18</v>
@@ -5366,10 +5366,10 @@
         <v>30</v>
       </c>
       <c r="Y19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA19">
         <v>18.5</v>
@@ -5378,154 +5378,154 @@
         <v>34</v>
       </c>
       <c r="AC19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD19">
         <v>13</v>
       </c>
       <c r="AE19">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF19">
         <v>65</v>
       </c>
       <c r="AG19">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AH19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ19">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AK19">
+        <v>70</v>
+      </c>
+      <c r="AL19">
+        <v>60</v>
+      </c>
+      <c r="AM19">
         <v>75</v>
-      </c>
-      <c r="AL19">
-        <v>65</v>
-      </c>
-      <c r="AM19">
-        <v>85</v>
       </c>
       <c r="AN19">
         <v>65</v>
       </c>
       <c r="AO19">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AP19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR19">
         <v>10</v>
       </c>
       <c r="AS19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT19">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AU19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX19">
-        <v>5.4</v>
+        <v>44</v>
       </c>
       <c r="AY19">
         <v>20</v>
       </c>
       <c r="AZ19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BB19">
+        <v>9.4</v>
+      </c>
+      <c r="BC19">
+        <v>50</v>
+      </c>
+      <c r="BD19">
+        <v>40</v>
+      </c>
+      <c r="BE19">
+        <v>55</v>
+      </c>
+      <c r="BF19">
+        <v>36</v>
+      </c>
+      <c r="BG19">
+        <v>5.1</v>
+      </c>
+      <c r="BH19">
         <v>5.7</v>
       </c>
-      <c r="BC19">
-        <v>5.5</v>
-      </c>
-      <c r="BD19">
-        <v>5.4</v>
-      </c>
-      <c r="BE19">
-        <v>5.5</v>
-      </c>
-      <c r="BF19">
-        <v>5.4</v>
-      </c>
-      <c r="BG19">
+      <c r="BI19">
+        <v>3.7</v>
+      </c>
+      <c r="BJ19">
+        <v>11.5</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>110</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>12.5</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>55</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>55</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
         <v>5.3</v>
       </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.01</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.01</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.01</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.01</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA19">
         <v>1.01</v>
@@ -5554,13 +5554,13 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H20">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -5578,31 +5578,31 @@
         <v>5.3</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P20">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q20">
         <v>1.66</v>
       </c>
       <c r="R20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S20">
         <v>2.68</v>
       </c>
       <c r="T20">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X20">
         <v>21</v>
@@ -5611,7 +5611,7 @@
         <v>20</v>
       </c>
       <c r="Z20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA20">
         <v>70</v>
@@ -5623,7 +5623,7 @@
         <v>9.6</v>
       </c>
       <c r="AD20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE20">
         <v>40</v>
@@ -5653,10 +5653,10 @@
         <v>70</v>
       </c>
       <c r="AN20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP20">
         <v>18.5</v>
@@ -5668,7 +5668,7 @@
         <v>26</v>
       </c>
       <c r="AS20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT20">
         <v>11.5</v>
@@ -5686,7 +5686,7 @@
         <v>13</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
         <v>13.5</v>
@@ -5698,7 +5698,7 @@
         <v>21</v>
       </c>
       <c r="BC20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD20">
         <v>25</v>
@@ -5710,7 +5710,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH20">
         <v>4.5</v>
@@ -5767,7 +5767,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5793,16 +5793,16 @@
         <v>177</v>
       </c>
       <c r="F21">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G21">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="H21">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I21">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J21">
         <v>3.9</v>
@@ -5817,34 +5817,34 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O21">
         <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R21">
         <v>1.71</v>
       </c>
       <c r="S21">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T21">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U21">
         <v>2.86</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W21">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X21">
         <v>27</v>
@@ -5871,22 +5871,22 @@
         <v>24</v>
       </c>
       <c r="AF21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH21">
         <v>14</v>
       </c>
       <c r="AI21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ21">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL21">
         <v>28</v>
@@ -5895,19 +5895,19 @@
         <v>48</v>
       </c>
       <c r="AN21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO21">
         <v>17</v>
       </c>
       <c r="AP21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS21">
         <v>32</v>
@@ -5940,7 +5940,7 @@
         <v>36</v>
       </c>
       <c r="BC21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21">
         <v>25</v>
@@ -5952,19 +5952,19 @@
         <v>12</v>
       </c>
       <c r="BG21">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI21">
         <v>3.6</v>
       </c>
       <c r="BJ21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL21">
         <v>70</v>
@@ -5994,10 +5994,10 @@
         <v>6.4</v>
       </c>
       <c r="BU21">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV21">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BW21">
         <v>1.01</v>
@@ -6012,7 +6012,7 @@
         <v>15</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB21" t="s">
         <v>195</v>
@@ -6035,22 +6035,22 @@
         <v>178</v>
       </c>
       <c r="F22">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G22">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H22">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I22">
         <v>5.7</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L22">
         <v>1.4</v>
@@ -6059,34 +6059,34 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P22">
+        <v>2.02</v>
+      </c>
+      <c r="Q22">
+        <v>1.93</v>
+      </c>
+      <c r="R22">
+        <v>1.4</v>
+      </c>
+      <c r="S22">
+        <v>3.35</v>
+      </c>
+      <c r="T22">
+        <v>1.87</v>
+      </c>
+      <c r="U22">
         <v>2.06</v>
-      </c>
-      <c r="Q22">
-        <v>1.91</v>
-      </c>
-      <c r="R22">
-        <v>1.41</v>
-      </c>
-      <c r="S22">
-        <v>3.3</v>
-      </c>
-      <c r="T22">
-        <v>1.84</v>
-      </c>
-      <c r="U22">
-        <v>2.1</v>
       </c>
       <c r="V22">
         <v>1.21</v>
       </c>
       <c r="W22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X22">
         <v>15.5</v>
@@ -6095,13 +6095,13 @@
         <v>19.5</v>
       </c>
       <c r="Z22">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AA22">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB22">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>9.199999999999999</v>
@@ -6119,49 +6119,49 @@
         <v>9.6</v>
       </c>
       <c r="AH22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI22">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ22">
         <v>18</v>
       </c>
       <c r="AK22">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL22">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM22">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO22">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AP22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR22">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AS22">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="AT22">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU22">
         <v>8.199999999999999</v>
       </c>
       <c r="AV22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW22">
         <v>60</v>
@@ -6179,13 +6179,13 @@
         <v>55</v>
       </c>
       <c r="BB22">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC22">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD22">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE22">
         <v>85</v>
@@ -6197,64 +6197,64 @@
         <v>60</v>
       </c>
       <c r="BH22">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BI22">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL22">
         <v>150</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN22">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO22">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR22">
         <v>28</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT22">
         <v>9.199999999999999</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV22">
         <v>48</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB22" t="s">
         <v>195</v>
@@ -6277,10 +6277,10 @@
         <v>179</v>
       </c>
       <c r="F23">
+        <v>1.49</v>
+      </c>
+      <c r="G23">
         <v>1.51</v>
-      </c>
-      <c r="G23">
-        <v>1.54</v>
       </c>
       <c r="H23">
         <v>6.8</v>
@@ -6289,46 +6289,46 @@
         <v>7.4</v>
       </c>
       <c r="J23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O23">
         <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q23">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R23">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S23">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U23">
         <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W23">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="X23">
         <v>27</v>
@@ -6343,7 +6343,7 @@
         <v>210</v>
       </c>
       <c r="AB23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC23">
         <v>12</v>
@@ -6352,19 +6352,19 @@
         <v>26</v>
       </c>
       <c r="AE23">
-        <v>95</v>
+        <v>480</v>
       </c>
       <c r="AF23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG23">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH23">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI23">
-        <v>390</v>
+        <v>160</v>
       </c>
       <c r="AJ23">
         <v>14</v>
@@ -6379,7 +6379,7 @@
         <v>320</v>
       </c>
       <c r="AN23">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AO23">
         <v>80</v>
@@ -6391,10 +6391,10 @@
         <v>26</v>
       </c>
       <c r="AR23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS23">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="AT23">
         <v>10</v>
@@ -6406,7 +6406,7 @@
         <v>23</v>
       </c>
       <c r="AW23">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AX23">
         <v>9.6</v>
@@ -6421,13 +6421,13 @@
         <v>60</v>
       </c>
       <c r="BB23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC23">
         <v>13</v>
       </c>
       <c r="BD23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE23">
         <v>75</v>
@@ -6442,61 +6442,61 @@
         <v>5.2</v>
       </c>
       <c r="BI23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BO23">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BP23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BV23">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB23" t="s">
         <v>195</v>
@@ -6519,16 +6519,16 @@
         <v>180</v>
       </c>
       <c r="F24">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G24">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H24">
         <v>4.5</v>
       </c>
       <c r="I24">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J24">
         <v>4.4</v>
@@ -6543,61 +6543,61 @@
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P24">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q24">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R24">
         <v>1.83</v>
       </c>
       <c r="S24">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T24">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U24">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V24">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W24">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA24">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="AB24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD24">
         <v>21</v>
       </c>
       <c r="AE24">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG24">
         <v>11</v>
@@ -6606,10 +6606,10 @@
         <v>16</v>
       </c>
       <c r="AI24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK24">
         <v>17</v>
@@ -6624,61 +6624,61 @@
         <v>6.6</v>
       </c>
       <c r="AO24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP24">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AQ24">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR24">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AS24">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AT24">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU24">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV24">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW24">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX24">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY24">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24">
         <v>12.5</v>
       </c>
       <c r="BA24">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC24">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD24">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE24">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BF24">
         <v>5.7</v>
       </c>
       <c r="BG24">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BH24">
         <v>5.7</v>
@@ -6687,22 +6687,22 @@
         <v>4.1</v>
       </c>
       <c r="BJ24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK24">
         <v>6.6</v>
       </c>
       <c r="BL24">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM24">
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO24">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP24">
         <v>11.5</v>
@@ -6711,31 +6711,31 @@
         <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS24">
         <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU24">
         <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX24">
         <v>32</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA24">
         <v>1.01</v>
@@ -6761,64 +6761,64 @@
         <v>181</v>
       </c>
       <c r="F25">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H25">
+        <v>2.06</v>
+      </c>
+      <c r="I25">
         <v>2.08</v>
       </c>
-      <c r="I25">
-        <v>2.1</v>
-      </c>
       <c r="J25">
+        <v>3.55</v>
+      </c>
+      <c r="K25">
         <v>3.6</v>
       </c>
-      <c r="K25">
-        <v>3.65</v>
-      </c>
       <c r="L25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M25">
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O25">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P25">
+        <v>1.96</v>
+      </c>
+      <c r="Q25">
         <v>2</v>
       </c>
-      <c r="Q25">
-        <v>1.99</v>
-      </c>
       <c r="R25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S25">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T25">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V25">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W25">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X25">
         <v>13.5</v>
       </c>
       <c r="Y25">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>12.5</v>
@@ -6830,10 +6830,10 @@
         <v>15</v>
       </c>
       <c r="AC25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE25">
         <v>21</v>
@@ -6842,16 +6842,16 @@
         <v>30</v>
       </c>
       <c r="AG25">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI25">
         <v>38</v>
       </c>
       <c r="AJ25">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK25">
         <v>50</v>
@@ -6860,10 +6860,10 @@
         <v>60</v>
       </c>
       <c r="AM25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN25">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO25">
         <v>15.5</v>
@@ -6872,7 +6872,7 @@
         <v>13</v>
       </c>
       <c r="AQ25">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR25">
         <v>11.5</v>
@@ -6884,7 +6884,7 @@
         <v>14</v>
       </c>
       <c r="AU25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV25">
         <v>10</v>
@@ -6917,19 +6917,19 @@
         <v>85</v>
       </c>
       <c r="BF25">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH25">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BI25">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="BJ25">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK25">
         <v>8.800000000000001</v>
@@ -6938,43 +6938,43 @@
         <v>150</v>
       </c>
       <c r="BM25">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="BN25">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO25">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BP25">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BQ25">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BR25">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS25">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BT25">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU25">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BV25">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BW25">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX25">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY25">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -7003,13 +7003,13 @@
         <v>182</v>
       </c>
       <c r="F26">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G26">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H26">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I26">
         <v>2.9</v>
@@ -7021,25 +7021,25 @@
         <v>3.6</v>
       </c>
       <c r="L26">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M26">
         <v>1.06</v>
       </c>
       <c r="N26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O26">
         <v>1.28</v>
       </c>
       <c r="P26">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q26">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R26">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S26">
         <v>3.15</v>
@@ -7048,28 +7048,28 @@
         <v>1.71</v>
       </c>
       <c r="U26">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V26">
         <v>1.52</v>
       </c>
       <c r="W26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X26">
         <v>16</v>
       </c>
       <c r="Y26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z26">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA26">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -7081,7 +7081,7 @@
         <v>29</v>
       </c>
       <c r="AF26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG26">
         <v>12</v>
@@ -7093,10 +7093,10 @@
         <v>40</v>
       </c>
       <c r="AJ26">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL26">
         <v>38</v>
@@ -7105,10 +7105,10 @@
         <v>75</v>
       </c>
       <c r="AN26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO26">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP26">
         <v>15</v>
@@ -7117,16 +7117,16 @@
         <v>12.5</v>
       </c>
       <c r="AR26">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS26">
         <v>42</v>
       </c>
       <c r="AT26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV26">
         <v>11</v>
@@ -7135,19 +7135,19 @@
         <v>27</v>
       </c>
       <c r="AX26">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY26">
         <v>11.5</v>
       </c>
       <c r="AZ26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC26">
         <v>24</v>
@@ -7156,34 +7156,34 @@
         <v>32</v>
       </c>
       <c r="BE26">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF26">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH26">
         <v>4.2</v>
       </c>
       <c r="BI26">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ26">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK26">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="BL26">
         <v>110</v>
       </c>
       <c r="BM26">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN26">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO26">
         <v>4.6</v>
@@ -7192,31 +7192,31 @@
         <v>22</v>
       </c>
       <c r="BQ26">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR26">
         <v>34</v>
       </c>
       <c r="BS26">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT26">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BU26">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW26">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BY26">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7245,37 +7245,37 @@
         <v>183</v>
       </c>
       <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
         <v>2.04</v>
-      </c>
-      <c r="G27">
-        <v>2.06</v>
       </c>
       <c r="H27">
         <v>4.2</v>
       </c>
       <c r="I27">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
         <v>3.6</v>
       </c>
       <c r="L27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M27">
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O27">
         <v>1.38</v>
       </c>
       <c r="P27">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q27">
         <v>2.12</v>
@@ -7284,19 +7284,19 @@
         <v>1.32</v>
       </c>
       <c r="S27">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T27">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X27">
         <v>12.5</v>
@@ -7308,19 +7308,19 @@
         <v>32</v>
       </c>
       <c r="AA27">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>17.5</v>
       </c>
       <c r="AE27">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF27">
         <v>13</v>
@@ -7332,10 +7332,10 @@
         <v>19</v>
       </c>
       <c r="AI27">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AJ27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27">
         <v>25</v>
@@ -7347,34 +7347,34 @@
         <v>390</v>
       </c>
       <c r="AN27">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO27">
         <v>75</v>
       </c>
       <c r="AP27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR27">
         <v>24</v>
       </c>
       <c r="AS27">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AT27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU27">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV27">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW27">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AX27">
         <v>10.5</v>
@@ -7383,85 +7383,85 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA27">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB27">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BC27">
         <v>19</v>
       </c>
       <c r="BD27">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE27">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="BF27">
         <v>14.5</v>
       </c>
       <c r="BG27">
+        <v>40</v>
+      </c>
+      <c r="BH27">
+        <v>3.75</v>
+      </c>
+      <c r="BI27">
+        <v>2.62</v>
+      </c>
+      <c r="BJ27">
         <v>10.5</v>
       </c>
-      <c r="BH27">
-        <v>1000</v>
-      </c>
-      <c r="BI27">
-        <v>1.01</v>
-      </c>
-      <c r="BJ27">
-        <v>1000</v>
-      </c>
       <c r="BK27">
         <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM27">
         <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS27">
         <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW27">
         <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY27">
         <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA27">
         <v>1.01</v>
@@ -7487,16 +7487,16 @@
         <v>184</v>
       </c>
       <c r="F28">
+        <v>1.93</v>
+      </c>
+      <c r="G28">
         <v>1.94</v>
       </c>
-      <c r="G28">
-        <v>1.96</v>
-      </c>
       <c r="H28">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28">
         <v>3.8</v>
@@ -7514,13 +7514,13 @@
         <v>4</v>
       </c>
       <c r="O28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P28">
         <v>2.02</v>
       </c>
       <c r="Q28">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R28">
         <v>1.39</v>
@@ -7529,16 +7529,16 @@
         <v>3.4</v>
       </c>
       <c r="T28">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U28">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V28">
         <v>1.28</v>
       </c>
       <c r="W28">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X28">
         <v>15</v>
@@ -7547,19 +7547,19 @@
         <v>16</v>
       </c>
       <c r="Z28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>8.199999999999999</v>
       </c>
       <c r="AD28">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE28">
         <v>55</v>
@@ -7574,19 +7574,19 @@
         <v>18</v>
       </c>
       <c r="AI28">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ28">
         <v>22</v>
       </c>
       <c r="AK28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL28">
         <v>36</v>
       </c>
       <c r="AM28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN28">
         <v>13</v>
@@ -7601,10 +7601,10 @@
         <v>15</v>
       </c>
       <c r="AR28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS28">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AT28">
         <v>8.800000000000001</v>
@@ -7613,7 +7613,7 @@
         <v>8</v>
       </c>
       <c r="AV28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW28">
         <v>48</v>
@@ -7634,7 +7634,7 @@
         <v>20</v>
       </c>
       <c r="BC28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD28">
         <v>32</v>
@@ -7649,64 +7649,64 @@
         <v>48</v>
       </c>
       <c r="BH28">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BI28">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BJ28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL28">
         <v>150</v>
       </c>
       <c r="BM28">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28">
         <v>4.5</v>
       </c>
       <c r="BO28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ28">
         <v>12</v>
       </c>
       <c r="BR28">
+        <v>28</v>
+      </c>
+      <c r="BS28">
+        <v>24</v>
+      </c>
+      <c r="BT28">
+        <v>7.6</v>
+      </c>
+      <c r="BU28">
+        <v>7</v>
+      </c>
+      <c r="BV28">
+        <v>36</v>
+      </c>
+      <c r="BW28">
         <v>30</v>
-      </c>
-      <c r="BS28">
-        <v>7.2</v>
-      </c>
-      <c r="BT28">
-        <v>7.8</v>
-      </c>
-      <c r="BU28">
-        <v>6.8</v>
-      </c>
-      <c r="BV28">
-        <v>40</v>
-      </c>
-      <c r="BW28">
-        <v>27</v>
       </c>
       <c r="BX28">
         <v>48</v>
       </c>
       <c r="BY28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BZ28">
         <v>25</v>
       </c>
       <c r="CA28">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="CB28" t="s">
         <v>195</v>
@@ -7729,28 +7729,28 @@
         <v>185</v>
       </c>
       <c r="F29">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H29">
         <v>1.44</v>
       </c>
       <c r="I29">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J29">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K29">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L29">
         <v>1.41</v>
       </c>
       <c r="M29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N29">
         <v>3.65</v>
@@ -7771,22 +7771,22 @@
         <v>3.5</v>
       </c>
       <c r="T29">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U29">
         <v>1.68</v>
       </c>
       <c r="V29">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="W29">
         <v>1.1</v>
       </c>
       <c r="X29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z29">
         <v>8.199999999999999</v>
@@ -7795,100 +7795,100 @@
         <v>13</v>
       </c>
       <c r="AB29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD29">
         <v>11</v>
       </c>
       <c r="AE29">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG29">
         <v>85</v>
       </c>
       <c r="AH29">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AI29">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AJ29">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AK29">
         <v>220</v>
       </c>
       <c r="AL29">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AM29">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN29">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AO29">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP29">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="AQ29">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR29">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS29">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AT29">
         <v>6.4</v>
       </c>
       <c r="AU29">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AV29">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AW29">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX29">
         <v>7.8</v>
       </c>
       <c r="AY29">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AZ29">
         <v>6.6</v>
       </c>
       <c r="BA29">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="BB29">
+        <v>8.4</v>
+      </c>
+      <c r="BC29">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC29">
-        <v>8</v>
-      </c>
       <c r="BD29">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG29">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7971,22 +7971,22 @@
         <v>186</v>
       </c>
       <c r="F30">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="G30">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="H30">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="I30">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J30">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="K30">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
         <v>1.55</v>
@@ -7995,19 +7995,19 @@
         <v>1.11</v>
       </c>
       <c r="N30">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="O30">
         <v>1.5</v>
       </c>
       <c r="P30">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Q30">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R30">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -8019,10 +8019,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="X30">
         <v>500</v>
@@ -8213,28 +8213,28 @@
         <v>187</v>
       </c>
       <c r="F31">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G31">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H31">
         <v>2.76</v>
       </c>
       <c r="I31">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K31">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L31">
         <v>1.41</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
         <v>3.6</v>
@@ -8243,7 +8243,7 @@
         <v>1.32</v>
       </c>
       <c r="P31">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q31">
         <v>1.98</v>
@@ -8291,22 +8291,22 @@
         <v>38</v>
       </c>
       <c r="AF31">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG31">
         <v>14</v>
       </c>
       <c r="AH31">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI31">
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL31">
         <v>48</v>
@@ -8321,115 +8321,115 @@
         <v>36</v>
       </c>
       <c r="AP31">
+        <v>4.3</v>
+      </c>
+      <c r="AQ31">
+        <v>4.1</v>
+      </c>
+      <c r="AR31">
+        <v>4.7</v>
+      </c>
+      <c r="AS31">
+        <v>5.3</v>
+      </c>
+      <c r="AT31">
+        <v>4</v>
+      </c>
+      <c r="AU31">
+        <v>3.45</v>
+      </c>
+      <c r="AV31">
+        <v>4.2</v>
+      </c>
+      <c r="AW31">
+        <v>5</v>
+      </c>
+      <c r="AX31">
+        <v>4.4</v>
+      </c>
+      <c r="AY31">
+        <v>4.1</v>
+      </c>
+      <c r="AZ31">
+        <v>4.4</v>
+      </c>
+      <c r="BA31">
+        <v>5.3</v>
+      </c>
+      <c r="BB31">
+        <v>5.1</v>
+      </c>
+      <c r="BC31">
+        <v>5</v>
+      </c>
+      <c r="BD31">
+        <v>5.2</v>
+      </c>
+      <c r="BE31">
+        <v>5.6</v>
+      </c>
+      <c r="BF31">
+        <v>4.8</v>
+      </c>
+      <c r="BG31">
+        <v>5</v>
+      </c>
+      <c r="BH31">
+        <v>3.75</v>
+      </c>
+      <c r="BI31">
+        <v>2.78</v>
+      </c>
+      <c r="BJ31">
         <v>10.5</v>
       </c>
-      <c r="AQ31">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR31">
-        <v>15.5</v>
-      </c>
-      <c r="AS31">
-        <v>4.9</v>
-      </c>
-      <c r="AT31">
-        <v>8.4</v>
-      </c>
-      <c r="AU31">
-        <v>6.2</v>
-      </c>
-      <c r="AV31">
-        <v>10</v>
-      </c>
-      <c r="AW31">
-        <v>4.7</v>
-      </c>
-      <c r="AX31">
-        <v>13</v>
-      </c>
-      <c r="AY31">
-        <v>9.4</v>
-      </c>
-      <c r="AZ31">
-        <v>13</v>
-      </c>
-      <c r="BA31">
-        <v>4.9</v>
-      </c>
-      <c r="BB31">
+      <c r="BK31">
+        <v>7.4</v>
+      </c>
+      <c r="BL31">
+        <v>140</v>
+      </c>
+      <c r="BM31">
+        <v>1.01</v>
+      </c>
+      <c r="BN31">
+        <v>6.4</v>
+      </c>
+      <c r="BO31">
         <v>4.8</v>
       </c>
-      <c r="BC31">
-        <v>4.6</v>
-      </c>
-      <c r="BD31">
-        <v>4.8</v>
-      </c>
-      <c r="BE31">
-        <v>5.1</v>
-      </c>
-      <c r="BF31">
-        <v>20</v>
-      </c>
-      <c r="BG31">
-        <v>4.7</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>1.01</v>
-      </c>
-      <c r="BJ31">
-        <v>1000</v>
-      </c>
-      <c r="BK31">
-        <v>1.01</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>1.01</v>
-      </c>
-      <c r="BN31">
-        <v>1000</v>
-      </c>
-      <c r="BO31">
-        <v>1.01</v>
-      </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ31">
         <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS31">
         <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW31">
         <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY31">
         <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA31">
         <v>1.01</v>
@@ -8455,25 +8455,25 @@
         <v>188</v>
       </c>
       <c r="F32">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="G32">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H32">
         <v>12</v>
       </c>
       <c r="I32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J32">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K32">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L32">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M32">
         <v>1.07</v>
@@ -8482,61 +8482,61 @@
         <v>3.75</v>
       </c>
       <c r="O32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P32">
         <v>1.92</v>
       </c>
       <c r="Q32">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S32">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T32">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U32">
         <v>1.62</v>
       </c>
       <c r="V32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W32">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="X32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y32">
         <v>80</v>
       </c>
       <c r="Z32">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA32">
-        <v>680</v>
+        <v>790</v>
       </c>
       <c r="AB32">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC32">
         <v>12.5</v>
       </c>
       <c r="AD32">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE32">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AF32">
         <v>7.2</v>
       </c>
       <c r="AG32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH32">
         <v>42</v>
@@ -8551,28 +8551,28 @@
         <v>17.5</v>
       </c>
       <c r="AL32">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM32">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO32">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="AP32">
         <v>12.5</v>
       </c>
       <c r="AQ32">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR32">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AS32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT32">
         <v>6.2</v>
@@ -8584,7 +8584,7 @@
         <v>36</v>
       </c>
       <c r="AW32">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AX32">
         <v>6.2</v>
@@ -8596,7 +8596,7 @@
         <v>30</v>
       </c>
       <c r="BA32">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB32">
         <v>9.199999999999999</v>
@@ -8608,7 +8608,7 @@
         <v>40</v>
       </c>
       <c r="BE32">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF32">
         <v>6.4</v>
@@ -8617,61 +8617,61 @@
         <v>15</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK32">
         <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="BM32">
         <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS32">
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BW32">
         <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BY32">
         <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA32">
         <v>1.01</v>
@@ -8697,25 +8697,25 @@
         <v>189</v>
       </c>
       <c r="F33">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G33">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H33">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I33">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J33">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K33">
         <v>3.45</v>
       </c>
       <c r="L33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M33">
         <v>1.11</v>
@@ -8730,31 +8730,31 @@
         <v>1.62</v>
       </c>
       <c r="Q33">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
         <v>1.22</v>
       </c>
       <c r="S33">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U33">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W33">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="X33">
         <v>10.5</v>
       </c>
       <c r="Y33">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z33">
         <v>85</v>
@@ -8766,13 +8766,13 @@
         <v>7.2</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD33">
         <v>21</v>
       </c>
       <c r="AE33">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF33">
         <v>11</v>
@@ -8814,10 +8814,10 @@
         <v>26</v>
       </c>
       <c r="AS33">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT33">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU33">
         <v>6.4</v>
@@ -8826,10 +8826,10 @@
         <v>16.5</v>
       </c>
       <c r="AW33">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX33">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY33">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>20</v>
       </c>
       <c r="BA33">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB33">
         <v>20</v>
@@ -8847,76 +8847,76 @@
         <v>21</v>
       </c>
       <c r="BD33">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE33">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF33">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG33">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH33">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL33">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB33" t="s">
         <v>195</v>
@@ -8939,223 +8939,223 @@
         <v>190</v>
       </c>
       <c r="F34">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G34">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H34">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J34">
         <v>3.4</v>
       </c>
       <c r="K34">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L34">
         <v>1.44</v>
       </c>
       <c r="M34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
         <v>3.5</v>
       </c>
       <c r="O34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P34">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q34">
         <v>2.06</v>
       </c>
       <c r="R34">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S34">
         <v>3.8</v>
       </c>
       <c r="T34">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U34">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V34">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB34">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF34">
+        <v>90</v>
+      </c>
+      <c r="AG34">
+        <v>18.5</v>
+      </c>
+      <c r="AH34">
+        <v>22</v>
+      </c>
+      <c r="AI34">
+        <v>42</v>
+      </c>
+      <c r="AJ34">
+        <v>900</v>
+      </c>
+      <c r="AK34">
+        <v>150</v>
+      </c>
+      <c r="AL34">
+        <v>85</v>
+      </c>
+      <c r="AM34">
+        <v>390</v>
+      </c>
+      <c r="AN34">
+        <v>500</v>
+      </c>
+      <c r="AO34">
+        <v>16</v>
+      </c>
+      <c r="AP34">
+        <v>10</v>
+      </c>
+      <c r="AQ34">
+        <v>6.4</v>
+      </c>
+      <c r="AR34">
+        <v>9</v>
+      </c>
+      <c r="AS34">
+        <v>17.5</v>
+      </c>
+      <c r="AT34">
+        <v>11.5</v>
+      </c>
+      <c r="AU34">
+        <v>6.4</v>
+      </c>
+      <c r="AV34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW34">
+        <v>16.5</v>
+      </c>
+      <c r="AX34">
+        <v>14.5</v>
+      </c>
+      <c r="AY34">
+        <v>14</v>
+      </c>
+      <c r="AZ34">
+        <v>15</v>
+      </c>
+      <c r="BA34">
         <v>30</v>
       </c>
-      <c r="AG34">
-        <v>26</v>
-      </c>
-      <c r="AH34">
-        <v>1000</v>
-      </c>
-      <c r="AI34">
-        <v>1000</v>
-      </c>
-      <c r="AJ34">
-        <v>1000</v>
-      </c>
-      <c r="AK34">
-        <v>1000</v>
-      </c>
-      <c r="AL34">
-        <v>1000</v>
-      </c>
-      <c r="AM34">
-        <v>1000</v>
-      </c>
-      <c r="AN34">
-        <v>1000</v>
-      </c>
-      <c r="AO34">
-        <v>1000</v>
-      </c>
-      <c r="AP34">
-        <v>1.12</v>
-      </c>
-      <c r="AQ34">
-        <v>1.12</v>
-      </c>
-      <c r="AR34">
-        <v>1.12</v>
-      </c>
-      <c r="AS34">
-        <v>1.12</v>
-      </c>
-      <c r="AT34">
-        <v>1.07</v>
-      </c>
-      <c r="AU34">
-        <v>1.12</v>
-      </c>
-      <c r="AV34">
-        <v>1.12</v>
-      </c>
-      <c r="AW34">
-        <v>1.12</v>
-      </c>
-      <c r="AX34">
-        <v>1.08</v>
-      </c>
-      <c r="AY34">
-        <v>1.07</v>
-      </c>
-      <c r="AZ34">
-        <v>1.12</v>
-      </c>
-      <c r="BA34">
-        <v>1.12</v>
-      </c>
       <c r="BB34">
-        <v>1.12</v>
+        <v>9</v>
       </c>
       <c r="BC34">
-        <v>1.12</v>
+        <v>8.6</v>
       </c>
       <c r="BD34">
-        <v>1.12</v>
+        <v>28</v>
       </c>
       <c r="BE34">
-        <v>1.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF34">
-        <v>1.12</v>
+        <v>11</v>
       </c>
       <c r="BG34">
-        <v>1.12</v>
+        <v>12</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK34">
         <v>1.01</v>
       </c>
       <c r="BL34">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM34">
         <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ34">
         <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS34">
         <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU34">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW34">
         <v>1.01</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY34">
         <v>1.01</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA34">
         <v>1.01</v>
@@ -9181,25 +9181,25 @@
         <v>191</v>
       </c>
       <c r="F35">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G35">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="H35">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I35">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J35">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K35">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L35">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M35">
         <v>1.07</v>
@@ -9208,196 +9208,196 @@
         <v>3.7</v>
       </c>
       <c r="O35">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P35">
         <v>1.9</v>
       </c>
       <c r="Q35">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S35">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T35">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U35">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X35">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="Y35">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="Z35">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AA35">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AB35">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AC35">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD35">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE35">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF35">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AG35">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AH35">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AI35">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ35">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AK35">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL35">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM35">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AN35">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO35">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ35">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR35">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS35">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU35">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV35">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW35">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX35">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY35">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA35">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB35">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC35">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD35">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE35">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF35">
-        <v>1.55</v>
+        <v>21</v>
       </c>
       <c r="BG35">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI35">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL35">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM35">
         <v>1.01</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ35">
         <v>1.01</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS35">
         <v>1.01</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW35">
         <v>1.01</v>
       </c>
       <c r="BX35">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY35">
         <v>1.01</v>
       </c>
       <c r="BZ35">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA35">
         <v>1.01</v>
@@ -9438,28 +9438,28 @@
         <v>3.05</v>
       </c>
       <c r="K36">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L36">
         <v>1.53</v>
       </c>
       <c r="M36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N36">
         <v>2.82</v>
       </c>
       <c r="O36">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P36">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q36">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R36">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S36">
         <v>4.8</v>
@@ -9489,7 +9489,7 @@
         <v>110</v>
       </c>
       <c r="AB36">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC36">
         <v>8.4</v>
@@ -9498,7 +9498,7 @@
         <v>19.5</v>
       </c>
       <c r="AE36">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF36">
         <v>15.5</v>
@@ -9531,58 +9531,58 @@
         <v>100</v>
       </c>
       <c r="AP36">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="AQ36">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="AR36">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="AS36">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT36">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AU36">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="AV36">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="AW36">
+        <v>5.1</v>
+      </c>
+      <c r="AX36">
+        <v>4.1</v>
+      </c>
+      <c r="AY36">
+        <v>3.9</v>
+      </c>
+      <c r="AZ36">
+        <v>4.5</v>
+      </c>
+      <c r="BA36">
+        <v>5.2</v>
+      </c>
+      <c r="BB36">
         <v>4.8</v>
       </c>
-      <c r="AX36">
-        <v>10</v>
-      </c>
-      <c r="AY36">
-        <v>9</v>
-      </c>
-      <c r="AZ36">
-        <v>16.5</v>
-      </c>
-      <c r="BA36">
-        <v>4.9</v>
-      </c>
-      <c r="BB36">
-        <v>4.5</v>
-      </c>
       <c r="BC36">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD36">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE36">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF36">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BG36">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH36">
         <v>3.15</v>
@@ -9597,7 +9597,7 @@
         <v>1.01</v>
       </c>
       <c r="BL36">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BM36">
         <v>1.01</v>
@@ -9677,7 +9677,7 @@
         <v>4.5</v>
       </c>
       <c r="J37">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K37">
         <v>3.55</v>
@@ -9689,7 +9689,7 @@
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O37">
         <v>1.39</v>
@@ -9698,7 +9698,7 @@
         <v>1.76</v>
       </c>
       <c r="Q37">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R37">
         <v>1.28</v>
@@ -9779,7 +9779,7 @@
         <v>11</v>
       </c>
       <c r="AR37">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AS37">
         <v>8.6</v>
@@ -9806,7 +9806,7 @@
         <v>17</v>
       </c>
       <c r="BA37">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB37">
         <v>8</v>
@@ -9827,61 +9827,61 @@
         <v>8.4</v>
       </c>
       <c r="BH37">
-        <v>970</v>
+        <v>3.45</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK37">
         <v>1.01</v>
       </c>
       <c r="BL37">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM37">
         <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO37">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ37">
         <v>1.01</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS37">
         <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU37">
         <v>1.01</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW37">
         <v>1.01</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY37">
         <v>1.01</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA37">
         <v>1.01</v>
@@ -9910,34 +9910,34 @@
         <v>1.71</v>
       </c>
       <c r="G38">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H38">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I38">
-        <v>110</v>
+        <v>6.2</v>
       </c>
       <c r="J38">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K38">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L38">
         <v>1.41</v>
       </c>
       <c r="M38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N38">
         <v>3.6</v>
       </c>
       <c r="O38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P38">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q38">
         <v>1.98</v>
@@ -9949,10 +9949,10 @@
         <v>3.5</v>
       </c>
       <c r="T38">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V38">
         <v>1.2</v>
@@ -9961,169 +9961,169 @@
         <v>2.18</v>
       </c>
       <c r="X38">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z38">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA38">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB38">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC38">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD38">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE38">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF38">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG38">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ38">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK38">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL38">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO38">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP38">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ38">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR38">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS38">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT38">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU38">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV38">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW38">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AX38">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY38">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ38">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA38">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB38">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC38">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BD38">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE38">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF38">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG38">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH38">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ38">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK38">
         <v>1.01</v>
       </c>
       <c r="BL38">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM38">
         <v>1.01</v>
       </c>
       <c r="BN38">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO38">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP38">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ38">
         <v>1.01</v>
       </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS38">
         <v>1.01</v>
       </c>
       <c r="BT38">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU38">
         <v>1.01</v>
       </c>
       <c r="BV38">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW38">
         <v>1.01</v>
       </c>
       <c r="BX38">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY38">
         <v>1.01</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA38">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-03.xlsx
@@ -622,7 +622,7 @@
     <t>Trujillanos</t>
   </si>
   <si>
-    <t>2026-09-03 06:35:31</t>
+    <t>2026-09-03 08:53:57</t>
   </si>
 </sst>
 </file>
@@ -1219,52 +1219,52 @@
         <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
+        <v>2.8</v>
+      </c>
+      <c r="I2">
+        <v>2.98</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>4.4</v>
+      </c>
+      <c r="L2">
+        <v>1.27</v>
+      </c>
+      <c r="M2">
+        <v>1.03</v>
+      </c>
+      <c r="N2">
+        <v>6.6</v>
+      </c>
+      <c r="O2">
+        <v>1.16</v>
+      </c>
+      <c r="P2">
         <v>2.86</v>
       </c>
-      <c r="I2">
-        <v>3.05</v>
-      </c>
-      <c r="J2">
-        <v>3.9</v>
-      </c>
-      <c r="K2">
-        <v>4.2</v>
-      </c>
-      <c r="L2">
-        <v>1.29</v>
-      </c>
-      <c r="M2">
-        <v>1.04</v>
-      </c>
-      <c r="N2">
-        <v>5.9</v>
-      </c>
-      <c r="O2">
-        <v>1.19</v>
-      </c>
-      <c r="P2">
-        <v>2.66</v>
-      </c>
       <c r="Q2">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S2">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="T2">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="U2">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
         <v>1.66</v>
@@ -1273,19 +1273,19 @@
         <v>32</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA2">
         <v>55</v>
       </c>
       <c r="AB2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -1294,10 +1294,10 @@
         <v>34</v>
       </c>
       <c r="AF2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>16.5</v>
@@ -1306,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK2">
         <v>30</v>
@@ -1315,28 +1315,28 @@
         <v>36</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AP2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU2">
         <v>8.800000000000001</v>
@@ -1345,7 +1345,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX2">
         <v>17</v>
@@ -1354,10 +1354,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB2">
         <v>23</v>
@@ -1366,73 +1366,73 @@
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BH2">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1458,7 +1458,7 @@
         <v>164</v>
       </c>
       <c r="F3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G3">
         <v>2.26</v>
@@ -1467,40 +1467,40 @@
         <v>3.55</v>
       </c>
       <c r="I3">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R3">
         <v>1.39</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U3">
         <v>2.16</v>
@@ -1515,13 +1515,13 @@
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1530,7 +1530,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>55</v>
@@ -1548,7 +1548,7 @@
         <v>55</v>
       </c>
       <c r="AJ3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK3">
         <v>24</v>
@@ -1557,13 +1557,13 @@
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN3">
         <v>17.5</v>
       </c>
       <c r="AO3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP3">
         <v>13</v>
@@ -1572,7 +1572,7 @@
         <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3">
         <v>46</v>
@@ -1587,7 +1587,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1596,64 +1596,64 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3">
         <v>36</v>
       </c>
       <c r="BB3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE3">
         <v>70</v>
       </c>
       <c r="BF3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH3">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BI3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
         <v>9.6</v>
       </c>
       <c r="BK3">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>130</v>
       </c>
       <c r="BM3">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT3">
         <v>7</v>
@@ -1665,19 +1665,19 @@
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>202</v>
@@ -1700,19 +1700,19 @@
         <v>165</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
         <v>2.42</v>
       </c>
       <c r="I4">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
         <v>3.5</v>
@@ -1724,16 +1724,16 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
         <v>1.3</v>
@@ -1748,22 +1748,22 @@
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB4">
         <v>11.5</v>
@@ -1772,151 +1772,151 @@
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
         <v>46</v>
       </c>
       <c r="AJ4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK4">
         <v>44</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM4">
         <v>120</v>
       </c>
       <c r="AN4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AO4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR4">
         <v>13</v>
       </c>
       <c r="AS4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AT4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AX4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AY4">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA4">
         <v>38</v>
       </c>
       <c r="BB4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BF4">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1942,22 +1942,22 @@
         <v>166</v>
       </c>
       <c r="F5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="G5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="I5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="K5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>1.25</v>
@@ -1966,37 +1966,37 @@
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P5">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q5">
         <v>1.47</v>
       </c>
       <c r="R5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S5">
         <v>2.16</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
         <v>1.04</v>
       </c>
       <c r="W5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="X5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y5">
         <v>75</v>
@@ -2008,7 +2008,7 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
         <v>24</v>
@@ -2017,103 +2017,103 @@
         <v>80</v>
       </c>
       <c r="AE5">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AF5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AI5">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ5">
         <v>8.6</v>
       </c>
       <c r="AK5">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM5">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR5">
+        <v>7.6</v>
+      </c>
+      <c r="AS5">
         <v>7.8</v>
-      </c>
-      <c r="AS5">
-        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
         <v>5.5</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY5">
         <v>5.5</v>
       </c>
       <c r="AZ5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC5">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF5">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ5">
         <v>16</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BL5">
         <v>200</v>
@@ -2122,16 +2122,16 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR5">
         <v>26</v>
@@ -2158,7 +2158,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -2184,64 +2184,64 @@
         <v>167</v>
       </c>
       <c r="F6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="I6">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L6">
         <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
+        <v>1.59</v>
+      </c>
+      <c r="R6">
         <v>1.58</v>
       </c>
-      <c r="R6">
-        <v>1.51</v>
-      </c>
       <c r="S6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T6">
         <v>1.54</v>
       </c>
       <c r="U6">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W6">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Z6">
         <v>22</v>
@@ -2250,7 +2250,7 @@
         <v>40</v>
       </c>
       <c r="AB6">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC6">
         <v>10</v>
@@ -2259,148 +2259,148 @@
         <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI6">
+        <v>36</v>
+      </c>
+      <c r="AJ6">
+        <v>55</v>
+      </c>
+      <c r="AK6">
+        <v>34</v>
+      </c>
+      <c r="AL6">
         <v>38</v>
       </c>
-      <c r="AJ6">
-        <v>48</v>
-      </c>
-      <c r="AK6">
-        <v>36</v>
-      </c>
-      <c r="AL6">
-        <v>42</v>
-      </c>
       <c r="AM6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN6">
         <v>21</v>
       </c>
       <c r="AO6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP6">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
+        <v>7</v>
+      </c>
+      <c r="AR6">
+        <v>7</v>
+      </c>
+      <c r="AS6">
         <v>5.5</v>
-      </c>
-      <c r="AR6">
-        <v>5.2</v>
-      </c>
-      <c r="AS6">
-        <v>5.8</v>
       </c>
       <c r="AT6">
         <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AV6">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW6">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AX6">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AY6">
         <v>5.5</v>
       </c>
       <c r="AZ6">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BA6">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB6">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC6">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="BD6">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF6">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="BG6">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BH6">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2426,7 +2426,7 @@
         <v>168</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G7">
         <v>1.94</v>
@@ -2438,52 +2438,52 @@
         <v>4.8</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q7">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S7">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="T7">
         <v>1.76</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V7">
         <v>1.26</v>
       </c>
       <c r="W7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y7">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Z7">
         <v>42</v>
@@ -2492,16 +2492,16 @@
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AF7">
         <v>12.5</v>
@@ -2510,16 +2510,16 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL7">
         <v>500</v>
@@ -2528,34 +2528,34 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO7">
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR7">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AX7">
         <v>10</v>
@@ -2564,7 +2564,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
         <v>9.199999999999999</v>
@@ -2573,31 +2573,31 @@
         <v>18</v>
       </c>
       <c r="BC7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BE7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>130</v>
@@ -2606,43 +2606,43 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BU7">
         <v>6</v>
       </c>
       <c r="BV7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW7">
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2668,223 +2668,223 @@
         <v>169</v>
       </c>
       <c r="F8">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="G8">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="H8">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q8">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="R8">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U8">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="X8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y8">
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA8">
         <v>46</v>
       </c>
       <c r="AB8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC8">
         <v>8.4</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH8">
         <v>15.5</v>
       </c>
       <c r="AI8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL8">
         <v>36</v>
       </c>
       <c r="AM8">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO8">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AP8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AX8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD8">
         <v>30</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="BF8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -2910,136 +2910,136 @@
         <v>170</v>
       </c>
       <c r="F9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="I9">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="J9">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M9">
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P9">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="Q9">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="S9">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="T9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U9">
         <v>2.42</v>
       </c>
       <c r="V9">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="W9">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X9">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Y9">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z9">
         <v>12.5</v>
       </c>
       <c r="AA9">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AB9">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AC9">
+        <v>13.5</v>
+      </c>
+      <c r="AD9">
+        <v>11.5</v>
+      </c>
+      <c r="AE9">
+        <v>14.5</v>
+      </c>
+      <c r="AF9">
+        <v>270</v>
+      </c>
+      <c r="AG9">
+        <v>34</v>
+      </c>
+      <c r="AH9">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>60</v>
+      </c>
+      <c r="AJ9">
+        <v>700</v>
+      </c>
+      <c r="AK9">
+        <v>400</v>
+      </c>
+      <c r="AL9">
+        <v>50</v>
+      </c>
+      <c r="AM9">
+        <v>580</v>
+      </c>
+      <c r="AN9">
+        <v>60</v>
+      </c>
+      <c r="AO9">
+        <v>6</v>
+      </c>
+      <c r="AP9">
+        <v>24</v>
+      </c>
+      <c r="AQ9">
         <v>12.5</v>
       </c>
-      <c r="AD9">
-        <v>11</v>
-      </c>
-      <c r="AE9">
-        <v>17.5</v>
-      </c>
-      <c r="AF9">
-        <v>120</v>
-      </c>
-      <c r="AG9">
-        <v>30</v>
-      </c>
-      <c r="AH9">
-        <v>19</v>
-      </c>
-      <c r="AI9">
-        <v>36</v>
-      </c>
-      <c r="AJ9">
-        <v>150</v>
-      </c>
-      <c r="AK9">
-        <v>150</v>
-      </c>
-      <c r="AL9">
-        <v>55</v>
-      </c>
-      <c r="AM9">
-        <v>85</v>
-      </c>
-      <c r="AN9">
-        <v>85</v>
-      </c>
-      <c r="AO9">
-        <v>5.5</v>
-      </c>
-      <c r="AP9">
-        <v>23</v>
-      </c>
-      <c r="AQ9">
-        <v>12</v>
-      </c>
       <c r="AR9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS9">
         <v>13.5</v>
       </c>
       <c r="AT9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV9">
         <v>9.6</v>
       </c>
       <c r="AW9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX9">
         <v>46</v>
@@ -3048,88 +3048,88 @@
         <v>20</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB9">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BC9">
         <v>46</v>
       </c>
       <c r="BD9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9">
         <v>50</v>
       </c>
       <c r="BF9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG9">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BH9">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI9">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="BL9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM9">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BN9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BO9">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP9">
         <v>55</v>
       </c>
       <c r="BQ9">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BR9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS9">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BT9">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU9">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BV9">
         <v>10.5</v>
       </c>
       <c r="BW9">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="BX9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BY9">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="s">
         <v>202</v>
@@ -3152,16 +3152,16 @@
         <v>171</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="G10">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="H10">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I10">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J10">
         <v>4.1</v>
@@ -3176,202 +3176,202 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P10">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="R10">
         <v>1.43</v>
       </c>
       <c r="S10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T10">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W10">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="X10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA10">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG10">
         <v>9.6</v>
       </c>
       <c r="AH10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ10">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AK10">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL10">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN10">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AO10">
         <v>75</v>
       </c>
       <c r="AP10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AS10">
-        <v>85</v>
+        <v>14.5</v>
       </c>
       <c r="AT10">
         <v>8.6</v>
       </c>
       <c r="AU10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW10">
         <v>50</v>
       </c>
       <c r="AX10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA10">
         <v>50</v>
       </c>
       <c r="BB10">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE10">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF10">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG10">
-        <v>55</v>
+        <v>13.5</v>
       </c>
       <c r="BH10">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="BJ10">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="BL10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="BP10">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>6.4</v>
+        <v>1.02</v>
       </c>
       <c r="BR10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>5.6</v>
+        <v>1.02</v>
       </c>
       <c r="BV10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>8.4</v>
+        <v>1.02</v>
       </c>
       <c r="CB10" t="s">
         <v>202</v>
@@ -3394,7 +3394,7 @@
         <v>172</v>
       </c>
       <c r="F11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G11">
         <v>2.9</v>
@@ -3403,13 +3403,13 @@
         <v>2.76</v>
       </c>
       <c r="I11">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J11">
         <v>3.3</v>
       </c>
       <c r="K11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
         <v>1.45</v>
@@ -3421,19 +3421,19 @@
         <v>3.55</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T11">
         <v>1.87</v>
@@ -3442,7 +3442,7 @@
         <v>2.1</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
         <v>1.52</v>
@@ -3466,7 +3466,7 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE11">
         <v>40</v>
@@ -3499,7 +3499,7 @@
         <v>36</v>
       </c>
       <c r="AO11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP11">
         <v>11.5</v>
@@ -3508,13 +3508,13 @@
         <v>9.6</v>
       </c>
       <c r="AR11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AT11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU11">
         <v>7</v>
@@ -3523,7 +3523,7 @@
         <v>11</v>
       </c>
       <c r="AW11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX11">
         <v>16</v>
@@ -3550,10 +3550,10 @@
         <v>75</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BH11">
         <v>3.65</v>
@@ -3565,22 +3565,22 @@
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL11">
         <v>150</v>
       </c>
       <c r="BM11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN11">
         <v>6.6</v>
       </c>
       <c r="BO11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ11">
         <v>4.7</v>
@@ -3589,7 +3589,7 @@
         <v>42</v>
       </c>
       <c r="BS11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT11">
         <v>6.6</v>
@@ -3607,13 +3607,13 @@
         <v>42</v>
       </c>
       <c r="BY11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ11">
         <v>36</v>
       </c>
       <c r="CA11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="s">
         <v>202</v>
@@ -3636,127 +3636,127 @@
         <v>173</v>
       </c>
       <c r="F12">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G12">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="H12">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>5.2</v>
       </c>
       <c r="K12">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L12">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P12">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="R12">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S12">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T12">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U12">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W12">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="X12">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Y12">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA12">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB12">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD12">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AE12">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AF12">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG12">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH12">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI12">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AJ12">
         <v>12.5</v>
       </c>
       <c r="AK12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL12">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM12">
-        <v>510</v>
+        <v>140</v>
       </c>
       <c r="AN12">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO12">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AP12">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AQ12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS12">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="AT12">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AU12">
         <v>11</v>
@@ -3765,61 +3765,61 @@
         <v>26</v>
       </c>
       <c r="AW12">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AX12">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
         <v>21</v>
       </c>
       <c r="BA12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BB12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC12">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD12">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BE12">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG12">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="BH12">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BI12">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK12">
         <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="BM12">
         <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO12">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BP12">
         <v>10.5</v>
@@ -3828,31 +3828,31 @@
         <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BS12">
         <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BU12">
         <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="BW12">
         <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BY12">
         <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CA12">
         <v>1.01</v>
@@ -3884,19 +3884,19 @@
         <v>1.41</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I13">
         <v>14</v>
       </c>
       <c r="J13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K13">
         <v>4.9</v>
       </c>
       <c r="L13">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -3905,25 +3905,25 @@
         <v>3.35</v>
       </c>
       <c r="O13">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q13">
         <v>2.18</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
         <v>4.2</v>
       </c>
       <c r="T13">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V13">
         <v>1.07</v>
@@ -3935,28 +3935,28 @@
         <v>12.5</v>
       </c>
       <c r="Y13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z13">
         <v>130</v>
       </c>
       <c r="AA13">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="AB13">
         <v>6</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE13">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AF13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3965,7 +3965,7 @@
         <v>44</v>
       </c>
       <c r="AI13">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AJ13">
         <v>11</v>
@@ -3980,7 +3980,7 @@
         <v>410</v>
       </c>
       <c r="AN13">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO13">
         <v>680</v>
@@ -3992,10 +3992,10 @@
         <v>26</v>
       </c>
       <c r="AR13">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13">
         <v>5.5</v>
@@ -4004,10 +4004,10 @@
         <v>10</v>
       </c>
       <c r="AV13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX13">
         <v>6</v>
@@ -4016,85 +4016,85 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BA13">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BB13">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC13">
         <v>16.5</v>
       </c>
       <c r="BD13">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE13">
+        <v>17.5</v>
+      </c>
+      <c r="BF13">
+        <v>7.8</v>
+      </c>
+      <c r="BG13">
         <v>16</v>
       </c>
-      <c r="BF13">
-        <v>8</v>
-      </c>
-      <c r="BG13">
-        <v>15</v>
-      </c>
       <c r="BH13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI13">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BK13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BO13">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="BP13">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BS13">
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
+        <v>180</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
         <v>170</v>
       </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
-      <c r="BX13">
-        <v>140</v>
-      </c>
       <c r="BY13">
         <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA13">
         <v>1.01</v>
@@ -4120,100 +4120,100 @@
         <v>175</v>
       </c>
       <c r="F14">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G14">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H14">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="I14">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="J14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
         <v>4.5</v>
       </c>
       <c r="L14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O14">
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S14">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T14">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="W14">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y14">
         <v>11.5</v>
       </c>
       <c r="Z14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB14">
         <v>23</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
         <v>9.800000000000001</v>
       </c>
       <c r="AE14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH14">
         <v>18</v>
       </c>
       <c r="AI14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL14">
         <v>55</v>
@@ -4222,13 +4222,13 @@
         <v>75</v>
       </c>
       <c r="AN14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO14">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP14">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
         <v>10.5</v>
@@ -4237,13 +4237,13 @@
         <v>11</v>
       </c>
       <c r="AS14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV14">
         <v>9.199999999999999</v>
@@ -4252,94 +4252,94 @@
         <v>14.5</v>
       </c>
       <c r="AX14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ14">
         <v>16</v>
       </c>
       <c r="BA14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB14">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="BC14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG14">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI14">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK14">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM14">
         <v>60</v>
       </c>
       <c r="BN14">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO14">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BQ14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BS14">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BT14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU14">
         <v>4.2</v>
       </c>
       <c r="BV14">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BW14">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BX14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BY14">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BZ14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CA14">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="CB14" t="s">
         <v>202</v>
@@ -4362,16 +4362,16 @@
         <v>176</v>
       </c>
       <c r="F15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G15">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H15">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I15">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="J15">
         <v>4.4</v>
@@ -4380,43 +4380,43 @@
         <v>4.7</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="Q15">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R15">
         <v>1.6</v>
       </c>
       <c r="S15">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="T15">
         <v>1.62</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="W15">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y15">
         <v>12</v>
@@ -4425,37 +4425,37 @@
         <v>12.5</v>
       </c>
       <c r="AA15">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AB15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC15">
         <v>11</v>
       </c>
       <c r="AD15">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF15">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AG15">
         <v>21</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ15">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AK15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL15">
         <v>55</v>
@@ -4464,37 +4464,37 @@
         <v>75</v>
       </c>
       <c r="AN15">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR15">
         <v>11</v>
       </c>
       <c r="AS15">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT15">
         <v>21</v>
       </c>
       <c r="AU15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV15">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AW15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY15">
         <v>17</v>
@@ -4509,7 +4509,7 @@
         <v>60</v>
       </c>
       <c r="BC15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD15">
         <v>42</v>
@@ -4518,70 +4518,70 @@
         <v>55</v>
       </c>
       <c r="BF15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG15">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH15">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>202</v>
@@ -4604,25 +4604,25 @@
         <v>177</v>
       </c>
       <c r="F16">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G16">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I16">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M16">
         <v>1.05</v>
@@ -4634,31 +4634,31 @@
         <v>1.25</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
         <v>1.76</v>
       </c>
       <c r="R16">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S16">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T16">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y16">
         <v>15</v>
@@ -4667,73 +4667,73 @@
         <v>23</v>
       </c>
       <c r="AA16">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AB16">
+        <v>13.5</v>
+      </c>
+      <c r="AC16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16">
         <v>14</v>
-      </c>
-      <c r="AC16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD16">
-        <v>13.5</v>
       </c>
       <c r="AE16">
         <v>32</v>
       </c>
       <c r="AF16">
+        <v>17.5</v>
+      </c>
+      <c r="AG16">
+        <v>12.5</v>
+      </c>
+      <c r="AH16">
         <v>18</v>
       </c>
-      <c r="AG16">
-        <v>13</v>
-      </c>
-      <c r="AH16">
-        <v>16.5</v>
-      </c>
       <c r="AI16">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AL16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM16">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP16">
         <v>15.5</v>
       </c>
       <c r="AQ16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS16">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT16">
         <v>11.5</v>
       </c>
       <c r="AU16">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX16">
         <v>15</v>
@@ -4742,13 +4742,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA16">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB16">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BC16">
         <v>21</v>
@@ -4760,28 +4760,28 @@
         <v>55</v>
       </c>
       <c r="BF16">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH16">
         <v>4.5</v>
       </c>
       <c r="BI16">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BL16">
         <v>110</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN16">
         <v>6.8</v>
@@ -4790,16 +4790,16 @@
         <v>4.3</v>
       </c>
       <c r="BP16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BR16">
         <v>34</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT16">
         <v>7.4</v>
@@ -4811,19 +4811,19 @@
         <v>26</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BX16">
         <v>36</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ16">
         <v>25</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB16" t="s">
         <v>202</v>
@@ -4846,10 +4846,10 @@
         <v>178</v>
       </c>
       <c r="F17">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G17">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="H17">
         <v>5.5</v>
@@ -4858,10 +4858,10 @@
         <v>6.4</v>
       </c>
       <c r="J17">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L17">
         <v>1.52</v>
@@ -4870,40 +4870,40 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O17">
         <v>1.47</v>
       </c>
       <c r="P17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q17">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R17">
         <v>1.22</v>
       </c>
       <c r="S17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T17">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V17">
         <v>1.2</v>
       </c>
       <c r="W17">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X17">
         <v>10.5</v>
       </c>
       <c r="Y17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z17">
         <v>48</v>
@@ -4921,10 +4921,10 @@
         <v>25</v>
       </c>
       <c r="AE17">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AF17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>11</v>
@@ -4948,37 +4948,37 @@
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO17">
         <v>600</v>
       </c>
       <c r="AP17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ17">
         <v>12.5</v>
       </c>
       <c r="AR17">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AS17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT17">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU17">
         <v>7</v>
       </c>
       <c r="AV17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY17">
         <v>9</v>
@@ -4987,85 +4987,85 @@
         <v>21</v>
       </c>
       <c r="BA17">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="BB17">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC17">
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF17">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH17">
         <v>3.2</v>
       </c>
       <c r="BI17">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ17">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL17">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO17">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BP17">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BQ17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS17">
         <v>27</v>
       </c>
       <c r="BT17">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BU17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV17">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BX17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY17">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="BZ17">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="CA17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CB17" t="s">
         <v>202</v>
@@ -5088,22 +5088,22 @@
         <v>179</v>
       </c>
       <c r="F18">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G18">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H18">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
         <v>1.25</v>
@@ -5112,19 +5112,19 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O18">
         <v>1.15</v>
       </c>
       <c r="P18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R18">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S18">
         <v>2.16</v>
@@ -5133,13 +5133,13 @@
         <v>1.45</v>
       </c>
       <c r="U18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X18">
         <v>34</v>
@@ -5157,16 +5157,16 @@
         <v>18</v>
       </c>
       <c r="AC18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE18">
         <v>29</v>
       </c>
       <c r="AF18">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
@@ -5178,10 +5178,10 @@
         <v>30</v>
       </c>
       <c r="AJ18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL18">
         <v>24</v>
@@ -5190,10 +5190,10 @@
         <v>46</v>
       </c>
       <c r="AN18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP18">
         <v>29</v>
@@ -5217,7 +5217,7 @@
         <v>13</v>
       </c>
       <c r="AW18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX18">
         <v>17.5</v>
@@ -5244,70 +5244,70 @@
         <v>38</v>
       </c>
       <c r="BF18">
+        <v>8.4</v>
+      </c>
+      <c r="BG18">
+        <v>14.5</v>
+      </c>
+      <c r="BH18">
+        <v>5.8</v>
+      </c>
+      <c r="BI18">
+        <v>4.7</v>
+      </c>
+      <c r="BJ18">
+        <v>9.4</v>
+      </c>
+      <c r="BK18">
+        <v>6.4</v>
+      </c>
+      <c r="BL18">
+        <v>70</v>
+      </c>
+      <c r="BM18">
+        <v>5.2</v>
+      </c>
+      <c r="BN18">
+        <v>6.6</v>
+      </c>
+      <c r="BO18">
+        <v>4.6</v>
+      </c>
+      <c r="BP18">
+        <v>16</v>
+      </c>
+      <c r="BQ18">
+        <v>4.6</v>
+      </c>
+      <c r="BR18">
+        <v>23</v>
+      </c>
+      <c r="BS18">
+        <v>4.5</v>
+      </c>
+      <c r="BT18">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG18">
-        <v>15</v>
-      </c>
-      <c r="BH18">
-        <v>5.1</v>
-      </c>
-      <c r="BI18">
-        <v>4.6</v>
-      </c>
-      <c r="BJ18">
-        <v>8.4</v>
-      </c>
-      <c r="BK18">
-        <v>7.2</v>
-      </c>
-      <c r="BL18">
-        <v>60</v>
-      </c>
-      <c r="BM18">
-        <v>12</v>
-      </c>
-      <c r="BN18">
-        <v>5.8</v>
-      </c>
-      <c r="BO18">
-        <v>5.1</v>
-      </c>
-      <c r="BP18">
+      <c r="BU18">
+        <v>5.6</v>
+      </c>
+      <c r="BV18">
+        <v>23</v>
+      </c>
+      <c r="BW18">
+        <v>4.5</v>
+      </c>
+      <c r="BX18">
+        <v>28</v>
+      </c>
+      <c r="BY18">
+        <v>4.7</v>
+      </c>
+      <c r="BZ18">
         <v>14</v>
       </c>
-      <c r="BQ18">
-        <v>10.5</v>
-      </c>
-      <c r="BR18">
-        <v>20</v>
-      </c>
-      <c r="BS18">
-        <v>8.6</v>
-      </c>
-      <c r="BT18">
-        <v>7.2</v>
-      </c>
-      <c r="BU18">
-        <v>4.8</v>
-      </c>
-      <c r="BV18">
-        <v>21</v>
-      </c>
-      <c r="BW18">
-        <v>8.6</v>
-      </c>
-      <c r="BX18">
-        <v>24</v>
-      </c>
-      <c r="BY18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ18">
-        <v>12.5</v>
-      </c>
       <c r="CA18">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="CB18" t="s">
         <v>202</v>
@@ -5333,79 +5333,79 @@
         <v>6.2</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H19">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I19">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="J19">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M19">
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P19">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="Q19">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R19">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S19">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="T19">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U19">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="W19">
         <v>1.17</v>
       </c>
       <c r="X19">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Y19">
         <v>14.5</v>
       </c>
       <c r="Z19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA19">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AB19">
         <v>34</v>
       </c>
       <c r="AC19">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE19">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF19">
         <v>65</v>
@@ -5414,10 +5414,10 @@
         <v>32</v>
       </c>
       <c r="AH19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AJ19">
         <v>170</v>
@@ -5426,94 +5426,94 @@
         <v>70</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM19">
         <v>75</v>
       </c>
       <c r="AN19">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO19">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AP19">
         <v>23</v>
       </c>
       <c r="AQ19">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT19">
         <v>26</v>
       </c>
       <c r="AU19">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV19">
         <v>9.6</v>
       </c>
       <c r="AW19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX19">
         <v>46</v>
       </c>
       <c r="AY19">
+        <v>21</v>
+      </c>
+      <c r="AZ19">
+        <v>17</v>
+      </c>
+      <c r="BA19">
         <v>20</v>
       </c>
-      <c r="AZ19">
-        <v>16.5</v>
-      </c>
-      <c r="BA19">
-        <v>21</v>
-      </c>
       <c r="BB19">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BC19">
         <v>46</v>
       </c>
       <c r="BD19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG19">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BI19">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ19">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
         <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM19">
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BO19">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
         <v>55</v>
@@ -5522,34 +5522,34 @@
         <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS19">
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU19">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BV19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CA19">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
         <v>202</v>
@@ -5572,19 +5572,19 @@
         <v>181</v>
       </c>
       <c r="F20">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H20">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I20">
+        <v>3.65</v>
+      </c>
+      <c r="J20">
         <v>3.95</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
       </c>
       <c r="K20">
         <v>4.1</v>
@@ -5605,7 +5605,7 @@
         <v>2.44</v>
       </c>
       <c r="Q20">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R20">
         <v>1.57</v>
@@ -5614,112 +5614,112 @@
         <v>2.7</v>
       </c>
       <c r="T20">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U20">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="X20">
         <v>23</v>
       </c>
       <c r="Y20">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z20">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA20">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD20">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE20">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF20">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH20">
         <v>16</v>
       </c>
       <c r="AI20">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ20">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK20">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL20">
         <v>28</v>
       </c>
       <c r="AM20">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN20">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AO20">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ20">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR20">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AS20">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AT20">
         <v>11.5</v>
       </c>
       <c r="AU20">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV20">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW20">
+        <v>32</v>
+      </c>
+      <c r="AX20">
+        <v>14</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>14</v>
+      </c>
+      <c r="BA20">
         <v>34</v>
       </c>
-      <c r="AX20">
-        <v>13</v>
-      </c>
-      <c r="AY20">
-        <v>9.4</v>
-      </c>
-      <c r="AZ20">
-        <v>14.5</v>
-      </c>
-      <c r="BA20">
-        <v>38</v>
-      </c>
       <c r="BB20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC20">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD20">
         <v>25</v>
@@ -5728,67 +5728,67 @@
         <v>55</v>
       </c>
       <c r="BF20">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG20">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BH20">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5814,22 +5814,22 @@
         <v>182</v>
       </c>
       <c r="F21">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="G21">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="H21">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="I21">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J21">
         <v>3.9</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>1.29</v>
@@ -5841,73 +5841,73 @@
         <v>6.4</v>
       </c>
       <c r="O21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q21">
         <v>1.53</v>
       </c>
       <c r="R21">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T21">
         <v>1.49</v>
       </c>
       <c r="U21">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W21">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y21">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Z21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB21">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
         <v>12.5</v>
       </c>
       <c r="AE21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF21">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AG21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH21">
         <v>14</v>
       </c>
       <c r="AI21">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AJ21">
         <v>42</v>
       </c>
       <c r="AK21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21">
         <v>36</v>
@@ -5919,34 +5919,34 @@
         <v>14.5</v>
       </c>
       <c r="AO21">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP21">
         <v>25</v>
       </c>
       <c r="AQ21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT21">
         <v>17</v>
       </c>
       <c r="AU21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY21">
         <v>11.5</v>
@@ -5955,10 +5955,10 @@
         <v>12.5</v>
       </c>
       <c r="BA21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC21">
         <v>22</v>
@@ -5967,73 +5967,73 @@
         <v>26</v>
       </c>
       <c r="BE21">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH21">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI21">
         <v>3.6</v>
       </c>
       <c r="BJ21">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BK21">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BL21">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BM21">
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO21">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP21">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BQ21">
         <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BS21">
         <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU21">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV21">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX21">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BY21">
         <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="CA21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>202</v>
@@ -6056,22 +6056,22 @@
         <v>183</v>
       </c>
       <c r="F22">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="G22">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="H22">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L22">
         <v>1.29</v>
@@ -6080,100 +6080,100 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>1.19</v>
       </c>
       <c r="P22">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q22">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R22">
         <v>1.66</v>
       </c>
       <c r="S22">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T22">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W22">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X22">
+        <v>27</v>
+      </c>
+      <c r="Y22">
         <v>34</v>
       </c>
-      <c r="Y22">
-        <v>32</v>
-      </c>
       <c r="Z22">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AA22">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AB22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD22">
+        <v>29</v>
+      </c>
+      <c r="AE22">
+        <v>210</v>
+      </c>
+      <c r="AF22">
+        <v>10.5</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+      <c r="AH22">
+        <v>22</v>
+      </c>
+      <c r="AI22">
+        <v>85</v>
+      </c>
+      <c r="AJ22">
+        <v>13</v>
+      </c>
+      <c r="AK22">
+        <v>14</v>
+      </c>
+      <c r="AL22">
         <v>28</v>
       </c>
-      <c r="AE22">
-        <v>95</v>
-      </c>
-      <c r="AF22">
-        <v>11.5</v>
-      </c>
-      <c r="AG22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH22">
-        <v>21</v>
-      </c>
-      <c r="AI22">
-        <v>160</v>
-      </c>
-      <c r="AJ22">
-        <v>13.5</v>
-      </c>
-      <c r="AK22">
-        <v>14.5</v>
-      </c>
-      <c r="AL22">
-        <v>36</v>
-      </c>
       <c r="AM22">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="AN22">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AO22">
         <v>320</v>
       </c>
       <c r="AP22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ22">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS22">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AT22">
         <v>10</v>
@@ -6182,25 +6182,25 @@
         <v>11</v>
       </c>
       <c r="AV22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW22">
         <v>70</v>
       </c>
       <c r="AX22">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA22">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC22">
         <v>13</v>
@@ -6212,70 +6212,70 @@
         <v>65</v>
       </c>
       <c r="BF22">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG22">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH22">
+        <v>5.3</v>
+      </c>
+      <c r="BI22">
+        <v>3.5</v>
+      </c>
+      <c r="BJ22">
+        <v>12.5</v>
+      </c>
+      <c r="BK22">
+        <v>7.6</v>
+      </c>
+      <c r="BL22">
+        <v>130</v>
+      </c>
+      <c r="BM22">
         <v>4.5</v>
       </c>
-      <c r="BI22">
-        <v>4</v>
-      </c>
-      <c r="BJ22">
+      <c r="BN22">
+        <v>5</v>
+      </c>
+      <c r="BO22">
+        <v>3.3</v>
+      </c>
+      <c r="BP22">
         <v>10</v>
       </c>
-      <c r="BK22">
-        <v>6</v>
-      </c>
-      <c r="BL22">
-        <v>120</v>
-      </c>
-      <c r="BM22">
-        <v>13.5</v>
-      </c>
-      <c r="BN22">
-        <v>4.3</v>
-      </c>
-      <c r="BO22">
-        <v>3.85</v>
-      </c>
-      <c r="BP22">
-        <v>8.6</v>
-      </c>
       <c r="BQ22">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR22">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BS22">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="BT22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BU22">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="BV22">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BW22">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX22">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY22">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ22">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="CA22">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="CB22" t="s">
         <v>202</v>
@@ -6298,25 +6298,25 @@
         <v>184</v>
       </c>
       <c r="F23">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G23">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H23">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
         <v>4.1</v>
       </c>
       <c r="L23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M23">
         <v>1.07</v>
@@ -6325,58 +6325,58 @@
         <v>4</v>
       </c>
       <c r="O23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P23">
         <v>2.02</v>
       </c>
       <c r="Q23">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R23">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S23">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T23">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U23">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X23">
         <v>15.5</v>
       </c>
       <c r="Y23">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z23">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AA23">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC23">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23">
         <v>22</v>
       </c>
       <c r="AE23">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG23">
         <v>9.6</v>
@@ -6388,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="AJ23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK23">
         <v>18.5</v>
@@ -6397,25 +6397,25 @@
         <v>36</v>
       </c>
       <c r="AM23">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN23">
         <v>11.5</v>
       </c>
       <c r="AO23">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="AP23">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ23">
         <v>17</v>
       </c>
       <c r="AR23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS23">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT23">
         <v>7.8</v>
@@ -6424,13 +6424,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW23">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX23">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY23">
         <v>9</v>
@@ -6445,7 +6445,7 @@
         <v>15.5</v>
       </c>
       <c r="BC23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD23">
         <v>32</v>
@@ -6454,70 +6454,70 @@
         <v>90</v>
       </c>
       <c r="BF23">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG23">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH23">
         <v>3.55</v>
       </c>
       <c r="BI23">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK23">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL23">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM23">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BN23">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BO23">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP23">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BQ23">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR23">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS23">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BT23">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV23">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BW23">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BX23">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BZ23">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CA23">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="CB23" t="s">
         <v>202</v>
@@ -6540,25 +6540,25 @@
         <v>185</v>
       </c>
       <c r="F24">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G24">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="H24">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I24">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J24">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K24">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M24">
         <v>1.03</v>
@@ -6567,19 +6567,19 @@
         <v>7.2</v>
       </c>
       <c r="O24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P24">
         <v>3.05</v>
       </c>
       <c r="Q24">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R24">
         <v>1.84</v>
       </c>
       <c r="S24">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T24">
         <v>1.51</v>
@@ -6588,178 +6588,178 @@
         <v>2.74</v>
       </c>
       <c r="V24">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W24">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="X24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA24">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="AB24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD24">
         <v>21</v>
       </c>
       <c r="AE24">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG24">
         <v>11</v>
       </c>
       <c r="AH24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ24">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK24">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM24">
         <v>55</v>
       </c>
       <c r="AN24">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AO24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP24">
+        <v>28</v>
+      </c>
+      <c r="AQ24">
         <v>27</v>
       </c>
-      <c r="AQ24">
-        <v>24</v>
-      </c>
       <c r="AR24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS24">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AT24">
         <v>13.5</v>
       </c>
       <c r="AU24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW24">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX24">
+        <v>13</v>
+      </c>
+      <c r="AY24">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24">
+        <v>14.5</v>
+      </c>
+      <c r="BA24">
+        <v>38</v>
+      </c>
+      <c r="BB24">
+        <v>16.5</v>
+      </c>
+      <c r="BC24">
         <v>13.5</v>
-      </c>
-      <c r="AY24">
-        <v>9.6</v>
-      </c>
-      <c r="AZ24">
-        <v>13.5</v>
-      </c>
-      <c r="BA24">
-        <v>28</v>
-      </c>
-      <c r="BB24">
-        <v>17.5</v>
-      </c>
-      <c r="BC24">
-        <v>14</v>
       </c>
       <c r="BD24">
         <v>20</v>
       </c>
       <c r="BE24">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF24">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG24">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH24">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="BJ24">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>6.6</v>
+        <v>1.02</v>
       </c>
       <c r="BL24">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BM24">
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="BP24">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR24">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT24">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BV24">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX24">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ24">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB24" t="s">
         <v>202</v>
@@ -6782,25 +6782,25 @@
         <v>186</v>
       </c>
       <c r="F25">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H25">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I25">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K25">
         <v>3.65</v>
       </c>
       <c r="L25">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M25">
         <v>1.08</v>
@@ -6815,25 +6815,25 @@
         <v>1.96</v>
       </c>
       <c r="Q25">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R25">
         <v>1.37</v>
       </c>
       <c r="S25">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T25">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U25">
         <v>2.16</v>
       </c>
       <c r="V25">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W25">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X25">
         <v>13.5</v>
@@ -6848,7 +6848,7 @@
         <v>23</v>
       </c>
       <c r="AB25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC25">
         <v>7.8</v>
@@ -6863,16 +6863,16 @@
         <v>30</v>
       </c>
       <c r="AG25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH25">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI25">
         <v>38</v>
       </c>
       <c r="AJ25">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK25">
         <v>55</v>
@@ -6881,13 +6881,13 @@
         <v>60</v>
       </c>
       <c r="AM25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN25">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP25">
         <v>13</v>
@@ -6899,25 +6899,25 @@
         <v>11.5</v>
       </c>
       <c r="AS25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT25">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU25">
         <v>7.4</v>
       </c>
       <c r="AV25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW25">
         <v>19.5</v>
       </c>
       <c r="AX25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ25">
         <v>17</v>
@@ -6941,61 +6941,61 @@
         <v>50</v>
       </c>
       <c r="BG25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH25">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="BI25">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="BJ25">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BK25">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BL25">
         <v>150</v>
       </c>
       <c r="BM25">
+        <v>5</v>
+      </c>
+      <c r="BN25">
+        <v>9</v>
+      </c>
+      <c r="BO25">
+        <v>6.8</v>
+      </c>
+      <c r="BP25">
+        <v>40</v>
+      </c>
+      <c r="BQ25">
+        <v>23</v>
+      </c>
+      <c r="BR25">
+        <v>55</v>
+      </c>
+      <c r="BS25">
+        <v>30</v>
+      </c>
+      <c r="BT25">
+        <v>5.6</v>
+      </c>
+      <c r="BU25">
+        <v>3.7</v>
+      </c>
+      <c r="BV25">
+        <v>17</v>
+      </c>
+      <c r="BW25">
+        <v>12.5</v>
+      </c>
+      <c r="BX25">
+        <v>34</v>
+      </c>
+      <c r="BY25">
         <v>20</v>
-      </c>
-      <c r="BN25">
-        <v>7.2</v>
-      </c>
-      <c r="BO25">
-        <v>6.6</v>
-      </c>
-      <c r="BP25">
-        <v>32</v>
-      </c>
-      <c r="BQ25">
-        <v>14</v>
-      </c>
-      <c r="BR25">
-        <v>44</v>
-      </c>
-      <c r="BS25">
-        <v>38</v>
-      </c>
-      <c r="BT25">
-        <v>4.7</v>
-      </c>
-      <c r="BU25">
-        <v>4.4</v>
-      </c>
-      <c r="BV25">
-        <v>14.5</v>
-      </c>
-      <c r="BW25">
-        <v>9</v>
-      </c>
-      <c r="BX25">
-        <v>28</v>
-      </c>
-      <c r="BY25">
-        <v>25</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -7024,76 +7024,76 @@
         <v>187</v>
       </c>
       <c r="F26">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G26">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H26">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I26">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L26">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M26">
         <v>1.06</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P26">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q26">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="R26">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S26">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T26">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U26">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V26">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X26">
         <v>17.5</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z26">
         <v>19.5</v>
       </c>
       <c r="AA26">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26">
         <v>12</v>
@@ -7117,34 +7117,34 @@
         <v>38</v>
       </c>
       <c r="AK26">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL26">
         <v>36</v>
       </c>
       <c r="AM26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN26">
+        <v>19</v>
+      </c>
+      <c r="AO26">
         <v>21</v>
-      </c>
-      <c r="AO26">
-        <v>23</v>
       </c>
       <c r="AP26">
         <v>16</v>
       </c>
       <c r="AQ26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR26">
         <v>18.5</v>
       </c>
       <c r="AS26">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU26">
         <v>7.8</v>
@@ -7153,22 +7153,22 @@
         <v>11.5</v>
       </c>
       <c r="AW26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY26">
         <v>11.5</v>
       </c>
       <c r="AZ26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA26">
+        <v>32</v>
+      </c>
+      <c r="BB26">
         <v>34</v>
-      </c>
-      <c r="BB26">
-        <v>32</v>
       </c>
       <c r="BC26">
         <v>25</v>
@@ -7180,64 +7180,64 @@
         <v>60</v>
       </c>
       <c r="BF26">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG26">
         <v>20</v>
       </c>
       <c r="BH26">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI26">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK26">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="BL26">
         <v>110</v>
       </c>
       <c r="BM26">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BN26">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO26">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP26">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BQ26">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BR26">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BS26">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BT26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU26">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV26">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BW26">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY26">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7266,58 +7266,58 @@
         <v>188</v>
       </c>
       <c r="F27">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="G27">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I27">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J27">
         <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L27">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O27">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q27">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T27">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V27">
         <v>1.27</v>
       </c>
       <c r="W27">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X27">
         <v>12.5</v>
@@ -7326,37 +7326,37 @@
         <v>14.5</v>
       </c>
       <c r="Z27">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA27">
         <v>110</v>
       </c>
       <c r="AB27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC27">
         <v>8.6</v>
       </c>
-      <c r="AC27">
-        <v>8</v>
-      </c>
       <c r="AD27">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE27">
         <v>70</v>
       </c>
       <c r="AF27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH27">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI27">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK27">
         <v>24</v>
@@ -7365,37 +7365,37 @@
         <v>44</v>
       </c>
       <c r="AM27">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="AN27">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO27">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="AP27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ27">
         <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT27">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU27">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV27">
         <v>15</v>
       </c>
       <c r="AW27">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AX27">
         <v>10</v>
@@ -7404,88 +7404,88 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA27">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB27">
         <v>20</v>
       </c>
       <c r="BC27">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE27">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG27">
+        <v>46</v>
+      </c>
+      <c r="BH27">
+        <v>3.6</v>
+      </c>
+      <c r="BI27">
+        <v>2.52</v>
+      </c>
+      <c r="BJ27">
+        <v>12.5</v>
+      </c>
+      <c r="BK27">
+        <v>4</v>
+      </c>
+      <c r="BL27">
+        <v>780</v>
+      </c>
+      <c r="BM27">
+        <v>4.9</v>
+      </c>
+      <c r="BN27">
+        <v>5.4</v>
+      </c>
+      <c r="BO27">
+        <v>3.55</v>
+      </c>
+      <c r="BP27">
+        <v>18</v>
+      </c>
+      <c r="BQ27">
+        <v>4.2</v>
+      </c>
+      <c r="BR27">
         <v>40</v>
       </c>
-      <c r="BH27">
-        <v>3.7</v>
-      </c>
-      <c r="BI27">
-        <v>2.9</v>
-      </c>
-      <c r="BJ27">
-        <v>10.5</v>
-      </c>
-      <c r="BK27">
-        <v>4.7</v>
-      </c>
-      <c r="BL27">
-        <v>870</v>
-      </c>
-      <c r="BM27">
-        <v>8</v>
-      </c>
-      <c r="BN27">
-        <v>4.8</v>
-      </c>
-      <c r="BO27">
-        <v>4</v>
-      </c>
-      <c r="BP27">
-        <v>15</v>
-      </c>
-      <c r="BQ27">
-        <v>10.5</v>
-      </c>
-      <c r="BR27">
-        <v>32</v>
-      </c>
       <c r="BS27">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT27">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU27">
         <v>5.7</v>
       </c>
       <c r="BV27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BW27">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BX27">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY27">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BZ27">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="CA27">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB27" t="s">
         <v>202</v>
@@ -7508,10 +7508,10 @@
         <v>189</v>
       </c>
       <c r="F28">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G28">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H28">
         <v>4.5</v>
@@ -7526,7 +7526,7 @@
         <v>3.85</v>
       </c>
       <c r="L28">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M28">
         <v>1.07</v>
@@ -7562,7 +7562,7 @@
         <v>2.06</v>
       </c>
       <c r="X28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y28">
         <v>16.5</v>
@@ -7571,16 +7571,16 @@
         <v>34</v>
       </c>
       <c r="AA28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB28">
         <v>9.199999999999999</v>
       </c>
       <c r="AC28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD28">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE28">
         <v>55</v>
@@ -7589,7 +7589,7 @@
         <v>11.5</v>
       </c>
       <c r="AG28">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH28">
         <v>18</v>
@@ -7604,22 +7604,22 @@
         <v>19</v>
       </c>
       <c r="AL28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM28">
         <v>100</v>
       </c>
       <c r="AN28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO28">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR28">
         <v>30</v>
@@ -7643,7 +7643,7 @@
         <v>11</v>
       </c>
       <c r="AY28">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28">
         <v>17</v>
@@ -7670,64 +7670,64 @@
         <v>50</v>
       </c>
       <c r="BH28">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BI28">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="BJ28">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK28">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL28">
         <v>150</v>
       </c>
       <c r="BM28">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BN28">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO28">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BP28">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BQ28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BR28">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BS28">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BT28">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU28">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BV28">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BW28">
+        <v>26</v>
+      </c>
+      <c r="BX28">
+        <v>60</v>
+      </c>
+      <c r="BY28">
+        <v>5.5</v>
+      </c>
+      <c r="BZ28">
         <v>29</v>
       </c>
-      <c r="BX28">
-        <v>50</v>
-      </c>
-      <c r="BY28">
-        <v>38</v>
-      </c>
-      <c r="BZ28">
-        <v>25</v>
-      </c>
       <c r="CA28">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="CB28" t="s">
         <v>202</v>
@@ -7750,7 +7750,7 @@
         <v>190</v>
       </c>
       <c r="F29">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G29">
         <v>10.5</v>
@@ -7759,7 +7759,7 @@
         <v>1.45</v>
       </c>
       <c r="I29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J29">
         <v>4.2</v>
@@ -7774,7 +7774,7 @@
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O29">
         <v>1.32</v>
@@ -7783,22 +7783,22 @@
         <v>1.89</v>
       </c>
       <c r="Q29">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R29">
         <v>1.34</v>
       </c>
       <c r="S29">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T29">
         <v>2.16</v>
       </c>
       <c r="U29">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V29">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="W29">
         <v>1.1</v>
@@ -7816,7 +7816,7 @@
         <v>13</v>
       </c>
       <c r="AB29">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AC29">
         <v>11</v>
@@ -7828,22 +7828,22 @@
         <v>18.5</v>
       </c>
       <c r="AF29">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG29">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AH29">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AI29">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ29">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="AK29">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="AL29">
         <v>470</v>
@@ -7852,7 +7852,7 @@
         <v>210</v>
       </c>
       <c r="AN29">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="AO29">
         <v>8.800000000000001</v>
@@ -7867,7 +7867,7 @@
         <v>6.8</v>
       </c>
       <c r="AS29">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AT29">
         <v>21</v>
@@ -7876,46 +7876,46 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV29">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AW29">
         <v>14.5</v>
       </c>
       <c r="AX29">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AY29">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AZ29">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BA29">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB29">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC29">
         <v>9.4</v>
       </c>
       <c r="BD29">
-        <v>9.4</v>
+        <v>75</v>
       </c>
       <c r="BE29">
-        <v>9.4</v>
+        <v>65</v>
       </c>
       <c r="BF29">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG29">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH29">
         <v>3.85</v>
       </c>
       <c r="BI29">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ29">
         <v>14.5</v>
@@ -7924,7 +7924,7 @@
         <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="BM29">
         <v>1.01</v>
@@ -7936,7 +7936,7 @@
         <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BQ29">
         <v>1.01</v>
@@ -7948,10 +7948,10 @@
         <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU29">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BV29">
         <v>10.5</v>
@@ -7992,58 +7992,58 @@
         <v>191</v>
       </c>
       <c r="F30">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="G30">
+        <v>2.74</v>
+      </c>
+      <c r="H30">
         <v>2.78</v>
       </c>
-      <c r="H30">
-        <v>2.74</v>
-      </c>
       <c r="I30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J30">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K30">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M30">
         <v>1.07</v>
       </c>
       <c r="N30">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O30">
         <v>1.31</v>
       </c>
       <c r="P30">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q30">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R30">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S30">
         <v>3.4</v>
       </c>
       <c r="T30">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U30">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V30">
         <v>1.5</v>
       </c>
       <c r="W30">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X30">
         <v>16</v>
@@ -8052,7 +8052,7 @@
         <v>13.5</v>
       </c>
       <c r="Z30">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA30">
         <v>130</v>
@@ -8064,7 +8064,7 @@
         <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE30">
         <v>38</v>
@@ -8073,112 +8073,112 @@
         <v>18.5</v>
       </c>
       <c r="AG30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH30">
         <v>18</v>
       </c>
       <c r="AI30">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AJ30">
         <v>44</v>
       </c>
       <c r="AK30">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL30">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AM30">
         <v>580</v>
       </c>
       <c r="AN30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO30">
         <v>34</v>
       </c>
       <c r="AP30">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="AQ30">
         <v>6.4</v>
       </c>
       <c r="AR30">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AS30">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AT30">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AU30">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV30">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AW30">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AY30">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="BB30">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC30">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BD30">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BE30">
+        <v>6.8</v>
+      </c>
+      <c r="BF30">
+        <v>5.8</v>
+      </c>
+      <c r="BG30">
         <v>6</v>
       </c>
-      <c r="BF30">
-        <v>20</v>
-      </c>
-      <c r="BG30">
-        <v>5.7</v>
-      </c>
       <c r="BH30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI30">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ30">
         <v>11</v>
       </c>
       <c r="BK30">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM30">
         <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BO30">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ30">
         <v>1.01</v>
@@ -8190,13 +8190,13 @@
         <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BU30">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV30">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BW30">
         <v>1.01</v>
@@ -8234,100 +8234,100 @@
         <v>192</v>
       </c>
       <c r="F31">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G31">
-        <v>5.9</v>
+        <v>2.88</v>
       </c>
       <c r="H31">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="I31">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J31">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L31">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M31">
         <v>1.11</v>
       </c>
       <c r="N31">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O31">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P31">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q31">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R31">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S31">
-        <v>2.64</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U31">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="X31">
+        <v>9.6</v>
+      </c>
+      <c r="Y31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z31">
+        <v>21</v>
+      </c>
+      <c r="AA31">
+        <v>160</v>
+      </c>
+      <c r="AB31">
+        <v>9</v>
+      </c>
+      <c r="AC31">
+        <v>7.4</v>
+      </c>
+      <c r="AD31">
+        <v>15</v>
+      </c>
+      <c r="AE31">
+        <v>50</v>
+      </c>
+      <c r="AF31">
+        <v>18</v>
+      </c>
+      <c r="AG31">
+        <v>13</v>
+      </c>
+      <c r="AH31">
+        <v>40</v>
+      </c>
+      <c r="AI31">
+        <v>150</v>
+      </c>
+      <c r="AJ31">
         <v>500</v>
       </c>
-      <c r="Y31">
-        <v>500</v>
-      </c>
-      <c r="Z31">
-        <v>500</v>
-      </c>
-      <c r="AA31">
-        <v>900</v>
-      </c>
-      <c r="AB31">
-        <v>500</v>
-      </c>
-      <c r="AC31">
-        <v>500</v>
-      </c>
-      <c r="AD31">
-        <v>500</v>
-      </c>
-      <c r="AE31">
-        <v>500</v>
-      </c>
-      <c r="AF31">
-        <v>500</v>
-      </c>
-      <c r="AG31">
-        <v>500</v>
-      </c>
-      <c r="AH31">
-        <v>500</v>
-      </c>
-      <c r="AI31">
-        <v>500</v>
-      </c>
-      <c r="AJ31">
-        <v>900</v>
-      </c>
       <c r="AK31">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AL31">
         <v>500</v>
@@ -8339,121 +8339,121 @@
         <v>600</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BC31">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BF31">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG31">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL31">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM31">
         <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="CB31" t="s">
         <v>202</v>
@@ -8476,25 +8476,25 @@
         <v>193</v>
       </c>
       <c r="F32">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G32">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I32">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K32">
         <v>3.75</v>
       </c>
       <c r="L32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M32">
         <v>1.11</v>
@@ -8506,13 +8506,13 @@
         <v>1.49</v>
       </c>
       <c r="P32">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q32">
         <v>2.52</v>
       </c>
       <c r="R32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S32">
         <v>5</v>
@@ -8521,7 +8521,7 @@
         <v>2.24</v>
       </c>
       <c r="U32">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V32">
         <v>1.19</v>
@@ -8533,13 +8533,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y32">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z32">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA32">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AB32">
         <v>6.4</v>
@@ -8551,145 +8551,145 @@
         <v>32</v>
       </c>
       <c r="AE32">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF32">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG32">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH32">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI32">
         <v>170</v>
       </c>
       <c r="AJ32">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK32">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM32">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AN32">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO32">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="AP32">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR32">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AS32">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT32">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU32">
         <v>7.2</v>
       </c>
       <c r="AV32">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AW32">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="AX32">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY32">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BA32">
-        <v>6.8</v>
+        <v>65</v>
       </c>
       <c r="BB32">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC32">
         <v>20</v>
       </c>
       <c r="BD32">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BE32">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF32">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG32">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH32">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI32">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ32">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK32">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO32">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ32">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BU32">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
+        <v>9.4</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
         <v>9.6</v>
-      </c>
-      <c r="BX32">
-        <v>1000</v>
-      </c>
-      <c r="BY32">
-        <v>9.800000000000001</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
@@ -8718,7 +8718,7 @@
         <v>194</v>
       </c>
       <c r="F33">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G33">
         <v>1.37</v>
@@ -8730,43 +8730,43 @@
         <v>14.5</v>
       </c>
       <c r="J33">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K33">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L33">
         <v>1.41</v>
       </c>
       <c r="M33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N33">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P33">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q33">
         <v>1.98</v>
       </c>
       <c r="R33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S33">
         <v>3.6</v>
       </c>
       <c r="T33">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U33">
         <v>1.61</v>
       </c>
       <c r="V33">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W33">
         <v>3.7</v>
@@ -8784,7 +8784,7 @@
         <v>720</v>
       </c>
       <c r="AB33">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC33">
         <v>12.5</v>
@@ -8793,10 +8793,10 @@
         <v>55</v>
       </c>
       <c r="AE33">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AF33">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AG33">
         <v>11</v>
@@ -8811,19 +8811,19 @@
         <v>10.5</v>
       </c>
       <c r="AK33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL33">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM33">
         <v>310</v>
       </c>
       <c r="AN33">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO33">
-        <v>590</v>
+        <v>540</v>
       </c>
       <c r="AP33">
         <v>13.5</v>
@@ -8835,7 +8835,7 @@
         <v>28</v>
       </c>
       <c r="AS33">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT33">
         <v>6.2</v>
@@ -8847,7 +8847,7 @@
         <v>40</v>
       </c>
       <c r="AW33">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX33">
         <v>6.2</v>
@@ -8859,7 +8859,7 @@
         <v>30</v>
       </c>
       <c r="BA33">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB33">
         <v>9.199999999999999</v>
@@ -8871,7 +8871,7 @@
         <v>46</v>
       </c>
       <c r="BE33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF33">
         <v>6.4</v>
@@ -8880,61 +8880,61 @@
         <v>15</v>
       </c>
       <c r="BH33">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
         <v>1.01</v>
       </c>
       <c r="BL33">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
         <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP33">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR33">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
         <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
         <v>1.01</v>
       </c>
       <c r="BV33">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
         <v>1.01</v>
       </c>
       <c r="BX33">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
         <v>1.01</v>
       </c>
       <c r="BZ33">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
         <v>1.01</v>
@@ -8960,16 +8960,16 @@
         <v>195</v>
       </c>
       <c r="F34">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G34">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H34">
         <v>4.4</v>
       </c>
       <c r="I34">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J34">
         <v>3.2</v>
@@ -8984,10 +8984,10 @@
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O34">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P34">
         <v>1.64</v>
@@ -8999,34 +8999,34 @@
         <v>1.22</v>
       </c>
       <c r="S34">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T34">
         <v>2.04</v>
       </c>
       <c r="U34">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V34">
         <v>1.27</v>
       </c>
       <c r="W34">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z34">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AA34">
         <v>900</v>
       </c>
       <c r="AB34">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC34">
         <v>7.8</v>
@@ -9035,7 +9035,7 @@
         <v>20</v>
       </c>
       <c r="AE34">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AF34">
         <v>12</v>
@@ -9050,13 +9050,13 @@
         <v>380</v>
       </c>
       <c r="AJ34">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK34">
         <v>28</v>
       </c>
       <c r="AL34">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM34">
         <v>580</v>
@@ -9065,19 +9065,19 @@
         <v>25</v>
       </c>
       <c r="AO34">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP34">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR34">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AS34">
-        <v>7.4</v>
+        <v>75</v>
       </c>
       <c r="AT34">
         <v>6.6</v>
@@ -9086,40 +9086,40 @@
         <v>6.6</v>
       </c>
       <c r="AV34">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW34">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AX34">
         <v>9.6</v>
       </c>
       <c r="AY34">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ34">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA34">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BB34">
         <v>21</v>
       </c>
       <c r="BC34">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BD34">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BE34">
-        <v>7.4</v>
+        <v>100</v>
       </c>
       <c r="BF34">
         <v>19.5</v>
       </c>
       <c r="BG34">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BH34">
         <v>3.3</v>
@@ -9131,13 +9131,13 @@
         <v>13.5</v>
       </c>
       <c r="BK34">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BL34">
-        <v>870</v>
+        <v>780</v>
       </c>
       <c r="BM34">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN34">
         <v>5.3</v>
@@ -9146,10 +9146,10 @@
         <v>3.55</v>
       </c>
       <c r="BP34">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ34">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR34">
         <v>46</v>
@@ -9158,10 +9158,10 @@
         <v>4.5</v>
       </c>
       <c r="BT34">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU34">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV34">
         <v>55</v>
@@ -9170,7 +9170,7 @@
         <v>4.7</v>
       </c>
       <c r="BX34">
-        <v>860</v>
+        <v>770</v>
       </c>
       <c r="BY34">
         <v>4.8</v>
@@ -9202,19 +9202,19 @@
         <v>196</v>
       </c>
       <c r="F35">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G35">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H35">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I35">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J35">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K35">
         <v>3.7</v>
@@ -9235,7 +9235,7 @@
         <v>1.81</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R35">
         <v>1.31</v>
@@ -9250,7 +9250,7 @@
         <v>2.04</v>
       </c>
       <c r="V35">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W35">
         <v>1.27</v>
@@ -9280,10 +9280,10 @@
         <v>23</v>
       </c>
       <c r="AF35">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AG35">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH35">
         <v>19.5</v>
@@ -9295,22 +9295,22 @@
         <v>900</v>
       </c>
       <c r="AK35">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="AL35">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AM35">
         <v>390</v>
       </c>
       <c r="AN35">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ35">
         <v>7.4</v>
@@ -9319,46 +9319,46 @@
         <v>10.5</v>
       </c>
       <c r="AS35">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AT35">
         <v>12.5</v>
       </c>
       <c r="AU35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV35">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW35">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX35">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AY35">
         <v>15.5</v>
       </c>
       <c r="AZ35">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA35">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BB35">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC35">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD35">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BE35">
+        <v>14.5</v>
+      </c>
+      <c r="BF35">
         <v>13</v>
-      </c>
-      <c r="BF35">
-        <v>12</v>
       </c>
       <c r="BG35">
         <v>14.5</v>
@@ -9370,16 +9370,16 @@
         <v>2.68</v>
       </c>
       <c r="BJ35">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BL35">
         <v>170</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN35">
         <v>8.800000000000001</v>
@@ -9391,37 +9391,37 @@
         <v>46</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR35">
         <v>60</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT35">
         <v>5.2</v>
       </c>
       <c r="BU35">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX35">
         <v>36</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BZ35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="CB35" t="s">
         <v>202</v>
@@ -9444,88 +9444,88 @@
         <v>197</v>
       </c>
       <c r="F36">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G36">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="H36">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J36">
         <v>3.3</v>
       </c>
       <c r="K36">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M36">
         <v>1.07</v>
       </c>
       <c r="N36">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O36">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P36">
+        <v>1.92</v>
+      </c>
+      <c r="Q36">
         <v>1.94</v>
       </c>
-      <c r="Q36">
-        <v>1.92</v>
-      </c>
       <c r="R36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S36">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T36">
         <v>1.72</v>
       </c>
       <c r="U36">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W36">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X36">
         <v>17.5</v>
       </c>
       <c r="Y36">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z36">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA36">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC36">
         <v>8.199999999999999</v>
       </c>
       <c r="AD36">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF36">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH36">
         <v>17.5</v>
@@ -9537,7 +9537,7 @@
         <v>95</v>
       </c>
       <c r="AK36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL36">
         <v>95</v>
@@ -9552,37 +9552,37 @@
         <v>34</v>
       </c>
       <c r="AP36">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ36">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR36">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AS36">
         <v>7.2</v>
       </c>
       <c r="AT36">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV36">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AW36">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX36">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY36">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ36">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA36">
         <v>7</v>
@@ -9600,7 +9600,7 @@
         <v>7.8</v>
       </c>
       <c r="BF36">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BG36">
         <v>6.8</v>
@@ -9609,13 +9609,13 @@
         <v>3.95</v>
       </c>
       <c r="BI36">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ36">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BK36">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL36">
         <v>140</v>
@@ -9624,10 +9624,10 @@
         <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BO36">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP36">
         <v>25</v>
@@ -9642,13 +9642,13 @@
         <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU36">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV36">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW36">
         <v>1.01</v>
@@ -9660,10 +9660,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="s">
         <v>202</v>
@@ -9710,13 +9710,13 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O37">
         <v>1.33</v>
       </c>
       <c r="P37">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q37">
         <v>1.32</v>
@@ -9725,7 +9725,7 @@
         <v>1.13</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
         <v>1.11</v>
@@ -9794,52 +9794,52 @@
         <v>1000</v>
       </c>
       <c r="AP37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF37">
         <v>1.01</v>
@@ -9928,181 +9928,181 @@
         <v>199</v>
       </c>
       <c r="F38">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G38">
         <v>2.38</v>
       </c>
       <c r="H38">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I38">
         <v>4.3</v>
       </c>
       <c r="J38">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L38">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M38">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N38">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="O38">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="P38">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="Q38">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="R38">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S38">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="T38">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U38">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="V38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W38">
         <v>1.72</v>
       </c>
       <c r="X38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z38">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA38">
         <v>110</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC38">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD38">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE38">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF38">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG38">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI38">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK38">
         <v>36</v>
       </c>
       <c r="AL38">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM38">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN38">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO38">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP38">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="AQ38">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AR38">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS38">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="AT38">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AU38">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AV38">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AW38">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AX38">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AY38">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AZ38">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA38">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB38">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC38">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD38">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BE38">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BF38">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BG38">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH38">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="BI38">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BJ38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK38">
         <v>1.01</v>
       </c>
       <c r="BL38">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="BM38">
         <v>1.01</v>
@@ -10114,13 +10114,13 @@
         <v>3.9</v>
       </c>
       <c r="BP38">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ38">
         <v>1.01</v>
       </c>
       <c r="BR38">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS38">
         <v>1.01</v>
@@ -10132,19 +10132,19 @@
         <v>5.5</v>
       </c>
       <c r="BV38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW38">
         <v>1.01</v>
       </c>
       <c r="BX38">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BY38">
         <v>1.01</v>
       </c>
       <c r="BZ38">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="CA38">
         <v>1.01</v>
@@ -10170,7 +10170,7 @@
         <v>200</v>
       </c>
       <c r="F39">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G39">
         <v>2.12</v>
@@ -10188,7 +10188,7 @@
         <v>3.55</v>
       </c>
       <c r="L39">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M39">
         <v>1.09</v>
@@ -10197,7 +10197,7 @@
         <v>3.3</v>
       </c>
       <c r="O39">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P39">
         <v>1.75</v>
@@ -10206,16 +10206,16 @@
         <v>2.26</v>
       </c>
       <c r="R39">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S39">
         <v>4.3</v>
       </c>
       <c r="T39">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U39">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V39">
         <v>1.28</v>
@@ -10230,7 +10230,7 @@
         <v>14</v>
       </c>
       <c r="Z39">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA39">
         <v>110</v>
@@ -10239,16 +10239,16 @@
         <v>8.4</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD39">
         <v>18</v>
       </c>
       <c r="AE39">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF39">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG39">
         <v>11</v>
@@ -10260,19 +10260,19 @@
         <v>90</v>
       </c>
       <c r="AJ39">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AK39">
         <v>25</v>
       </c>
       <c r="AL39">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM39">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN39">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO39">
         <v>90</v>
@@ -10281,16 +10281,16 @@
         <v>10</v>
       </c>
       <c r="AQ39">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR39">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AS39">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AT39">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU39">
         <v>6.8</v>
@@ -10299,22 +10299,22 @@
         <v>14.5</v>
       </c>
       <c r="AW39">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AX39">
         <v>10</v>
       </c>
       <c r="AY39">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ39">
         <v>17</v>
       </c>
       <c r="BA39">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BB39">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BC39">
         <v>20</v>
@@ -10329,67 +10329,67 @@
         <v>17</v>
       </c>
       <c r="BG39">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BH39">
         <v>3.45</v>
       </c>
       <c r="BI39">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK39">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BL39">
         <v>180</v>
       </c>
       <c r="BM39">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BN39">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO39">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP39">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BQ39">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR39">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS39">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT39">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BU39">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV39">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW39">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BX39">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY39">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BZ39">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="CA39">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="CB39" t="s">
         <v>202</v>
@@ -10415,13 +10415,13 @@
         <v>1.71</v>
       </c>
       <c r="G40">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I40">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J40">
         <v>3.65</v>
@@ -10436,25 +10436,25 @@
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O40">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P40">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q40">
         <v>1.98</v>
       </c>
       <c r="R40">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S40">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T40">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U40">
         <v>1.94</v>
@@ -10463,7 +10463,7 @@
         <v>1.2</v>
       </c>
       <c r="W40">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X40">
         <v>16.5</v>
@@ -10472,7 +10472,7 @@
         <v>18.5</v>
       </c>
       <c r="Z40">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA40">
         <v>170</v>
@@ -10508,7 +10508,7 @@
         <v>20</v>
       </c>
       <c r="AL40">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM40">
         <v>150</v>
@@ -10520,67 +10520,67 @@
         <v>120</v>
       </c>
       <c r="AP40">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ40">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="AR40">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS40">
-        <v>8.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="AT40">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU40">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV40">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="AW40">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="AX40">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AY40">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ40">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BA40">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BB40">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BC40">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BD40">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="BE40">
-        <v>8.199999999999999</v>
+        <v>80</v>
       </c>
       <c r="BF40">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG40">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BH40">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI40">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK40">
         <v>1.01</v>
@@ -10592,31 +10592,31 @@
         <v>1.01</v>
       </c>
       <c r="BN40">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BO40">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP40">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BQ40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR40">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS40">
         <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BU40">
         <v>1.01</v>
       </c>
       <c r="BV40">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW40">
         <v>1.01</v>
